--- a/P01113_template.xlsx
+++ b/P01113_template.xlsx
@@ -2372,7 +2372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S304"/>
+  <dimension ref="A1:S204"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="33" min="1" max="1"/>
@@ -13356,5408 +13356,8 @@
       <c r="R204" s="59" t="n"/>
       <c r="S204" s="60" t="n"/>
     </row>
-    <row r="205" ht="15" customHeight="1" s="34">
-      <c r="A205" s="54" t="n"/>
-      <c r="B205" s="54" t="n"/>
-      <c r="C205" s="54" t="n"/>
-      <c r="D205" s="55">
-        <f>IF($A205="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C205,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E205" s="55">
-        <f>IF($A205="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C205,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F205" s="56">
-        <f>IF($A205="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C205,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G205" s="57" t="n"/>
-      <c r="H205" s="54" t="n"/>
-      <c r="I205" s="54" t="n"/>
-      <c r="J205" s="39">
-        <f>IF($A205="","",IF($E205="Informational","GREEN",IF($G205="",IF($E205="Mandatory","RED","YELLOW"),IF($N205="Exact",IF(UPPER(TRIM($G205&amp;""))=UPPER(TRIM($F205&amp;"")),"GREEN",$P205),IF(NOT(ISNUMBER($G205)),$P205,IF($N205="Min",IF($G205&gt;=$F205,"GREEN",IF($G205&gt;=$F205-$O205,"YELLOW",$P205)),IF($N205="Max",IF($G205&lt;=$F205,"GREEN",IF($G205&lt;=$F205+$O205,"YELLOW",$P205)),IF($N205="Range",IF(ABS($G205-$F205)&lt;=$O205,"GREEN",$P205),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K205" s="39">
-        <f>IF($A205="","",IF($H205="Non-Compliant","RED",IF(AND(OR($H205="Alternative Offer",$H205="Partially Compliant"),$J205="GREEN"),"YELLOW",IF(AND($J205="GREEN",ISNUMBER($R205),$R205&lt;Baseline!$B$9),"YELLOW",$J205))))</f>
-        <v/>
-      </c>
-      <c r="L205" s="39">
-        <f>IF($A205="","",IF($K205="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A205,Exceptions!$C$5:$C$104,$B205,Exceptions!$D$5:$D$104,$C205,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K205)))</f>
-        <v/>
-      </c>
-      <c r="M205" s="39">
-        <f>IF($A205="","",IF($H205="","Declaration missing",IF($H205="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R205),$R205&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H205="Fully Compliant",$J205&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N205" s="58">
-        <f>IF($A205="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C205,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O205" s="58">
-        <f>IF($A205="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C205,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P205" s="58">
-        <f>IF($A205="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C205,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q205" s="58">
-        <f>IF($A205="","",$A205&amp;"|"&amp;$B205&amp;"|"&amp;$C205)</f>
-        <v/>
-      </c>
-      <c r="R205" s="59" t="n"/>
-      <c r="S205" s="60" t="n"/>
-    </row>
-    <row r="206" ht="15" customHeight="1" s="34">
-      <c r="A206" s="54" t="n"/>
-      <c r="B206" s="54" t="n"/>
-      <c r="C206" s="54" t="n"/>
-      <c r="D206" s="55">
-        <f>IF($A206="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C206,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E206" s="55">
-        <f>IF($A206="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C206,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F206" s="56">
-        <f>IF($A206="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C206,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G206" s="57" t="n"/>
-      <c r="H206" s="54" t="n"/>
-      <c r="I206" s="54" t="n"/>
-      <c r="J206" s="39">
-        <f>IF($A206="","",IF($E206="Informational","GREEN",IF($G206="",IF($E206="Mandatory","RED","YELLOW"),IF($N206="Exact",IF(UPPER(TRIM($G206&amp;""))=UPPER(TRIM($F206&amp;"")),"GREEN",$P206),IF(NOT(ISNUMBER($G206)),$P206,IF($N206="Min",IF($G206&gt;=$F206,"GREEN",IF($G206&gt;=$F206-$O206,"YELLOW",$P206)),IF($N206="Max",IF($G206&lt;=$F206,"GREEN",IF($G206&lt;=$F206+$O206,"YELLOW",$P206)),IF($N206="Range",IF(ABS($G206-$F206)&lt;=$O206,"GREEN",$P206),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K206" s="39">
-        <f>IF($A206="","",IF($H206="Non-Compliant","RED",IF(AND(OR($H206="Alternative Offer",$H206="Partially Compliant"),$J206="GREEN"),"YELLOW",IF(AND($J206="GREEN",ISNUMBER($R206),$R206&lt;Baseline!$B$9),"YELLOW",$J206))))</f>
-        <v/>
-      </c>
-      <c r="L206" s="39">
-        <f>IF($A206="","",IF($K206="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A206,Exceptions!$C$5:$C$104,$B206,Exceptions!$D$5:$D$104,$C206,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K206)))</f>
-        <v/>
-      </c>
-      <c r="M206" s="39">
-        <f>IF($A206="","",IF($H206="","Declaration missing",IF($H206="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R206),$R206&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H206="Fully Compliant",$J206&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N206" s="58">
-        <f>IF($A206="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C206,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O206" s="58">
-        <f>IF($A206="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C206,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P206" s="58">
-        <f>IF($A206="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C206,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q206" s="58">
-        <f>IF($A206="","",$A206&amp;"|"&amp;$B206&amp;"|"&amp;$C206)</f>
-        <v/>
-      </c>
-      <c r="R206" s="59" t="n"/>
-      <c r="S206" s="60" t="n"/>
-    </row>
-    <row r="207" ht="15" customHeight="1" s="34">
-      <c r="A207" s="54" t="n"/>
-      <c r="B207" s="54" t="n"/>
-      <c r="C207" s="54" t="n"/>
-      <c r="D207" s="55">
-        <f>IF($A207="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C207,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E207" s="55">
-        <f>IF($A207="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C207,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F207" s="56">
-        <f>IF($A207="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C207,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G207" s="57" t="n"/>
-      <c r="H207" s="54" t="n"/>
-      <c r="I207" s="54" t="n"/>
-      <c r="J207" s="39">
-        <f>IF($A207="","",IF($E207="Informational","GREEN",IF($G207="",IF($E207="Mandatory","RED","YELLOW"),IF($N207="Exact",IF(UPPER(TRIM($G207&amp;""))=UPPER(TRIM($F207&amp;"")),"GREEN",$P207),IF(NOT(ISNUMBER($G207)),$P207,IF($N207="Min",IF($G207&gt;=$F207,"GREEN",IF($G207&gt;=$F207-$O207,"YELLOW",$P207)),IF($N207="Max",IF($G207&lt;=$F207,"GREEN",IF($G207&lt;=$F207+$O207,"YELLOW",$P207)),IF($N207="Range",IF(ABS($G207-$F207)&lt;=$O207,"GREEN",$P207),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K207" s="39">
-        <f>IF($A207="","",IF($H207="Non-Compliant","RED",IF(AND(OR($H207="Alternative Offer",$H207="Partially Compliant"),$J207="GREEN"),"YELLOW",IF(AND($J207="GREEN",ISNUMBER($R207),$R207&lt;Baseline!$B$9),"YELLOW",$J207))))</f>
-        <v/>
-      </c>
-      <c r="L207" s="39">
-        <f>IF($A207="","",IF($K207="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A207,Exceptions!$C$5:$C$104,$B207,Exceptions!$D$5:$D$104,$C207,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K207)))</f>
-        <v/>
-      </c>
-      <c r="M207" s="39">
-        <f>IF($A207="","",IF($H207="","Declaration missing",IF($H207="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R207),$R207&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H207="Fully Compliant",$J207&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N207" s="58">
-        <f>IF($A207="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C207,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O207" s="58">
-        <f>IF($A207="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C207,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P207" s="58">
-        <f>IF($A207="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C207,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q207" s="58">
-        <f>IF($A207="","",$A207&amp;"|"&amp;$B207&amp;"|"&amp;$C207)</f>
-        <v/>
-      </c>
-      <c r="R207" s="59" t="n"/>
-      <c r="S207" s="60" t="n"/>
-    </row>
-    <row r="208" ht="15" customHeight="1" s="34">
-      <c r="A208" s="54" t="n"/>
-      <c r="B208" s="54" t="n"/>
-      <c r="C208" s="54" t="n"/>
-      <c r="D208" s="55">
-        <f>IF($A208="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C208,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E208" s="55">
-        <f>IF($A208="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C208,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F208" s="56">
-        <f>IF($A208="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C208,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G208" s="57" t="n"/>
-      <c r="H208" s="54" t="n"/>
-      <c r="I208" s="54" t="n"/>
-      <c r="J208" s="39">
-        <f>IF($A208="","",IF($E208="Informational","GREEN",IF($G208="",IF($E208="Mandatory","RED","YELLOW"),IF($N208="Exact",IF(UPPER(TRIM($G208&amp;""))=UPPER(TRIM($F208&amp;"")),"GREEN",$P208),IF(NOT(ISNUMBER($G208)),$P208,IF($N208="Min",IF($G208&gt;=$F208,"GREEN",IF($G208&gt;=$F208-$O208,"YELLOW",$P208)),IF($N208="Max",IF($G208&lt;=$F208,"GREEN",IF($G208&lt;=$F208+$O208,"YELLOW",$P208)),IF($N208="Range",IF(ABS($G208-$F208)&lt;=$O208,"GREEN",$P208),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K208" s="39">
-        <f>IF($A208="","",IF($H208="Non-Compliant","RED",IF(AND(OR($H208="Alternative Offer",$H208="Partially Compliant"),$J208="GREEN"),"YELLOW",IF(AND($J208="GREEN",ISNUMBER($R208),$R208&lt;Baseline!$B$9),"YELLOW",$J208))))</f>
-        <v/>
-      </c>
-      <c r="L208" s="39">
-        <f>IF($A208="","",IF($K208="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A208,Exceptions!$C$5:$C$104,$B208,Exceptions!$D$5:$D$104,$C208,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K208)))</f>
-        <v/>
-      </c>
-      <c r="M208" s="39">
-        <f>IF($A208="","",IF($H208="","Declaration missing",IF($H208="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R208),$R208&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H208="Fully Compliant",$J208&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N208" s="58">
-        <f>IF($A208="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C208,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O208" s="58">
-        <f>IF($A208="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C208,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P208" s="58">
-        <f>IF($A208="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C208,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q208" s="58">
-        <f>IF($A208="","",$A208&amp;"|"&amp;$B208&amp;"|"&amp;$C208)</f>
-        <v/>
-      </c>
-      <c r="R208" s="59" t="n"/>
-      <c r="S208" s="60" t="n"/>
-    </row>
-    <row r="209" ht="15" customHeight="1" s="34">
-      <c r="A209" s="54" t="n"/>
-      <c r="B209" s="54" t="n"/>
-      <c r="C209" s="54" t="n"/>
-      <c r="D209" s="55">
-        <f>IF($A209="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C209,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E209" s="55">
-        <f>IF($A209="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C209,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F209" s="56">
-        <f>IF($A209="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C209,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G209" s="57" t="n"/>
-      <c r="H209" s="54" t="n"/>
-      <c r="I209" s="54" t="n"/>
-      <c r="J209" s="39">
-        <f>IF($A209="","",IF($E209="Informational","GREEN",IF($G209="",IF($E209="Mandatory","RED","YELLOW"),IF($N209="Exact",IF(UPPER(TRIM($G209&amp;""))=UPPER(TRIM($F209&amp;"")),"GREEN",$P209),IF(NOT(ISNUMBER($G209)),$P209,IF($N209="Min",IF($G209&gt;=$F209,"GREEN",IF($G209&gt;=$F209-$O209,"YELLOW",$P209)),IF($N209="Max",IF($G209&lt;=$F209,"GREEN",IF($G209&lt;=$F209+$O209,"YELLOW",$P209)),IF($N209="Range",IF(ABS($G209-$F209)&lt;=$O209,"GREEN",$P209),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K209" s="39">
-        <f>IF($A209="","",IF($H209="Non-Compliant","RED",IF(AND(OR($H209="Alternative Offer",$H209="Partially Compliant"),$J209="GREEN"),"YELLOW",IF(AND($J209="GREEN",ISNUMBER($R209),$R209&lt;Baseline!$B$9),"YELLOW",$J209))))</f>
-        <v/>
-      </c>
-      <c r="L209" s="39">
-        <f>IF($A209="","",IF($K209="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A209,Exceptions!$C$5:$C$104,$B209,Exceptions!$D$5:$D$104,$C209,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K209)))</f>
-        <v/>
-      </c>
-      <c r="M209" s="39">
-        <f>IF($A209="","",IF($H209="","Declaration missing",IF($H209="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R209),$R209&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H209="Fully Compliant",$J209&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N209" s="58">
-        <f>IF($A209="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C209,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O209" s="58">
-        <f>IF($A209="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C209,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P209" s="58">
-        <f>IF($A209="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C209,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q209" s="58">
-        <f>IF($A209="","",$A209&amp;"|"&amp;$B209&amp;"|"&amp;$C209)</f>
-        <v/>
-      </c>
-      <c r="R209" s="59" t="n"/>
-      <c r="S209" s="60" t="n"/>
-    </row>
-    <row r="210" ht="15" customHeight="1" s="34">
-      <c r="A210" s="54" t="n"/>
-      <c r="B210" s="54" t="n"/>
-      <c r="C210" s="54" t="n"/>
-      <c r="D210" s="55">
-        <f>IF($A210="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C210,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E210" s="55">
-        <f>IF($A210="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C210,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F210" s="56">
-        <f>IF($A210="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C210,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G210" s="57" t="n"/>
-      <c r="H210" s="54" t="n"/>
-      <c r="I210" s="54" t="n"/>
-      <c r="J210" s="39">
-        <f>IF($A210="","",IF($E210="Informational","GREEN",IF($G210="",IF($E210="Mandatory","RED","YELLOW"),IF($N210="Exact",IF(UPPER(TRIM($G210&amp;""))=UPPER(TRIM($F210&amp;"")),"GREEN",$P210),IF(NOT(ISNUMBER($G210)),$P210,IF($N210="Min",IF($G210&gt;=$F210,"GREEN",IF($G210&gt;=$F210-$O210,"YELLOW",$P210)),IF($N210="Max",IF($G210&lt;=$F210,"GREEN",IF($G210&lt;=$F210+$O210,"YELLOW",$P210)),IF($N210="Range",IF(ABS($G210-$F210)&lt;=$O210,"GREEN",$P210),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K210" s="39">
-        <f>IF($A210="","",IF($H210="Non-Compliant","RED",IF(AND(OR($H210="Alternative Offer",$H210="Partially Compliant"),$J210="GREEN"),"YELLOW",IF(AND($J210="GREEN",ISNUMBER($R210),$R210&lt;Baseline!$B$9),"YELLOW",$J210))))</f>
-        <v/>
-      </c>
-      <c r="L210" s="39">
-        <f>IF($A210="","",IF($K210="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A210,Exceptions!$C$5:$C$104,$B210,Exceptions!$D$5:$D$104,$C210,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K210)))</f>
-        <v/>
-      </c>
-      <c r="M210" s="39">
-        <f>IF($A210="","",IF($H210="","Declaration missing",IF($H210="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R210),$R210&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H210="Fully Compliant",$J210&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N210" s="58">
-        <f>IF($A210="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C210,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O210" s="58">
-        <f>IF($A210="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C210,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P210" s="58">
-        <f>IF($A210="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C210,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q210" s="58">
-        <f>IF($A210="","",$A210&amp;"|"&amp;$B210&amp;"|"&amp;$C210)</f>
-        <v/>
-      </c>
-      <c r="R210" s="59" t="n"/>
-      <c r="S210" s="60" t="n"/>
-    </row>
-    <row r="211" ht="15" customHeight="1" s="34">
-      <c r="A211" s="54" t="n"/>
-      <c r="B211" s="54" t="n"/>
-      <c r="C211" s="54" t="n"/>
-      <c r="D211" s="55">
-        <f>IF($A211="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C211,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E211" s="55">
-        <f>IF($A211="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C211,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F211" s="56">
-        <f>IF($A211="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C211,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G211" s="57" t="n"/>
-      <c r="H211" s="54" t="n"/>
-      <c r="I211" s="54" t="n"/>
-      <c r="J211" s="39">
-        <f>IF($A211="","",IF($E211="Informational","GREEN",IF($G211="",IF($E211="Mandatory","RED","YELLOW"),IF($N211="Exact",IF(UPPER(TRIM($G211&amp;""))=UPPER(TRIM($F211&amp;"")),"GREEN",$P211),IF(NOT(ISNUMBER($G211)),$P211,IF($N211="Min",IF($G211&gt;=$F211,"GREEN",IF($G211&gt;=$F211-$O211,"YELLOW",$P211)),IF($N211="Max",IF($G211&lt;=$F211,"GREEN",IF($G211&lt;=$F211+$O211,"YELLOW",$P211)),IF($N211="Range",IF(ABS($G211-$F211)&lt;=$O211,"GREEN",$P211),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K211" s="39">
-        <f>IF($A211="","",IF($H211="Non-Compliant","RED",IF(AND(OR($H211="Alternative Offer",$H211="Partially Compliant"),$J211="GREEN"),"YELLOW",IF(AND($J211="GREEN",ISNUMBER($R211),$R211&lt;Baseline!$B$9),"YELLOW",$J211))))</f>
-        <v/>
-      </c>
-      <c r="L211" s="39">
-        <f>IF($A211="","",IF($K211="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A211,Exceptions!$C$5:$C$104,$B211,Exceptions!$D$5:$D$104,$C211,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K211)))</f>
-        <v/>
-      </c>
-      <c r="M211" s="39">
-        <f>IF($A211="","",IF($H211="","Declaration missing",IF($H211="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R211),$R211&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H211="Fully Compliant",$J211&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N211" s="58">
-        <f>IF($A211="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C211,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O211" s="58">
-        <f>IF($A211="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C211,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P211" s="58">
-        <f>IF($A211="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C211,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q211" s="58">
-        <f>IF($A211="","",$A211&amp;"|"&amp;$B211&amp;"|"&amp;$C211)</f>
-        <v/>
-      </c>
-      <c r="R211" s="59" t="n"/>
-      <c r="S211" s="60" t="n"/>
-    </row>
-    <row r="212" ht="15" customHeight="1" s="34">
-      <c r="A212" s="54" t="n"/>
-      <c r="B212" s="54" t="n"/>
-      <c r="C212" s="54" t="n"/>
-      <c r="D212" s="55">
-        <f>IF($A212="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C212,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E212" s="55">
-        <f>IF($A212="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C212,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F212" s="56">
-        <f>IF($A212="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C212,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G212" s="57" t="n"/>
-      <c r="H212" s="54" t="n"/>
-      <c r="I212" s="54" t="n"/>
-      <c r="J212" s="39">
-        <f>IF($A212="","",IF($E212="Informational","GREEN",IF($G212="",IF($E212="Mandatory","RED","YELLOW"),IF($N212="Exact",IF(UPPER(TRIM($G212&amp;""))=UPPER(TRIM($F212&amp;"")),"GREEN",$P212),IF(NOT(ISNUMBER($G212)),$P212,IF($N212="Min",IF($G212&gt;=$F212,"GREEN",IF($G212&gt;=$F212-$O212,"YELLOW",$P212)),IF($N212="Max",IF($G212&lt;=$F212,"GREEN",IF($G212&lt;=$F212+$O212,"YELLOW",$P212)),IF($N212="Range",IF(ABS($G212-$F212)&lt;=$O212,"GREEN",$P212),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K212" s="39">
-        <f>IF($A212="","",IF($H212="Non-Compliant","RED",IF(AND(OR($H212="Alternative Offer",$H212="Partially Compliant"),$J212="GREEN"),"YELLOW",IF(AND($J212="GREEN",ISNUMBER($R212),$R212&lt;Baseline!$B$9),"YELLOW",$J212))))</f>
-        <v/>
-      </c>
-      <c r="L212" s="39">
-        <f>IF($A212="","",IF($K212="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A212,Exceptions!$C$5:$C$104,$B212,Exceptions!$D$5:$D$104,$C212,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K212)))</f>
-        <v/>
-      </c>
-      <c r="M212" s="39">
-        <f>IF($A212="","",IF($H212="","Declaration missing",IF($H212="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R212),$R212&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H212="Fully Compliant",$J212&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N212" s="58">
-        <f>IF($A212="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C212,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O212" s="58">
-        <f>IF($A212="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C212,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P212" s="58">
-        <f>IF($A212="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C212,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q212" s="58">
-        <f>IF($A212="","",$A212&amp;"|"&amp;$B212&amp;"|"&amp;$C212)</f>
-        <v/>
-      </c>
-      <c r="R212" s="59" t="n"/>
-      <c r="S212" s="60" t="n"/>
-    </row>
-    <row r="213" ht="15" customHeight="1" s="34">
-      <c r="A213" s="54" t="n"/>
-      <c r="B213" s="54" t="n"/>
-      <c r="C213" s="54" t="n"/>
-      <c r="D213" s="55">
-        <f>IF($A213="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C213,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E213" s="55">
-        <f>IF($A213="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C213,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F213" s="56">
-        <f>IF($A213="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C213,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G213" s="57" t="n"/>
-      <c r="H213" s="54" t="n"/>
-      <c r="I213" s="54" t="n"/>
-      <c r="J213" s="39">
-        <f>IF($A213="","",IF($E213="Informational","GREEN",IF($G213="",IF($E213="Mandatory","RED","YELLOW"),IF($N213="Exact",IF(UPPER(TRIM($G213&amp;""))=UPPER(TRIM($F213&amp;"")),"GREEN",$P213),IF(NOT(ISNUMBER($G213)),$P213,IF($N213="Min",IF($G213&gt;=$F213,"GREEN",IF($G213&gt;=$F213-$O213,"YELLOW",$P213)),IF($N213="Max",IF($G213&lt;=$F213,"GREEN",IF($G213&lt;=$F213+$O213,"YELLOW",$P213)),IF($N213="Range",IF(ABS($G213-$F213)&lt;=$O213,"GREEN",$P213),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K213" s="39">
-        <f>IF($A213="","",IF($H213="Non-Compliant","RED",IF(AND(OR($H213="Alternative Offer",$H213="Partially Compliant"),$J213="GREEN"),"YELLOW",IF(AND($J213="GREEN",ISNUMBER($R213),$R213&lt;Baseline!$B$9),"YELLOW",$J213))))</f>
-        <v/>
-      </c>
-      <c r="L213" s="39">
-        <f>IF($A213="","",IF($K213="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A213,Exceptions!$C$5:$C$104,$B213,Exceptions!$D$5:$D$104,$C213,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K213)))</f>
-        <v/>
-      </c>
-      <c r="M213" s="39">
-        <f>IF($A213="","",IF($H213="","Declaration missing",IF($H213="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R213),$R213&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H213="Fully Compliant",$J213&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N213" s="58">
-        <f>IF($A213="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C213,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O213" s="58">
-        <f>IF($A213="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C213,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P213" s="58">
-        <f>IF($A213="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C213,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q213" s="58">
-        <f>IF($A213="","",$A213&amp;"|"&amp;$B213&amp;"|"&amp;$C213)</f>
-        <v/>
-      </c>
-      <c r="R213" s="59" t="n"/>
-      <c r="S213" s="60" t="n"/>
-    </row>
-    <row r="214" ht="15" customHeight="1" s="34">
-      <c r="A214" s="54" t="n"/>
-      <c r="B214" s="54" t="n"/>
-      <c r="C214" s="54" t="n"/>
-      <c r="D214" s="55">
-        <f>IF($A214="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C214,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E214" s="55">
-        <f>IF($A214="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C214,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F214" s="56">
-        <f>IF($A214="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C214,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G214" s="57" t="n"/>
-      <c r="H214" s="54" t="n"/>
-      <c r="I214" s="54" t="n"/>
-      <c r="J214" s="39">
-        <f>IF($A214="","",IF($E214="Informational","GREEN",IF($G214="",IF($E214="Mandatory","RED","YELLOW"),IF($N214="Exact",IF(UPPER(TRIM($G214&amp;""))=UPPER(TRIM($F214&amp;"")),"GREEN",$P214),IF(NOT(ISNUMBER($G214)),$P214,IF($N214="Min",IF($G214&gt;=$F214,"GREEN",IF($G214&gt;=$F214-$O214,"YELLOW",$P214)),IF($N214="Max",IF($G214&lt;=$F214,"GREEN",IF($G214&lt;=$F214+$O214,"YELLOW",$P214)),IF($N214="Range",IF(ABS($G214-$F214)&lt;=$O214,"GREEN",$P214),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K214" s="39">
-        <f>IF($A214="","",IF($H214="Non-Compliant","RED",IF(AND(OR($H214="Alternative Offer",$H214="Partially Compliant"),$J214="GREEN"),"YELLOW",IF(AND($J214="GREEN",ISNUMBER($R214),$R214&lt;Baseline!$B$9),"YELLOW",$J214))))</f>
-        <v/>
-      </c>
-      <c r="L214" s="39">
-        <f>IF($A214="","",IF($K214="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A214,Exceptions!$C$5:$C$104,$B214,Exceptions!$D$5:$D$104,$C214,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K214)))</f>
-        <v/>
-      </c>
-      <c r="M214" s="39">
-        <f>IF($A214="","",IF($H214="","Declaration missing",IF($H214="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R214),$R214&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H214="Fully Compliant",$J214&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N214" s="58">
-        <f>IF($A214="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C214,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O214" s="58">
-        <f>IF($A214="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C214,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P214" s="58">
-        <f>IF($A214="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C214,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q214" s="58">
-        <f>IF($A214="","",$A214&amp;"|"&amp;$B214&amp;"|"&amp;$C214)</f>
-        <v/>
-      </c>
-      <c r="R214" s="59" t="n"/>
-      <c r="S214" s="60" t="n"/>
-    </row>
-    <row r="215" ht="15" customHeight="1" s="34">
-      <c r="A215" s="54" t="n"/>
-      <c r="B215" s="54" t="n"/>
-      <c r="C215" s="54" t="n"/>
-      <c r="D215" s="55">
-        <f>IF($A215="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C215,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E215" s="55">
-        <f>IF($A215="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C215,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F215" s="56">
-        <f>IF($A215="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C215,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G215" s="57" t="n"/>
-      <c r="H215" s="54" t="n"/>
-      <c r="I215" s="54" t="n"/>
-      <c r="J215" s="39">
-        <f>IF($A215="","",IF($E215="Informational","GREEN",IF($G215="",IF($E215="Mandatory","RED","YELLOW"),IF($N215="Exact",IF(UPPER(TRIM($G215&amp;""))=UPPER(TRIM($F215&amp;"")),"GREEN",$P215),IF(NOT(ISNUMBER($G215)),$P215,IF($N215="Min",IF($G215&gt;=$F215,"GREEN",IF($G215&gt;=$F215-$O215,"YELLOW",$P215)),IF($N215="Max",IF($G215&lt;=$F215,"GREEN",IF($G215&lt;=$F215+$O215,"YELLOW",$P215)),IF($N215="Range",IF(ABS($G215-$F215)&lt;=$O215,"GREEN",$P215),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K215" s="39">
-        <f>IF($A215="","",IF($H215="Non-Compliant","RED",IF(AND(OR($H215="Alternative Offer",$H215="Partially Compliant"),$J215="GREEN"),"YELLOW",IF(AND($J215="GREEN",ISNUMBER($R215),$R215&lt;Baseline!$B$9),"YELLOW",$J215))))</f>
-        <v/>
-      </c>
-      <c r="L215" s="39">
-        <f>IF($A215="","",IF($K215="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A215,Exceptions!$C$5:$C$104,$B215,Exceptions!$D$5:$D$104,$C215,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K215)))</f>
-        <v/>
-      </c>
-      <c r="M215" s="39">
-        <f>IF($A215="","",IF($H215="","Declaration missing",IF($H215="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R215),$R215&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H215="Fully Compliant",$J215&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N215" s="58">
-        <f>IF($A215="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C215,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O215" s="58">
-        <f>IF($A215="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C215,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P215" s="58">
-        <f>IF($A215="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C215,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q215" s="58">
-        <f>IF($A215="","",$A215&amp;"|"&amp;$B215&amp;"|"&amp;$C215)</f>
-        <v/>
-      </c>
-      <c r="R215" s="59" t="n"/>
-      <c r="S215" s="60" t="n"/>
-    </row>
-    <row r="216" ht="15" customHeight="1" s="34">
-      <c r="A216" s="54" t="n"/>
-      <c r="B216" s="54" t="n"/>
-      <c r="C216" s="54" t="n"/>
-      <c r="D216" s="55">
-        <f>IF($A216="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C216,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E216" s="55">
-        <f>IF($A216="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C216,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F216" s="56">
-        <f>IF($A216="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C216,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G216" s="57" t="n"/>
-      <c r="H216" s="54" t="n"/>
-      <c r="I216" s="54" t="n"/>
-      <c r="J216" s="39">
-        <f>IF($A216="","",IF($E216="Informational","GREEN",IF($G216="",IF($E216="Mandatory","RED","YELLOW"),IF($N216="Exact",IF(UPPER(TRIM($G216&amp;""))=UPPER(TRIM($F216&amp;"")),"GREEN",$P216),IF(NOT(ISNUMBER($G216)),$P216,IF($N216="Min",IF($G216&gt;=$F216,"GREEN",IF($G216&gt;=$F216-$O216,"YELLOW",$P216)),IF($N216="Max",IF($G216&lt;=$F216,"GREEN",IF($G216&lt;=$F216+$O216,"YELLOW",$P216)),IF($N216="Range",IF(ABS($G216-$F216)&lt;=$O216,"GREEN",$P216),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K216" s="39">
-        <f>IF($A216="","",IF($H216="Non-Compliant","RED",IF(AND(OR($H216="Alternative Offer",$H216="Partially Compliant"),$J216="GREEN"),"YELLOW",IF(AND($J216="GREEN",ISNUMBER($R216),$R216&lt;Baseline!$B$9),"YELLOW",$J216))))</f>
-        <v/>
-      </c>
-      <c r="L216" s="39">
-        <f>IF($A216="","",IF($K216="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A216,Exceptions!$C$5:$C$104,$B216,Exceptions!$D$5:$D$104,$C216,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K216)))</f>
-        <v/>
-      </c>
-      <c r="M216" s="39">
-        <f>IF($A216="","",IF($H216="","Declaration missing",IF($H216="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R216),$R216&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H216="Fully Compliant",$J216&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N216" s="58">
-        <f>IF($A216="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C216,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O216" s="58">
-        <f>IF($A216="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C216,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P216" s="58">
-        <f>IF($A216="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C216,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q216" s="58">
-        <f>IF($A216="","",$A216&amp;"|"&amp;$B216&amp;"|"&amp;$C216)</f>
-        <v/>
-      </c>
-      <c r="R216" s="59" t="n"/>
-      <c r="S216" s="60" t="n"/>
-    </row>
-    <row r="217" ht="15" customHeight="1" s="34">
-      <c r="A217" s="54" t="n"/>
-      <c r="B217" s="54" t="n"/>
-      <c r="C217" s="54" t="n"/>
-      <c r="D217" s="55">
-        <f>IF($A217="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C217,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E217" s="55">
-        <f>IF($A217="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C217,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F217" s="56">
-        <f>IF($A217="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C217,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G217" s="57" t="n"/>
-      <c r="H217" s="54" t="n"/>
-      <c r="I217" s="54" t="n"/>
-      <c r="J217" s="39">
-        <f>IF($A217="","",IF($E217="Informational","GREEN",IF($G217="",IF($E217="Mandatory","RED","YELLOW"),IF($N217="Exact",IF(UPPER(TRIM($G217&amp;""))=UPPER(TRIM($F217&amp;"")),"GREEN",$P217),IF(NOT(ISNUMBER($G217)),$P217,IF($N217="Min",IF($G217&gt;=$F217,"GREEN",IF($G217&gt;=$F217-$O217,"YELLOW",$P217)),IF($N217="Max",IF($G217&lt;=$F217,"GREEN",IF($G217&lt;=$F217+$O217,"YELLOW",$P217)),IF($N217="Range",IF(ABS($G217-$F217)&lt;=$O217,"GREEN",$P217),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K217" s="39">
-        <f>IF($A217="","",IF($H217="Non-Compliant","RED",IF(AND(OR($H217="Alternative Offer",$H217="Partially Compliant"),$J217="GREEN"),"YELLOW",IF(AND($J217="GREEN",ISNUMBER($R217),$R217&lt;Baseline!$B$9),"YELLOW",$J217))))</f>
-        <v/>
-      </c>
-      <c r="L217" s="39">
-        <f>IF($A217="","",IF($K217="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A217,Exceptions!$C$5:$C$104,$B217,Exceptions!$D$5:$D$104,$C217,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K217)))</f>
-        <v/>
-      </c>
-      <c r="M217" s="39">
-        <f>IF($A217="","",IF($H217="","Declaration missing",IF($H217="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R217),$R217&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H217="Fully Compliant",$J217&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N217" s="58">
-        <f>IF($A217="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C217,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O217" s="58">
-        <f>IF($A217="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C217,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P217" s="58">
-        <f>IF($A217="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C217,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q217" s="58">
-        <f>IF($A217="","",$A217&amp;"|"&amp;$B217&amp;"|"&amp;$C217)</f>
-        <v/>
-      </c>
-      <c r="R217" s="59" t="n"/>
-      <c r="S217" s="60" t="n"/>
-    </row>
-    <row r="218" ht="15" customHeight="1" s="34">
-      <c r="A218" s="54" t="n"/>
-      <c r="B218" s="54" t="n"/>
-      <c r="C218" s="54" t="n"/>
-      <c r="D218" s="55">
-        <f>IF($A218="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C218,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E218" s="55">
-        <f>IF($A218="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C218,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F218" s="56">
-        <f>IF($A218="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C218,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G218" s="57" t="n"/>
-      <c r="H218" s="54" t="n"/>
-      <c r="I218" s="54" t="n"/>
-      <c r="J218" s="39">
-        <f>IF($A218="","",IF($E218="Informational","GREEN",IF($G218="",IF($E218="Mandatory","RED","YELLOW"),IF($N218="Exact",IF(UPPER(TRIM($G218&amp;""))=UPPER(TRIM($F218&amp;"")),"GREEN",$P218),IF(NOT(ISNUMBER($G218)),$P218,IF($N218="Min",IF($G218&gt;=$F218,"GREEN",IF($G218&gt;=$F218-$O218,"YELLOW",$P218)),IF($N218="Max",IF($G218&lt;=$F218,"GREEN",IF($G218&lt;=$F218+$O218,"YELLOW",$P218)),IF($N218="Range",IF(ABS($G218-$F218)&lt;=$O218,"GREEN",$P218),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K218" s="39">
-        <f>IF($A218="","",IF($H218="Non-Compliant","RED",IF(AND(OR($H218="Alternative Offer",$H218="Partially Compliant"),$J218="GREEN"),"YELLOW",IF(AND($J218="GREEN",ISNUMBER($R218),$R218&lt;Baseline!$B$9),"YELLOW",$J218))))</f>
-        <v/>
-      </c>
-      <c r="L218" s="39">
-        <f>IF($A218="","",IF($K218="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A218,Exceptions!$C$5:$C$104,$B218,Exceptions!$D$5:$D$104,$C218,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K218)))</f>
-        <v/>
-      </c>
-      <c r="M218" s="39">
-        <f>IF($A218="","",IF($H218="","Declaration missing",IF($H218="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R218),$R218&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H218="Fully Compliant",$J218&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N218" s="58">
-        <f>IF($A218="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C218,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O218" s="58">
-        <f>IF($A218="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C218,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P218" s="58">
-        <f>IF($A218="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C218,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q218" s="58">
-        <f>IF($A218="","",$A218&amp;"|"&amp;$B218&amp;"|"&amp;$C218)</f>
-        <v/>
-      </c>
-      <c r="R218" s="59" t="n"/>
-      <c r="S218" s="60" t="n"/>
-    </row>
-    <row r="219" ht="15" customHeight="1" s="34">
-      <c r="A219" s="54" t="n"/>
-      <c r="B219" s="54" t="n"/>
-      <c r="C219" s="54" t="n"/>
-      <c r="D219" s="55">
-        <f>IF($A219="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C219,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E219" s="55">
-        <f>IF($A219="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C219,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F219" s="56">
-        <f>IF($A219="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C219,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G219" s="57" t="n"/>
-      <c r="H219" s="54" t="n"/>
-      <c r="I219" s="54" t="n"/>
-      <c r="J219" s="39">
-        <f>IF($A219="","",IF($E219="Informational","GREEN",IF($G219="",IF($E219="Mandatory","RED","YELLOW"),IF($N219="Exact",IF(UPPER(TRIM($G219&amp;""))=UPPER(TRIM($F219&amp;"")),"GREEN",$P219),IF(NOT(ISNUMBER($G219)),$P219,IF($N219="Min",IF($G219&gt;=$F219,"GREEN",IF($G219&gt;=$F219-$O219,"YELLOW",$P219)),IF($N219="Max",IF($G219&lt;=$F219,"GREEN",IF($G219&lt;=$F219+$O219,"YELLOW",$P219)),IF($N219="Range",IF(ABS($G219-$F219)&lt;=$O219,"GREEN",$P219),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K219" s="39">
-        <f>IF($A219="","",IF($H219="Non-Compliant","RED",IF(AND(OR($H219="Alternative Offer",$H219="Partially Compliant"),$J219="GREEN"),"YELLOW",IF(AND($J219="GREEN",ISNUMBER($R219),$R219&lt;Baseline!$B$9),"YELLOW",$J219))))</f>
-        <v/>
-      </c>
-      <c r="L219" s="39">
-        <f>IF($A219="","",IF($K219="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A219,Exceptions!$C$5:$C$104,$B219,Exceptions!$D$5:$D$104,$C219,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K219)))</f>
-        <v/>
-      </c>
-      <c r="M219" s="39">
-        <f>IF($A219="","",IF($H219="","Declaration missing",IF($H219="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R219),$R219&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H219="Fully Compliant",$J219&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N219" s="58">
-        <f>IF($A219="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C219,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O219" s="58">
-        <f>IF($A219="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C219,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P219" s="58">
-        <f>IF($A219="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C219,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q219" s="58">
-        <f>IF($A219="","",$A219&amp;"|"&amp;$B219&amp;"|"&amp;$C219)</f>
-        <v/>
-      </c>
-      <c r="R219" s="59" t="n"/>
-      <c r="S219" s="60" t="n"/>
-    </row>
-    <row r="220" ht="15" customHeight="1" s="34">
-      <c r="A220" s="54" t="n"/>
-      <c r="B220" s="54" t="n"/>
-      <c r="C220" s="54" t="n"/>
-      <c r="D220" s="55">
-        <f>IF($A220="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C220,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E220" s="55">
-        <f>IF($A220="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C220,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F220" s="56">
-        <f>IF($A220="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C220,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G220" s="57" t="n"/>
-      <c r="H220" s="54" t="n"/>
-      <c r="I220" s="54" t="n"/>
-      <c r="J220" s="39">
-        <f>IF($A220="","",IF($E220="Informational","GREEN",IF($G220="",IF($E220="Mandatory","RED","YELLOW"),IF($N220="Exact",IF(UPPER(TRIM($G220&amp;""))=UPPER(TRIM($F220&amp;"")),"GREEN",$P220),IF(NOT(ISNUMBER($G220)),$P220,IF($N220="Min",IF($G220&gt;=$F220,"GREEN",IF($G220&gt;=$F220-$O220,"YELLOW",$P220)),IF($N220="Max",IF($G220&lt;=$F220,"GREEN",IF($G220&lt;=$F220+$O220,"YELLOW",$P220)),IF($N220="Range",IF(ABS($G220-$F220)&lt;=$O220,"GREEN",$P220),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K220" s="39">
-        <f>IF($A220="","",IF($H220="Non-Compliant","RED",IF(AND(OR($H220="Alternative Offer",$H220="Partially Compliant"),$J220="GREEN"),"YELLOW",IF(AND($J220="GREEN",ISNUMBER($R220),$R220&lt;Baseline!$B$9),"YELLOW",$J220))))</f>
-        <v/>
-      </c>
-      <c r="L220" s="39">
-        <f>IF($A220="","",IF($K220="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A220,Exceptions!$C$5:$C$104,$B220,Exceptions!$D$5:$D$104,$C220,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K220)))</f>
-        <v/>
-      </c>
-      <c r="M220" s="39">
-        <f>IF($A220="","",IF($H220="","Declaration missing",IF($H220="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R220),$R220&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H220="Fully Compliant",$J220&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N220" s="58">
-        <f>IF($A220="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C220,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O220" s="58">
-        <f>IF($A220="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C220,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P220" s="58">
-        <f>IF($A220="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C220,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q220" s="58">
-        <f>IF($A220="","",$A220&amp;"|"&amp;$B220&amp;"|"&amp;$C220)</f>
-        <v/>
-      </c>
-      <c r="R220" s="59" t="n"/>
-      <c r="S220" s="60" t="n"/>
-    </row>
-    <row r="221" ht="15" customHeight="1" s="34">
-      <c r="A221" s="54" t="n"/>
-      <c r="B221" s="54" t="n"/>
-      <c r="C221" s="54" t="n"/>
-      <c r="D221" s="55">
-        <f>IF($A221="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C221,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E221" s="55">
-        <f>IF($A221="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C221,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F221" s="56">
-        <f>IF($A221="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C221,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G221" s="57" t="n"/>
-      <c r="H221" s="54" t="n"/>
-      <c r="I221" s="54" t="n"/>
-      <c r="J221" s="39">
-        <f>IF($A221="","",IF($E221="Informational","GREEN",IF($G221="",IF($E221="Mandatory","RED","YELLOW"),IF($N221="Exact",IF(UPPER(TRIM($G221&amp;""))=UPPER(TRIM($F221&amp;"")),"GREEN",$P221),IF(NOT(ISNUMBER($G221)),$P221,IF($N221="Min",IF($G221&gt;=$F221,"GREEN",IF($G221&gt;=$F221-$O221,"YELLOW",$P221)),IF($N221="Max",IF($G221&lt;=$F221,"GREEN",IF($G221&lt;=$F221+$O221,"YELLOW",$P221)),IF($N221="Range",IF(ABS($G221-$F221)&lt;=$O221,"GREEN",$P221),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K221" s="39">
-        <f>IF($A221="","",IF($H221="Non-Compliant","RED",IF(AND(OR($H221="Alternative Offer",$H221="Partially Compliant"),$J221="GREEN"),"YELLOW",IF(AND($J221="GREEN",ISNUMBER($R221),$R221&lt;Baseline!$B$9),"YELLOW",$J221))))</f>
-        <v/>
-      </c>
-      <c r="L221" s="39">
-        <f>IF($A221="","",IF($K221="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A221,Exceptions!$C$5:$C$104,$B221,Exceptions!$D$5:$D$104,$C221,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K221)))</f>
-        <v/>
-      </c>
-      <c r="M221" s="39">
-        <f>IF($A221="","",IF($H221="","Declaration missing",IF($H221="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R221),$R221&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H221="Fully Compliant",$J221&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N221" s="58">
-        <f>IF($A221="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C221,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O221" s="58">
-        <f>IF($A221="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C221,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P221" s="58">
-        <f>IF($A221="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C221,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q221" s="58">
-        <f>IF($A221="","",$A221&amp;"|"&amp;$B221&amp;"|"&amp;$C221)</f>
-        <v/>
-      </c>
-      <c r="R221" s="59" t="n"/>
-      <c r="S221" s="60" t="n"/>
-    </row>
-    <row r="222" ht="15" customHeight="1" s="34">
-      <c r="A222" s="54" t="n"/>
-      <c r="B222" s="54" t="n"/>
-      <c r="C222" s="54" t="n"/>
-      <c r="D222" s="55">
-        <f>IF($A222="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C222,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E222" s="55">
-        <f>IF($A222="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C222,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F222" s="56">
-        <f>IF($A222="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C222,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G222" s="57" t="n"/>
-      <c r="H222" s="54" t="n"/>
-      <c r="I222" s="54" t="n"/>
-      <c r="J222" s="39">
-        <f>IF($A222="","",IF($E222="Informational","GREEN",IF($G222="",IF($E222="Mandatory","RED","YELLOW"),IF($N222="Exact",IF(UPPER(TRIM($G222&amp;""))=UPPER(TRIM($F222&amp;"")),"GREEN",$P222),IF(NOT(ISNUMBER($G222)),$P222,IF($N222="Min",IF($G222&gt;=$F222,"GREEN",IF($G222&gt;=$F222-$O222,"YELLOW",$P222)),IF($N222="Max",IF($G222&lt;=$F222,"GREEN",IF($G222&lt;=$F222+$O222,"YELLOW",$P222)),IF($N222="Range",IF(ABS($G222-$F222)&lt;=$O222,"GREEN",$P222),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K222" s="39">
-        <f>IF($A222="","",IF($H222="Non-Compliant","RED",IF(AND(OR($H222="Alternative Offer",$H222="Partially Compliant"),$J222="GREEN"),"YELLOW",IF(AND($J222="GREEN",ISNUMBER($R222),$R222&lt;Baseline!$B$9),"YELLOW",$J222))))</f>
-        <v/>
-      </c>
-      <c r="L222" s="39">
-        <f>IF($A222="","",IF($K222="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A222,Exceptions!$C$5:$C$104,$B222,Exceptions!$D$5:$D$104,$C222,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K222)))</f>
-        <v/>
-      </c>
-      <c r="M222" s="39">
-        <f>IF($A222="","",IF($H222="","Declaration missing",IF($H222="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R222),$R222&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H222="Fully Compliant",$J222&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N222" s="58">
-        <f>IF($A222="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C222,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O222" s="58">
-        <f>IF($A222="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C222,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P222" s="58">
-        <f>IF($A222="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C222,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q222" s="58">
-        <f>IF($A222="","",$A222&amp;"|"&amp;$B222&amp;"|"&amp;$C222)</f>
-        <v/>
-      </c>
-      <c r="R222" s="59" t="n"/>
-      <c r="S222" s="60" t="n"/>
-    </row>
-    <row r="223" ht="15" customHeight="1" s="34">
-      <c r="A223" s="54" t="n"/>
-      <c r="B223" s="54" t="n"/>
-      <c r="C223" s="54" t="n"/>
-      <c r="D223" s="55">
-        <f>IF($A223="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C223,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E223" s="55">
-        <f>IF($A223="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C223,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F223" s="56">
-        <f>IF($A223="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C223,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G223" s="57" t="n"/>
-      <c r="H223" s="54" t="n"/>
-      <c r="I223" s="54" t="n"/>
-      <c r="J223" s="39">
-        <f>IF($A223="","",IF($E223="Informational","GREEN",IF($G223="",IF($E223="Mandatory","RED","YELLOW"),IF($N223="Exact",IF(UPPER(TRIM($G223&amp;""))=UPPER(TRIM($F223&amp;"")),"GREEN",$P223),IF(NOT(ISNUMBER($G223)),$P223,IF($N223="Min",IF($G223&gt;=$F223,"GREEN",IF($G223&gt;=$F223-$O223,"YELLOW",$P223)),IF($N223="Max",IF($G223&lt;=$F223,"GREEN",IF($G223&lt;=$F223+$O223,"YELLOW",$P223)),IF($N223="Range",IF(ABS($G223-$F223)&lt;=$O223,"GREEN",$P223),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K223" s="39">
-        <f>IF($A223="","",IF($H223="Non-Compliant","RED",IF(AND(OR($H223="Alternative Offer",$H223="Partially Compliant"),$J223="GREEN"),"YELLOW",IF(AND($J223="GREEN",ISNUMBER($R223),$R223&lt;Baseline!$B$9),"YELLOW",$J223))))</f>
-        <v/>
-      </c>
-      <c r="L223" s="39">
-        <f>IF($A223="","",IF($K223="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A223,Exceptions!$C$5:$C$104,$B223,Exceptions!$D$5:$D$104,$C223,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K223)))</f>
-        <v/>
-      </c>
-      <c r="M223" s="39">
-        <f>IF($A223="","",IF($H223="","Declaration missing",IF($H223="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R223),$R223&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H223="Fully Compliant",$J223&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N223" s="58">
-        <f>IF($A223="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C223,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O223" s="58">
-        <f>IF($A223="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C223,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P223" s="58">
-        <f>IF($A223="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C223,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q223" s="58">
-        <f>IF($A223="","",$A223&amp;"|"&amp;$B223&amp;"|"&amp;$C223)</f>
-        <v/>
-      </c>
-      <c r="R223" s="59" t="n"/>
-      <c r="S223" s="60" t="n"/>
-    </row>
-    <row r="224" ht="15" customHeight="1" s="34">
-      <c r="A224" s="54" t="n"/>
-      <c r="B224" s="54" t="n"/>
-      <c r="C224" s="54" t="n"/>
-      <c r="D224" s="55">
-        <f>IF($A224="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C224,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E224" s="55">
-        <f>IF($A224="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C224,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F224" s="56">
-        <f>IF($A224="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C224,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G224" s="57" t="n"/>
-      <c r="H224" s="54" t="n"/>
-      <c r="I224" s="54" t="n"/>
-      <c r="J224" s="39">
-        <f>IF($A224="","",IF($E224="Informational","GREEN",IF($G224="",IF($E224="Mandatory","RED","YELLOW"),IF($N224="Exact",IF(UPPER(TRIM($G224&amp;""))=UPPER(TRIM($F224&amp;"")),"GREEN",$P224),IF(NOT(ISNUMBER($G224)),$P224,IF($N224="Min",IF($G224&gt;=$F224,"GREEN",IF($G224&gt;=$F224-$O224,"YELLOW",$P224)),IF($N224="Max",IF($G224&lt;=$F224,"GREEN",IF($G224&lt;=$F224+$O224,"YELLOW",$P224)),IF($N224="Range",IF(ABS($G224-$F224)&lt;=$O224,"GREEN",$P224),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K224" s="39">
-        <f>IF($A224="","",IF($H224="Non-Compliant","RED",IF(AND(OR($H224="Alternative Offer",$H224="Partially Compliant"),$J224="GREEN"),"YELLOW",IF(AND($J224="GREEN",ISNUMBER($R224),$R224&lt;Baseline!$B$9),"YELLOW",$J224))))</f>
-        <v/>
-      </c>
-      <c r="L224" s="39">
-        <f>IF($A224="","",IF($K224="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A224,Exceptions!$C$5:$C$104,$B224,Exceptions!$D$5:$D$104,$C224,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K224)))</f>
-        <v/>
-      </c>
-      <c r="M224" s="39">
-        <f>IF($A224="","",IF($H224="","Declaration missing",IF($H224="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R224),$R224&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H224="Fully Compliant",$J224&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N224" s="58">
-        <f>IF($A224="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C224,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O224" s="58">
-        <f>IF($A224="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C224,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P224" s="58">
-        <f>IF($A224="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C224,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q224" s="58">
-        <f>IF($A224="","",$A224&amp;"|"&amp;$B224&amp;"|"&amp;$C224)</f>
-        <v/>
-      </c>
-      <c r="R224" s="59" t="n"/>
-      <c r="S224" s="60" t="n"/>
-    </row>
-    <row r="225" ht="15" customHeight="1" s="34">
-      <c r="A225" s="54" t="n"/>
-      <c r="B225" s="54" t="n"/>
-      <c r="C225" s="54" t="n"/>
-      <c r="D225" s="55">
-        <f>IF($A225="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C225,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E225" s="55">
-        <f>IF($A225="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C225,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F225" s="56">
-        <f>IF($A225="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C225,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G225" s="57" t="n"/>
-      <c r="H225" s="54" t="n"/>
-      <c r="I225" s="54" t="n"/>
-      <c r="J225" s="39">
-        <f>IF($A225="","",IF($E225="Informational","GREEN",IF($G225="",IF($E225="Mandatory","RED","YELLOW"),IF($N225="Exact",IF(UPPER(TRIM($G225&amp;""))=UPPER(TRIM($F225&amp;"")),"GREEN",$P225),IF(NOT(ISNUMBER($G225)),$P225,IF($N225="Min",IF($G225&gt;=$F225,"GREEN",IF($G225&gt;=$F225-$O225,"YELLOW",$P225)),IF($N225="Max",IF($G225&lt;=$F225,"GREEN",IF($G225&lt;=$F225+$O225,"YELLOW",$P225)),IF($N225="Range",IF(ABS($G225-$F225)&lt;=$O225,"GREEN",$P225),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K225" s="39">
-        <f>IF($A225="","",IF($H225="Non-Compliant","RED",IF(AND(OR($H225="Alternative Offer",$H225="Partially Compliant"),$J225="GREEN"),"YELLOW",IF(AND($J225="GREEN",ISNUMBER($R225),$R225&lt;Baseline!$B$9),"YELLOW",$J225))))</f>
-        <v/>
-      </c>
-      <c r="L225" s="39">
-        <f>IF($A225="","",IF($K225="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A225,Exceptions!$C$5:$C$104,$B225,Exceptions!$D$5:$D$104,$C225,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K225)))</f>
-        <v/>
-      </c>
-      <c r="M225" s="39">
-        <f>IF($A225="","",IF($H225="","Declaration missing",IF($H225="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R225),$R225&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H225="Fully Compliant",$J225&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N225" s="58">
-        <f>IF($A225="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C225,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O225" s="58">
-        <f>IF($A225="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C225,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P225" s="58">
-        <f>IF($A225="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C225,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q225" s="58">
-        <f>IF($A225="","",$A225&amp;"|"&amp;$B225&amp;"|"&amp;$C225)</f>
-        <v/>
-      </c>
-      <c r="R225" s="59" t="n"/>
-      <c r="S225" s="60" t="n"/>
-    </row>
-    <row r="226" ht="15" customHeight="1" s="34">
-      <c r="A226" s="54" t="n"/>
-      <c r="B226" s="54" t="n"/>
-      <c r="C226" s="54" t="n"/>
-      <c r="D226" s="55">
-        <f>IF($A226="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C226,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E226" s="55">
-        <f>IF($A226="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C226,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F226" s="56">
-        <f>IF($A226="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C226,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G226" s="57" t="n"/>
-      <c r="H226" s="54" t="n"/>
-      <c r="I226" s="54" t="n"/>
-      <c r="J226" s="39">
-        <f>IF($A226="","",IF($E226="Informational","GREEN",IF($G226="",IF($E226="Mandatory","RED","YELLOW"),IF($N226="Exact",IF(UPPER(TRIM($G226&amp;""))=UPPER(TRIM($F226&amp;"")),"GREEN",$P226),IF(NOT(ISNUMBER($G226)),$P226,IF($N226="Min",IF($G226&gt;=$F226,"GREEN",IF($G226&gt;=$F226-$O226,"YELLOW",$P226)),IF($N226="Max",IF($G226&lt;=$F226,"GREEN",IF($G226&lt;=$F226+$O226,"YELLOW",$P226)),IF($N226="Range",IF(ABS($G226-$F226)&lt;=$O226,"GREEN",$P226),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K226" s="39">
-        <f>IF($A226="","",IF($H226="Non-Compliant","RED",IF(AND(OR($H226="Alternative Offer",$H226="Partially Compliant"),$J226="GREEN"),"YELLOW",IF(AND($J226="GREEN",ISNUMBER($R226),$R226&lt;Baseline!$B$9),"YELLOW",$J226))))</f>
-        <v/>
-      </c>
-      <c r="L226" s="39">
-        <f>IF($A226="","",IF($K226="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A226,Exceptions!$C$5:$C$104,$B226,Exceptions!$D$5:$D$104,$C226,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K226)))</f>
-        <v/>
-      </c>
-      <c r="M226" s="39">
-        <f>IF($A226="","",IF($H226="","Declaration missing",IF($H226="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R226),$R226&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H226="Fully Compliant",$J226&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N226" s="58">
-        <f>IF($A226="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C226,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O226" s="58">
-        <f>IF($A226="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C226,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P226" s="58">
-        <f>IF($A226="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C226,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q226" s="58">
-        <f>IF($A226="","",$A226&amp;"|"&amp;$B226&amp;"|"&amp;$C226)</f>
-        <v/>
-      </c>
-      <c r="R226" s="59" t="n"/>
-      <c r="S226" s="60" t="n"/>
-    </row>
-    <row r="227" ht="15" customHeight="1" s="34">
-      <c r="A227" s="54" t="n"/>
-      <c r="B227" s="54" t="n"/>
-      <c r="C227" s="54" t="n"/>
-      <c r="D227" s="55">
-        <f>IF($A227="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C227,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E227" s="55">
-        <f>IF($A227="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C227,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F227" s="56">
-        <f>IF($A227="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C227,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G227" s="57" t="n"/>
-      <c r="H227" s="54" t="n"/>
-      <c r="I227" s="54" t="n"/>
-      <c r="J227" s="39">
-        <f>IF($A227="","",IF($E227="Informational","GREEN",IF($G227="",IF($E227="Mandatory","RED","YELLOW"),IF($N227="Exact",IF(UPPER(TRIM($G227&amp;""))=UPPER(TRIM($F227&amp;"")),"GREEN",$P227),IF(NOT(ISNUMBER($G227)),$P227,IF($N227="Min",IF($G227&gt;=$F227,"GREEN",IF($G227&gt;=$F227-$O227,"YELLOW",$P227)),IF($N227="Max",IF($G227&lt;=$F227,"GREEN",IF($G227&lt;=$F227+$O227,"YELLOW",$P227)),IF($N227="Range",IF(ABS($G227-$F227)&lt;=$O227,"GREEN",$P227),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K227" s="39">
-        <f>IF($A227="","",IF($H227="Non-Compliant","RED",IF(AND(OR($H227="Alternative Offer",$H227="Partially Compliant"),$J227="GREEN"),"YELLOW",IF(AND($J227="GREEN",ISNUMBER($R227),$R227&lt;Baseline!$B$9),"YELLOW",$J227))))</f>
-        <v/>
-      </c>
-      <c r="L227" s="39">
-        <f>IF($A227="","",IF($K227="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A227,Exceptions!$C$5:$C$104,$B227,Exceptions!$D$5:$D$104,$C227,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K227)))</f>
-        <v/>
-      </c>
-      <c r="M227" s="39">
-        <f>IF($A227="","",IF($H227="","Declaration missing",IF($H227="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R227),$R227&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H227="Fully Compliant",$J227&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N227" s="58">
-        <f>IF($A227="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C227,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O227" s="58">
-        <f>IF($A227="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C227,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P227" s="58">
-        <f>IF($A227="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C227,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q227" s="58">
-        <f>IF($A227="","",$A227&amp;"|"&amp;$B227&amp;"|"&amp;$C227)</f>
-        <v/>
-      </c>
-      <c r="R227" s="59" t="n"/>
-      <c r="S227" s="60" t="n"/>
-    </row>
-    <row r="228" ht="15" customHeight="1" s="34">
-      <c r="A228" s="54" t="n"/>
-      <c r="B228" s="54" t="n"/>
-      <c r="C228" s="54" t="n"/>
-      <c r="D228" s="55">
-        <f>IF($A228="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C228,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E228" s="55">
-        <f>IF($A228="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C228,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F228" s="56">
-        <f>IF($A228="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C228,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G228" s="57" t="n"/>
-      <c r="H228" s="54" t="n"/>
-      <c r="I228" s="54" t="n"/>
-      <c r="J228" s="39">
-        <f>IF($A228="","",IF($E228="Informational","GREEN",IF($G228="",IF($E228="Mandatory","RED","YELLOW"),IF($N228="Exact",IF(UPPER(TRIM($G228&amp;""))=UPPER(TRIM($F228&amp;"")),"GREEN",$P228),IF(NOT(ISNUMBER($G228)),$P228,IF($N228="Min",IF($G228&gt;=$F228,"GREEN",IF($G228&gt;=$F228-$O228,"YELLOW",$P228)),IF($N228="Max",IF($G228&lt;=$F228,"GREEN",IF($G228&lt;=$F228+$O228,"YELLOW",$P228)),IF($N228="Range",IF(ABS($G228-$F228)&lt;=$O228,"GREEN",$P228),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K228" s="39">
-        <f>IF($A228="","",IF($H228="Non-Compliant","RED",IF(AND(OR($H228="Alternative Offer",$H228="Partially Compliant"),$J228="GREEN"),"YELLOW",IF(AND($J228="GREEN",ISNUMBER($R228),$R228&lt;Baseline!$B$9),"YELLOW",$J228))))</f>
-        <v/>
-      </c>
-      <c r="L228" s="39">
-        <f>IF($A228="","",IF($K228="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A228,Exceptions!$C$5:$C$104,$B228,Exceptions!$D$5:$D$104,$C228,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K228)))</f>
-        <v/>
-      </c>
-      <c r="M228" s="39">
-        <f>IF($A228="","",IF($H228="","Declaration missing",IF($H228="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R228),$R228&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H228="Fully Compliant",$J228&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N228" s="58">
-        <f>IF($A228="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C228,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O228" s="58">
-        <f>IF($A228="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C228,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P228" s="58">
-        <f>IF($A228="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C228,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q228" s="58">
-        <f>IF($A228="","",$A228&amp;"|"&amp;$B228&amp;"|"&amp;$C228)</f>
-        <v/>
-      </c>
-      <c r="R228" s="59" t="n"/>
-      <c r="S228" s="60" t="n"/>
-    </row>
-    <row r="229" ht="15" customHeight="1" s="34">
-      <c r="A229" s="54" t="n"/>
-      <c r="B229" s="54" t="n"/>
-      <c r="C229" s="54" t="n"/>
-      <c r="D229" s="55">
-        <f>IF($A229="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C229,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E229" s="55">
-        <f>IF($A229="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C229,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F229" s="56">
-        <f>IF($A229="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C229,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G229" s="57" t="n"/>
-      <c r="H229" s="54" t="n"/>
-      <c r="I229" s="54" t="n"/>
-      <c r="J229" s="39">
-        <f>IF($A229="","",IF($E229="Informational","GREEN",IF($G229="",IF($E229="Mandatory","RED","YELLOW"),IF($N229="Exact",IF(UPPER(TRIM($G229&amp;""))=UPPER(TRIM($F229&amp;"")),"GREEN",$P229),IF(NOT(ISNUMBER($G229)),$P229,IF($N229="Min",IF($G229&gt;=$F229,"GREEN",IF($G229&gt;=$F229-$O229,"YELLOW",$P229)),IF($N229="Max",IF($G229&lt;=$F229,"GREEN",IF($G229&lt;=$F229+$O229,"YELLOW",$P229)),IF($N229="Range",IF(ABS($G229-$F229)&lt;=$O229,"GREEN",$P229),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K229" s="39">
-        <f>IF($A229="","",IF($H229="Non-Compliant","RED",IF(AND(OR($H229="Alternative Offer",$H229="Partially Compliant"),$J229="GREEN"),"YELLOW",IF(AND($J229="GREEN",ISNUMBER($R229),$R229&lt;Baseline!$B$9),"YELLOW",$J229))))</f>
-        <v/>
-      </c>
-      <c r="L229" s="39">
-        <f>IF($A229="","",IF($K229="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A229,Exceptions!$C$5:$C$104,$B229,Exceptions!$D$5:$D$104,$C229,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K229)))</f>
-        <v/>
-      </c>
-      <c r="M229" s="39">
-        <f>IF($A229="","",IF($H229="","Declaration missing",IF($H229="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R229),$R229&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H229="Fully Compliant",$J229&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N229" s="58">
-        <f>IF($A229="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C229,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O229" s="58">
-        <f>IF($A229="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C229,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P229" s="58">
-        <f>IF($A229="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C229,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q229" s="58">
-        <f>IF($A229="","",$A229&amp;"|"&amp;$B229&amp;"|"&amp;$C229)</f>
-        <v/>
-      </c>
-      <c r="R229" s="59" t="n"/>
-      <c r="S229" s="60" t="n"/>
-    </row>
-    <row r="230" ht="15" customHeight="1" s="34">
-      <c r="A230" s="54" t="n"/>
-      <c r="B230" s="54" t="n"/>
-      <c r="C230" s="54" t="n"/>
-      <c r="D230" s="55">
-        <f>IF($A230="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C230,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E230" s="55">
-        <f>IF($A230="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C230,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F230" s="56">
-        <f>IF($A230="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C230,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G230" s="57" t="n"/>
-      <c r="H230" s="54" t="n"/>
-      <c r="I230" s="54" t="n"/>
-      <c r="J230" s="39">
-        <f>IF($A230="","",IF($E230="Informational","GREEN",IF($G230="",IF($E230="Mandatory","RED","YELLOW"),IF($N230="Exact",IF(UPPER(TRIM($G230&amp;""))=UPPER(TRIM($F230&amp;"")),"GREEN",$P230),IF(NOT(ISNUMBER($G230)),$P230,IF($N230="Min",IF($G230&gt;=$F230,"GREEN",IF($G230&gt;=$F230-$O230,"YELLOW",$P230)),IF($N230="Max",IF($G230&lt;=$F230,"GREEN",IF($G230&lt;=$F230+$O230,"YELLOW",$P230)),IF($N230="Range",IF(ABS($G230-$F230)&lt;=$O230,"GREEN",$P230),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K230" s="39">
-        <f>IF($A230="","",IF($H230="Non-Compliant","RED",IF(AND(OR($H230="Alternative Offer",$H230="Partially Compliant"),$J230="GREEN"),"YELLOW",IF(AND($J230="GREEN",ISNUMBER($R230),$R230&lt;Baseline!$B$9),"YELLOW",$J230))))</f>
-        <v/>
-      </c>
-      <c r="L230" s="39">
-        <f>IF($A230="","",IF($K230="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A230,Exceptions!$C$5:$C$104,$B230,Exceptions!$D$5:$D$104,$C230,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K230)))</f>
-        <v/>
-      </c>
-      <c r="M230" s="39">
-        <f>IF($A230="","",IF($H230="","Declaration missing",IF($H230="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R230),$R230&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H230="Fully Compliant",$J230&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N230" s="58">
-        <f>IF($A230="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C230,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O230" s="58">
-        <f>IF($A230="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C230,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P230" s="58">
-        <f>IF($A230="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C230,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q230" s="58">
-        <f>IF($A230="","",$A230&amp;"|"&amp;$B230&amp;"|"&amp;$C230)</f>
-        <v/>
-      </c>
-      <c r="R230" s="59" t="n"/>
-      <c r="S230" s="60" t="n"/>
-    </row>
-    <row r="231" ht="15" customHeight="1" s="34">
-      <c r="A231" s="54" t="n"/>
-      <c r="B231" s="54" t="n"/>
-      <c r="C231" s="54" t="n"/>
-      <c r="D231" s="55">
-        <f>IF($A231="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C231,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E231" s="55">
-        <f>IF($A231="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C231,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F231" s="56">
-        <f>IF($A231="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C231,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G231" s="57" t="n"/>
-      <c r="H231" s="54" t="n"/>
-      <c r="I231" s="54" t="n"/>
-      <c r="J231" s="39">
-        <f>IF($A231="","",IF($E231="Informational","GREEN",IF($G231="",IF($E231="Mandatory","RED","YELLOW"),IF($N231="Exact",IF(UPPER(TRIM($G231&amp;""))=UPPER(TRIM($F231&amp;"")),"GREEN",$P231),IF(NOT(ISNUMBER($G231)),$P231,IF($N231="Min",IF($G231&gt;=$F231,"GREEN",IF($G231&gt;=$F231-$O231,"YELLOW",$P231)),IF($N231="Max",IF($G231&lt;=$F231,"GREEN",IF($G231&lt;=$F231+$O231,"YELLOW",$P231)),IF($N231="Range",IF(ABS($G231-$F231)&lt;=$O231,"GREEN",$P231),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K231" s="39">
-        <f>IF($A231="","",IF($H231="Non-Compliant","RED",IF(AND(OR($H231="Alternative Offer",$H231="Partially Compliant"),$J231="GREEN"),"YELLOW",IF(AND($J231="GREEN",ISNUMBER($R231),$R231&lt;Baseline!$B$9),"YELLOW",$J231))))</f>
-        <v/>
-      </c>
-      <c r="L231" s="39">
-        <f>IF($A231="","",IF($K231="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A231,Exceptions!$C$5:$C$104,$B231,Exceptions!$D$5:$D$104,$C231,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K231)))</f>
-        <v/>
-      </c>
-      <c r="M231" s="39">
-        <f>IF($A231="","",IF($H231="","Declaration missing",IF($H231="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R231),$R231&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H231="Fully Compliant",$J231&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N231" s="58">
-        <f>IF($A231="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C231,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O231" s="58">
-        <f>IF($A231="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C231,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P231" s="58">
-        <f>IF($A231="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C231,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q231" s="58">
-        <f>IF($A231="","",$A231&amp;"|"&amp;$B231&amp;"|"&amp;$C231)</f>
-        <v/>
-      </c>
-      <c r="R231" s="59" t="n"/>
-      <c r="S231" s="60" t="n"/>
-    </row>
-    <row r="232" ht="15" customHeight="1" s="34">
-      <c r="A232" s="54" t="n"/>
-      <c r="B232" s="54" t="n"/>
-      <c r="C232" s="54" t="n"/>
-      <c r="D232" s="55">
-        <f>IF($A232="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C232,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E232" s="55">
-        <f>IF($A232="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C232,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F232" s="56">
-        <f>IF($A232="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C232,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G232" s="57" t="n"/>
-      <c r="H232" s="54" t="n"/>
-      <c r="I232" s="54" t="n"/>
-      <c r="J232" s="39">
-        <f>IF($A232="","",IF($E232="Informational","GREEN",IF($G232="",IF($E232="Mandatory","RED","YELLOW"),IF($N232="Exact",IF(UPPER(TRIM($G232&amp;""))=UPPER(TRIM($F232&amp;"")),"GREEN",$P232),IF(NOT(ISNUMBER($G232)),$P232,IF($N232="Min",IF($G232&gt;=$F232,"GREEN",IF($G232&gt;=$F232-$O232,"YELLOW",$P232)),IF($N232="Max",IF($G232&lt;=$F232,"GREEN",IF($G232&lt;=$F232+$O232,"YELLOW",$P232)),IF($N232="Range",IF(ABS($G232-$F232)&lt;=$O232,"GREEN",$P232),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K232" s="39">
-        <f>IF($A232="","",IF($H232="Non-Compliant","RED",IF(AND(OR($H232="Alternative Offer",$H232="Partially Compliant"),$J232="GREEN"),"YELLOW",IF(AND($J232="GREEN",ISNUMBER($R232),$R232&lt;Baseline!$B$9),"YELLOW",$J232))))</f>
-        <v/>
-      </c>
-      <c r="L232" s="39">
-        <f>IF($A232="","",IF($K232="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A232,Exceptions!$C$5:$C$104,$B232,Exceptions!$D$5:$D$104,$C232,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K232)))</f>
-        <v/>
-      </c>
-      <c r="M232" s="39">
-        <f>IF($A232="","",IF($H232="","Declaration missing",IF($H232="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R232),$R232&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H232="Fully Compliant",$J232&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N232" s="58">
-        <f>IF($A232="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C232,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O232" s="58">
-        <f>IF($A232="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C232,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P232" s="58">
-        <f>IF($A232="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C232,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q232" s="58">
-        <f>IF($A232="","",$A232&amp;"|"&amp;$B232&amp;"|"&amp;$C232)</f>
-        <v/>
-      </c>
-      <c r="R232" s="59" t="n"/>
-      <c r="S232" s="60" t="n"/>
-    </row>
-    <row r="233" ht="15" customHeight="1" s="34">
-      <c r="A233" s="54" t="n"/>
-      <c r="B233" s="54" t="n"/>
-      <c r="C233" s="54" t="n"/>
-      <c r="D233" s="55">
-        <f>IF($A233="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C233,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E233" s="55">
-        <f>IF($A233="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C233,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F233" s="56">
-        <f>IF($A233="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C233,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G233" s="57" t="n"/>
-      <c r="H233" s="54" t="n"/>
-      <c r="I233" s="54" t="n"/>
-      <c r="J233" s="39">
-        <f>IF($A233="","",IF($E233="Informational","GREEN",IF($G233="",IF($E233="Mandatory","RED","YELLOW"),IF($N233="Exact",IF(UPPER(TRIM($G233&amp;""))=UPPER(TRIM($F233&amp;"")),"GREEN",$P233),IF(NOT(ISNUMBER($G233)),$P233,IF($N233="Min",IF($G233&gt;=$F233,"GREEN",IF($G233&gt;=$F233-$O233,"YELLOW",$P233)),IF($N233="Max",IF($G233&lt;=$F233,"GREEN",IF($G233&lt;=$F233+$O233,"YELLOW",$P233)),IF($N233="Range",IF(ABS($G233-$F233)&lt;=$O233,"GREEN",$P233),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K233" s="39">
-        <f>IF($A233="","",IF($H233="Non-Compliant","RED",IF(AND(OR($H233="Alternative Offer",$H233="Partially Compliant"),$J233="GREEN"),"YELLOW",IF(AND($J233="GREEN",ISNUMBER($R233),$R233&lt;Baseline!$B$9),"YELLOW",$J233))))</f>
-        <v/>
-      </c>
-      <c r="L233" s="39">
-        <f>IF($A233="","",IF($K233="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A233,Exceptions!$C$5:$C$104,$B233,Exceptions!$D$5:$D$104,$C233,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K233)))</f>
-        <v/>
-      </c>
-      <c r="M233" s="39">
-        <f>IF($A233="","",IF($H233="","Declaration missing",IF($H233="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R233),$R233&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H233="Fully Compliant",$J233&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N233" s="58">
-        <f>IF($A233="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C233,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O233" s="58">
-        <f>IF($A233="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C233,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P233" s="58">
-        <f>IF($A233="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C233,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q233" s="58">
-        <f>IF($A233="","",$A233&amp;"|"&amp;$B233&amp;"|"&amp;$C233)</f>
-        <v/>
-      </c>
-      <c r="R233" s="59" t="n"/>
-      <c r="S233" s="60" t="n"/>
-    </row>
-    <row r="234" ht="15" customHeight="1" s="34">
-      <c r="A234" s="54" t="n"/>
-      <c r="B234" s="54" t="n"/>
-      <c r="C234" s="54" t="n"/>
-      <c r="D234" s="55">
-        <f>IF($A234="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C234,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E234" s="55">
-        <f>IF($A234="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C234,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F234" s="56">
-        <f>IF($A234="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C234,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G234" s="57" t="n"/>
-      <c r="H234" s="54" t="n"/>
-      <c r="I234" s="54" t="n"/>
-      <c r="J234" s="39">
-        <f>IF($A234="","",IF($E234="Informational","GREEN",IF($G234="",IF($E234="Mandatory","RED","YELLOW"),IF($N234="Exact",IF(UPPER(TRIM($G234&amp;""))=UPPER(TRIM($F234&amp;"")),"GREEN",$P234),IF(NOT(ISNUMBER($G234)),$P234,IF($N234="Min",IF($G234&gt;=$F234,"GREEN",IF($G234&gt;=$F234-$O234,"YELLOW",$P234)),IF($N234="Max",IF($G234&lt;=$F234,"GREEN",IF($G234&lt;=$F234+$O234,"YELLOW",$P234)),IF($N234="Range",IF(ABS($G234-$F234)&lt;=$O234,"GREEN",$P234),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K234" s="39">
-        <f>IF($A234="","",IF($H234="Non-Compliant","RED",IF(AND(OR($H234="Alternative Offer",$H234="Partially Compliant"),$J234="GREEN"),"YELLOW",IF(AND($J234="GREEN",ISNUMBER($R234),$R234&lt;Baseline!$B$9),"YELLOW",$J234))))</f>
-        <v/>
-      </c>
-      <c r="L234" s="39">
-        <f>IF($A234="","",IF($K234="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A234,Exceptions!$C$5:$C$104,$B234,Exceptions!$D$5:$D$104,$C234,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K234)))</f>
-        <v/>
-      </c>
-      <c r="M234" s="39">
-        <f>IF($A234="","",IF($H234="","Declaration missing",IF($H234="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R234),$R234&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H234="Fully Compliant",$J234&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N234" s="58">
-        <f>IF($A234="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C234,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O234" s="58">
-        <f>IF($A234="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C234,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P234" s="58">
-        <f>IF($A234="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C234,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q234" s="58">
-        <f>IF($A234="","",$A234&amp;"|"&amp;$B234&amp;"|"&amp;$C234)</f>
-        <v/>
-      </c>
-      <c r="R234" s="59" t="n"/>
-      <c r="S234" s="60" t="n"/>
-    </row>
-    <row r="235" ht="15" customHeight="1" s="34">
-      <c r="A235" s="54" t="n"/>
-      <c r="B235" s="54" t="n"/>
-      <c r="C235" s="54" t="n"/>
-      <c r="D235" s="55">
-        <f>IF($A235="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C235,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E235" s="55">
-        <f>IF($A235="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C235,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F235" s="56">
-        <f>IF($A235="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C235,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G235" s="57" t="n"/>
-      <c r="H235" s="54" t="n"/>
-      <c r="I235" s="54" t="n"/>
-      <c r="J235" s="39">
-        <f>IF($A235="","",IF($E235="Informational","GREEN",IF($G235="",IF($E235="Mandatory","RED","YELLOW"),IF($N235="Exact",IF(UPPER(TRIM($G235&amp;""))=UPPER(TRIM($F235&amp;"")),"GREEN",$P235),IF(NOT(ISNUMBER($G235)),$P235,IF($N235="Min",IF($G235&gt;=$F235,"GREEN",IF($G235&gt;=$F235-$O235,"YELLOW",$P235)),IF($N235="Max",IF($G235&lt;=$F235,"GREEN",IF($G235&lt;=$F235+$O235,"YELLOW",$P235)),IF($N235="Range",IF(ABS($G235-$F235)&lt;=$O235,"GREEN",$P235),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K235" s="39">
-        <f>IF($A235="","",IF($H235="Non-Compliant","RED",IF(AND(OR($H235="Alternative Offer",$H235="Partially Compliant"),$J235="GREEN"),"YELLOW",IF(AND($J235="GREEN",ISNUMBER($R235),$R235&lt;Baseline!$B$9),"YELLOW",$J235))))</f>
-        <v/>
-      </c>
-      <c r="L235" s="39">
-        <f>IF($A235="","",IF($K235="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A235,Exceptions!$C$5:$C$104,$B235,Exceptions!$D$5:$D$104,$C235,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K235)))</f>
-        <v/>
-      </c>
-      <c r="M235" s="39">
-        <f>IF($A235="","",IF($H235="","Declaration missing",IF($H235="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R235),$R235&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H235="Fully Compliant",$J235&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N235" s="58">
-        <f>IF($A235="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C235,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O235" s="58">
-        <f>IF($A235="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C235,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P235" s="58">
-        <f>IF($A235="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C235,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q235" s="58">
-        <f>IF($A235="","",$A235&amp;"|"&amp;$B235&amp;"|"&amp;$C235)</f>
-        <v/>
-      </c>
-      <c r="R235" s="59" t="n"/>
-      <c r="S235" s="60" t="n"/>
-    </row>
-    <row r="236" ht="15" customHeight="1" s="34">
-      <c r="A236" s="54" t="n"/>
-      <c r="B236" s="54" t="n"/>
-      <c r="C236" s="54" t="n"/>
-      <c r="D236" s="55">
-        <f>IF($A236="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C236,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E236" s="55">
-        <f>IF($A236="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C236,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F236" s="56">
-        <f>IF($A236="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C236,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G236" s="57" t="n"/>
-      <c r="H236" s="54" t="n"/>
-      <c r="I236" s="54" t="n"/>
-      <c r="J236" s="39">
-        <f>IF($A236="","",IF($E236="Informational","GREEN",IF($G236="",IF($E236="Mandatory","RED","YELLOW"),IF($N236="Exact",IF(UPPER(TRIM($G236&amp;""))=UPPER(TRIM($F236&amp;"")),"GREEN",$P236),IF(NOT(ISNUMBER($G236)),$P236,IF($N236="Min",IF($G236&gt;=$F236,"GREEN",IF($G236&gt;=$F236-$O236,"YELLOW",$P236)),IF($N236="Max",IF($G236&lt;=$F236,"GREEN",IF($G236&lt;=$F236+$O236,"YELLOW",$P236)),IF($N236="Range",IF(ABS($G236-$F236)&lt;=$O236,"GREEN",$P236),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K236" s="39">
-        <f>IF($A236="","",IF($H236="Non-Compliant","RED",IF(AND(OR($H236="Alternative Offer",$H236="Partially Compliant"),$J236="GREEN"),"YELLOW",IF(AND($J236="GREEN",ISNUMBER($R236),$R236&lt;Baseline!$B$9),"YELLOW",$J236))))</f>
-        <v/>
-      </c>
-      <c r="L236" s="39">
-        <f>IF($A236="","",IF($K236="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A236,Exceptions!$C$5:$C$104,$B236,Exceptions!$D$5:$D$104,$C236,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K236)))</f>
-        <v/>
-      </c>
-      <c r="M236" s="39">
-        <f>IF($A236="","",IF($H236="","Declaration missing",IF($H236="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R236),$R236&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H236="Fully Compliant",$J236&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N236" s="58">
-        <f>IF($A236="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C236,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O236" s="58">
-        <f>IF($A236="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C236,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P236" s="58">
-        <f>IF($A236="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C236,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q236" s="58">
-        <f>IF($A236="","",$A236&amp;"|"&amp;$B236&amp;"|"&amp;$C236)</f>
-        <v/>
-      </c>
-      <c r="R236" s="59" t="n"/>
-      <c r="S236" s="60" t="n"/>
-    </row>
-    <row r="237" ht="15" customHeight="1" s="34">
-      <c r="A237" s="54" t="n"/>
-      <c r="B237" s="54" t="n"/>
-      <c r="C237" s="54" t="n"/>
-      <c r="D237" s="55">
-        <f>IF($A237="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C237,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E237" s="55">
-        <f>IF($A237="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C237,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F237" s="56">
-        <f>IF($A237="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C237,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G237" s="57" t="n"/>
-      <c r="H237" s="54" t="n"/>
-      <c r="I237" s="54" t="n"/>
-      <c r="J237" s="39">
-        <f>IF($A237="","",IF($E237="Informational","GREEN",IF($G237="",IF($E237="Mandatory","RED","YELLOW"),IF($N237="Exact",IF(UPPER(TRIM($G237&amp;""))=UPPER(TRIM($F237&amp;"")),"GREEN",$P237),IF(NOT(ISNUMBER($G237)),$P237,IF($N237="Min",IF($G237&gt;=$F237,"GREEN",IF($G237&gt;=$F237-$O237,"YELLOW",$P237)),IF($N237="Max",IF($G237&lt;=$F237,"GREEN",IF($G237&lt;=$F237+$O237,"YELLOW",$P237)),IF($N237="Range",IF(ABS($G237-$F237)&lt;=$O237,"GREEN",$P237),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K237" s="39">
-        <f>IF($A237="","",IF($H237="Non-Compliant","RED",IF(AND(OR($H237="Alternative Offer",$H237="Partially Compliant"),$J237="GREEN"),"YELLOW",IF(AND($J237="GREEN",ISNUMBER($R237),$R237&lt;Baseline!$B$9),"YELLOW",$J237))))</f>
-        <v/>
-      </c>
-      <c r="L237" s="39">
-        <f>IF($A237="","",IF($K237="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A237,Exceptions!$C$5:$C$104,$B237,Exceptions!$D$5:$D$104,$C237,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K237)))</f>
-        <v/>
-      </c>
-      <c r="M237" s="39">
-        <f>IF($A237="","",IF($H237="","Declaration missing",IF($H237="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R237),$R237&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H237="Fully Compliant",$J237&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N237" s="58">
-        <f>IF($A237="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C237,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O237" s="58">
-        <f>IF($A237="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C237,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P237" s="58">
-        <f>IF($A237="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C237,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q237" s="58">
-        <f>IF($A237="","",$A237&amp;"|"&amp;$B237&amp;"|"&amp;$C237)</f>
-        <v/>
-      </c>
-      <c r="R237" s="59" t="n"/>
-      <c r="S237" s="60" t="n"/>
-    </row>
-    <row r="238" ht="15" customHeight="1" s="34">
-      <c r="A238" s="54" t="n"/>
-      <c r="B238" s="54" t="n"/>
-      <c r="C238" s="54" t="n"/>
-      <c r="D238" s="55">
-        <f>IF($A238="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C238,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E238" s="55">
-        <f>IF($A238="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C238,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F238" s="56">
-        <f>IF($A238="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C238,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G238" s="57" t="n"/>
-      <c r="H238" s="54" t="n"/>
-      <c r="I238" s="54" t="n"/>
-      <c r="J238" s="39">
-        <f>IF($A238="","",IF($E238="Informational","GREEN",IF($G238="",IF($E238="Mandatory","RED","YELLOW"),IF($N238="Exact",IF(UPPER(TRIM($G238&amp;""))=UPPER(TRIM($F238&amp;"")),"GREEN",$P238),IF(NOT(ISNUMBER($G238)),$P238,IF($N238="Min",IF($G238&gt;=$F238,"GREEN",IF($G238&gt;=$F238-$O238,"YELLOW",$P238)),IF($N238="Max",IF($G238&lt;=$F238,"GREEN",IF($G238&lt;=$F238+$O238,"YELLOW",$P238)),IF($N238="Range",IF(ABS($G238-$F238)&lt;=$O238,"GREEN",$P238),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K238" s="39">
-        <f>IF($A238="","",IF($H238="Non-Compliant","RED",IF(AND(OR($H238="Alternative Offer",$H238="Partially Compliant"),$J238="GREEN"),"YELLOW",IF(AND($J238="GREEN",ISNUMBER($R238),$R238&lt;Baseline!$B$9),"YELLOW",$J238))))</f>
-        <v/>
-      </c>
-      <c r="L238" s="39">
-        <f>IF($A238="","",IF($K238="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A238,Exceptions!$C$5:$C$104,$B238,Exceptions!$D$5:$D$104,$C238,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K238)))</f>
-        <v/>
-      </c>
-      <c r="M238" s="39">
-        <f>IF($A238="","",IF($H238="","Declaration missing",IF($H238="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R238),$R238&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H238="Fully Compliant",$J238&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N238" s="58">
-        <f>IF($A238="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C238,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O238" s="58">
-        <f>IF($A238="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C238,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P238" s="58">
-        <f>IF($A238="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C238,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q238" s="58">
-        <f>IF($A238="","",$A238&amp;"|"&amp;$B238&amp;"|"&amp;$C238)</f>
-        <v/>
-      </c>
-      <c r="R238" s="59" t="n"/>
-      <c r="S238" s="60" t="n"/>
-    </row>
-    <row r="239" ht="15" customHeight="1" s="34">
-      <c r="A239" s="54" t="n"/>
-      <c r="B239" s="54" t="n"/>
-      <c r="C239" s="54" t="n"/>
-      <c r="D239" s="55">
-        <f>IF($A239="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C239,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E239" s="55">
-        <f>IF($A239="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C239,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F239" s="56">
-        <f>IF($A239="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C239,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G239" s="57" t="n"/>
-      <c r="H239" s="54" t="n"/>
-      <c r="I239" s="54" t="n"/>
-      <c r="J239" s="39">
-        <f>IF($A239="","",IF($E239="Informational","GREEN",IF($G239="",IF($E239="Mandatory","RED","YELLOW"),IF($N239="Exact",IF(UPPER(TRIM($G239&amp;""))=UPPER(TRIM($F239&amp;"")),"GREEN",$P239),IF(NOT(ISNUMBER($G239)),$P239,IF($N239="Min",IF($G239&gt;=$F239,"GREEN",IF($G239&gt;=$F239-$O239,"YELLOW",$P239)),IF($N239="Max",IF($G239&lt;=$F239,"GREEN",IF($G239&lt;=$F239+$O239,"YELLOW",$P239)),IF($N239="Range",IF(ABS($G239-$F239)&lt;=$O239,"GREEN",$P239),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K239" s="39">
-        <f>IF($A239="","",IF($H239="Non-Compliant","RED",IF(AND(OR($H239="Alternative Offer",$H239="Partially Compliant"),$J239="GREEN"),"YELLOW",IF(AND($J239="GREEN",ISNUMBER($R239),$R239&lt;Baseline!$B$9),"YELLOW",$J239))))</f>
-        <v/>
-      </c>
-      <c r="L239" s="39">
-        <f>IF($A239="","",IF($K239="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A239,Exceptions!$C$5:$C$104,$B239,Exceptions!$D$5:$D$104,$C239,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K239)))</f>
-        <v/>
-      </c>
-      <c r="M239" s="39">
-        <f>IF($A239="","",IF($H239="","Declaration missing",IF($H239="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R239),$R239&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H239="Fully Compliant",$J239&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N239" s="58">
-        <f>IF($A239="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C239,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O239" s="58">
-        <f>IF($A239="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C239,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P239" s="58">
-        <f>IF($A239="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C239,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q239" s="58">
-        <f>IF($A239="","",$A239&amp;"|"&amp;$B239&amp;"|"&amp;$C239)</f>
-        <v/>
-      </c>
-      <c r="R239" s="59" t="n"/>
-      <c r="S239" s="60" t="n"/>
-    </row>
-    <row r="240" ht="15" customHeight="1" s="34">
-      <c r="A240" s="54" t="n"/>
-      <c r="B240" s="54" t="n"/>
-      <c r="C240" s="54" t="n"/>
-      <c r="D240" s="55">
-        <f>IF($A240="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C240,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E240" s="55">
-        <f>IF($A240="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C240,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F240" s="56">
-        <f>IF($A240="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C240,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G240" s="57" t="n"/>
-      <c r="H240" s="54" t="n"/>
-      <c r="I240" s="54" t="n"/>
-      <c r="J240" s="39">
-        <f>IF($A240="","",IF($E240="Informational","GREEN",IF($G240="",IF($E240="Mandatory","RED","YELLOW"),IF($N240="Exact",IF(UPPER(TRIM($G240&amp;""))=UPPER(TRIM($F240&amp;"")),"GREEN",$P240),IF(NOT(ISNUMBER($G240)),$P240,IF($N240="Min",IF($G240&gt;=$F240,"GREEN",IF($G240&gt;=$F240-$O240,"YELLOW",$P240)),IF($N240="Max",IF($G240&lt;=$F240,"GREEN",IF($G240&lt;=$F240+$O240,"YELLOW",$P240)),IF($N240="Range",IF(ABS($G240-$F240)&lt;=$O240,"GREEN",$P240),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K240" s="39">
-        <f>IF($A240="","",IF($H240="Non-Compliant","RED",IF(AND(OR($H240="Alternative Offer",$H240="Partially Compliant"),$J240="GREEN"),"YELLOW",IF(AND($J240="GREEN",ISNUMBER($R240),$R240&lt;Baseline!$B$9),"YELLOW",$J240))))</f>
-        <v/>
-      </c>
-      <c r="L240" s="39">
-        <f>IF($A240="","",IF($K240="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A240,Exceptions!$C$5:$C$104,$B240,Exceptions!$D$5:$D$104,$C240,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K240)))</f>
-        <v/>
-      </c>
-      <c r="M240" s="39">
-        <f>IF($A240="","",IF($H240="","Declaration missing",IF($H240="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R240),$R240&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H240="Fully Compliant",$J240&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N240" s="58">
-        <f>IF($A240="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C240,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O240" s="58">
-        <f>IF($A240="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C240,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P240" s="58">
-        <f>IF($A240="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C240,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q240" s="58">
-        <f>IF($A240="","",$A240&amp;"|"&amp;$B240&amp;"|"&amp;$C240)</f>
-        <v/>
-      </c>
-      <c r="R240" s="59" t="n"/>
-      <c r="S240" s="60" t="n"/>
-    </row>
-    <row r="241" ht="15" customHeight="1" s="34">
-      <c r="A241" s="54" t="n"/>
-      <c r="B241" s="54" t="n"/>
-      <c r="C241" s="54" t="n"/>
-      <c r="D241" s="55">
-        <f>IF($A241="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C241,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E241" s="55">
-        <f>IF($A241="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C241,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F241" s="56">
-        <f>IF($A241="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C241,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G241" s="57" t="n"/>
-      <c r="H241" s="54" t="n"/>
-      <c r="I241" s="54" t="n"/>
-      <c r="J241" s="39">
-        <f>IF($A241="","",IF($E241="Informational","GREEN",IF($G241="",IF($E241="Mandatory","RED","YELLOW"),IF($N241="Exact",IF(UPPER(TRIM($G241&amp;""))=UPPER(TRIM($F241&amp;"")),"GREEN",$P241),IF(NOT(ISNUMBER($G241)),$P241,IF($N241="Min",IF($G241&gt;=$F241,"GREEN",IF($G241&gt;=$F241-$O241,"YELLOW",$P241)),IF($N241="Max",IF($G241&lt;=$F241,"GREEN",IF($G241&lt;=$F241+$O241,"YELLOW",$P241)),IF($N241="Range",IF(ABS($G241-$F241)&lt;=$O241,"GREEN",$P241),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K241" s="39">
-        <f>IF($A241="","",IF($H241="Non-Compliant","RED",IF(AND(OR($H241="Alternative Offer",$H241="Partially Compliant"),$J241="GREEN"),"YELLOW",IF(AND($J241="GREEN",ISNUMBER($R241),$R241&lt;Baseline!$B$9),"YELLOW",$J241))))</f>
-        <v/>
-      </c>
-      <c r="L241" s="39">
-        <f>IF($A241="","",IF($K241="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A241,Exceptions!$C$5:$C$104,$B241,Exceptions!$D$5:$D$104,$C241,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K241)))</f>
-        <v/>
-      </c>
-      <c r="M241" s="39">
-        <f>IF($A241="","",IF($H241="","Declaration missing",IF($H241="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R241),$R241&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H241="Fully Compliant",$J241&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N241" s="58">
-        <f>IF($A241="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C241,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O241" s="58">
-        <f>IF($A241="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C241,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P241" s="58">
-        <f>IF($A241="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C241,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q241" s="58">
-        <f>IF($A241="","",$A241&amp;"|"&amp;$B241&amp;"|"&amp;$C241)</f>
-        <v/>
-      </c>
-      <c r="R241" s="59" t="n"/>
-      <c r="S241" s="60" t="n"/>
-    </row>
-    <row r="242" ht="15" customHeight="1" s="34">
-      <c r="A242" s="54" t="n"/>
-      <c r="B242" s="54" t="n"/>
-      <c r="C242" s="54" t="n"/>
-      <c r="D242" s="55">
-        <f>IF($A242="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C242,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E242" s="55">
-        <f>IF($A242="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C242,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F242" s="56">
-        <f>IF($A242="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C242,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G242" s="57" t="n"/>
-      <c r="H242" s="54" t="n"/>
-      <c r="I242" s="54" t="n"/>
-      <c r="J242" s="39">
-        <f>IF($A242="","",IF($E242="Informational","GREEN",IF($G242="",IF($E242="Mandatory","RED","YELLOW"),IF($N242="Exact",IF(UPPER(TRIM($G242&amp;""))=UPPER(TRIM($F242&amp;"")),"GREEN",$P242),IF(NOT(ISNUMBER($G242)),$P242,IF($N242="Min",IF($G242&gt;=$F242,"GREEN",IF($G242&gt;=$F242-$O242,"YELLOW",$P242)),IF($N242="Max",IF($G242&lt;=$F242,"GREEN",IF($G242&lt;=$F242+$O242,"YELLOW",$P242)),IF($N242="Range",IF(ABS($G242-$F242)&lt;=$O242,"GREEN",$P242),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K242" s="39">
-        <f>IF($A242="","",IF($H242="Non-Compliant","RED",IF(AND(OR($H242="Alternative Offer",$H242="Partially Compliant"),$J242="GREEN"),"YELLOW",IF(AND($J242="GREEN",ISNUMBER($R242),$R242&lt;Baseline!$B$9),"YELLOW",$J242))))</f>
-        <v/>
-      </c>
-      <c r="L242" s="39">
-        <f>IF($A242="","",IF($K242="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A242,Exceptions!$C$5:$C$104,$B242,Exceptions!$D$5:$D$104,$C242,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K242)))</f>
-        <v/>
-      </c>
-      <c r="M242" s="39">
-        <f>IF($A242="","",IF($H242="","Declaration missing",IF($H242="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R242),$R242&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H242="Fully Compliant",$J242&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N242" s="58">
-        <f>IF($A242="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C242,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O242" s="58">
-        <f>IF($A242="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C242,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P242" s="58">
-        <f>IF($A242="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C242,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q242" s="58">
-        <f>IF($A242="","",$A242&amp;"|"&amp;$B242&amp;"|"&amp;$C242)</f>
-        <v/>
-      </c>
-      <c r="R242" s="59" t="n"/>
-      <c r="S242" s="60" t="n"/>
-    </row>
-    <row r="243" ht="15" customHeight="1" s="34">
-      <c r="A243" s="54" t="n"/>
-      <c r="B243" s="54" t="n"/>
-      <c r="C243" s="54" t="n"/>
-      <c r="D243" s="55">
-        <f>IF($A243="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C243,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E243" s="55">
-        <f>IF($A243="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C243,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F243" s="56">
-        <f>IF($A243="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C243,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G243" s="57" t="n"/>
-      <c r="H243" s="54" t="n"/>
-      <c r="I243" s="54" t="n"/>
-      <c r="J243" s="39">
-        <f>IF($A243="","",IF($E243="Informational","GREEN",IF($G243="",IF($E243="Mandatory","RED","YELLOW"),IF($N243="Exact",IF(UPPER(TRIM($G243&amp;""))=UPPER(TRIM($F243&amp;"")),"GREEN",$P243),IF(NOT(ISNUMBER($G243)),$P243,IF($N243="Min",IF($G243&gt;=$F243,"GREEN",IF($G243&gt;=$F243-$O243,"YELLOW",$P243)),IF($N243="Max",IF($G243&lt;=$F243,"GREEN",IF($G243&lt;=$F243+$O243,"YELLOW",$P243)),IF($N243="Range",IF(ABS($G243-$F243)&lt;=$O243,"GREEN",$P243),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K243" s="39">
-        <f>IF($A243="","",IF($H243="Non-Compliant","RED",IF(AND(OR($H243="Alternative Offer",$H243="Partially Compliant"),$J243="GREEN"),"YELLOW",IF(AND($J243="GREEN",ISNUMBER($R243),$R243&lt;Baseline!$B$9),"YELLOW",$J243))))</f>
-        <v/>
-      </c>
-      <c r="L243" s="39">
-        <f>IF($A243="","",IF($K243="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A243,Exceptions!$C$5:$C$104,$B243,Exceptions!$D$5:$D$104,$C243,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K243)))</f>
-        <v/>
-      </c>
-      <c r="M243" s="39">
-        <f>IF($A243="","",IF($H243="","Declaration missing",IF($H243="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R243),$R243&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H243="Fully Compliant",$J243&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N243" s="58">
-        <f>IF($A243="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C243,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O243" s="58">
-        <f>IF($A243="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C243,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P243" s="58">
-        <f>IF($A243="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C243,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q243" s="58">
-        <f>IF($A243="","",$A243&amp;"|"&amp;$B243&amp;"|"&amp;$C243)</f>
-        <v/>
-      </c>
-      <c r="R243" s="59" t="n"/>
-      <c r="S243" s="60" t="n"/>
-    </row>
-    <row r="244" ht="15" customHeight="1" s="34">
-      <c r="A244" s="54" t="n"/>
-      <c r="B244" s="54" t="n"/>
-      <c r="C244" s="54" t="n"/>
-      <c r="D244" s="55">
-        <f>IF($A244="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C244,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E244" s="55">
-        <f>IF($A244="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C244,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F244" s="56">
-        <f>IF($A244="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C244,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G244" s="57" t="n"/>
-      <c r="H244" s="54" t="n"/>
-      <c r="I244" s="54" t="n"/>
-      <c r="J244" s="39">
-        <f>IF($A244="","",IF($E244="Informational","GREEN",IF($G244="",IF($E244="Mandatory","RED","YELLOW"),IF($N244="Exact",IF(UPPER(TRIM($G244&amp;""))=UPPER(TRIM($F244&amp;"")),"GREEN",$P244),IF(NOT(ISNUMBER($G244)),$P244,IF($N244="Min",IF($G244&gt;=$F244,"GREEN",IF($G244&gt;=$F244-$O244,"YELLOW",$P244)),IF($N244="Max",IF($G244&lt;=$F244,"GREEN",IF($G244&lt;=$F244+$O244,"YELLOW",$P244)),IF($N244="Range",IF(ABS($G244-$F244)&lt;=$O244,"GREEN",$P244),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K244" s="39">
-        <f>IF($A244="","",IF($H244="Non-Compliant","RED",IF(AND(OR($H244="Alternative Offer",$H244="Partially Compliant"),$J244="GREEN"),"YELLOW",IF(AND($J244="GREEN",ISNUMBER($R244),$R244&lt;Baseline!$B$9),"YELLOW",$J244))))</f>
-        <v/>
-      </c>
-      <c r="L244" s="39">
-        <f>IF($A244="","",IF($K244="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A244,Exceptions!$C$5:$C$104,$B244,Exceptions!$D$5:$D$104,$C244,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K244)))</f>
-        <v/>
-      </c>
-      <c r="M244" s="39">
-        <f>IF($A244="","",IF($H244="","Declaration missing",IF($H244="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R244),$R244&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H244="Fully Compliant",$J244&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N244" s="58">
-        <f>IF($A244="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C244,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O244" s="58">
-        <f>IF($A244="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C244,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P244" s="58">
-        <f>IF($A244="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C244,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q244" s="58">
-        <f>IF($A244="","",$A244&amp;"|"&amp;$B244&amp;"|"&amp;$C244)</f>
-        <v/>
-      </c>
-      <c r="R244" s="59" t="n"/>
-      <c r="S244" s="60" t="n"/>
-    </row>
-    <row r="245" ht="15" customHeight="1" s="34">
-      <c r="A245" s="54" t="n"/>
-      <c r="B245" s="54" t="n"/>
-      <c r="C245" s="54" t="n"/>
-      <c r="D245" s="55">
-        <f>IF($A245="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C245,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E245" s="55">
-        <f>IF($A245="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C245,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F245" s="56">
-        <f>IF($A245="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C245,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G245" s="57" t="n"/>
-      <c r="H245" s="54" t="n"/>
-      <c r="I245" s="54" t="n"/>
-      <c r="J245" s="39">
-        <f>IF($A245="","",IF($E245="Informational","GREEN",IF($G245="",IF($E245="Mandatory","RED","YELLOW"),IF($N245="Exact",IF(UPPER(TRIM($G245&amp;""))=UPPER(TRIM($F245&amp;"")),"GREEN",$P245),IF(NOT(ISNUMBER($G245)),$P245,IF($N245="Min",IF($G245&gt;=$F245,"GREEN",IF($G245&gt;=$F245-$O245,"YELLOW",$P245)),IF($N245="Max",IF($G245&lt;=$F245,"GREEN",IF($G245&lt;=$F245+$O245,"YELLOW",$P245)),IF($N245="Range",IF(ABS($G245-$F245)&lt;=$O245,"GREEN",$P245),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K245" s="39">
-        <f>IF($A245="","",IF($H245="Non-Compliant","RED",IF(AND(OR($H245="Alternative Offer",$H245="Partially Compliant"),$J245="GREEN"),"YELLOW",IF(AND($J245="GREEN",ISNUMBER($R245),$R245&lt;Baseline!$B$9),"YELLOW",$J245))))</f>
-        <v/>
-      </c>
-      <c r="L245" s="39">
-        <f>IF($A245="","",IF($K245="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A245,Exceptions!$C$5:$C$104,$B245,Exceptions!$D$5:$D$104,$C245,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K245)))</f>
-        <v/>
-      </c>
-      <c r="M245" s="39">
-        <f>IF($A245="","",IF($H245="","Declaration missing",IF($H245="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R245),$R245&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H245="Fully Compliant",$J245&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N245" s="58">
-        <f>IF($A245="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C245,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O245" s="58">
-        <f>IF($A245="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C245,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P245" s="58">
-        <f>IF($A245="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C245,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q245" s="58">
-        <f>IF($A245="","",$A245&amp;"|"&amp;$B245&amp;"|"&amp;$C245)</f>
-        <v/>
-      </c>
-      <c r="R245" s="59" t="n"/>
-      <c r="S245" s="60" t="n"/>
-    </row>
-    <row r="246" ht="15" customHeight="1" s="34">
-      <c r="A246" s="54" t="n"/>
-      <c r="B246" s="54" t="n"/>
-      <c r="C246" s="54" t="n"/>
-      <c r="D246" s="55">
-        <f>IF($A246="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C246,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E246" s="55">
-        <f>IF($A246="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C246,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F246" s="56">
-        <f>IF($A246="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C246,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G246" s="57" t="n"/>
-      <c r="H246" s="54" t="n"/>
-      <c r="I246" s="54" t="n"/>
-      <c r="J246" s="39">
-        <f>IF($A246="","",IF($E246="Informational","GREEN",IF($G246="",IF($E246="Mandatory","RED","YELLOW"),IF($N246="Exact",IF(UPPER(TRIM($G246&amp;""))=UPPER(TRIM($F246&amp;"")),"GREEN",$P246),IF(NOT(ISNUMBER($G246)),$P246,IF($N246="Min",IF($G246&gt;=$F246,"GREEN",IF($G246&gt;=$F246-$O246,"YELLOW",$P246)),IF($N246="Max",IF($G246&lt;=$F246,"GREEN",IF($G246&lt;=$F246+$O246,"YELLOW",$P246)),IF($N246="Range",IF(ABS($G246-$F246)&lt;=$O246,"GREEN",$P246),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K246" s="39">
-        <f>IF($A246="","",IF($H246="Non-Compliant","RED",IF(AND(OR($H246="Alternative Offer",$H246="Partially Compliant"),$J246="GREEN"),"YELLOW",IF(AND($J246="GREEN",ISNUMBER($R246),$R246&lt;Baseline!$B$9),"YELLOW",$J246))))</f>
-        <v/>
-      </c>
-      <c r="L246" s="39">
-        <f>IF($A246="","",IF($K246="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A246,Exceptions!$C$5:$C$104,$B246,Exceptions!$D$5:$D$104,$C246,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K246)))</f>
-        <v/>
-      </c>
-      <c r="M246" s="39">
-        <f>IF($A246="","",IF($H246="","Declaration missing",IF($H246="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R246),$R246&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H246="Fully Compliant",$J246&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N246" s="58">
-        <f>IF($A246="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C246,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O246" s="58">
-        <f>IF($A246="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C246,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P246" s="58">
-        <f>IF($A246="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C246,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q246" s="58">
-        <f>IF($A246="","",$A246&amp;"|"&amp;$B246&amp;"|"&amp;$C246)</f>
-        <v/>
-      </c>
-      <c r="R246" s="59" t="n"/>
-      <c r="S246" s="60" t="n"/>
-    </row>
-    <row r="247" ht="15" customHeight="1" s="34">
-      <c r="A247" s="54" t="n"/>
-      <c r="B247" s="54" t="n"/>
-      <c r="C247" s="54" t="n"/>
-      <c r="D247" s="55">
-        <f>IF($A247="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C247,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E247" s="55">
-        <f>IF($A247="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C247,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F247" s="56">
-        <f>IF($A247="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C247,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G247" s="57" t="n"/>
-      <c r="H247" s="54" t="n"/>
-      <c r="I247" s="54" t="n"/>
-      <c r="J247" s="39">
-        <f>IF($A247="","",IF($E247="Informational","GREEN",IF($G247="",IF($E247="Mandatory","RED","YELLOW"),IF($N247="Exact",IF(UPPER(TRIM($G247&amp;""))=UPPER(TRIM($F247&amp;"")),"GREEN",$P247),IF(NOT(ISNUMBER($G247)),$P247,IF($N247="Min",IF($G247&gt;=$F247,"GREEN",IF($G247&gt;=$F247-$O247,"YELLOW",$P247)),IF($N247="Max",IF($G247&lt;=$F247,"GREEN",IF($G247&lt;=$F247+$O247,"YELLOW",$P247)),IF($N247="Range",IF(ABS($G247-$F247)&lt;=$O247,"GREEN",$P247),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K247" s="39">
-        <f>IF($A247="","",IF($H247="Non-Compliant","RED",IF(AND(OR($H247="Alternative Offer",$H247="Partially Compliant"),$J247="GREEN"),"YELLOW",IF(AND($J247="GREEN",ISNUMBER($R247),$R247&lt;Baseline!$B$9),"YELLOW",$J247))))</f>
-        <v/>
-      </c>
-      <c r="L247" s="39">
-        <f>IF($A247="","",IF($K247="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A247,Exceptions!$C$5:$C$104,$B247,Exceptions!$D$5:$D$104,$C247,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K247)))</f>
-        <v/>
-      </c>
-      <c r="M247" s="39">
-        <f>IF($A247="","",IF($H247="","Declaration missing",IF($H247="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R247),$R247&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H247="Fully Compliant",$J247&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N247" s="58">
-        <f>IF($A247="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C247,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O247" s="58">
-        <f>IF($A247="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C247,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P247" s="58">
-        <f>IF($A247="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C247,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q247" s="58">
-        <f>IF($A247="","",$A247&amp;"|"&amp;$B247&amp;"|"&amp;$C247)</f>
-        <v/>
-      </c>
-      <c r="R247" s="59" t="n"/>
-      <c r="S247" s="60" t="n"/>
-    </row>
-    <row r="248" ht="15" customHeight="1" s="34">
-      <c r="A248" s="54" t="n"/>
-      <c r="B248" s="54" t="n"/>
-      <c r="C248" s="54" t="n"/>
-      <c r="D248" s="55">
-        <f>IF($A248="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C248,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E248" s="55">
-        <f>IF($A248="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C248,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F248" s="56">
-        <f>IF($A248="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C248,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G248" s="57" t="n"/>
-      <c r="H248" s="54" t="n"/>
-      <c r="I248" s="54" t="n"/>
-      <c r="J248" s="39">
-        <f>IF($A248="","",IF($E248="Informational","GREEN",IF($G248="",IF($E248="Mandatory","RED","YELLOW"),IF($N248="Exact",IF(UPPER(TRIM($G248&amp;""))=UPPER(TRIM($F248&amp;"")),"GREEN",$P248),IF(NOT(ISNUMBER($G248)),$P248,IF($N248="Min",IF($G248&gt;=$F248,"GREEN",IF($G248&gt;=$F248-$O248,"YELLOW",$P248)),IF($N248="Max",IF($G248&lt;=$F248,"GREEN",IF($G248&lt;=$F248+$O248,"YELLOW",$P248)),IF($N248="Range",IF(ABS($G248-$F248)&lt;=$O248,"GREEN",$P248),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K248" s="39">
-        <f>IF($A248="","",IF($H248="Non-Compliant","RED",IF(AND(OR($H248="Alternative Offer",$H248="Partially Compliant"),$J248="GREEN"),"YELLOW",IF(AND($J248="GREEN",ISNUMBER($R248),$R248&lt;Baseline!$B$9),"YELLOW",$J248))))</f>
-        <v/>
-      </c>
-      <c r="L248" s="39">
-        <f>IF($A248="","",IF($K248="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A248,Exceptions!$C$5:$C$104,$B248,Exceptions!$D$5:$D$104,$C248,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K248)))</f>
-        <v/>
-      </c>
-      <c r="M248" s="39">
-        <f>IF($A248="","",IF($H248="","Declaration missing",IF($H248="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R248),$R248&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H248="Fully Compliant",$J248&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N248" s="58">
-        <f>IF($A248="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C248,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O248" s="58">
-        <f>IF($A248="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C248,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P248" s="58">
-        <f>IF($A248="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C248,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q248" s="58">
-        <f>IF($A248="","",$A248&amp;"|"&amp;$B248&amp;"|"&amp;$C248)</f>
-        <v/>
-      </c>
-      <c r="R248" s="59" t="n"/>
-      <c r="S248" s="60" t="n"/>
-    </row>
-    <row r="249" ht="15" customHeight="1" s="34">
-      <c r="A249" s="54" t="n"/>
-      <c r="B249" s="54" t="n"/>
-      <c r="C249" s="54" t="n"/>
-      <c r="D249" s="55">
-        <f>IF($A249="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C249,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E249" s="55">
-        <f>IF($A249="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C249,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F249" s="56">
-        <f>IF($A249="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C249,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G249" s="57" t="n"/>
-      <c r="H249" s="54" t="n"/>
-      <c r="I249" s="54" t="n"/>
-      <c r="J249" s="39">
-        <f>IF($A249="","",IF($E249="Informational","GREEN",IF($G249="",IF($E249="Mandatory","RED","YELLOW"),IF($N249="Exact",IF(UPPER(TRIM($G249&amp;""))=UPPER(TRIM($F249&amp;"")),"GREEN",$P249),IF(NOT(ISNUMBER($G249)),$P249,IF($N249="Min",IF($G249&gt;=$F249,"GREEN",IF($G249&gt;=$F249-$O249,"YELLOW",$P249)),IF($N249="Max",IF($G249&lt;=$F249,"GREEN",IF($G249&lt;=$F249+$O249,"YELLOW",$P249)),IF($N249="Range",IF(ABS($G249-$F249)&lt;=$O249,"GREEN",$P249),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K249" s="39">
-        <f>IF($A249="","",IF($H249="Non-Compliant","RED",IF(AND(OR($H249="Alternative Offer",$H249="Partially Compliant"),$J249="GREEN"),"YELLOW",IF(AND($J249="GREEN",ISNUMBER($R249),$R249&lt;Baseline!$B$9),"YELLOW",$J249))))</f>
-        <v/>
-      </c>
-      <c r="L249" s="39">
-        <f>IF($A249="","",IF($K249="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A249,Exceptions!$C$5:$C$104,$B249,Exceptions!$D$5:$D$104,$C249,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K249)))</f>
-        <v/>
-      </c>
-      <c r="M249" s="39">
-        <f>IF($A249="","",IF($H249="","Declaration missing",IF($H249="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R249),$R249&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H249="Fully Compliant",$J249&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N249" s="58">
-        <f>IF($A249="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C249,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O249" s="58">
-        <f>IF($A249="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C249,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P249" s="58">
-        <f>IF($A249="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C249,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q249" s="58">
-        <f>IF($A249="","",$A249&amp;"|"&amp;$B249&amp;"|"&amp;$C249)</f>
-        <v/>
-      </c>
-      <c r="R249" s="59" t="n"/>
-      <c r="S249" s="60" t="n"/>
-    </row>
-    <row r="250" ht="15" customHeight="1" s="34">
-      <c r="A250" s="54" t="n"/>
-      <c r="B250" s="54" t="n"/>
-      <c r="C250" s="54" t="n"/>
-      <c r="D250" s="55">
-        <f>IF($A250="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C250,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E250" s="55">
-        <f>IF($A250="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C250,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F250" s="56">
-        <f>IF($A250="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C250,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G250" s="57" t="n"/>
-      <c r="H250" s="54" t="n"/>
-      <c r="I250" s="54" t="n"/>
-      <c r="J250" s="39">
-        <f>IF($A250="","",IF($E250="Informational","GREEN",IF($G250="",IF($E250="Mandatory","RED","YELLOW"),IF($N250="Exact",IF(UPPER(TRIM($G250&amp;""))=UPPER(TRIM($F250&amp;"")),"GREEN",$P250),IF(NOT(ISNUMBER($G250)),$P250,IF($N250="Min",IF($G250&gt;=$F250,"GREEN",IF($G250&gt;=$F250-$O250,"YELLOW",$P250)),IF($N250="Max",IF($G250&lt;=$F250,"GREEN",IF($G250&lt;=$F250+$O250,"YELLOW",$P250)),IF($N250="Range",IF(ABS($G250-$F250)&lt;=$O250,"GREEN",$P250),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K250" s="39">
-        <f>IF($A250="","",IF($H250="Non-Compliant","RED",IF(AND(OR($H250="Alternative Offer",$H250="Partially Compliant"),$J250="GREEN"),"YELLOW",IF(AND($J250="GREEN",ISNUMBER($R250),$R250&lt;Baseline!$B$9),"YELLOW",$J250))))</f>
-        <v/>
-      </c>
-      <c r="L250" s="39">
-        <f>IF($A250="","",IF($K250="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A250,Exceptions!$C$5:$C$104,$B250,Exceptions!$D$5:$D$104,$C250,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K250)))</f>
-        <v/>
-      </c>
-      <c r="M250" s="39">
-        <f>IF($A250="","",IF($H250="","Declaration missing",IF($H250="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R250),$R250&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H250="Fully Compliant",$J250&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N250" s="58">
-        <f>IF($A250="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C250,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O250" s="58">
-        <f>IF($A250="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C250,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P250" s="58">
-        <f>IF($A250="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C250,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q250" s="58">
-        <f>IF($A250="","",$A250&amp;"|"&amp;$B250&amp;"|"&amp;$C250)</f>
-        <v/>
-      </c>
-      <c r="R250" s="59" t="n"/>
-      <c r="S250" s="60" t="n"/>
-    </row>
-    <row r="251" ht="15" customHeight="1" s="34">
-      <c r="A251" s="54" t="n"/>
-      <c r="B251" s="54" t="n"/>
-      <c r="C251" s="54" t="n"/>
-      <c r="D251" s="55">
-        <f>IF($A251="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C251,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E251" s="55">
-        <f>IF($A251="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C251,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F251" s="56">
-        <f>IF($A251="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C251,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G251" s="57" t="n"/>
-      <c r="H251" s="54" t="n"/>
-      <c r="I251" s="54" t="n"/>
-      <c r="J251" s="39">
-        <f>IF($A251="","",IF($E251="Informational","GREEN",IF($G251="",IF($E251="Mandatory","RED","YELLOW"),IF($N251="Exact",IF(UPPER(TRIM($G251&amp;""))=UPPER(TRIM($F251&amp;"")),"GREEN",$P251),IF(NOT(ISNUMBER($G251)),$P251,IF($N251="Min",IF($G251&gt;=$F251,"GREEN",IF($G251&gt;=$F251-$O251,"YELLOW",$P251)),IF($N251="Max",IF($G251&lt;=$F251,"GREEN",IF($G251&lt;=$F251+$O251,"YELLOW",$P251)),IF($N251="Range",IF(ABS($G251-$F251)&lt;=$O251,"GREEN",$P251),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K251" s="39">
-        <f>IF($A251="","",IF($H251="Non-Compliant","RED",IF(AND(OR($H251="Alternative Offer",$H251="Partially Compliant"),$J251="GREEN"),"YELLOW",IF(AND($J251="GREEN",ISNUMBER($R251),$R251&lt;Baseline!$B$9),"YELLOW",$J251))))</f>
-        <v/>
-      </c>
-      <c r="L251" s="39">
-        <f>IF($A251="","",IF($K251="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A251,Exceptions!$C$5:$C$104,$B251,Exceptions!$D$5:$D$104,$C251,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K251)))</f>
-        <v/>
-      </c>
-      <c r="M251" s="39">
-        <f>IF($A251="","",IF($H251="","Declaration missing",IF($H251="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R251),$R251&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H251="Fully Compliant",$J251&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N251" s="58">
-        <f>IF($A251="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C251,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O251" s="58">
-        <f>IF($A251="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C251,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P251" s="58">
-        <f>IF($A251="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C251,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q251" s="58">
-        <f>IF($A251="","",$A251&amp;"|"&amp;$B251&amp;"|"&amp;$C251)</f>
-        <v/>
-      </c>
-      <c r="R251" s="59" t="n"/>
-      <c r="S251" s="60" t="n"/>
-    </row>
-    <row r="252" ht="15" customHeight="1" s="34">
-      <c r="A252" s="54" t="n"/>
-      <c r="B252" s="54" t="n"/>
-      <c r="C252" s="54" t="n"/>
-      <c r="D252" s="55">
-        <f>IF($A252="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C252,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E252" s="55">
-        <f>IF($A252="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C252,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F252" s="56">
-        <f>IF($A252="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C252,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G252" s="57" t="n"/>
-      <c r="H252" s="54" t="n"/>
-      <c r="I252" s="54" t="n"/>
-      <c r="J252" s="39">
-        <f>IF($A252="","",IF($E252="Informational","GREEN",IF($G252="",IF($E252="Mandatory","RED","YELLOW"),IF($N252="Exact",IF(UPPER(TRIM($G252&amp;""))=UPPER(TRIM($F252&amp;"")),"GREEN",$P252),IF(NOT(ISNUMBER($G252)),$P252,IF($N252="Min",IF($G252&gt;=$F252,"GREEN",IF($G252&gt;=$F252-$O252,"YELLOW",$P252)),IF($N252="Max",IF($G252&lt;=$F252,"GREEN",IF($G252&lt;=$F252+$O252,"YELLOW",$P252)),IF($N252="Range",IF(ABS($G252-$F252)&lt;=$O252,"GREEN",$P252),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K252" s="39">
-        <f>IF($A252="","",IF($H252="Non-Compliant","RED",IF(AND(OR($H252="Alternative Offer",$H252="Partially Compliant"),$J252="GREEN"),"YELLOW",IF(AND($J252="GREEN",ISNUMBER($R252),$R252&lt;Baseline!$B$9),"YELLOW",$J252))))</f>
-        <v/>
-      </c>
-      <c r="L252" s="39">
-        <f>IF($A252="","",IF($K252="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A252,Exceptions!$C$5:$C$104,$B252,Exceptions!$D$5:$D$104,$C252,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K252)))</f>
-        <v/>
-      </c>
-      <c r="M252" s="39">
-        <f>IF($A252="","",IF($H252="","Declaration missing",IF($H252="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R252),$R252&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H252="Fully Compliant",$J252&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N252" s="58">
-        <f>IF($A252="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C252,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O252" s="58">
-        <f>IF($A252="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C252,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P252" s="58">
-        <f>IF($A252="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C252,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q252" s="58">
-        <f>IF($A252="","",$A252&amp;"|"&amp;$B252&amp;"|"&amp;$C252)</f>
-        <v/>
-      </c>
-      <c r="R252" s="59" t="n"/>
-      <c r="S252" s="60" t="n"/>
-    </row>
-    <row r="253" ht="15" customHeight="1" s="34">
-      <c r="A253" s="54" t="n"/>
-      <c r="B253" s="54" t="n"/>
-      <c r="C253" s="54" t="n"/>
-      <c r="D253" s="55">
-        <f>IF($A253="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C253,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E253" s="55">
-        <f>IF($A253="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C253,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F253" s="56">
-        <f>IF($A253="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C253,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G253" s="57" t="n"/>
-      <c r="H253" s="54" t="n"/>
-      <c r="I253" s="54" t="n"/>
-      <c r="J253" s="39">
-        <f>IF($A253="","",IF($E253="Informational","GREEN",IF($G253="",IF($E253="Mandatory","RED","YELLOW"),IF($N253="Exact",IF(UPPER(TRIM($G253&amp;""))=UPPER(TRIM($F253&amp;"")),"GREEN",$P253),IF(NOT(ISNUMBER($G253)),$P253,IF($N253="Min",IF($G253&gt;=$F253,"GREEN",IF($G253&gt;=$F253-$O253,"YELLOW",$P253)),IF($N253="Max",IF($G253&lt;=$F253,"GREEN",IF($G253&lt;=$F253+$O253,"YELLOW",$P253)),IF($N253="Range",IF(ABS($G253-$F253)&lt;=$O253,"GREEN",$P253),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K253" s="39">
-        <f>IF($A253="","",IF($H253="Non-Compliant","RED",IF(AND(OR($H253="Alternative Offer",$H253="Partially Compliant"),$J253="GREEN"),"YELLOW",IF(AND($J253="GREEN",ISNUMBER($R253),$R253&lt;Baseline!$B$9),"YELLOW",$J253))))</f>
-        <v/>
-      </c>
-      <c r="L253" s="39">
-        <f>IF($A253="","",IF($K253="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A253,Exceptions!$C$5:$C$104,$B253,Exceptions!$D$5:$D$104,$C253,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K253)))</f>
-        <v/>
-      </c>
-      <c r="M253" s="39">
-        <f>IF($A253="","",IF($H253="","Declaration missing",IF($H253="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R253),$R253&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H253="Fully Compliant",$J253&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N253" s="58">
-        <f>IF($A253="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C253,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O253" s="58">
-        <f>IF($A253="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C253,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P253" s="58">
-        <f>IF($A253="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C253,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q253" s="58">
-        <f>IF($A253="","",$A253&amp;"|"&amp;$B253&amp;"|"&amp;$C253)</f>
-        <v/>
-      </c>
-      <c r="R253" s="59" t="n"/>
-      <c r="S253" s="60" t="n"/>
-    </row>
-    <row r="254" ht="15" customHeight="1" s="34">
-      <c r="A254" s="54" t="n"/>
-      <c r="B254" s="54" t="n"/>
-      <c r="C254" s="54" t="n"/>
-      <c r="D254" s="55">
-        <f>IF($A254="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C254,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E254" s="55">
-        <f>IF($A254="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C254,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F254" s="56">
-        <f>IF($A254="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C254,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G254" s="57" t="n"/>
-      <c r="H254" s="54" t="n"/>
-      <c r="I254" s="54" t="n"/>
-      <c r="J254" s="39">
-        <f>IF($A254="","",IF($E254="Informational","GREEN",IF($G254="",IF($E254="Mandatory","RED","YELLOW"),IF($N254="Exact",IF(UPPER(TRIM($G254&amp;""))=UPPER(TRIM($F254&amp;"")),"GREEN",$P254),IF(NOT(ISNUMBER($G254)),$P254,IF($N254="Min",IF($G254&gt;=$F254,"GREEN",IF($G254&gt;=$F254-$O254,"YELLOW",$P254)),IF($N254="Max",IF($G254&lt;=$F254,"GREEN",IF($G254&lt;=$F254+$O254,"YELLOW",$P254)),IF($N254="Range",IF(ABS($G254-$F254)&lt;=$O254,"GREEN",$P254),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K254" s="39">
-        <f>IF($A254="","",IF($H254="Non-Compliant","RED",IF(AND(OR($H254="Alternative Offer",$H254="Partially Compliant"),$J254="GREEN"),"YELLOW",IF(AND($J254="GREEN",ISNUMBER($R254),$R254&lt;Baseline!$B$9),"YELLOW",$J254))))</f>
-        <v/>
-      </c>
-      <c r="L254" s="39">
-        <f>IF($A254="","",IF($K254="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A254,Exceptions!$C$5:$C$104,$B254,Exceptions!$D$5:$D$104,$C254,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K254)))</f>
-        <v/>
-      </c>
-      <c r="M254" s="39">
-        <f>IF($A254="","",IF($H254="","Declaration missing",IF($H254="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R254),$R254&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H254="Fully Compliant",$J254&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N254" s="58">
-        <f>IF($A254="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C254,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O254" s="58">
-        <f>IF($A254="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C254,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P254" s="58">
-        <f>IF($A254="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C254,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q254" s="58">
-        <f>IF($A254="","",$A254&amp;"|"&amp;$B254&amp;"|"&amp;$C254)</f>
-        <v/>
-      </c>
-      <c r="R254" s="59" t="n"/>
-      <c r="S254" s="60" t="n"/>
-    </row>
-    <row r="255" ht="15" customHeight="1" s="34">
-      <c r="A255" s="54" t="n"/>
-      <c r="B255" s="54" t="n"/>
-      <c r="C255" s="54" t="n"/>
-      <c r="D255" s="55">
-        <f>IF($A255="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C255,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E255" s="55">
-        <f>IF($A255="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C255,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F255" s="56">
-        <f>IF($A255="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C255,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G255" s="57" t="n"/>
-      <c r="H255" s="54" t="n"/>
-      <c r="I255" s="54" t="n"/>
-      <c r="J255" s="39">
-        <f>IF($A255="","",IF($E255="Informational","GREEN",IF($G255="",IF($E255="Mandatory","RED","YELLOW"),IF($N255="Exact",IF(UPPER(TRIM($G255&amp;""))=UPPER(TRIM($F255&amp;"")),"GREEN",$P255),IF(NOT(ISNUMBER($G255)),$P255,IF($N255="Min",IF($G255&gt;=$F255,"GREEN",IF($G255&gt;=$F255-$O255,"YELLOW",$P255)),IF($N255="Max",IF($G255&lt;=$F255,"GREEN",IF($G255&lt;=$F255+$O255,"YELLOW",$P255)),IF($N255="Range",IF(ABS($G255-$F255)&lt;=$O255,"GREEN",$P255),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K255" s="39">
-        <f>IF($A255="","",IF($H255="Non-Compliant","RED",IF(AND(OR($H255="Alternative Offer",$H255="Partially Compliant"),$J255="GREEN"),"YELLOW",IF(AND($J255="GREEN",ISNUMBER($R255),$R255&lt;Baseline!$B$9),"YELLOW",$J255))))</f>
-        <v/>
-      </c>
-      <c r="L255" s="39">
-        <f>IF($A255="","",IF($K255="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A255,Exceptions!$C$5:$C$104,$B255,Exceptions!$D$5:$D$104,$C255,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K255)))</f>
-        <v/>
-      </c>
-      <c r="M255" s="39">
-        <f>IF($A255="","",IF($H255="","Declaration missing",IF($H255="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R255),$R255&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H255="Fully Compliant",$J255&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N255" s="58">
-        <f>IF($A255="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C255,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O255" s="58">
-        <f>IF($A255="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C255,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P255" s="58">
-        <f>IF($A255="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C255,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q255" s="58">
-        <f>IF($A255="","",$A255&amp;"|"&amp;$B255&amp;"|"&amp;$C255)</f>
-        <v/>
-      </c>
-      <c r="R255" s="59" t="n"/>
-      <c r="S255" s="60" t="n"/>
-    </row>
-    <row r="256" ht="15" customHeight="1" s="34">
-      <c r="A256" s="54" t="n"/>
-      <c r="B256" s="54" t="n"/>
-      <c r="C256" s="54" t="n"/>
-      <c r="D256" s="55">
-        <f>IF($A256="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C256,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E256" s="55">
-        <f>IF($A256="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C256,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F256" s="56">
-        <f>IF($A256="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C256,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G256" s="57" t="n"/>
-      <c r="H256" s="54" t="n"/>
-      <c r="I256" s="54" t="n"/>
-      <c r="J256" s="39">
-        <f>IF($A256="","",IF($E256="Informational","GREEN",IF($G256="",IF($E256="Mandatory","RED","YELLOW"),IF($N256="Exact",IF(UPPER(TRIM($G256&amp;""))=UPPER(TRIM($F256&amp;"")),"GREEN",$P256),IF(NOT(ISNUMBER($G256)),$P256,IF($N256="Min",IF($G256&gt;=$F256,"GREEN",IF($G256&gt;=$F256-$O256,"YELLOW",$P256)),IF($N256="Max",IF($G256&lt;=$F256,"GREEN",IF($G256&lt;=$F256+$O256,"YELLOW",$P256)),IF($N256="Range",IF(ABS($G256-$F256)&lt;=$O256,"GREEN",$P256),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K256" s="39">
-        <f>IF($A256="","",IF($H256="Non-Compliant","RED",IF(AND(OR($H256="Alternative Offer",$H256="Partially Compliant"),$J256="GREEN"),"YELLOW",IF(AND($J256="GREEN",ISNUMBER($R256),$R256&lt;Baseline!$B$9),"YELLOW",$J256))))</f>
-        <v/>
-      </c>
-      <c r="L256" s="39">
-        <f>IF($A256="","",IF($K256="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A256,Exceptions!$C$5:$C$104,$B256,Exceptions!$D$5:$D$104,$C256,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K256)))</f>
-        <v/>
-      </c>
-      <c r="M256" s="39">
-        <f>IF($A256="","",IF($H256="","Declaration missing",IF($H256="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R256),$R256&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H256="Fully Compliant",$J256&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N256" s="58">
-        <f>IF($A256="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C256,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O256" s="58">
-        <f>IF($A256="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C256,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P256" s="58">
-        <f>IF($A256="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C256,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q256" s="58">
-        <f>IF($A256="","",$A256&amp;"|"&amp;$B256&amp;"|"&amp;$C256)</f>
-        <v/>
-      </c>
-      <c r="R256" s="59" t="n"/>
-      <c r="S256" s="60" t="n"/>
-    </row>
-    <row r="257" ht="15" customHeight="1" s="34">
-      <c r="A257" s="54" t="n"/>
-      <c r="B257" s="54" t="n"/>
-      <c r="C257" s="54" t="n"/>
-      <c r="D257" s="55">
-        <f>IF($A257="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C257,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E257" s="55">
-        <f>IF($A257="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C257,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F257" s="56">
-        <f>IF($A257="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C257,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G257" s="57" t="n"/>
-      <c r="H257" s="54" t="n"/>
-      <c r="I257" s="54" t="n"/>
-      <c r="J257" s="39">
-        <f>IF($A257="","",IF($E257="Informational","GREEN",IF($G257="",IF($E257="Mandatory","RED","YELLOW"),IF($N257="Exact",IF(UPPER(TRIM($G257&amp;""))=UPPER(TRIM($F257&amp;"")),"GREEN",$P257),IF(NOT(ISNUMBER($G257)),$P257,IF($N257="Min",IF($G257&gt;=$F257,"GREEN",IF($G257&gt;=$F257-$O257,"YELLOW",$P257)),IF($N257="Max",IF($G257&lt;=$F257,"GREEN",IF($G257&lt;=$F257+$O257,"YELLOW",$P257)),IF($N257="Range",IF(ABS($G257-$F257)&lt;=$O257,"GREEN",$P257),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K257" s="39">
-        <f>IF($A257="","",IF($H257="Non-Compliant","RED",IF(AND(OR($H257="Alternative Offer",$H257="Partially Compliant"),$J257="GREEN"),"YELLOW",IF(AND($J257="GREEN",ISNUMBER($R257),$R257&lt;Baseline!$B$9),"YELLOW",$J257))))</f>
-        <v/>
-      </c>
-      <c r="L257" s="39">
-        <f>IF($A257="","",IF($K257="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A257,Exceptions!$C$5:$C$104,$B257,Exceptions!$D$5:$D$104,$C257,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K257)))</f>
-        <v/>
-      </c>
-      <c r="M257" s="39">
-        <f>IF($A257="","",IF($H257="","Declaration missing",IF($H257="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R257),$R257&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H257="Fully Compliant",$J257&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N257" s="58">
-        <f>IF($A257="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C257,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O257" s="58">
-        <f>IF($A257="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C257,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P257" s="58">
-        <f>IF($A257="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C257,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q257" s="58">
-        <f>IF($A257="","",$A257&amp;"|"&amp;$B257&amp;"|"&amp;$C257)</f>
-        <v/>
-      </c>
-      <c r="R257" s="59" t="n"/>
-      <c r="S257" s="60" t="n"/>
-    </row>
-    <row r="258" ht="15" customHeight="1" s="34">
-      <c r="A258" s="54" t="n"/>
-      <c r="B258" s="54" t="n"/>
-      <c r="C258" s="54" t="n"/>
-      <c r="D258" s="55">
-        <f>IF($A258="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C258,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E258" s="55">
-        <f>IF($A258="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C258,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F258" s="56">
-        <f>IF($A258="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C258,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G258" s="57" t="n"/>
-      <c r="H258" s="54" t="n"/>
-      <c r="I258" s="54" t="n"/>
-      <c r="J258" s="39">
-        <f>IF($A258="","",IF($E258="Informational","GREEN",IF($G258="",IF($E258="Mandatory","RED","YELLOW"),IF($N258="Exact",IF(UPPER(TRIM($G258&amp;""))=UPPER(TRIM($F258&amp;"")),"GREEN",$P258),IF(NOT(ISNUMBER($G258)),$P258,IF($N258="Min",IF($G258&gt;=$F258,"GREEN",IF($G258&gt;=$F258-$O258,"YELLOW",$P258)),IF($N258="Max",IF($G258&lt;=$F258,"GREEN",IF($G258&lt;=$F258+$O258,"YELLOW",$P258)),IF($N258="Range",IF(ABS($G258-$F258)&lt;=$O258,"GREEN",$P258),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K258" s="39">
-        <f>IF($A258="","",IF($H258="Non-Compliant","RED",IF(AND(OR($H258="Alternative Offer",$H258="Partially Compliant"),$J258="GREEN"),"YELLOW",IF(AND($J258="GREEN",ISNUMBER($R258),$R258&lt;Baseline!$B$9),"YELLOW",$J258))))</f>
-        <v/>
-      </c>
-      <c r="L258" s="39">
-        <f>IF($A258="","",IF($K258="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A258,Exceptions!$C$5:$C$104,$B258,Exceptions!$D$5:$D$104,$C258,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K258)))</f>
-        <v/>
-      </c>
-      <c r="M258" s="39">
-        <f>IF($A258="","",IF($H258="","Declaration missing",IF($H258="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R258),$R258&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H258="Fully Compliant",$J258&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N258" s="58">
-        <f>IF($A258="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C258,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O258" s="58">
-        <f>IF($A258="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C258,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P258" s="58">
-        <f>IF($A258="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C258,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q258" s="58">
-        <f>IF($A258="","",$A258&amp;"|"&amp;$B258&amp;"|"&amp;$C258)</f>
-        <v/>
-      </c>
-      <c r="R258" s="59" t="n"/>
-      <c r="S258" s="60" t="n"/>
-    </row>
-    <row r="259" ht="15" customHeight="1" s="34">
-      <c r="A259" s="54" t="n"/>
-      <c r="B259" s="54" t="n"/>
-      <c r="C259" s="54" t="n"/>
-      <c r="D259" s="55">
-        <f>IF($A259="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C259,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E259" s="55">
-        <f>IF($A259="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C259,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F259" s="56">
-        <f>IF($A259="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C259,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G259" s="57" t="n"/>
-      <c r="H259" s="54" t="n"/>
-      <c r="I259" s="54" t="n"/>
-      <c r="J259" s="39">
-        <f>IF($A259="","",IF($E259="Informational","GREEN",IF($G259="",IF($E259="Mandatory","RED","YELLOW"),IF($N259="Exact",IF(UPPER(TRIM($G259&amp;""))=UPPER(TRIM($F259&amp;"")),"GREEN",$P259),IF(NOT(ISNUMBER($G259)),$P259,IF($N259="Min",IF($G259&gt;=$F259,"GREEN",IF($G259&gt;=$F259-$O259,"YELLOW",$P259)),IF($N259="Max",IF($G259&lt;=$F259,"GREEN",IF($G259&lt;=$F259+$O259,"YELLOW",$P259)),IF($N259="Range",IF(ABS($G259-$F259)&lt;=$O259,"GREEN",$P259),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K259" s="39">
-        <f>IF($A259="","",IF($H259="Non-Compliant","RED",IF(AND(OR($H259="Alternative Offer",$H259="Partially Compliant"),$J259="GREEN"),"YELLOW",IF(AND($J259="GREEN",ISNUMBER($R259),$R259&lt;Baseline!$B$9),"YELLOW",$J259))))</f>
-        <v/>
-      </c>
-      <c r="L259" s="39">
-        <f>IF($A259="","",IF($K259="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A259,Exceptions!$C$5:$C$104,$B259,Exceptions!$D$5:$D$104,$C259,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K259)))</f>
-        <v/>
-      </c>
-      <c r="M259" s="39">
-        <f>IF($A259="","",IF($H259="","Declaration missing",IF($H259="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R259),$R259&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H259="Fully Compliant",$J259&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N259" s="58">
-        <f>IF($A259="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C259,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O259" s="58">
-        <f>IF($A259="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C259,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P259" s="58">
-        <f>IF($A259="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C259,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q259" s="58">
-        <f>IF($A259="","",$A259&amp;"|"&amp;$B259&amp;"|"&amp;$C259)</f>
-        <v/>
-      </c>
-      <c r="R259" s="59" t="n"/>
-      <c r="S259" s="60" t="n"/>
-    </row>
-    <row r="260" ht="15" customHeight="1" s="34">
-      <c r="A260" s="54" t="n"/>
-      <c r="B260" s="54" t="n"/>
-      <c r="C260" s="54" t="n"/>
-      <c r="D260" s="55">
-        <f>IF($A260="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C260,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E260" s="55">
-        <f>IF($A260="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C260,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F260" s="56">
-        <f>IF($A260="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C260,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G260" s="57" t="n"/>
-      <c r="H260" s="54" t="n"/>
-      <c r="I260" s="54" t="n"/>
-      <c r="J260" s="39">
-        <f>IF($A260="","",IF($E260="Informational","GREEN",IF($G260="",IF($E260="Mandatory","RED","YELLOW"),IF($N260="Exact",IF(UPPER(TRIM($G260&amp;""))=UPPER(TRIM($F260&amp;"")),"GREEN",$P260),IF(NOT(ISNUMBER($G260)),$P260,IF($N260="Min",IF($G260&gt;=$F260,"GREEN",IF($G260&gt;=$F260-$O260,"YELLOW",$P260)),IF($N260="Max",IF($G260&lt;=$F260,"GREEN",IF($G260&lt;=$F260+$O260,"YELLOW",$P260)),IF($N260="Range",IF(ABS($G260-$F260)&lt;=$O260,"GREEN",$P260),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K260" s="39">
-        <f>IF($A260="","",IF($H260="Non-Compliant","RED",IF(AND(OR($H260="Alternative Offer",$H260="Partially Compliant"),$J260="GREEN"),"YELLOW",IF(AND($J260="GREEN",ISNUMBER($R260),$R260&lt;Baseline!$B$9),"YELLOW",$J260))))</f>
-        <v/>
-      </c>
-      <c r="L260" s="39">
-        <f>IF($A260="","",IF($K260="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A260,Exceptions!$C$5:$C$104,$B260,Exceptions!$D$5:$D$104,$C260,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K260)))</f>
-        <v/>
-      </c>
-      <c r="M260" s="39">
-        <f>IF($A260="","",IF($H260="","Declaration missing",IF($H260="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R260),$R260&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H260="Fully Compliant",$J260&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N260" s="58">
-        <f>IF($A260="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C260,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O260" s="58">
-        <f>IF($A260="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C260,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P260" s="58">
-        <f>IF($A260="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C260,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q260" s="58">
-        <f>IF($A260="","",$A260&amp;"|"&amp;$B260&amp;"|"&amp;$C260)</f>
-        <v/>
-      </c>
-      <c r="R260" s="59" t="n"/>
-      <c r="S260" s="60" t="n"/>
-    </row>
-    <row r="261" ht="15" customHeight="1" s="34">
-      <c r="A261" s="54" t="n"/>
-      <c r="B261" s="54" t="n"/>
-      <c r="C261" s="54" t="n"/>
-      <c r="D261" s="55">
-        <f>IF($A261="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C261,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E261" s="55">
-        <f>IF($A261="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C261,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F261" s="56">
-        <f>IF($A261="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C261,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G261" s="57" t="n"/>
-      <c r="H261" s="54" t="n"/>
-      <c r="I261" s="54" t="n"/>
-      <c r="J261" s="39">
-        <f>IF($A261="","",IF($E261="Informational","GREEN",IF($G261="",IF($E261="Mandatory","RED","YELLOW"),IF($N261="Exact",IF(UPPER(TRIM($G261&amp;""))=UPPER(TRIM($F261&amp;"")),"GREEN",$P261),IF(NOT(ISNUMBER($G261)),$P261,IF($N261="Min",IF($G261&gt;=$F261,"GREEN",IF($G261&gt;=$F261-$O261,"YELLOW",$P261)),IF($N261="Max",IF($G261&lt;=$F261,"GREEN",IF($G261&lt;=$F261+$O261,"YELLOW",$P261)),IF($N261="Range",IF(ABS($G261-$F261)&lt;=$O261,"GREEN",$P261),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K261" s="39">
-        <f>IF($A261="","",IF($H261="Non-Compliant","RED",IF(AND(OR($H261="Alternative Offer",$H261="Partially Compliant"),$J261="GREEN"),"YELLOW",IF(AND($J261="GREEN",ISNUMBER($R261),$R261&lt;Baseline!$B$9),"YELLOW",$J261))))</f>
-        <v/>
-      </c>
-      <c r="L261" s="39">
-        <f>IF($A261="","",IF($K261="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A261,Exceptions!$C$5:$C$104,$B261,Exceptions!$D$5:$D$104,$C261,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K261)))</f>
-        <v/>
-      </c>
-      <c r="M261" s="39">
-        <f>IF($A261="","",IF($H261="","Declaration missing",IF($H261="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R261),$R261&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H261="Fully Compliant",$J261&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N261" s="58">
-        <f>IF($A261="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C261,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O261" s="58">
-        <f>IF($A261="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C261,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P261" s="58">
-        <f>IF($A261="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C261,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q261" s="58">
-        <f>IF($A261="","",$A261&amp;"|"&amp;$B261&amp;"|"&amp;$C261)</f>
-        <v/>
-      </c>
-      <c r="R261" s="59" t="n"/>
-      <c r="S261" s="60" t="n"/>
-    </row>
-    <row r="262" ht="15" customHeight="1" s="34">
-      <c r="A262" s="54" t="n"/>
-      <c r="B262" s="54" t="n"/>
-      <c r="C262" s="54" t="n"/>
-      <c r="D262" s="55">
-        <f>IF($A262="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C262,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E262" s="55">
-        <f>IF($A262="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C262,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F262" s="56">
-        <f>IF($A262="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C262,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G262" s="57" t="n"/>
-      <c r="H262" s="54" t="n"/>
-      <c r="I262" s="54" t="n"/>
-      <c r="J262" s="39">
-        <f>IF($A262="","",IF($E262="Informational","GREEN",IF($G262="",IF($E262="Mandatory","RED","YELLOW"),IF($N262="Exact",IF(UPPER(TRIM($G262&amp;""))=UPPER(TRIM($F262&amp;"")),"GREEN",$P262),IF(NOT(ISNUMBER($G262)),$P262,IF($N262="Min",IF($G262&gt;=$F262,"GREEN",IF($G262&gt;=$F262-$O262,"YELLOW",$P262)),IF($N262="Max",IF($G262&lt;=$F262,"GREEN",IF($G262&lt;=$F262+$O262,"YELLOW",$P262)),IF($N262="Range",IF(ABS($G262-$F262)&lt;=$O262,"GREEN",$P262),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K262" s="39">
-        <f>IF($A262="","",IF($H262="Non-Compliant","RED",IF(AND(OR($H262="Alternative Offer",$H262="Partially Compliant"),$J262="GREEN"),"YELLOW",IF(AND($J262="GREEN",ISNUMBER($R262),$R262&lt;Baseline!$B$9),"YELLOW",$J262))))</f>
-        <v/>
-      </c>
-      <c r="L262" s="39">
-        <f>IF($A262="","",IF($K262="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A262,Exceptions!$C$5:$C$104,$B262,Exceptions!$D$5:$D$104,$C262,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K262)))</f>
-        <v/>
-      </c>
-      <c r="M262" s="39">
-        <f>IF($A262="","",IF($H262="","Declaration missing",IF($H262="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R262),$R262&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H262="Fully Compliant",$J262&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N262" s="58">
-        <f>IF($A262="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C262,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O262" s="58">
-        <f>IF($A262="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C262,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P262" s="58">
-        <f>IF($A262="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C262,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q262" s="58">
-        <f>IF($A262="","",$A262&amp;"|"&amp;$B262&amp;"|"&amp;$C262)</f>
-        <v/>
-      </c>
-      <c r="R262" s="59" t="n"/>
-      <c r="S262" s="60" t="n"/>
-    </row>
-    <row r="263" ht="15" customHeight="1" s="34">
-      <c r="A263" s="54" t="n"/>
-      <c r="B263" s="54" t="n"/>
-      <c r="C263" s="54" t="n"/>
-      <c r="D263" s="55">
-        <f>IF($A263="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C263,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E263" s="55">
-        <f>IF($A263="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C263,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F263" s="56">
-        <f>IF($A263="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C263,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G263" s="57" t="n"/>
-      <c r="H263" s="54" t="n"/>
-      <c r="I263" s="54" t="n"/>
-      <c r="J263" s="39">
-        <f>IF($A263="","",IF($E263="Informational","GREEN",IF($G263="",IF($E263="Mandatory","RED","YELLOW"),IF($N263="Exact",IF(UPPER(TRIM($G263&amp;""))=UPPER(TRIM($F263&amp;"")),"GREEN",$P263),IF(NOT(ISNUMBER($G263)),$P263,IF($N263="Min",IF($G263&gt;=$F263,"GREEN",IF($G263&gt;=$F263-$O263,"YELLOW",$P263)),IF($N263="Max",IF($G263&lt;=$F263,"GREEN",IF($G263&lt;=$F263+$O263,"YELLOW",$P263)),IF($N263="Range",IF(ABS($G263-$F263)&lt;=$O263,"GREEN",$P263),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K263" s="39">
-        <f>IF($A263="","",IF($H263="Non-Compliant","RED",IF(AND(OR($H263="Alternative Offer",$H263="Partially Compliant"),$J263="GREEN"),"YELLOW",IF(AND($J263="GREEN",ISNUMBER($R263),$R263&lt;Baseline!$B$9),"YELLOW",$J263))))</f>
-        <v/>
-      </c>
-      <c r="L263" s="39">
-        <f>IF($A263="","",IF($K263="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A263,Exceptions!$C$5:$C$104,$B263,Exceptions!$D$5:$D$104,$C263,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K263)))</f>
-        <v/>
-      </c>
-      <c r="M263" s="39">
-        <f>IF($A263="","",IF($H263="","Declaration missing",IF($H263="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R263),$R263&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H263="Fully Compliant",$J263&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N263" s="58">
-        <f>IF($A263="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C263,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O263" s="58">
-        <f>IF($A263="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C263,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P263" s="58">
-        <f>IF($A263="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C263,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q263" s="58">
-        <f>IF($A263="","",$A263&amp;"|"&amp;$B263&amp;"|"&amp;$C263)</f>
-        <v/>
-      </c>
-      <c r="R263" s="59" t="n"/>
-      <c r="S263" s="60" t="n"/>
-    </row>
-    <row r="264" ht="15" customHeight="1" s="34">
-      <c r="A264" s="54" t="n"/>
-      <c r="B264" s="54" t="n"/>
-      <c r="C264" s="54" t="n"/>
-      <c r="D264" s="55">
-        <f>IF($A264="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C264,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E264" s="55">
-        <f>IF($A264="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C264,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F264" s="56">
-        <f>IF($A264="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C264,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G264" s="57" t="n"/>
-      <c r="H264" s="54" t="n"/>
-      <c r="I264" s="54" t="n"/>
-      <c r="J264" s="39">
-        <f>IF($A264="","",IF($E264="Informational","GREEN",IF($G264="",IF($E264="Mandatory","RED","YELLOW"),IF($N264="Exact",IF(UPPER(TRIM($G264&amp;""))=UPPER(TRIM($F264&amp;"")),"GREEN",$P264),IF(NOT(ISNUMBER($G264)),$P264,IF($N264="Min",IF($G264&gt;=$F264,"GREEN",IF($G264&gt;=$F264-$O264,"YELLOW",$P264)),IF($N264="Max",IF($G264&lt;=$F264,"GREEN",IF($G264&lt;=$F264+$O264,"YELLOW",$P264)),IF($N264="Range",IF(ABS($G264-$F264)&lt;=$O264,"GREEN",$P264),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K264" s="39">
-        <f>IF($A264="","",IF($H264="Non-Compliant","RED",IF(AND(OR($H264="Alternative Offer",$H264="Partially Compliant"),$J264="GREEN"),"YELLOW",IF(AND($J264="GREEN",ISNUMBER($R264),$R264&lt;Baseline!$B$9),"YELLOW",$J264))))</f>
-        <v/>
-      </c>
-      <c r="L264" s="39">
-        <f>IF($A264="","",IF($K264="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A264,Exceptions!$C$5:$C$104,$B264,Exceptions!$D$5:$D$104,$C264,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K264)))</f>
-        <v/>
-      </c>
-      <c r="M264" s="39">
-        <f>IF($A264="","",IF($H264="","Declaration missing",IF($H264="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R264),$R264&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H264="Fully Compliant",$J264&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N264" s="58">
-        <f>IF($A264="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C264,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O264" s="58">
-        <f>IF($A264="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C264,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P264" s="58">
-        <f>IF($A264="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C264,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q264" s="58">
-        <f>IF($A264="","",$A264&amp;"|"&amp;$B264&amp;"|"&amp;$C264)</f>
-        <v/>
-      </c>
-      <c r="R264" s="59" t="n"/>
-      <c r="S264" s="60" t="n"/>
-    </row>
-    <row r="265" ht="15" customHeight="1" s="34">
-      <c r="A265" s="54" t="n"/>
-      <c r="B265" s="54" t="n"/>
-      <c r="C265" s="54" t="n"/>
-      <c r="D265" s="55">
-        <f>IF($A265="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C265,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E265" s="55">
-        <f>IF($A265="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C265,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F265" s="56">
-        <f>IF($A265="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C265,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G265" s="57" t="n"/>
-      <c r="H265" s="54" t="n"/>
-      <c r="I265" s="54" t="n"/>
-      <c r="J265" s="39">
-        <f>IF($A265="","",IF($E265="Informational","GREEN",IF($G265="",IF($E265="Mandatory","RED","YELLOW"),IF($N265="Exact",IF(UPPER(TRIM($G265&amp;""))=UPPER(TRIM($F265&amp;"")),"GREEN",$P265),IF(NOT(ISNUMBER($G265)),$P265,IF($N265="Min",IF($G265&gt;=$F265,"GREEN",IF($G265&gt;=$F265-$O265,"YELLOW",$P265)),IF($N265="Max",IF($G265&lt;=$F265,"GREEN",IF($G265&lt;=$F265+$O265,"YELLOW",$P265)),IF($N265="Range",IF(ABS($G265-$F265)&lt;=$O265,"GREEN",$P265),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K265" s="39">
-        <f>IF($A265="","",IF($H265="Non-Compliant","RED",IF(AND(OR($H265="Alternative Offer",$H265="Partially Compliant"),$J265="GREEN"),"YELLOW",IF(AND($J265="GREEN",ISNUMBER($R265),$R265&lt;Baseline!$B$9),"YELLOW",$J265))))</f>
-        <v/>
-      </c>
-      <c r="L265" s="39">
-        <f>IF($A265="","",IF($K265="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A265,Exceptions!$C$5:$C$104,$B265,Exceptions!$D$5:$D$104,$C265,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K265)))</f>
-        <v/>
-      </c>
-      <c r="M265" s="39">
-        <f>IF($A265="","",IF($H265="","Declaration missing",IF($H265="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R265),$R265&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H265="Fully Compliant",$J265&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N265" s="58">
-        <f>IF($A265="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C265,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O265" s="58">
-        <f>IF($A265="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C265,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P265" s="58">
-        <f>IF($A265="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C265,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q265" s="58">
-        <f>IF($A265="","",$A265&amp;"|"&amp;$B265&amp;"|"&amp;$C265)</f>
-        <v/>
-      </c>
-      <c r="R265" s="59" t="n"/>
-      <c r="S265" s="60" t="n"/>
-    </row>
-    <row r="266" ht="15" customHeight="1" s="34">
-      <c r="A266" s="54" t="n"/>
-      <c r="B266" s="54" t="n"/>
-      <c r="C266" s="54" t="n"/>
-      <c r="D266" s="55">
-        <f>IF($A266="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C266,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E266" s="55">
-        <f>IF($A266="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C266,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F266" s="56">
-        <f>IF($A266="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C266,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G266" s="57" t="n"/>
-      <c r="H266" s="54" t="n"/>
-      <c r="I266" s="54" t="n"/>
-      <c r="J266" s="39">
-        <f>IF($A266="","",IF($E266="Informational","GREEN",IF($G266="",IF($E266="Mandatory","RED","YELLOW"),IF($N266="Exact",IF(UPPER(TRIM($G266&amp;""))=UPPER(TRIM($F266&amp;"")),"GREEN",$P266),IF(NOT(ISNUMBER($G266)),$P266,IF($N266="Min",IF($G266&gt;=$F266,"GREEN",IF($G266&gt;=$F266-$O266,"YELLOW",$P266)),IF($N266="Max",IF($G266&lt;=$F266,"GREEN",IF($G266&lt;=$F266+$O266,"YELLOW",$P266)),IF($N266="Range",IF(ABS($G266-$F266)&lt;=$O266,"GREEN",$P266),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K266" s="39">
-        <f>IF($A266="","",IF($H266="Non-Compliant","RED",IF(AND(OR($H266="Alternative Offer",$H266="Partially Compliant"),$J266="GREEN"),"YELLOW",IF(AND($J266="GREEN",ISNUMBER($R266),$R266&lt;Baseline!$B$9),"YELLOW",$J266))))</f>
-        <v/>
-      </c>
-      <c r="L266" s="39">
-        <f>IF($A266="","",IF($K266="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A266,Exceptions!$C$5:$C$104,$B266,Exceptions!$D$5:$D$104,$C266,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K266)))</f>
-        <v/>
-      </c>
-      <c r="M266" s="39">
-        <f>IF($A266="","",IF($H266="","Declaration missing",IF($H266="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R266),$R266&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H266="Fully Compliant",$J266&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N266" s="58">
-        <f>IF($A266="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C266,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O266" s="58">
-        <f>IF($A266="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C266,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P266" s="58">
-        <f>IF($A266="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C266,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q266" s="58">
-        <f>IF($A266="","",$A266&amp;"|"&amp;$B266&amp;"|"&amp;$C266)</f>
-        <v/>
-      </c>
-      <c r="R266" s="59" t="n"/>
-      <c r="S266" s="60" t="n"/>
-    </row>
-    <row r="267" ht="15" customHeight="1" s="34">
-      <c r="A267" s="54" t="n"/>
-      <c r="B267" s="54" t="n"/>
-      <c r="C267" s="54" t="n"/>
-      <c r="D267" s="55">
-        <f>IF($A267="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C267,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E267" s="55">
-        <f>IF($A267="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C267,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F267" s="56">
-        <f>IF($A267="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C267,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G267" s="57" t="n"/>
-      <c r="H267" s="54" t="n"/>
-      <c r="I267" s="54" t="n"/>
-      <c r="J267" s="39">
-        <f>IF($A267="","",IF($E267="Informational","GREEN",IF($G267="",IF($E267="Mandatory","RED","YELLOW"),IF($N267="Exact",IF(UPPER(TRIM($G267&amp;""))=UPPER(TRIM($F267&amp;"")),"GREEN",$P267),IF(NOT(ISNUMBER($G267)),$P267,IF($N267="Min",IF($G267&gt;=$F267,"GREEN",IF($G267&gt;=$F267-$O267,"YELLOW",$P267)),IF($N267="Max",IF($G267&lt;=$F267,"GREEN",IF($G267&lt;=$F267+$O267,"YELLOW",$P267)),IF($N267="Range",IF(ABS($G267-$F267)&lt;=$O267,"GREEN",$P267),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K267" s="39">
-        <f>IF($A267="","",IF($H267="Non-Compliant","RED",IF(AND(OR($H267="Alternative Offer",$H267="Partially Compliant"),$J267="GREEN"),"YELLOW",IF(AND($J267="GREEN",ISNUMBER($R267),$R267&lt;Baseline!$B$9),"YELLOW",$J267))))</f>
-        <v/>
-      </c>
-      <c r="L267" s="39">
-        <f>IF($A267="","",IF($K267="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A267,Exceptions!$C$5:$C$104,$B267,Exceptions!$D$5:$D$104,$C267,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K267)))</f>
-        <v/>
-      </c>
-      <c r="M267" s="39">
-        <f>IF($A267="","",IF($H267="","Declaration missing",IF($H267="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R267),$R267&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H267="Fully Compliant",$J267&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N267" s="58">
-        <f>IF($A267="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C267,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O267" s="58">
-        <f>IF($A267="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C267,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P267" s="58">
-        <f>IF($A267="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C267,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q267" s="58">
-        <f>IF($A267="","",$A267&amp;"|"&amp;$B267&amp;"|"&amp;$C267)</f>
-        <v/>
-      </c>
-      <c r="R267" s="59" t="n"/>
-      <c r="S267" s="60" t="n"/>
-    </row>
-    <row r="268" ht="15" customHeight="1" s="34">
-      <c r="A268" s="54" t="n"/>
-      <c r="B268" s="54" t="n"/>
-      <c r="C268" s="54" t="n"/>
-      <c r="D268" s="55">
-        <f>IF($A268="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C268,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E268" s="55">
-        <f>IF($A268="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C268,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F268" s="56">
-        <f>IF($A268="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C268,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G268" s="57" t="n"/>
-      <c r="H268" s="54" t="n"/>
-      <c r="I268" s="54" t="n"/>
-      <c r="J268" s="39">
-        <f>IF($A268="","",IF($E268="Informational","GREEN",IF($G268="",IF($E268="Mandatory","RED","YELLOW"),IF($N268="Exact",IF(UPPER(TRIM($G268&amp;""))=UPPER(TRIM($F268&amp;"")),"GREEN",$P268),IF(NOT(ISNUMBER($G268)),$P268,IF($N268="Min",IF($G268&gt;=$F268,"GREEN",IF($G268&gt;=$F268-$O268,"YELLOW",$P268)),IF($N268="Max",IF($G268&lt;=$F268,"GREEN",IF($G268&lt;=$F268+$O268,"YELLOW",$P268)),IF($N268="Range",IF(ABS($G268-$F268)&lt;=$O268,"GREEN",$P268),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K268" s="39">
-        <f>IF($A268="","",IF($H268="Non-Compliant","RED",IF(AND(OR($H268="Alternative Offer",$H268="Partially Compliant"),$J268="GREEN"),"YELLOW",IF(AND($J268="GREEN",ISNUMBER($R268),$R268&lt;Baseline!$B$9),"YELLOW",$J268))))</f>
-        <v/>
-      </c>
-      <c r="L268" s="39">
-        <f>IF($A268="","",IF($K268="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A268,Exceptions!$C$5:$C$104,$B268,Exceptions!$D$5:$D$104,$C268,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K268)))</f>
-        <v/>
-      </c>
-      <c r="M268" s="39">
-        <f>IF($A268="","",IF($H268="","Declaration missing",IF($H268="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R268),$R268&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H268="Fully Compliant",$J268&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N268" s="58">
-        <f>IF($A268="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C268,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O268" s="58">
-        <f>IF($A268="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C268,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P268" s="58">
-        <f>IF($A268="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C268,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q268" s="58">
-        <f>IF($A268="","",$A268&amp;"|"&amp;$B268&amp;"|"&amp;$C268)</f>
-        <v/>
-      </c>
-      <c r="R268" s="59" t="n"/>
-      <c r="S268" s="60" t="n"/>
-    </row>
-    <row r="269" ht="15" customHeight="1" s="34">
-      <c r="A269" s="54" t="n"/>
-      <c r="B269" s="54" t="n"/>
-      <c r="C269" s="54" t="n"/>
-      <c r="D269" s="55">
-        <f>IF($A269="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C269,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E269" s="55">
-        <f>IF($A269="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C269,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F269" s="56">
-        <f>IF($A269="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C269,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G269" s="57" t="n"/>
-      <c r="H269" s="54" t="n"/>
-      <c r="I269" s="54" t="n"/>
-      <c r="J269" s="39">
-        <f>IF($A269="","",IF($E269="Informational","GREEN",IF($G269="",IF($E269="Mandatory","RED","YELLOW"),IF($N269="Exact",IF(UPPER(TRIM($G269&amp;""))=UPPER(TRIM($F269&amp;"")),"GREEN",$P269),IF(NOT(ISNUMBER($G269)),$P269,IF($N269="Min",IF($G269&gt;=$F269,"GREEN",IF($G269&gt;=$F269-$O269,"YELLOW",$P269)),IF($N269="Max",IF($G269&lt;=$F269,"GREEN",IF($G269&lt;=$F269+$O269,"YELLOW",$P269)),IF($N269="Range",IF(ABS($G269-$F269)&lt;=$O269,"GREEN",$P269),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K269" s="39">
-        <f>IF($A269="","",IF($H269="Non-Compliant","RED",IF(AND(OR($H269="Alternative Offer",$H269="Partially Compliant"),$J269="GREEN"),"YELLOW",IF(AND($J269="GREEN",ISNUMBER($R269),$R269&lt;Baseline!$B$9),"YELLOW",$J269))))</f>
-        <v/>
-      </c>
-      <c r="L269" s="39">
-        <f>IF($A269="","",IF($K269="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A269,Exceptions!$C$5:$C$104,$B269,Exceptions!$D$5:$D$104,$C269,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K269)))</f>
-        <v/>
-      </c>
-      <c r="M269" s="39">
-        <f>IF($A269="","",IF($H269="","Declaration missing",IF($H269="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R269),$R269&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H269="Fully Compliant",$J269&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N269" s="58">
-        <f>IF($A269="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C269,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O269" s="58">
-        <f>IF($A269="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C269,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P269" s="58">
-        <f>IF($A269="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C269,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q269" s="58">
-        <f>IF($A269="","",$A269&amp;"|"&amp;$B269&amp;"|"&amp;$C269)</f>
-        <v/>
-      </c>
-      <c r="R269" s="59" t="n"/>
-      <c r="S269" s="60" t="n"/>
-    </row>
-    <row r="270" ht="15" customHeight="1" s="34">
-      <c r="A270" s="54" t="n"/>
-      <c r="B270" s="54" t="n"/>
-      <c r="C270" s="54" t="n"/>
-      <c r="D270" s="55">
-        <f>IF($A270="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C270,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E270" s="55">
-        <f>IF($A270="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C270,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F270" s="56">
-        <f>IF($A270="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C270,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G270" s="57" t="n"/>
-      <c r="H270" s="54" t="n"/>
-      <c r="I270" s="54" t="n"/>
-      <c r="J270" s="39">
-        <f>IF($A270="","",IF($E270="Informational","GREEN",IF($G270="",IF($E270="Mandatory","RED","YELLOW"),IF($N270="Exact",IF(UPPER(TRIM($G270&amp;""))=UPPER(TRIM($F270&amp;"")),"GREEN",$P270),IF(NOT(ISNUMBER($G270)),$P270,IF($N270="Min",IF($G270&gt;=$F270,"GREEN",IF($G270&gt;=$F270-$O270,"YELLOW",$P270)),IF($N270="Max",IF($G270&lt;=$F270,"GREEN",IF($G270&lt;=$F270+$O270,"YELLOW",$P270)),IF($N270="Range",IF(ABS($G270-$F270)&lt;=$O270,"GREEN",$P270),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K270" s="39">
-        <f>IF($A270="","",IF($H270="Non-Compliant","RED",IF(AND(OR($H270="Alternative Offer",$H270="Partially Compliant"),$J270="GREEN"),"YELLOW",IF(AND($J270="GREEN",ISNUMBER($R270),$R270&lt;Baseline!$B$9),"YELLOW",$J270))))</f>
-        <v/>
-      </c>
-      <c r="L270" s="39">
-        <f>IF($A270="","",IF($K270="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A270,Exceptions!$C$5:$C$104,$B270,Exceptions!$D$5:$D$104,$C270,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K270)))</f>
-        <v/>
-      </c>
-      <c r="M270" s="39">
-        <f>IF($A270="","",IF($H270="","Declaration missing",IF($H270="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R270),$R270&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H270="Fully Compliant",$J270&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N270" s="58">
-        <f>IF($A270="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C270,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O270" s="58">
-        <f>IF($A270="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C270,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P270" s="58">
-        <f>IF($A270="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C270,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q270" s="58">
-        <f>IF($A270="","",$A270&amp;"|"&amp;$B270&amp;"|"&amp;$C270)</f>
-        <v/>
-      </c>
-      <c r="R270" s="59" t="n"/>
-      <c r="S270" s="60" t="n"/>
-    </row>
-    <row r="271" ht="15" customHeight="1" s="34">
-      <c r="A271" s="54" t="n"/>
-      <c r="B271" s="54" t="n"/>
-      <c r="C271" s="54" t="n"/>
-      <c r="D271" s="55">
-        <f>IF($A271="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C271,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E271" s="55">
-        <f>IF($A271="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C271,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F271" s="56">
-        <f>IF($A271="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C271,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G271" s="57" t="n"/>
-      <c r="H271" s="54" t="n"/>
-      <c r="I271" s="54" t="n"/>
-      <c r="J271" s="39">
-        <f>IF($A271="","",IF($E271="Informational","GREEN",IF($G271="",IF($E271="Mandatory","RED","YELLOW"),IF($N271="Exact",IF(UPPER(TRIM($G271&amp;""))=UPPER(TRIM($F271&amp;"")),"GREEN",$P271),IF(NOT(ISNUMBER($G271)),$P271,IF($N271="Min",IF($G271&gt;=$F271,"GREEN",IF($G271&gt;=$F271-$O271,"YELLOW",$P271)),IF($N271="Max",IF($G271&lt;=$F271,"GREEN",IF($G271&lt;=$F271+$O271,"YELLOW",$P271)),IF($N271="Range",IF(ABS($G271-$F271)&lt;=$O271,"GREEN",$P271),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K271" s="39">
-        <f>IF($A271="","",IF($H271="Non-Compliant","RED",IF(AND(OR($H271="Alternative Offer",$H271="Partially Compliant"),$J271="GREEN"),"YELLOW",IF(AND($J271="GREEN",ISNUMBER($R271),$R271&lt;Baseline!$B$9),"YELLOW",$J271))))</f>
-        <v/>
-      </c>
-      <c r="L271" s="39">
-        <f>IF($A271="","",IF($K271="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A271,Exceptions!$C$5:$C$104,$B271,Exceptions!$D$5:$D$104,$C271,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K271)))</f>
-        <v/>
-      </c>
-      <c r="M271" s="39">
-        <f>IF($A271="","",IF($H271="","Declaration missing",IF($H271="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R271),$R271&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H271="Fully Compliant",$J271&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N271" s="58">
-        <f>IF($A271="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C271,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O271" s="58">
-        <f>IF($A271="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C271,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P271" s="58">
-        <f>IF($A271="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C271,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q271" s="58">
-        <f>IF($A271="","",$A271&amp;"|"&amp;$B271&amp;"|"&amp;$C271)</f>
-        <v/>
-      </c>
-      <c r="R271" s="59" t="n"/>
-      <c r="S271" s="60" t="n"/>
-    </row>
-    <row r="272" ht="15" customHeight="1" s="34">
-      <c r="A272" s="54" t="n"/>
-      <c r="B272" s="54" t="n"/>
-      <c r="C272" s="54" t="n"/>
-      <c r="D272" s="55">
-        <f>IF($A272="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C272,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E272" s="55">
-        <f>IF($A272="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C272,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F272" s="56">
-        <f>IF($A272="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C272,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G272" s="57" t="n"/>
-      <c r="H272" s="54" t="n"/>
-      <c r="I272" s="54" t="n"/>
-      <c r="J272" s="39">
-        <f>IF($A272="","",IF($E272="Informational","GREEN",IF($G272="",IF($E272="Mandatory","RED","YELLOW"),IF($N272="Exact",IF(UPPER(TRIM($G272&amp;""))=UPPER(TRIM($F272&amp;"")),"GREEN",$P272),IF(NOT(ISNUMBER($G272)),$P272,IF($N272="Min",IF($G272&gt;=$F272,"GREEN",IF($G272&gt;=$F272-$O272,"YELLOW",$P272)),IF($N272="Max",IF($G272&lt;=$F272,"GREEN",IF($G272&lt;=$F272+$O272,"YELLOW",$P272)),IF($N272="Range",IF(ABS($G272-$F272)&lt;=$O272,"GREEN",$P272),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K272" s="39">
-        <f>IF($A272="","",IF($H272="Non-Compliant","RED",IF(AND(OR($H272="Alternative Offer",$H272="Partially Compliant"),$J272="GREEN"),"YELLOW",IF(AND($J272="GREEN",ISNUMBER($R272),$R272&lt;Baseline!$B$9),"YELLOW",$J272))))</f>
-        <v/>
-      </c>
-      <c r="L272" s="39">
-        <f>IF($A272="","",IF($K272="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A272,Exceptions!$C$5:$C$104,$B272,Exceptions!$D$5:$D$104,$C272,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K272)))</f>
-        <v/>
-      </c>
-      <c r="M272" s="39">
-        <f>IF($A272="","",IF($H272="","Declaration missing",IF($H272="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R272),$R272&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H272="Fully Compliant",$J272&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N272" s="58">
-        <f>IF($A272="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C272,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O272" s="58">
-        <f>IF($A272="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C272,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P272" s="58">
-        <f>IF($A272="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C272,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q272" s="58">
-        <f>IF($A272="","",$A272&amp;"|"&amp;$B272&amp;"|"&amp;$C272)</f>
-        <v/>
-      </c>
-      <c r="R272" s="59" t="n"/>
-      <c r="S272" s="60" t="n"/>
-    </row>
-    <row r="273" ht="15" customHeight="1" s="34">
-      <c r="A273" s="54" t="n"/>
-      <c r="B273" s="54" t="n"/>
-      <c r="C273" s="54" t="n"/>
-      <c r="D273" s="55">
-        <f>IF($A273="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C273,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E273" s="55">
-        <f>IF($A273="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C273,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F273" s="56">
-        <f>IF($A273="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C273,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G273" s="57" t="n"/>
-      <c r="H273" s="54" t="n"/>
-      <c r="I273" s="54" t="n"/>
-      <c r="J273" s="39">
-        <f>IF($A273="","",IF($E273="Informational","GREEN",IF($G273="",IF($E273="Mandatory","RED","YELLOW"),IF($N273="Exact",IF(UPPER(TRIM($G273&amp;""))=UPPER(TRIM($F273&amp;"")),"GREEN",$P273),IF(NOT(ISNUMBER($G273)),$P273,IF($N273="Min",IF($G273&gt;=$F273,"GREEN",IF($G273&gt;=$F273-$O273,"YELLOW",$P273)),IF($N273="Max",IF($G273&lt;=$F273,"GREEN",IF($G273&lt;=$F273+$O273,"YELLOW",$P273)),IF($N273="Range",IF(ABS($G273-$F273)&lt;=$O273,"GREEN",$P273),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K273" s="39">
-        <f>IF($A273="","",IF($H273="Non-Compliant","RED",IF(AND(OR($H273="Alternative Offer",$H273="Partially Compliant"),$J273="GREEN"),"YELLOW",IF(AND($J273="GREEN",ISNUMBER($R273),$R273&lt;Baseline!$B$9),"YELLOW",$J273))))</f>
-        <v/>
-      </c>
-      <c r="L273" s="39">
-        <f>IF($A273="","",IF($K273="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A273,Exceptions!$C$5:$C$104,$B273,Exceptions!$D$5:$D$104,$C273,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K273)))</f>
-        <v/>
-      </c>
-      <c r="M273" s="39">
-        <f>IF($A273="","",IF($H273="","Declaration missing",IF($H273="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R273),$R273&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H273="Fully Compliant",$J273&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N273" s="58">
-        <f>IF($A273="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C273,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O273" s="58">
-        <f>IF($A273="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C273,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P273" s="58">
-        <f>IF($A273="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C273,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q273" s="58">
-        <f>IF($A273="","",$A273&amp;"|"&amp;$B273&amp;"|"&amp;$C273)</f>
-        <v/>
-      </c>
-      <c r="R273" s="59" t="n"/>
-      <c r="S273" s="60" t="n"/>
-    </row>
-    <row r="274" ht="15" customHeight="1" s="34">
-      <c r="A274" s="54" t="n"/>
-      <c r="B274" s="54" t="n"/>
-      <c r="C274" s="54" t="n"/>
-      <c r="D274" s="55">
-        <f>IF($A274="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C274,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E274" s="55">
-        <f>IF($A274="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C274,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F274" s="56">
-        <f>IF($A274="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C274,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G274" s="57" t="n"/>
-      <c r="H274" s="54" t="n"/>
-      <c r="I274" s="54" t="n"/>
-      <c r="J274" s="39">
-        <f>IF($A274="","",IF($E274="Informational","GREEN",IF($G274="",IF($E274="Mandatory","RED","YELLOW"),IF($N274="Exact",IF(UPPER(TRIM($G274&amp;""))=UPPER(TRIM($F274&amp;"")),"GREEN",$P274),IF(NOT(ISNUMBER($G274)),$P274,IF($N274="Min",IF($G274&gt;=$F274,"GREEN",IF($G274&gt;=$F274-$O274,"YELLOW",$P274)),IF($N274="Max",IF($G274&lt;=$F274,"GREEN",IF($G274&lt;=$F274+$O274,"YELLOW",$P274)),IF($N274="Range",IF(ABS($G274-$F274)&lt;=$O274,"GREEN",$P274),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K274" s="39">
-        <f>IF($A274="","",IF($H274="Non-Compliant","RED",IF(AND(OR($H274="Alternative Offer",$H274="Partially Compliant"),$J274="GREEN"),"YELLOW",IF(AND($J274="GREEN",ISNUMBER($R274),$R274&lt;Baseline!$B$9),"YELLOW",$J274))))</f>
-        <v/>
-      </c>
-      <c r="L274" s="39">
-        <f>IF($A274="","",IF($K274="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A274,Exceptions!$C$5:$C$104,$B274,Exceptions!$D$5:$D$104,$C274,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K274)))</f>
-        <v/>
-      </c>
-      <c r="M274" s="39">
-        <f>IF($A274="","",IF($H274="","Declaration missing",IF($H274="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R274),$R274&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H274="Fully Compliant",$J274&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N274" s="58">
-        <f>IF($A274="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C274,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O274" s="58">
-        <f>IF($A274="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C274,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P274" s="58">
-        <f>IF($A274="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C274,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q274" s="58">
-        <f>IF($A274="","",$A274&amp;"|"&amp;$B274&amp;"|"&amp;$C274)</f>
-        <v/>
-      </c>
-      <c r="R274" s="59" t="n"/>
-      <c r="S274" s="60" t="n"/>
-    </row>
-    <row r="275" ht="15" customHeight="1" s="34">
-      <c r="A275" s="54" t="n"/>
-      <c r="B275" s="54" t="n"/>
-      <c r="C275" s="54" t="n"/>
-      <c r="D275" s="55">
-        <f>IF($A275="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C275,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E275" s="55">
-        <f>IF($A275="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C275,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F275" s="56">
-        <f>IF($A275="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C275,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G275" s="57" t="n"/>
-      <c r="H275" s="54" t="n"/>
-      <c r="I275" s="54" t="n"/>
-      <c r="J275" s="39">
-        <f>IF($A275="","",IF($E275="Informational","GREEN",IF($G275="",IF($E275="Mandatory","RED","YELLOW"),IF($N275="Exact",IF(UPPER(TRIM($G275&amp;""))=UPPER(TRIM($F275&amp;"")),"GREEN",$P275),IF(NOT(ISNUMBER($G275)),$P275,IF($N275="Min",IF($G275&gt;=$F275,"GREEN",IF($G275&gt;=$F275-$O275,"YELLOW",$P275)),IF($N275="Max",IF($G275&lt;=$F275,"GREEN",IF($G275&lt;=$F275+$O275,"YELLOW",$P275)),IF($N275="Range",IF(ABS($G275-$F275)&lt;=$O275,"GREEN",$P275),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K275" s="39">
-        <f>IF($A275="","",IF($H275="Non-Compliant","RED",IF(AND(OR($H275="Alternative Offer",$H275="Partially Compliant"),$J275="GREEN"),"YELLOW",IF(AND($J275="GREEN",ISNUMBER($R275),$R275&lt;Baseline!$B$9),"YELLOW",$J275))))</f>
-        <v/>
-      </c>
-      <c r="L275" s="39">
-        <f>IF($A275="","",IF($K275="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A275,Exceptions!$C$5:$C$104,$B275,Exceptions!$D$5:$D$104,$C275,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K275)))</f>
-        <v/>
-      </c>
-      <c r="M275" s="39">
-        <f>IF($A275="","",IF($H275="","Declaration missing",IF($H275="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R275),$R275&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H275="Fully Compliant",$J275&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N275" s="58">
-        <f>IF($A275="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C275,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O275" s="58">
-        <f>IF($A275="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C275,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P275" s="58">
-        <f>IF($A275="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C275,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q275" s="58">
-        <f>IF($A275="","",$A275&amp;"|"&amp;$B275&amp;"|"&amp;$C275)</f>
-        <v/>
-      </c>
-      <c r="R275" s="59" t="n"/>
-      <c r="S275" s="60" t="n"/>
-    </row>
-    <row r="276" ht="15" customHeight="1" s="34">
-      <c r="A276" s="54" t="n"/>
-      <c r="B276" s="54" t="n"/>
-      <c r="C276" s="54" t="n"/>
-      <c r="D276" s="55">
-        <f>IF($A276="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C276,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E276" s="55">
-        <f>IF($A276="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C276,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F276" s="56">
-        <f>IF($A276="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C276,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G276" s="57" t="n"/>
-      <c r="H276" s="54" t="n"/>
-      <c r="I276" s="54" t="n"/>
-      <c r="J276" s="39">
-        <f>IF($A276="","",IF($E276="Informational","GREEN",IF($G276="",IF($E276="Mandatory","RED","YELLOW"),IF($N276="Exact",IF(UPPER(TRIM($G276&amp;""))=UPPER(TRIM($F276&amp;"")),"GREEN",$P276),IF(NOT(ISNUMBER($G276)),$P276,IF($N276="Min",IF($G276&gt;=$F276,"GREEN",IF($G276&gt;=$F276-$O276,"YELLOW",$P276)),IF($N276="Max",IF($G276&lt;=$F276,"GREEN",IF($G276&lt;=$F276+$O276,"YELLOW",$P276)),IF($N276="Range",IF(ABS($G276-$F276)&lt;=$O276,"GREEN",$P276),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K276" s="39">
-        <f>IF($A276="","",IF($H276="Non-Compliant","RED",IF(AND(OR($H276="Alternative Offer",$H276="Partially Compliant"),$J276="GREEN"),"YELLOW",IF(AND($J276="GREEN",ISNUMBER($R276),$R276&lt;Baseline!$B$9),"YELLOW",$J276))))</f>
-        <v/>
-      </c>
-      <c r="L276" s="39">
-        <f>IF($A276="","",IF($K276="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A276,Exceptions!$C$5:$C$104,$B276,Exceptions!$D$5:$D$104,$C276,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K276)))</f>
-        <v/>
-      </c>
-      <c r="M276" s="39">
-        <f>IF($A276="","",IF($H276="","Declaration missing",IF($H276="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R276),$R276&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H276="Fully Compliant",$J276&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N276" s="58">
-        <f>IF($A276="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C276,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O276" s="58">
-        <f>IF($A276="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C276,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P276" s="58">
-        <f>IF($A276="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C276,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q276" s="58">
-        <f>IF($A276="","",$A276&amp;"|"&amp;$B276&amp;"|"&amp;$C276)</f>
-        <v/>
-      </c>
-      <c r="R276" s="59" t="n"/>
-      <c r="S276" s="60" t="n"/>
-    </row>
-    <row r="277" ht="15" customHeight="1" s="34">
-      <c r="A277" s="54" t="n"/>
-      <c r="B277" s="54" t="n"/>
-      <c r="C277" s="54" t="n"/>
-      <c r="D277" s="55">
-        <f>IF($A277="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C277,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E277" s="55">
-        <f>IF($A277="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C277,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F277" s="56">
-        <f>IF($A277="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C277,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G277" s="57" t="n"/>
-      <c r="H277" s="54" t="n"/>
-      <c r="I277" s="54" t="n"/>
-      <c r="J277" s="39">
-        <f>IF($A277="","",IF($E277="Informational","GREEN",IF($G277="",IF($E277="Mandatory","RED","YELLOW"),IF($N277="Exact",IF(UPPER(TRIM($G277&amp;""))=UPPER(TRIM($F277&amp;"")),"GREEN",$P277),IF(NOT(ISNUMBER($G277)),$P277,IF($N277="Min",IF($G277&gt;=$F277,"GREEN",IF($G277&gt;=$F277-$O277,"YELLOW",$P277)),IF($N277="Max",IF($G277&lt;=$F277,"GREEN",IF($G277&lt;=$F277+$O277,"YELLOW",$P277)),IF($N277="Range",IF(ABS($G277-$F277)&lt;=$O277,"GREEN",$P277),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K277" s="39">
-        <f>IF($A277="","",IF($H277="Non-Compliant","RED",IF(AND(OR($H277="Alternative Offer",$H277="Partially Compliant"),$J277="GREEN"),"YELLOW",IF(AND($J277="GREEN",ISNUMBER($R277),$R277&lt;Baseline!$B$9),"YELLOW",$J277))))</f>
-        <v/>
-      </c>
-      <c r="L277" s="39">
-        <f>IF($A277="","",IF($K277="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A277,Exceptions!$C$5:$C$104,$B277,Exceptions!$D$5:$D$104,$C277,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K277)))</f>
-        <v/>
-      </c>
-      <c r="M277" s="39">
-        <f>IF($A277="","",IF($H277="","Declaration missing",IF($H277="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R277),$R277&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H277="Fully Compliant",$J277&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N277" s="58">
-        <f>IF($A277="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C277,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O277" s="58">
-        <f>IF($A277="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C277,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P277" s="58">
-        <f>IF($A277="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C277,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q277" s="58">
-        <f>IF($A277="","",$A277&amp;"|"&amp;$B277&amp;"|"&amp;$C277)</f>
-        <v/>
-      </c>
-      <c r="R277" s="59" t="n"/>
-      <c r="S277" s="60" t="n"/>
-    </row>
-    <row r="278" ht="15" customHeight="1" s="34">
-      <c r="A278" s="54" t="n"/>
-      <c r="B278" s="54" t="n"/>
-      <c r="C278" s="54" t="n"/>
-      <c r="D278" s="55">
-        <f>IF($A278="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C278,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E278" s="55">
-        <f>IF($A278="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C278,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F278" s="56">
-        <f>IF($A278="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C278,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G278" s="57" t="n"/>
-      <c r="H278" s="54" t="n"/>
-      <c r="I278" s="54" t="n"/>
-      <c r="J278" s="39">
-        <f>IF($A278="","",IF($E278="Informational","GREEN",IF($G278="",IF($E278="Mandatory","RED","YELLOW"),IF($N278="Exact",IF(UPPER(TRIM($G278&amp;""))=UPPER(TRIM($F278&amp;"")),"GREEN",$P278),IF(NOT(ISNUMBER($G278)),$P278,IF($N278="Min",IF($G278&gt;=$F278,"GREEN",IF($G278&gt;=$F278-$O278,"YELLOW",$P278)),IF($N278="Max",IF($G278&lt;=$F278,"GREEN",IF($G278&lt;=$F278+$O278,"YELLOW",$P278)),IF($N278="Range",IF(ABS($G278-$F278)&lt;=$O278,"GREEN",$P278),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K278" s="39">
-        <f>IF($A278="","",IF($H278="Non-Compliant","RED",IF(AND(OR($H278="Alternative Offer",$H278="Partially Compliant"),$J278="GREEN"),"YELLOW",IF(AND($J278="GREEN",ISNUMBER($R278),$R278&lt;Baseline!$B$9),"YELLOW",$J278))))</f>
-        <v/>
-      </c>
-      <c r="L278" s="39">
-        <f>IF($A278="","",IF($K278="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A278,Exceptions!$C$5:$C$104,$B278,Exceptions!$D$5:$D$104,$C278,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K278)))</f>
-        <v/>
-      </c>
-      <c r="M278" s="39">
-        <f>IF($A278="","",IF($H278="","Declaration missing",IF($H278="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R278),$R278&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H278="Fully Compliant",$J278&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N278" s="58">
-        <f>IF($A278="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C278,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O278" s="58">
-        <f>IF($A278="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C278,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P278" s="58">
-        <f>IF($A278="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C278,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q278" s="58">
-        <f>IF($A278="","",$A278&amp;"|"&amp;$B278&amp;"|"&amp;$C278)</f>
-        <v/>
-      </c>
-      <c r="R278" s="59" t="n"/>
-      <c r="S278" s="60" t="n"/>
-    </row>
-    <row r="279" ht="15" customHeight="1" s="34">
-      <c r="A279" s="54" t="n"/>
-      <c r="B279" s="54" t="n"/>
-      <c r="C279" s="54" t="n"/>
-      <c r="D279" s="55">
-        <f>IF($A279="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C279,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E279" s="55">
-        <f>IF($A279="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C279,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F279" s="56">
-        <f>IF($A279="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C279,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G279" s="57" t="n"/>
-      <c r="H279" s="54" t="n"/>
-      <c r="I279" s="54" t="n"/>
-      <c r="J279" s="39">
-        <f>IF($A279="","",IF($E279="Informational","GREEN",IF($G279="",IF($E279="Mandatory","RED","YELLOW"),IF($N279="Exact",IF(UPPER(TRIM($G279&amp;""))=UPPER(TRIM($F279&amp;"")),"GREEN",$P279),IF(NOT(ISNUMBER($G279)),$P279,IF($N279="Min",IF($G279&gt;=$F279,"GREEN",IF($G279&gt;=$F279-$O279,"YELLOW",$P279)),IF($N279="Max",IF($G279&lt;=$F279,"GREEN",IF($G279&lt;=$F279+$O279,"YELLOW",$P279)),IF($N279="Range",IF(ABS($G279-$F279)&lt;=$O279,"GREEN",$P279),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K279" s="39">
-        <f>IF($A279="","",IF($H279="Non-Compliant","RED",IF(AND(OR($H279="Alternative Offer",$H279="Partially Compliant"),$J279="GREEN"),"YELLOW",IF(AND($J279="GREEN",ISNUMBER($R279),$R279&lt;Baseline!$B$9),"YELLOW",$J279))))</f>
-        <v/>
-      </c>
-      <c r="L279" s="39">
-        <f>IF($A279="","",IF($K279="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A279,Exceptions!$C$5:$C$104,$B279,Exceptions!$D$5:$D$104,$C279,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K279)))</f>
-        <v/>
-      </c>
-      <c r="M279" s="39">
-        <f>IF($A279="","",IF($H279="","Declaration missing",IF($H279="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R279),$R279&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H279="Fully Compliant",$J279&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N279" s="58">
-        <f>IF($A279="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C279,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O279" s="58">
-        <f>IF($A279="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C279,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P279" s="58">
-        <f>IF($A279="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C279,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q279" s="58">
-        <f>IF($A279="","",$A279&amp;"|"&amp;$B279&amp;"|"&amp;$C279)</f>
-        <v/>
-      </c>
-      <c r="R279" s="59" t="n"/>
-      <c r="S279" s="60" t="n"/>
-    </row>
-    <row r="280" ht="15" customHeight="1" s="34">
-      <c r="A280" s="54" t="n"/>
-      <c r="B280" s="54" t="n"/>
-      <c r="C280" s="54" t="n"/>
-      <c r="D280" s="55">
-        <f>IF($A280="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C280,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E280" s="55">
-        <f>IF($A280="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C280,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F280" s="56">
-        <f>IF($A280="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C280,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G280" s="57" t="n"/>
-      <c r="H280" s="54" t="n"/>
-      <c r="I280" s="54" t="n"/>
-      <c r="J280" s="39">
-        <f>IF($A280="","",IF($E280="Informational","GREEN",IF($G280="",IF($E280="Mandatory","RED","YELLOW"),IF($N280="Exact",IF(UPPER(TRIM($G280&amp;""))=UPPER(TRIM($F280&amp;"")),"GREEN",$P280),IF(NOT(ISNUMBER($G280)),$P280,IF($N280="Min",IF($G280&gt;=$F280,"GREEN",IF($G280&gt;=$F280-$O280,"YELLOW",$P280)),IF($N280="Max",IF($G280&lt;=$F280,"GREEN",IF($G280&lt;=$F280+$O280,"YELLOW",$P280)),IF($N280="Range",IF(ABS($G280-$F280)&lt;=$O280,"GREEN",$P280),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K280" s="39">
-        <f>IF($A280="","",IF($H280="Non-Compliant","RED",IF(AND(OR($H280="Alternative Offer",$H280="Partially Compliant"),$J280="GREEN"),"YELLOW",IF(AND($J280="GREEN",ISNUMBER($R280),$R280&lt;Baseline!$B$9),"YELLOW",$J280))))</f>
-        <v/>
-      </c>
-      <c r="L280" s="39">
-        <f>IF($A280="","",IF($K280="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A280,Exceptions!$C$5:$C$104,$B280,Exceptions!$D$5:$D$104,$C280,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K280)))</f>
-        <v/>
-      </c>
-      <c r="M280" s="39">
-        <f>IF($A280="","",IF($H280="","Declaration missing",IF($H280="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R280),$R280&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H280="Fully Compliant",$J280&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N280" s="58">
-        <f>IF($A280="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C280,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O280" s="58">
-        <f>IF($A280="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C280,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P280" s="58">
-        <f>IF($A280="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C280,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q280" s="58">
-        <f>IF($A280="","",$A280&amp;"|"&amp;$B280&amp;"|"&amp;$C280)</f>
-        <v/>
-      </c>
-      <c r="R280" s="59" t="n"/>
-      <c r="S280" s="60" t="n"/>
-    </row>
-    <row r="281" ht="15" customHeight="1" s="34">
-      <c r="A281" s="54" t="n"/>
-      <c r="B281" s="54" t="n"/>
-      <c r="C281" s="54" t="n"/>
-      <c r="D281" s="55">
-        <f>IF($A281="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C281,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E281" s="55">
-        <f>IF($A281="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C281,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F281" s="56">
-        <f>IF($A281="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C281,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G281" s="57" t="n"/>
-      <c r="H281" s="54" t="n"/>
-      <c r="I281" s="54" t="n"/>
-      <c r="J281" s="39">
-        <f>IF($A281="","",IF($E281="Informational","GREEN",IF($G281="",IF($E281="Mandatory","RED","YELLOW"),IF($N281="Exact",IF(UPPER(TRIM($G281&amp;""))=UPPER(TRIM($F281&amp;"")),"GREEN",$P281),IF(NOT(ISNUMBER($G281)),$P281,IF($N281="Min",IF($G281&gt;=$F281,"GREEN",IF($G281&gt;=$F281-$O281,"YELLOW",$P281)),IF($N281="Max",IF($G281&lt;=$F281,"GREEN",IF($G281&lt;=$F281+$O281,"YELLOW",$P281)),IF($N281="Range",IF(ABS($G281-$F281)&lt;=$O281,"GREEN",$P281),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K281" s="39">
-        <f>IF($A281="","",IF($H281="Non-Compliant","RED",IF(AND(OR($H281="Alternative Offer",$H281="Partially Compliant"),$J281="GREEN"),"YELLOW",IF(AND($J281="GREEN",ISNUMBER($R281),$R281&lt;Baseline!$B$9),"YELLOW",$J281))))</f>
-        <v/>
-      </c>
-      <c r="L281" s="39">
-        <f>IF($A281="","",IF($K281="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A281,Exceptions!$C$5:$C$104,$B281,Exceptions!$D$5:$D$104,$C281,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K281)))</f>
-        <v/>
-      </c>
-      <c r="M281" s="39">
-        <f>IF($A281="","",IF($H281="","Declaration missing",IF($H281="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R281),$R281&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H281="Fully Compliant",$J281&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N281" s="58">
-        <f>IF($A281="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C281,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O281" s="58">
-        <f>IF($A281="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C281,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P281" s="58">
-        <f>IF($A281="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C281,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q281" s="58">
-        <f>IF($A281="","",$A281&amp;"|"&amp;$B281&amp;"|"&amp;$C281)</f>
-        <v/>
-      </c>
-      <c r="R281" s="59" t="n"/>
-      <c r="S281" s="60" t="n"/>
-    </row>
-    <row r="282" ht="15" customHeight="1" s="34">
-      <c r="A282" s="54" t="n"/>
-      <c r="B282" s="54" t="n"/>
-      <c r="C282" s="54" t="n"/>
-      <c r="D282" s="55">
-        <f>IF($A282="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C282,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E282" s="55">
-        <f>IF($A282="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C282,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F282" s="56">
-        <f>IF($A282="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C282,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G282" s="57" t="n"/>
-      <c r="H282" s="54" t="n"/>
-      <c r="I282" s="54" t="n"/>
-      <c r="J282" s="39">
-        <f>IF($A282="","",IF($E282="Informational","GREEN",IF($G282="",IF($E282="Mandatory","RED","YELLOW"),IF($N282="Exact",IF(UPPER(TRIM($G282&amp;""))=UPPER(TRIM($F282&amp;"")),"GREEN",$P282),IF(NOT(ISNUMBER($G282)),$P282,IF($N282="Min",IF($G282&gt;=$F282,"GREEN",IF($G282&gt;=$F282-$O282,"YELLOW",$P282)),IF($N282="Max",IF($G282&lt;=$F282,"GREEN",IF($G282&lt;=$F282+$O282,"YELLOW",$P282)),IF($N282="Range",IF(ABS($G282-$F282)&lt;=$O282,"GREEN",$P282),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K282" s="39">
-        <f>IF($A282="","",IF($H282="Non-Compliant","RED",IF(AND(OR($H282="Alternative Offer",$H282="Partially Compliant"),$J282="GREEN"),"YELLOW",IF(AND($J282="GREEN",ISNUMBER($R282),$R282&lt;Baseline!$B$9),"YELLOW",$J282))))</f>
-        <v/>
-      </c>
-      <c r="L282" s="39">
-        <f>IF($A282="","",IF($K282="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A282,Exceptions!$C$5:$C$104,$B282,Exceptions!$D$5:$D$104,$C282,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K282)))</f>
-        <v/>
-      </c>
-      <c r="M282" s="39">
-        <f>IF($A282="","",IF($H282="","Declaration missing",IF($H282="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R282),$R282&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H282="Fully Compliant",$J282&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N282" s="58">
-        <f>IF($A282="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C282,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O282" s="58">
-        <f>IF($A282="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C282,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P282" s="58">
-        <f>IF($A282="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C282,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q282" s="58">
-        <f>IF($A282="","",$A282&amp;"|"&amp;$B282&amp;"|"&amp;$C282)</f>
-        <v/>
-      </c>
-      <c r="R282" s="59" t="n"/>
-      <c r="S282" s="60" t="n"/>
-    </row>
-    <row r="283" ht="15" customHeight="1" s="34">
-      <c r="A283" s="54" t="n"/>
-      <c r="B283" s="54" t="n"/>
-      <c r="C283" s="54" t="n"/>
-      <c r="D283" s="55">
-        <f>IF($A283="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C283,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E283" s="55">
-        <f>IF($A283="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C283,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F283" s="56">
-        <f>IF($A283="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C283,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G283" s="57" t="n"/>
-      <c r="H283" s="54" t="n"/>
-      <c r="I283" s="54" t="n"/>
-      <c r="J283" s="39">
-        <f>IF($A283="","",IF($E283="Informational","GREEN",IF($G283="",IF($E283="Mandatory","RED","YELLOW"),IF($N283="Exact",IF(UPPER(TRIM($G283&amp;""))=UPPER(TRIM($F283&amp;"")),"GREEN",$P283),IF(NOT(ISNUMBER($G283)),$P283,IF($N283="Min",IF($G283&gt;=$F283,"GREEN",IF($G283&gt;=$F283-$O283,"YELLOW",$P283)),IF($N283="Max",IF($G283&lt;=$F283,"GREEN",IF($G283&lt;=$F283+$O283,"YELLOW",$P283)),IF($N283="Range",IF(ABS($G283-$F283)&lt;=$O283,"GREEN",$P283),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K283" s="39">
-        <f>IF($A283="","",IF($H283="Non-Compliant","RED",IF(AND(OR($H283="Alternative Offer",$H283="Partially Compliant"),$J283="GREEN"),"YELLOW",IF(AND($J283="GREEN",ISNUMBER($R283),$R283&lt;Baseline!$B$9),"YELLOW",$J283))))</f>
-        <v/>
-      </c>
-      <c r="L283" s="39">
-        <f>IF($A283="","",IF($K283="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A283,Exceptions!$C$5:$C$104,$B283,Exceptions!$D$5:$D$104,$C283,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K283)))</f>
-        <v/>
-      </c>
-      <c r="M283" s="39">
-        <f>IF($A283="","",IF($H283="","Declaration missing",IF($H283="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R283),$R283&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H283="Fully Compliant",$J283&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N283" s="58">
-        <f>IF($A283="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C283,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O283" s="58">
-        <f>IF($A283="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C283,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P283" s="58">
-        <f>IF($A283="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C283,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q283" s="58">
-        <f>IF($A283="","",$A283&amp;"|"&amp;$B283&amp;"|"&amp;$C283)</f>
-        <v/>
-      </c>
-      <c r="R283" s="59" t="n"/>
-      <c r="S283" s="60" t="n"/>
-    </row>
-    <row r="284" ht="15" customHeight="1" s="34">
-      <c r="A284" s="54" t="n"/>
-      <c r="B284" s="54" t="n"/>
-      <c r="C284" s="54" t="n"/>
-      <c r="D284" s="55">
-        <f>IF($A284="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C284,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E284" s="55">
-        <f>IF($A284="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C284,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F284" s="56">
-        <f>IF($A284="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C284,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G284" s="57" t="n"/>
-      <c r="H284" s="54" t="n"/>
-      <c r="I284" s="54" t="n"/>
-      <c r="J284" s="39">
-        <f>IF($A284="","",IF($E284="Informational","GREEN",IF($G284="",IF($E284="Mandatory","RED","YELLOW"),IF($N284="Exact",IF(UPPER(TRIM($G284&amp;""))=UPPER(TRIM($F284&amp;"")),"GREEN",$P284),IF(NOT(ISNUMBER($G284)),$P284,IF($N284="Min",IF($G284&gt;=$F284,"GREEN",IF($G284&gt;=$F284-$O284,"YELLOW",$P284)),IF($N284="Max",IF($G284&lt;=$F284,"GREEN",IF($G284&lt;=$F284+$O284,"YELLOW",$P284)),IF($N284="Range",IF(ABS($G284-$F284)&lt;=$O284,"GREEN",$P284),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K284" s="39">
-        <f>IF($A284="","",IF($H284="Non-Compliant","RED",IF(AND(OR($H284="Alternative Offer",$H284="Partially Compliant"),$J284="GREEN"),"YELLOW",IF(AND($J284="GREEN",ISNUMBER($R284),$R284&lt;Baseline!$B$9),"YELLOW",$J284))))</f>
-        <v/>
-      </c>
-      <c r="L284" s="39">
-        <f>IF($A284="","",IF($K284="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A284,Exceptions!$C$5:$C$104,$B284,Exceptions!$D$5:$D$104,$C284,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K284)))</f>
-        <v/>
-      </c>
-      <c r="M284" s="39">
-        <f>IF($A284="","",IF($H284="","Declaration missing",IF($H284="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R284),$R284&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H284="Fully Compliant",$J284&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N284" s="58">
-        <f>IF($A284="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C284,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O284" s="58">
-        <f>IF($A284="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C284,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P284" s="58">
-        <f>IF($A284="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C284,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q284" s="58">
-        <f>IF($A284="","",$A284&amp;"|"&amp;$B284&amp;"|"&amp;$C284)</f>
-        <v/>
-      </c>
-      <c r="R284" s="59" t="n"/>
-      <c r="S284" s="60" t="n"/>
-    </row>
-    <row r="285" ht="15" customHeight="1" s="34">
-      <c r="A285" s="54" t="n"/>
-      <c r="B285" s="54" t="n"/>
-      <c r="C285" s="54" t="n"/>
-      <c r="D285" s="55">
-        <f>IF($A285="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C285,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E285" s="55">
-        <f>IF($A285="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C285,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F285" s="56">
-        <f>IF($A285="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C285,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G285" s="57" t="n"/>
-      <c r="H285" s="54" t="n"/>
-      <c r="I285" s="54" t="n"/>
-      <c r="J285" s="39">
-        <f>IF($A285="","",IF($E285="Informational","GREEN",IF($G285="",IF($E285="Mandatory","RED","YELLOW"),IF($N285="Exact",IF(UPPER(TRIM($G285&amp;""))=UPPER(TRIM($F285&amp;"")),"GREEN",$P285),IF(NOT(ISNUMBER($G285)),$P285,IF($N285="Min",IF($G285&gt;=$F285,"GREEN",IF($G285&gt;=$F285-$O285,"YELLOW",$P285)),IF($N285="Max",IF($G285&lt;=$F285,"GREEN",IF($G285&lt;=$F285+$O285,"YELLOW",$P285)),IF($N285="Range",IF(ABS($G285-$F285)&lt;=$O285,"GREEN",$P285),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K285" s="39">
-        <f>IF($A285="","",IF($H285="Non-Compliant","RED",IF(AND(OR($H285="Alternative Offer",$H285="Partially Compliant"),$J285="GREEN"),"YELLOW",IF(AND($J285="GREEN",ISNUMBER($R285),$R285&lt;Baseline!$B$9),"YELLOW",$J285))))</f>
-        <v/>
-      </c>
-      <c r="L285" s="39">
-        <f>IF($A285="","",IF($K285="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A285,Exceptions!$C$5:$C$104,$B285,Exceptions!$D$5:$D$104,$C285,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K285)))</f>
-        <v/>
-      </c>
-      <c r="M285" s="39">
-        <f>IF($A285="","",IF($H285="","Declaration missing",IF($H285="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R285),$R285&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H285="Fully Compliant",$J285&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N285" s="58">
-        <f>IF($A285="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C285,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O285" s="58">
-        <f>IF($A285="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C285,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P285" s="58">
-        <f>IF($A285="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C285,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q285" s="58">
-        <f>IF($A285="","",$A285&amp;"|"&amp;$B285&amp;"|"&amp;$C285)</f>
-        <v/>
-      </c>
-      <c r="R285" s="59" t="n"/>
-      <c r="S285" s="60" t="n"/>
-    </row>
-    <row r="286" ht="15" customHeight="1" s="34">
-      <c r="A286" s="54" t="n"/>
-      <c r="B286" s="54" t="n"/>
-      <c r="C286" s="54" t="n"/>
-      <c r="D286" s="55">
-        <f>IF($A286="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C286,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E286" s="55">
-        <f>IF($A286="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C286,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F286" s="56">
-        <f>IF($A286="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C286,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G286" s="57" t="n"/>
-      <c r="H286" s="54" t="n"/>
-      <c r="I286" s="54" t="n"/>
-      <c r="J286" s="39">
-        <f>IF($A286="","",IF($E286="Informational","GREEN",IF($G286="",IF($E286="Mandatory","RED","YELLOW"),IF($N286="Exact",IF(UPPER(TRIM($G286&amp;""))=UPPER(TRIM($F286&amp;"")),"GREEN",$P286),IF(NOT(ISNUMBER($G286)),$P286,IF($N286="Min",IF($G286&gt;=$F286,"GREEN",IF($G286&gt;=$F286-$O286,"YELLOW",$P286)),IF($N286="Max",IF($G286&lt;=$F286,"GREEN",IF($G286&lt;=$F286+$O286,"YELLOW",$P286)),IF($N286="Range",IF(ABS($G286-$F286)&lt;=$O286,"GREEN",$P286),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K286" s="39">
-        <f>IF($A286="","",IF($H286="Non-Compliant","RED",IF(AND(OR($H286="Alternative Offer",$H286="Partially Compliant"),$J286="GREEN"),"YELLOW",IF(AND($J286="GREEN",ISNUMBER($R286),$R286&lt;Baseline!$B$9),"YELLOW",$J286))))</f>
-        <v/>
-      </c>
-      <c r="L286" s="39">
-        <f>IF($A286="","",IF($K286="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A286,Exceptions!$C$5:$C$104,$B286,Exceptions!$D$5:$D$104,$C286,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K286)))</f>
-        <v/>
-      </c>
-      <c r="M286" s="39">
-        <f>IF($A286="","",IF($H286="","Declaration missing",IF($H286="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R286),$R286&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H286="Fully Compliant",$J286&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N286" s="58">
-        <f>IF($A286="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C286,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O286" s="58">
-        <f>IF($A286="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C286,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P286" s="58">
-        <f>IF($A286="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C286,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q286" s="58">
-        <f>IF($A286="","",$A286&amp;"|"&amp;$B286&amp;"|"&amp;$C286)</f>
-        <v/>
-      </c>
-      <c r="R286" s="59" t="n"/>
-      <c r="S286" s="60" t="n"/>
-    </row>
-    <row r="287" ht="15" customHeight="1" s="34">
-      <c r="A287" s="54" t="n"/>
-      <c r="B287" s="54" t="n"/>
-      <c r="C287" s="54" t="n"/>
-      <c r="D287" s="55">
-        <f>IF($A287="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C287,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E287" s="55">
-        <f>IF($A287="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C287,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F287" s="56">
-        <f>IF($A287="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C287,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G287" s="57" t="n"/>
-      <c r="H287" s="54" t="n"/>
-      <c r="I287" s="54" t="n"/>
-      <c r="J287" s="39">
-        <f>IF($A287="","",IF($E287="Informational","GREEN",IF($G287="",IF($E287="Mandatory","RED","YELLOW"),IF($N287="Exact",IF(UPPER(TRIM($G287&amp;""))=UPPER(TRIM($F287&amp;"")),"GREEN",$P287),IF(NOT(ISNUMBER($G287)),$P287,IF($N287="Min",IF($G287&gt;=$F287,"GREEN",IF($G287&gt;=$F287-$O287,"YELLOW",$P287)),IF($N287="Max",IF($G287&lt;=$F287,"GREEN",IF($G287&lt;=$F287+$O287,"YELLOW",$P287)),IF($N287="Range",IF(ABS($G287-$F287)&lt;=$O287,"GREEN",$P287),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K287" s="39">
-        <f>IF($A287="","",IF($H287="Non-Compliant","RED",IF(AND(OR($H287="Alternative Offer",$H287="Partially Compliant"),$J287="GREEN"),"YELLOW",IF(AND($J287="GREEN",ISNUMBER($R287),$R287&lt;Baseline!$B$9),"YELLOW",$J287))))</f>
-        <v/>
-      </c>
-      <c r="L287" s="39">
-        <f>IF($A287="","",IF($K287="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A287,Exceptions!$C$5:$C$104,$B287,Exceptions!$D$5:$D$104,$C287,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K287)))</f>
-        <v/>
-      </c>
-      <c r="M287" s="39">
-        <f>IF($A287="","",IF($H287="","Declaration missing",IF($H287="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R287),$R287&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H287="Fully Compliant",$J287&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N287" s="58">
-        <f>IF($A287="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C287,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O287" s="58">
-        <f>IF($A287="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C287,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P287" s="58">
-        <f>IF($A287="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C287,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q287" s="58">
-        <f>IF($A287="","",$A287&amp;"|"&amp;$B287&amp;"|"&amp;$C287)</f>
-        <v/>
-      </c>
-      <c r="R287" s="59" t="n"/>
-      <c r="S287" s="60" t="n"/>
-    </row>
-    <row r="288" ht="15" customHeight="1" s="34">
-      <c r="A288" s="54" t="n"/>
-      <c r="B288" s="54" t="n"/>
-      <c r="C288" s="54" t="n"/>
-      <c r="D288" s="55">
-        <f>IF($A288="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C288,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E288" s="55">
-        <f>IF($A288="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C288,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F288" s="56">
-        <f>IF($A288="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C288,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G288" s="57" t="n"/>
-      <c r="H288" s="54" t="n"/>
-      <c r="I288" s="54" t="n"/>
-      <c r="J288" s="39">
-        <f>IF($A288="","",IF($E288="Informational","GREEN",IF($G288="",IF($E288="Mandatory","RED","YELLOW"),IF($N288="Exact",IF(UPPER(TRIM($G288&amp;""))=UPPER(TRIM($F288&amp;"")),"GREEN",$P288),IF(NOT(ISNUMBER($G288)),$P288,IF($N288="Min",IF($G288&gt;=$F288,"GREEN",IF($G288&gt;=$F288-$O288,"YELLOW",$P288)),IF($N288="Max",IF($G288&lt;=$F288,"GREEN",IF($G288&lt;=$F288+$O288,"YELLOW",$P288)),IF($N288="Range",IF(ABS($G288-$F288)&lt;=$O288,"GREEN",$P288),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K288" s="39">
-        <f>IF($A288="","",IF($H288="Non-Compliant","RED",IF(AND(OR($H288="Alternative Offer",$H288="Partially Compliant"),$J288="GREEN"),"YELLOW",IF(AND($J288="GREEN",ISNUMBER($R288),$R288&lt;Baseline!$B$9),"YELLOW",$J288))))</f>
-        <v/>
-      </c>
-      <c r="L288" s="39">
-        <f>IF($A288="","",IF($K288="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A288,Exceptions!$C$5:$C$104,$B288,Exceptions!$D$5:$D$104,$C288,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K288)))</f>
-        <v/>
-      </c>
-      <c r="M288" s="39">
-        <f>IF($A288="","",IF($H288="","Declaration missing",IF($H288="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R288),$R288&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H288="Fully Compliant",$J288&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N288" s="58">
-        <f>IF($A288="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C288,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O288" s="58">
-        <f>IF($A288="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C288,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P288" s="58">
-        <f>IF($A288="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C288,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q288" s="58">
-        <f>IF($A288="","",$A288&amp;"|"&amp;$B288&amp;"|"&amp;$C288)</f>
-        <v/>
-      </c>
-      <c r="R288" s="59" t="n"/>
-      <c r="S288" s="60" t="n"/>
-    </row>
-    <row r="289" ht="15" customHeight="1" s="34">
-      <c r="A289" s="54" t="n"/>
-      <c r="B289" s="54" t="n"/>
-      <c r="C289" s="54" t="n"/>
-      <c r="D289" s="55">
-        <f>IF($A289="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C289,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E289" s="55">
-        <f>IF($A289="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C289,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F289" s="56">
-        <f>IF($A289="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C289,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G289" s="57" t="n"/>
-      <c r="H289" s="54" t="n"/>
-      <c r="I289" s="54" t="n"/>
-      <c r="J289" s="39">
-        <f>IF($A289="","",IF($E289="Informational","GREEN",IF($G289="",IF($E289="Mandatory","RED","YELLOW"),IF($N289="Exact",IF(UPPER(TRIM($G289&amp;""))=UPPER(TRIM($F289&amp;"")),"GREEN",$P289),IF(NOT(ISNUMBER($G289)),$P289,IF($N289="Min",IF($G289&gt;=$F289,"GREEN",IF($G289&gt;=$F289-$O289,"YELLOW",$P289)),IF($N289="Max",IF($G289&lt;=$F289,"GREEN",IF($G289&lt;=$F289+$O289,"YELLOW",$P289)),IF($N289="Range",IF(ABS($G289-$F289)&lt;=$O289,"GREEN",$P289),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K289" s="39">
-        <f>IF($A289="","",IF($H289="Non-Compliant","RED",IF(AND(OR($H289="Alternative Offer",$H289="Partially Compliant"),$J289="GREEN"),"YELLOW",IF(AND($J289="GREEN",ISNUMBER($R289),$R289&lt;Baseline!$B$9),"YELLOW",$J289))))</f>
-        <v/>
-      </c>
-      <c r="L289" s="39">
-        <f>IF($A289="","",IF($K289="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A289,Exceptions!$C$5:$C$104,$B289,Exceptions!$D$5:$D$104,$C289,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K289)))</f>
-        <v/>
-      </c>
-      <c r="M289" s="39">
-        <f>IF($A289="","",IF($H289="","Declaration missing",IF($H289="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R289),$R289&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H289="Fully Compliant",$J289&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N289" s="58">
-        <f>IF($A289="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C289,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O289" s="58">
-        <f>IF($A289="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C289,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P289" s="58">
-        <f>IF($A289="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C289,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q289" s="58">
-        <f>IF($A289="","",$A289&amp;"|"&amp;$B289&amp;"|"&amp;$C289)</f>
-        <v/>
-      </c>
-      <c r="R289" s="59" t="n"/>
-      <c r="S289" s="60" t="n"/>
-    </row>
-    <row r="290" ht="15" customHeight="1" s="34">
-      <c r="A290" s="54" t="n"/>
-      <c r="B290" s="54" t="n"/>
-      <c r="C290" s="54" t="n"/>
-      <c r="D290" s="55">
-        <f>IF($A290="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C290,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E290" s="55">
-        <f>IF($A290="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C290,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F290" s="56">
-        <f>IF($A290="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C290,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G290" s="57" t="n"/>
-      <c r="H290" s="54" t="n"/>
-      <c r="I290" s="54" t="n"/>
-      <c r="J290" s="39">
-        <f>IF($A290="","",IF($E290="Informational","GREEN",IF($G290="",IF($E290="Mandatory","RED","YELLOW"),IF($N290="Exact",IF(UPPER(TRIM($G290&amp;""))=UPPER(TRIM($F290&amp;"")),"GREEN",$P290),IF(NOT(ISNUMBER($G290)),$P290,IF($N290="Min",IF($G290&gt;=$F290,"GREEN",IF($G290&gt;=$F290-$O290,"YELLOW",$P290)),IF($N290="Max",IF($G290&lt;=$F290,"GREEN",IF($G290&lt;=$F290+$O290,"YELLOW",$P290)),IF($N290="Range",IF(ABS($G290-$F290)&lt;=$O290,"GREEN",$P290),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K290" s="39">
-        <f>IF($A290="","",IF($H290="Non-Compliant","RED",IF(AND(OR($H290="Alternative Offer",$H290="Partially Compliant"),$J290="GREEN"),"YELLOW",IF(AND($J290="GREEN",ISNUMBER($R290),$R290&lt;Baseline!$B$9),"YELLOW",$J290))))</f>
-        <v/>
-      </c>
-      <c r="L290" s="39">
-        <f>IF($A290="","",IF($K290="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A290,Exceptions!$C$5:$C$104,$B290,Exceptions!$D$5:$D$104,$C290,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K290)))</f>
-        <v/>
-      </c>
-      <c r="M290" s="39">
-        <f>IF($A290="","",IF($H290="","Declaration missing",IF($H290="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R290),$R290&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H290="Fully Compliant",$J290&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N290" s="58">
-        <f>IF($A290="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C290,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O290" s="58">
-        <f>IF($A290="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C290,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P290" s="58">
-        <f>IF($A290="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C290,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q290" s="58">
-        <f>IF($A290="","",$A290&amp;"|"&amp;$B290&amp;"|"&amp;$C290)</f>
-        <v/>
-      </c>
-      <c r="R290" s="59" t="n"/>
-      <c r="S290" s="60" t="n"/>
-    </row>
-    <row r="291" ht="15" customHeight="1" s="34">
-      <c r="A291" s="54" t="n"/>
-      <c r="B291" s="54" t="n"/>
-      <c r="C291" s="54" t="n"/>
-      <c r="D291" s="55">
-        <f>IF($A291="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C291,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E291" s="55">
-        <f>IF($A291="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C291,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F291" s="56">
-        <f>IF($A291="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C291,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G291" s="57" t="n"/>
-      <c r="H291" s="54" t="n"/>
-      <c r="I291" s="54" t="n"/>
-      <c r="J291" s="39">
-        <f>IF($A291="","",IF($E291="Informational","GREEN",IF($G291="",IF($E291="Mandatory","RED","YELLOW"),IF($N291="Exact",IF(UPPER(TRIM($G291&amp;""))=UPPER(TRIM($F291&amp;"")),"GREEN",$P291),IF(NOT(ISNUMBER($G291)),$P291,IF($N291="Min",IF($G291&gt;=$F291,"GREEN",IF($G291&gt;=$F291-$O291,"YELLOW",$P291)),IF($N291="Max",IF($G291&lt;=$F291,"GREEN",IF($G291&lt;=$F291+$O291,"YELLOW",$P291)),IF($N291="Range",IF(ABS($G291-$F291)&lt;=$O291,"GREEN",$P291),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K291" s="39">
-        <f>IF($A291="","",IF($H291="Non-Compliant","RED",IF(AND(OR($H291="Alternative Offer",$H291="Partially Compliant"),$J291="GREEN"),"YELLOW",IF(AND($J291="GREEN",ISNUMBER($R291),$R291&lt;Baseline!$B$9),"YELLOW",$J291))))</f>
-        <v/>
-      </c>
-      <c r="L291" s="39">
-        <f>IF($A291="","",IF($K291="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A291,Exceptions!$C$5:$C$104,$B291,Exceptions!$D$5:$D$104,$C291,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K291)))</f>
-        <v/>
-      </c>
-      <c r="M291" s="39">
-        <f>IF($A291="","",IF($H291="","Declaration missing",IF($H291="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R291),$R291&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H291="Fully Compliant",$J291&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N291" s="58">
-        <f>IF($A291="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C291,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O291" s="58">
-        <f>IF($A291="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C291,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P291" s="58">
-        <f>IF($A291="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C291,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q291" s="58">
-        <f>IF($A291="","",$A291&amp;"|"&amp;$B291&amp;"|"&amp;$C291)</f>
-        <v/>
-      </c>
-      <c r="R291" s="59" t="n"/>
-      <c r="S291" s="60" t="n"/>
-    </row>
-    <row r="292" ht="15" customHeight="1" s="34">
-      <c r="A292" s="54" t="n"/>
-      <c r="B292" s="54" t="n"/>
-      <c r="C292" s="54" t="n"/>
-      <c r="D292" s="55">
-        <f>IF($A292="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C292,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E292" s="55">
-        <f>IF($A292="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C292,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F292" s="56">
-        <f>IF($A292="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C292,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G292" s="57" t="n"/>
-      <c r="H292" s="54" t="n"/>
-      <c r="I292" s="54" t="n"/>
-      <c r="J292" s="39">
-        <f>IF($A292="","",IF($E292="Informational","GREEN",IF($G292="",IF($E292="Mandatory","RED","YELLOW"),IF($N292="Exact",IF(UPPER(TRIM($G292&amp;""))=UPPER(TRIM($F292&amp;"")),"GREEN",$P292),IF(NOT(ISNUMBER($G292)),$P292,IF($N292="Min",IF($G292&gt;=$F292,"GREEN",IF($G292&gt;=$F292-$O292,"YELLOW",$P292)),IF($N292="Max",IF($G292&lt;=$F292,"GREEN",IF($G292&lt;=$F292+$O292,"YELLOW",$P292)),IF($N292="Range",IF(ABS($G292-$F292)&lt;=$O292,"GREEN",$P292),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K292" s="39">
-        <f>IF($A292="","",IF($H292="Non-Compliant","RED",IF(AND(OR($H292="Alternative Offer",$H292="Partially Compliant"),$J292="GREEN"),"YELLOW",IF(AND($J292="GREEN",ISNUMBER($R292),$R292&lt;Baseline!$B$9),"YELLOW",$J292))))</f>
-        <v/>
-      </c>
-      <c r="L292" s="39">
-        <f>IF($A292="","",IF($K292="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A292,Exceptions!$C$5:$C$104,$B292,Exceptions!$D$5:$D$104,$C292,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K292)))</f>
-        <v/>
-      </c>
-      <c r="M292" s="39">
-        <f>IF($A292="","",IF($H292="","Declaration missing",IF($H292="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R292),$R292&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H292="Fully Compliant",$J292&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N292" s="58">
-        <f>IF($A292="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C292,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O292" s="58">
-        <f>IF($A292="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C292,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P292" s="58">
-        <f>IF($A292="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C292,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q292" s="58">
-        <f>IF($A292="","",$A292&amp;"|"&amp;$B292&amp;"|"&amp;$C292)</f>
-        <v/>
-      </c>
-      <c r="R292" s="59" t="n"/>
-      <c r="S292" s="60" t="n"/>
-    </row>
-    <row r="293" ht="15" customHeight="1" s="34">
-      <c r="A293" s="54" t="n"/>
-      <c r="B293" s="54" t="n"/>
-      <c r="C293" s="54" t="n"/>
-      <c r="D293" s="55">
-        <f>IF($A293="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C293,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E293" s="55">
-        <f>IF($A293="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C293,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F293" s="56">
-        <f>IF($A293="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C293,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G293" s="57" t="n"/>
-      <c r="H293" s="54" t="n"/>
-      <c r="I293" s="54" t="n"/>
-      <c r="J293" s="39">
-        <f>IF($A293="","",IF($E293="Informational","GREEN",IF($G293="",IF($E293="Mandatory","RED","YELLOW"),IF($N293="Exact",IF(UPPER(TRIM($G293&amp;""))=UPPER(TRIM($F293&amp;"")),"GREEN",$P293),IF(NOT(ISNUMBER($G293)),$P293,IF($N293="Min",IF($G293&gt;=$F293,"GREEN",IF($G293&gt;=$F293-$O293,"YELLOW",$P293)),IF($N293="Max",IF($G293&lt;=$F293,"GREEN",IF($G293&lt;=$F293+$O293,"YELLOW",$P293)),IF($N293="Range",IF(ABS($G293-$F293)&lt;=$O293,"GREEN",$P293),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K293" s="39">
-        <f>IF($A293="","",IF($H293="Non-Compliant","RED",IF(AND(OR($H293="Alternative Offer",$H293="Partially Compliant"),$J293="GREEN"),"YELLOW",IF(AND($J293="GREEN",ISNUMBER($R293),$R293&lt;Baseline!$B$9),"YELLOW",$J293))))</f>
-        <v/>
-      </c>
-      <c r="L293" s="39">
-        <f>IF($A293="","",IF($K293="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A293,Exceptions!$C$5:$C$104,$B293,Exceptions!$D$5:$D$104,$C293,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K293)))</f>
-        <v/>
-      </c>
-      <c r="M293" s="39">
-        <f>IF($A293="","",IF($H293="","Declaration missing",IF($H293="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R293),$R293&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H293="Fully Compliant",$J293&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N293" s="58">
-        <f>IF($A293="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C293,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O293" s="58">
-        <f>IF($A293="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C293,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P293" s="58">
-        <f>IF($A293="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C293,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q293" s="58">
-        <f>IF($A293="","",$A293&amp;"|"&amp;$B293&amp;"|"&amp;$C293)</f>
-        <v/>
-      </c>
-      <c r="R293" s="59" t="n"/>
-      <c r="S293" s="60" t="n"/>
-    </row>
-    <row r="294" ht="15" customHeight="1" s="34">
-      <c r="A294" s="54" t="n"/>
-      <c r="B294" s="54" t="n"/>
-      <c r="C294" s="54" t="n"/>
-      <c r="D294" s="55">
-        <f>IF($A294="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C294,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E294" s="55">
-        <f>IF($A294="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C294,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F294" s="56">
-        <f>IF($A294="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C294,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G294" s="57" t="n"/>
-      <c r="H294" s="54" t="n"/>
-      <c r="I294" s="54" t="n"/>
-      <c r="J294" s="39">
-        <f>IF($A294="","",IF($E294="Informational","GREEN",IF($G294="",IF($E294="Mandatory","RED","YELLOW"),IF($N294="Exact",IF(UPPER(TRIM($G294&amp;""))=UPPER(TRIM($F294&amp;"")),"GREEN",$P294),IF(NOT(ISNUMBER($G294)),$P294,IF($N294="Min",IF($G294&gt;=$F294,"GREEN",IF($G294&gt;=$F294-$O294,"YELLOW",$P294)),IF($N294="Max",IF($G294&lt;=$F294,"GREEN",IF($G294&lt;=$F294+$O294,"YELLOW",$P294)),IF($N294="Range",IF(ABS($G294-$F294)&lt;=$O294,"GREEN",$P294),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K294" s="39">
-        <f>IF($A294="","",IF($H294="Non-Compliant","RED",IF(AND(OR($H294="Alternative Offer",$H294="Partially Compliant"),$J294="GREEN"),"YELLOW",IF(AND($J294="GREEN",ISNUMBER($R294),$R294&lt;Baseline!$B$9),"YELLOW",$J294))))</f>
-        <v/>
-      </c>
-      <c r="L294" s="39">
-        <f>IF($A294="","",IF($K294="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A294,Exceptions!$C$5:$C$104,$B294,Exceptions!$D$5:$D$104,$C294,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K294)))</f>
-        <v/>
-      </c>
-      <c r="M294" s="39">
-        <f>IF($A294="","",IF($H294="","Declaration missing",IF($H294="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R294),$R294&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H294="Fully Compliant",$J294&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N294" s="58">
-        <f>IF($A294="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C294,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O294" s="58">
-        <f>IF($A294="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C294,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P294" s="58">
-        <f>IF($A294="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C294,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q294" s="58">
-        <f>IF($A294="","",$A294&amp;"|"&amp;$B294&amp;"|"&amp;$C294)</f>
-        <v/>
-      </c>
-      <c r="R294" s="59" t="n"/>
-      <c r="S294" s="60" t="n"/>
-    </row>
-    <row r="295" ht="15" customHeight="1" s="34">
-      <c r="A295" s="54" t="n"/>
-      <c r="B295" s="54" t="n"/>
-      <c r="C295" s="54" t="n"/>
-      <c r="D295" s="55">
-        <f>IF($A295="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C295,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E295" s="55">
-        <f>IF($A295="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C295,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F295" s="56">
-        <f>IF($A295="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C295,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G295" s="57" t="n"/>
-      <c r="H295" s="54" t="n"/>
-      <c r="I295" s="54" t="n"/>
-      <c r="J295" s="39">
-        <f>IF($A295="","",IF($E295="Informational","GREEN",IF($G295="",IF($E295="Mandatory","RED","YELLOW"),IF($N295="Exact",IF(UPPER(TRIM($G295&amp;""))=UPPER(TRIM($F295&amp;"")),"GREEN",$P295),IF(NOT(ISNUMBER($G295)),$P295,IF($N295="Min",IF($G295&gt;=$F295,"GREEN",IF($G295&gt;=$F295-$O295,"YELLOW",$P295)),IF($N295="Max",IF($G295&lt;=$F295,"GREEN",IF($G295&lt;=$F295+$O295,"YELLOW",$P295)),IF($N295="Range",IF(ABS($G295-$F295)&lt;=$O295,"GREEN",$P295),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K295" s="39">
-        <f>IF($A295="","",IF($H295="Non-Compliant","RED",IF(AND(OR($H295="Alternative Offer",$H295="Partially Compliant"),$J295="GREEN"),"YELLOW",IF(AND($J295="GREEN",ISNUMBER($R295),$R295&lt;Baseline!$B$9),"YELLOW",$J295))))</f>
-        <v/>
-      </c>
-      <c r="L295" s="39">
-        <f>IF($A295="","",IF($K295="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A295,Exceptions!$C$5:$C$104,$B295,Exceptions!$D$5:$D$104,$C295,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K295)))</f>
-        <v/>
-      </c>
-      <c r="M295" s="39">
-        <f>IF($A295="","",IF($H295="","Declaration missing",IF($H295="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R295),$R295&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H295="Fully Compliant",$J295&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N295" s="58">
-        <f>IF($A295="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C295,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O295" s="58">
-        <f>IF($A295="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C295,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P295" s="58">
-        <f>IF($A295="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C295,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q295" s="58">
-        <f>IF($A295="","",$A295&amp;"|"&amp;$B295&amp;"|"&amp;$C295)</f>
-        <v/>
-      </c>
-      <c r="R295" s="59" t="n"/>
-      <c r="S295" s="60" t="n"/>
-    </row>
-    <row r="296" ht="15" customHeight="1" s="34">
-      <c r="A296" s="54" t="n"/>
-      <c r="B296" s="54" t="n"/>
-      <c r="C296" s="54" t="n"/>
-      <c r="D296" s="55">
-        <f>IF($A296="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C296,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E296" s="55">
-        <f>IF($A296="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C296,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F296" s="56">
-        <f>IF($A296="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C296,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G296" s="57" t="n"/>
-      <c r="H296" s="54" t="n"/>
-      <c r="I296" s="54" t="n"/>
-      <c r="J296" s="39">
-        <f>IF($A296="","",IF($E296="Informational","GREEN",IF($G296="",IF($E296="Mandatory","RED","YELLOW"),IF($N296="Exact",IF(UPPER(TRIM($G296&amp;""))=UPPER(TRIM($F296&amp;"")),"GREEN",$P296),IF(NOT(ISNUMBER($G296)),$P296,IF($N296="Min",IF($G296&gt;=$F296,"GREEN",IF($G296&gt;=$F296-$O296,"YELLOW",$P296)),IF($N296="Max",IF($G296&lt;=$F296,"GREEN",IF($G296&lt;=$F296+$O296,"YELLOW",$P296)),IF($N296="Range",IF(ABS($G296-$F296)&lt;=$O296,"GREEN",$P296),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K296" s="39">
-        <f>IF($A296="","",IF($H296="Non-Compliant","RED",IF(AND(OR($H296="Alternative Offer",$H296="Partially Compliant"),$J296="GREEN"),"YELLOW",IF(AND($J296="GREEN",ISNUMBER($R296),$R296&lt;Baseline!$B$9),"YELLOW",$J296))))</f>
-        <v/>
-      </c>
-      <c r="L296" s="39">
-        <f>IF($A296="","",IF($K296="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A296,Exceptions!$C$5:$C$104,$B296,Exceptions!$D$5:$D$104,$C296,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K296)))</f>
-        <v/>
-      </c>
-      <c r="M296" s="39">
-        <f>IF($A296="","",IF($H296="","Declaration missing",IF($H296="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R296),$R296&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H296="Fully Compliant",$J296&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N296" s="58">
-        <f>IF($A296="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C296,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O296" s="58">
-        <f>IF($A296="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C296,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P296" s="58">
-        <f>IF($A296="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C296,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q296" s="58">
-        <f>IF($A296="","",$A296&amp;"|"&amp;$B296&amp;"|"&amp;$C296)</f>
-        <v/>
-      </c>
-      <c r="R296" s="59" t="n"/>
-      <c r="S296" s="60" t="n"/>
-    </row>
-    <row r="297" ht="15" customHeight="1" s="34">
-      <c r="A297" s="54" t="n"/>
-      <c r="B297" s="54" t="n"/>
-      <c r="C297" s="54" t="n"/>
-      <c r="D297" s="55">
-        <f>IF($A297="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C297,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E297" s="55">
-        <f>IF($A297="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C297,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F297" s="56">
-        <f>IF($A297="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C297,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G297" s="57" t="n"/>
-      <c r="H297" s="54" t="n"/>
-      <c r="I297" s="54" t="n"/>
-      <c r="J297" s="39">
-        <f>IF($A297="","",IF($E297="Informational","GREEN",IF($G297="",IF($E297="Mandatory","RED","YELLOW"),IF($N297="Exact",IF(UPPER(TRIM($G297&amp;""))=UPPER(TRIM($F297&amp;"")),"GREEN",$P297),IF(NOT(ISNUMBER($G297)),$P297,IF($N297="Min",IF($G297&gt;=$F297,"GREEN",IF($G297&gt;=$F297-$O297,"YELLOW",$P297)),IF($N297="Max",IF($G297&lt;=$F297,"GREEN",IF($G297&lt;=$F297+$O297,"YELLOW",$P297)),IF($N297="Range",IF(ABS($G297-$F297)&lt;=$O297,"GREEN",$P297),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K297" s="39">
-        <f>IF($A297="","",IF($H297="Non-Compliant","RED",IF(AND(OR($H297="Alternative Offer",$H297="Partially Compliant"),$J297="GREEN"),"YELLOW",IF(AND($J297="GREEN",ISNUMBER($R297),$R297&lt;Baseline!$B$9),"YELLOW",$J297))))</f>
-        <v/>
-      </c>
-      <c r="L297" s="39">
-        <f>IF($A297="","",IF($K297="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A297,Exceptions!$C$5:$C$104,$B297,Exceptions!$D$5:$D$104,$C297,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K297)))</f>
-        <v/>
-      </c>
-      <c r="M297" s="39">
-        <f>IF($A297="","",IF($H297="","Declaration missing",IF($H297="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R297),$R297&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H297="Fully Compliant",$J297&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N297" s="58">
-        <f>IF($A297="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C297,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O297" s="58">
-        <f>IF($A297="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C297,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P297" s="58">
-        <f>IF($A297="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C297,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q297" s="58">
-        <f>IF($A297="","",$A297&amp;"|"&amp;$B297&amp;"|"&amp;$C297)</f>
-        <v/>
-      </c>
-      <c r="R297" s="59" t="n"/>
-      <c r="S297" s="60" t="n"/>
-    </row>
-    <row r="298" ht="15" customHeight="1" s="34">
-      <c r="A298" s="54" t="n"/>
-      <c r="B298" s="54" t="n"/>
-      <c r="C298" s="54" t="n"/>
-      <c r="D298" s="55">
-        <f>IF($A298="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C298,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E298" s="55">
-        <f>IF($A298="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C298,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F298" s="56">
-        <f>IF($A298="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C298,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G298" s="57" t="n"/>
-      <c r="H298" s="54" t="n"/>
-      <c r="I298" s="54" t="n"/>
-      <c r="J298" s="39">
-        <f>IF($A298="","",IF($E298="Informational","GREEN",IF($G298="",IF($E298="Mandatory","RED","YELLOW"),IF($N298="Exact",IF(UPPER(TRIM($G298&amp;""))=UPPER(TRIM($F298&amp;"")),"GREEN",$P298),IF(NOT(ISNUMBER($G298)),$P298,IF($N298="Min",IF($G298&gt;=$F298,"GREEN",IF($G298&gt;=$F298-$O298,"YELLOW",$P298)),IF($N298="Max",IF($G298&lt;=$F298,"GREEN",IF($G298&lt;=$F298+$O298,"YELLOW",$P298)),IF($N298="Range",IF(ABS($G298-$F298)&lt;=$O298,"GREEN",$P298),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K298" s="39">
-        <f>IF($A298="","",IF($H298="Non-Compliant","RED",IF(AND(OR($H298="Alternative Offer",$H298="Partially Compliant"),$J298="GREEN"),"YELLOW",IF(AND($J298="GREEN",ISNUMBER($R298),$R298&lt;Baseline!$B$9),"YELLOW",$J298))))</f>
-        <v/>
-      </c>
-      <c r="L298" s="39">
-        <f>IF($A298="","",IF($K298="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A298,Exceptions!$C$5:$C$104,$B298,Exceptions!$D$5:$D$104,$C298,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K298)))</f>
-        <v/>
-      </c>
-      <c r="M298" s="39">
-        <f>IF($A298="","",IF($H298="","Declaration missing",IF($H298="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R298),$R298&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H298="Fully Compliant",$J298&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N298" s="58">
-        <f>IF($A298="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C298,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O298" s="58">
-        <f>IF($A298="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C298,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P298" s="58">
-        <f>IF($A298="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C298,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q298" s="58">
-        <f>IF($A298="","",$A298&amp;"|"&amp;$B298&amp;"|"&amp;$C298)</f>
-        <v/>
-      </c>
-      <c r="R298" s="59" t="n"/>
-      <c r="S298" s="60" t="n"/>
-    </row>
-    <row r="299" ht="15" customHeight="1" s="34">
-      <c r="A299" s="54" t="n"/>
-      <c r="B299" s="54" t="n"/>
-      <c r="C299" s="54" t="n"/>
-      <c r="D299" s="55">
-        <f>IF($A299="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C299,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E299" s="55">
-        <f>IF($A299="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C299,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F299" s="56">
-        <f>IF($A299="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C299,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G299" s="57" t="n"/>
-      <c r="H299" s="54" t="n"/>
-      <c r="I299" s="54" t="n"/>
-      <c r="J299" s="39">
-        <f>IF($A299="","",IF($E299="Informational","GREEN",IF($G299="",IF($E299="Mandatory","RED","YELLOW"),IF($N299="Exact",IF(UPPER(TRIM($G299&amp;""))=UPPER(TRIM($F299&amp;"")),"GREEN",$P299),IF(NOT(ISNUMBER($G299)),$P299,IF($N299="Min",IF($G299&gt;=$F299,"GREEN",IF($G299&gt;=$F299-$O299,"YELLOW",$P299)),IF($N299="Max",IF($G299&lt;=$F299,"GREEN",IF($G299&lt;=$F299+$O299,"YELLOW",$P299)),IF($N299="Range",IF(ABS($G299-$F299)&lt;=$O299,"GREEN",$P299),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K299" s="39">
-        <f>IF($A299="","",IF($H299="Non-Compliant","RED",IF(AND(OR($H299="Alternative Offer",$H299="Partially Compliant"),$J299="GREEN"),"YELLOW",IF(AND($J299="GREEN",ISNUMBER($R299),$R299&lt;Baseline!$B$9),"YELLOW",$J299))))</f>
-        <v/>
-      </c>
-      <c r="L299" s="39">
-        <f>IF($A299="","",IF($K299="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A299,Exceptions!$C$5:$C$104,$B299,Exceptions!$D$5:$D$104,$C299,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K299)))</f>
-        <v/>
-      </c>
-      <c r="M299" s="39">
-        <f>IF($A299="","",IF($H299="","Declaration missing",IF($H299="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R299),$R299&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H299="Fully Compliant",$J299&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N299" s="58">
-        <f>IF($A299="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C299,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O299" s="58">
-        <f>IF($A299="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C299,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P299" s="58">
-        <f>IF($A299="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C299,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q299" s="58">
-        <f>IF($A299="","",$A299&amp;"|"&amp;$B299&amp;"|"&amp;$C299)</f>
-        <v/>
-      </c>
-      <c r="R299" s="59" t="n"/>
-      <c r="S299" s="60" t="n"/>
-    </row>
-    <row r="300" ht="15" customHeight="1" s="34">
-      <c r="A300" s="54" t="n"/>
-      <c r="B300" s="54" t="n"/>
-      <c r="C300" s="54" t="n"/>
-      <c r="D300" s="55">
-        <f>IF($A300="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C300,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E300" s="55">
-        <f>IF($A300="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C300,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F300" s="56">
-        <f>IF($A300="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C300,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G300" s="57" t="n"/>
-      <c r="H300" s="54" t="n"/>
-      <c r="I300" s="54" t="n"/>
-      <c r="J300" s="39">
-        <f>IF($A300="","",IF($E300="Informational","GREEN",IF($G300="",IF($E300="Mandatory","RED","YELLOW"),IF($N300="Exact",IF(UPPER(TRIM($G300&amp;""))=UPPER(TRIM($F300&amp;"")),"GREEN",$P300),IF(NOT(ISNUMBER($G300)),$P300,IF($N300="Min",IF($G300&gt;=$F300,"GREEN",IF($G300&gt;=$F300-$O300,"YELLOW",$P300)),IF($N300="Max",IF($G300&lt;=$F300,"GREEN",IF($G300&lt;=$F300+$O300,"YELLOW",$P300)),IF($N300="Range",IF(ABS($G300-$F300)&lt;=$O300,"GREEN",$P300),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K300" s="39">
-        <f>IF($A300="","",IF($H300="Non-Compliant","RED",IF(AND(OR($H300="Alternative Offer",$H300="Partially Compliant"),$J300="GREEN"),"YELLOW",IF(AND($J300="GREEN",ISNUMBER($R300),$R300&lt;Baseline!$B$9),"YELLOW",$J300))))</f>
-        <v/>
-      </c>
-      <c r="L300" s="39">
-        <f>IF($A300="","",IF($K300="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A300,Exceptions!$C$5:$C$104,$B300,Exceptions!$D$5:$D$104,$C300,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K300)))</f>
-        <v/>
-      </c>
-      <c r="M300" s="39">
-        <f>IF($A300="","",IF($H300="","Declaration missing",IF($H300="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R300),$R300&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H300="Fully Compliant",$J300&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N300" s="58">
-        <f>IF($A300="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C300,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O300" s="58">
-        <f>IF($A300="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C300,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P300" s="58">
-        <f>IF($A300="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C300,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q300" s="58">
-        <f>IF($A300="","",$A300&amp;"|"&amp;$B300&amp;"|"&amp;$C300)</f>
-        <v/>
-      </c>
-      <c r="R300" s="59" t="n"/>
-      <c r="S300" s="60" t="n"/>
-    </row>
-    <row r="301" ht="15" customHeight="1" s="34">
-      <c r="A301" s="54" t="n"/>
-      <c r="B301" s="54" t="n"/>
-      <c r="C301" s="54" t="n"/>
-      <c r="D301" s="55">
-        <f>IF($A301="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C301,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E301" s="55">
-        <f>IF($A301="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C301,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F301" s="56">
-        <f>IF($A301="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C301,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G301" s="57" t="n"/>
-      <c r="H301" s="54" t="n"/>
-      <c r="I301" s="54" t="n"/>
-      <c r="J301" s="39">
-        <f>IF($A301="","",IF($E301="Informational","GREEN",IF($G301="",IF($E301="Mandatory","RED","YELLOW"),IF($N301="Exact",IF(UPPER(TRIM($G301&amp;""))=UPPER(TRIM($F301&amp;"")),"GREEN",$P301),IF(NOT(ISNUMBER($G301)),$P301,IF($N301="Min",IF($G301&gt;=$F301,"GREEN",IF($G301&gt;=$F301-$O301,"YELLOW",$P301)),IF($N301="Max",IF($G301&lt;=$F301,"GREEN",IF($G301&lt;=$F301+$O301,"YELLOW",$P301)),IF($N301="Range",IF(ABS($G301-$F301)&lt;=$O301,"GREEN",$P301),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K301" s="39">
-        <f>IF($A301="","",IF($H301="Non-Compliant","RED",IF(AND(OR($H301="Alternative Offer",$H301="Partially Compliant"),$J301="GREEN"),"YELLOW",IF(AND($J301="GREEN",ISNUMBER($R301),$R301&lt;Baseline!$B$9),"YELLOW",$J301))))</f>
-        <v/>
-      </c>
-      <c r="L301" s="39">
-        <f>IF($A301="","",IF($K301="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A301,Exceptions!$C$5:$C$104,$B301,Exceptions!$D$5:$D$104,$C301,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K301)))</f>
-        <v/>
-      </c>
-      <c r="M301" s="39">
-        <f>IF($A301="","",IF($H301="","Declaration missing",IF($H301="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R301),$R301&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H301="Fully Compliant",$J301&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N301" s="58">
-        <f>IF($A301="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C301,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O301" s="58">
-        <f>IF($A301="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C301,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P301" s="58">
-        <f>IF($A301="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C301,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q301" s="58">
-        <f>IF($A301="","",$A301&amp;"|"&amp;$B301&amp;"|"&amp;$C301)</f>
-        <v/>
-      </c>
-      <c r="R301" s="59" t="n"/>
-      <c r="S301" s="60" t="n"/>
-    </row>
-    <row r="302" ht="15" customHeight="1" s="34">
-      <c r="A302" s="54" t="n"/>
-      <c r="B302" s="54" t="n"/>
-      <c r="C302" s="54" t="n"/>
-      <c r="D302" s="55">
-        <f>IF($A302="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C302,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E302" s="55">
-        <f>IF($A302="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C302,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F302" s="56">
-        <f>IF($A302="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C302,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G302" s="57" t="n"/>
-      <c r="H302" s="54" t="n"/>
-      <c r="I302" s="54" t="n"/>
-      <c r="J302" s="39">
-        <f>IF($A302="","",IF($E302="Informational","GREEN",IF($G302="",IF($E302="Mandatory","RED","YELLOW"),IF($N302="Exact",IF(UPPER(TRIM($G302&amp;""))=UPPER(TRIM($F302&amp;"")),"GREEN",$P302),IF(NOT(ISNUMBER($G302)),$P302,IF($N302="Min",IF($G302&gt;=$F302,"GREEN",IF($G302&gt;=$F302-$O302,"YELLOW",$P302)),IF($N302="Max",IF($G302&lt;=$F302,"GREEN",IF($G302&lt;=$F302+$O302,"YELLOW",$P302)),IF($N302="Range",IF(ABS($G302-$F302)&lt;=$O302,"GREEN",$P302),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K302" s="39">
-        <f>IF($A302="","",IF($H302="Non-Compliant","RED",IF(AND(OR($H302="Alternative Offer",$H302="Partially Compliant"),$J302="GREEN"),"YELLOW",IF(AND($J302="GREEN",ISNUMBER($R302),$R302&lt;Baseline!$B$9),"YELLOW",$J302))))</f>
-        <v/>
-      </c>
-      <c r="L302" s="39">
-        <f>IF($A302="","",IF($K302="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A302,Exceptions!$C$5:$C$104,$B302,Exceptions!$D$5:$D$104,$C302,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K302)))</f>
-        <v/>
-      </c>
-      <c r="M302" s="39">
-        <f>IF($A302="","",IF($H302="","Declaration missing",IF($H302="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R302),$R302&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H302="Fully Compliant",$J302&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N302" s="58">
-        <f>IF($A302="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C302,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O302" s="58">
-        <f>IF($A302="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C302,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P302" s="58">
-        <f>IF($A302="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C302,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q302" s="58">
-        <f>IF($A302="","",$A302&amp;"|"&amp;$B302&amp;"|"&amp;$C302)</f>
-        <v/>
-      </c>
-      <c r="R302" s="59" t="n"/>
-      <c r="S302" s="60" t="n"/>
-    </row>
-    <row r="303" ht="15" customHeight="1" s="34">
-      <c r="A303" s="54" t="n"/>
-      <c r="B303" s="54" t="n"/>
-      <c r="C303" s="54" t="n"/>
-      <c r="D303" s="55">
-        <f>IF($A303="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C303,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E303" s="55">
-        <f>IF($A303="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C303,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F303" s="56">
-        <f>IF($A303="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C303,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G303" s="57" t="n"/>
-      <c r="H303" s="54" t="n"/>
-      <c r="I303" s="54" t="n"/>
-      <c r="J303" s="39">
-        <f>IF($A303="","",IF($E303="Informational","GREEN",IF($G303="",IF($E303="Mandatory","RED","YELLOW"),IF($N303="Exact",IF(UPPER(TRIM($G303&amp;""))=UPPER(TRIM($F303&amp;"")),"GREEN",$P303),IF(NOT(ISNUMBER($G303)),$P303,IF($N303="Min",IF($G303&gt;=$F303,"GREEN",IF($G303&gt;=$F303-$O303,"YELLOW",$P303)),IF($N303="Max",IF($G303&lt;=$F303,"GREEN",IF($G303&lt;=$F303+$O303,"YELLOW",$P303)),IF($N303="Range",IF(ABS($G303-$F303)&lt;=$O303,"GREEN",$P303),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K303" s="39">
-        <f>IF($A303="","",IF($H303="Non-Compliant","RED",IF(AND(OR($H303="Alternative Offer",$H303="Partially Compliant"),$J303="GREEN"),"YELLOW",IF(AND($J303="GREEN",ISNUMBER($R303),$R303&lt;Baseline!$B$9),"YELLOW",$J303))))</f>
-        <v/>
-      </c>
-      <c r="L303" s="39">
-        <f>IF($A303="","",IF($K303="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A303,Exceptions!$C$5:$C$104,$B303,Exceptions!$D$5:$D$104,$C303,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K303)))</f>
-        <v/>
-      </c>
-      <c r="M303" s="39">
-        <f>IF($A303="","",IF($H303="","Declaration missing",IF($H303="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R303),$R303&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H303="Fully Compliant",$J303&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N303" s="58">
-        <f>IF($A303="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C303,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O303" s="58">
-        <f>IF($A303="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C303,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P303" s="58">
-        <f>IF($A303="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C303,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q303" s="58">
-        <f>IF($A303="","",$A303&amp;"|"&amp;$B303&amp;"|"&amp;$C303)</f>
-        <v/>
-      </c>
-      <c r="R303" s="59" t="n"/>
-      <c r="S303" s="60" t="n"/>
-    </row>
-    <row r="304" ht="15" customHeight="1" s="34">
-      <c r="A304" s="54" t="n"/>
-      <c r="B304" s="54" t="n"/>
-      <c r="C304" s="54" t="n"/>
-      <c r="D304" s="55">
-        <f>IF($A304="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C304,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
-        <v/>
-      </c>
-      <c r="E304" s="55">
-        <f>IF($A304="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C304,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F304" s="56">
-        <f>IF($A304="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C304,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G304" s="57" t="n"/>
-      <c r="H304" s="54" t="n"/>
-      <c r="I304" s="54" t="n"/>
-      <c r="J304" s="39">
-        <f>IF($A304="","",IF($E304="Informational","GREEN",IF($G304="",IF($E304="Mandatory","RED","YELLOW"),IF($N304="Exact",IF(UPPER(TRIM($G304&amp;""))=UPPER(TRIM($F304&amp;"")),"GREEN",$P304),IF(NOT(ISNUMBER($G304)),$P304,IF($N304="Min",IF($G304&gt;=$F304,"GREEN",IF($G304&gt;=$F304-$O304,"YELLOW",$P304)),IF($N304="Max",IF($G304&lt;=$F304,"GREEN",IF($G304&lt;=$F304+$O304,"YELLOW",$P304)),IF($N304="Range",IF(ABS($G304-$F304)&lt;=$O304,"GREEN",$P304),"CHECK RULE"))))))))</f>
-        <v/>
-      </c>
-      <c r="K304" s="39">
-        <f>IF($A304="","",IF($H304="Non-Compliant","RED",IF(AND(OR($H304="Alternative Offer",$H304="Partially Compliant"),$J304="GREEN"),"YELLOW",IF(AND($J304="GREEN",ISNUMBER($R304),$R304&lt;Baseline!$B$9),"YELLOW",$J304))))</f>
-        <v/>
-      </c>
-      <c r="L304" s="39">
-        <f>IF($A304="","",IF($K304="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A304,Exceptions!$C$5:$C$104,$B304,Exceptions!$D$5:$D$104,$C304,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K304)))</f>
-        <v/>
-      </c>
-      <c r="M304" s="39">
-        <f>IF($A304="","",IF($H304="","Declaration missing",IF($H304="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R304),$R304&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H304="Fully Compliant",$J304&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
-        <v/>
-      </c>
-      <c r="N304" s="58">
-        <f>IF($A304="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C304,Baseline!$A$20:$A$49,0)),""))</f>
-        <v/>
-      </c>
-      <c r="O304" s="58">
-        <f>IF($A304="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C304,Baseline!$A$20:$A$49,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P304" s="58">
-        <f>IF($A304="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C304,Baseline!$A$20:$A$49,0)),"RED"))</f>
-        <v/>
-      </c>
-      <c r="Q304" s="58">
-        <f>IF($A304="","",$A304&amp;"|"&amp;$B304&amp;"|"&amp;$C304)</f>
-        <v/>
-      </c>
-      <c r="R304" s="59" t="n"/>
-      <c r="S304" s="60" t="n"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="J5:L304">
+  <conditionalFormatting sqref="J5:L204">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
       <formula>"RED"</formula>
     </cfRule>
@@ -18784,7 +13384,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H5:H204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Fully Compliant,Partially Compliant,Non-Compliant,Alternative Offer,Not Stated"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -21299,7 +15899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="33" min="1" max="1"/>
@@ -21307,15 +15907,6 @@
     <col width="13" customWidth="1" style="33" min="3" max="3"/>
     <col width="22" customWidth="1" style="33" min="4" max="4"/>
     <col width="13" customWidth="1" style="33" min="5" max="12"/>
-    <col width="13" customWidth="1" style="34" min="6" max="6"/>
-    <col width="13" customWidth="1" style="34" min="7" max="7"/>
-    <col width="13" customWidth="1" style="34" min="8" max="8"/>
-    <col width="13" customWidth="1" style="34" min="9" max="9"/>
-    <col width="13" customWidth="1" style="34" min="10" max="10"/>
-    <col width="13" customWidth="1" style="34" min="11" max="11"/>
-    <col width="13" customWidth="1" style="34" min="12" max="12"/>
-    <col width="13" customWidth="1" style="34" min="13" max="13"/>
-    <col width="13" customWidth="1" style="34" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" s="34">
@@ -21335,8 +15926,6 @@
       <c r="J1" s="36" t="n"/>
       <c r="K1" s="36" t="n"/>
       <c r="L1" s="36" t="n"/>
-      <c r="M1" s="36" t="n"/>
-      <c r="N1" s="36" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="34">
       <c r="A2" s="36" t="n"/>
@@ -21351,8 +15940,6 @@
       <c r="J2" s="36" t="n"/>
       <c r="K2" s="36" t="n"/>
       <c r="L2" s="36" t="n"/>
-      <c r="M2" s="36" t="n"/>
-      <c r="N2" s="36" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="34">
       <c r="A3" s="36" t="n"/>
@@ -21367,8 +15954,6 @@
       <c r="J3" s="36" t="n"/>
       <c r="K3" s="36" t="n"/>
       <c r="L3" s="36" t="n"/>
-      <c r="M3" s="36" t="n"/>
-      <c r="N3" s="36" t="n"/>
     </row>
     <row r="4" ht="27.75" customHeight="1" s="34">
       <c r="A4" s="36" t="n"/>
@@ -21387,8 +15972,6 @@
       <c r="J4" s="64" t="n"/>
       <c r="K4" s="64" t="n"/>
       <c r="L4" s="64" t="n"/>
-      <c r="M4" s="64" t="n"/>
-      <c r="N4" s="64" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="34">
       <c r="A5" s="36" t="n"/>
@@ -21400,43 +15983,35 @@
         </is>
       </c>
       <c r="E5" s="65">
-        <f>IF(E4="","",IF(COUNTIF(Submissions!$A$5:$A$304,E4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=E4)*Submissions!$B$5:$B$304))))</f>
+        <f>IF(E4="","",IF(COUNTIF(Submissions!$A$5:$A$204,E4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=E4)*Submissions!$B$5:$B$204))))</f>
         <v/>
       </c>
       <c r="F5" s="65">
-        <f>IF(F4="","",IF(COUNTIF(Submissions!$A$5:$A$304,F4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=F4)*Submissions!$B$5:$B$304))))</f>
+        <f>IF(F4="","",IF(COUNTIF(Submissions!$A$5:$A$204,F4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=F4)*Submissions!$B$5:$B$204))))</f>
         <v/>
       </c>
       <c r="G5" s="65">
-        <f>IF(G4="","",IF(COUNTIF(Submissions!$A$5:$A$304,G4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=G4)*Submissions!$B$5:$B$304))))</f>
+        <f>IF(G4="","",IF(COUNTIF(Submissions!$A$5:$A$204,G4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=G4)*Submissions!$B$5:$B$204))))</f>
         <v/>
       </c>
       <c r="H5" s="65">
-        <f>IF(H4="","",IF(COUNTIF(Submissions!$A$5:$A$304,H4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=H4)*Submissions!$B$5:$B$304))))</f>
+        <f>IF(H4="","",IF(COUNTIF(Submissions!$A$5:$A$204,H4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=H4)*Submissions!$B$5:$B$204))))</f>
         <v/>
       </c>
       <c r="I5" s="65">
-        <f>IF(I4="","",IF(COUNTIF(Submissions!$A$5:$A$304,I4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=I4)*Submissions!$B$5:$B$304))))</f>
+        <f>IF(I4="","",IF(COUNTIF(Submissions!$A$5:$A$204,I4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=I4)*Submissions!$B$5:$B$204))))</f>
         <v/>
       </c>
       <c r="J5" s="65">
-        <f>IF(J4="","",IF(COUNTIF(Submissions!$A$5:$A$304,J4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=J4)*Submissions!$B$5:$B$304))))</f>
+        <f>IF(J4="","",IF(COUNTIF(Submissions!$A$5:$A$204,J4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=J4)*Submissions!$B$5:$B$204))))</f>
         <v/>
       </c>
       <c r="K5" s="65">
-        <f>IF(K4="","",IF(COUNTIF(Submissions!$A$5:$A$304,K4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=K4)*Submissions!$B$5:$B$304))))</f>
+        <f>IF(K4="","",IF(COUNTIF(Submissions!$A$5:$A$204,K4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=K4)*Submissions!$B$5:$B$204))))</f>
         <v/>
       </c>
       <c r="L5" s="65">
-        <f>IF(L4="","",IF(COUNTIF(Submissions!$A$5:$A$304,L4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=L4)*Submissions!$B$5:$B$304))))</f>
-        <v/>
-      </c>
-      <c r="M5" s="65">
-        <f>IF(M4="","",IF(COUNTIF(Submissions!$A$5:$A$304,M4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=M4)*Submissions!$B$5:$B$304))))</f>
-        <v/>
-      </c>
-      <c r="N5" s="65">
-        <f>IF(N4="","",IF(COUNTIF(Submissions!$A$5:$A$304,N4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=N4)*Submissions!$B$5:$B$304))))</f>
+        <f>IF(L4="","",IF(COUNTIF(Submissions!$A$5:$A$204,L4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=L4)*Submissions!$B$5:$B$204))))</f>
         <v/>
       </c>
     </row>
@@ -21497,16 +16072,6 @@
         </is>
       </c>
       <c r="L6" s="48" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="M6" s="48" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="N6" s="48" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -21530,43 +16095,35 @@
         <v/>
       </c>
       <c r="E7" s="68">
-        <f>IF(OR($A7="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F7" s="68">
-        <f>IF(OR($A7="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G7" s="68">
-        <f>IF(OR($A7="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H7" s="68">
-        <f>IF(OR($A7="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I7" s="68">
-        <f>IF(OR($A7="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J7" s="68">
-        <f>IF(OR($A7="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K7" s="68">
-        <f>IF(OR($A7="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L7" s="68">
-        <f>IF(OR($A7="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M7" s="68">
-        <f>IF(OR($A7="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N7" s="68">
-        <f>IF(OR($A7="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -21588,43 +16145,35 @@
         <v/>
       </c>
       <c r="E8" s="68">
-        <f>IF(OR($A8="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F8" s="68">
-        <f>IF(OR($A8="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G8" s="68">
-        <f>IF(OR($A8="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H8" s="68">
-        <f>IF(OR($A8="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I8" s="68">
-        <f>IF(OR($A8="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J8" s="68">
-        <f>IF(OR($A8="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K8" s="68">
-        <f>IF(OR($A8="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L8" s="68">
-        <f>IF(OR($A8="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M8" s="68">
-        <f>IF(OR($A8="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N8" s="68">
-        <f>IF(OR($A8="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -21646,43 +16195,35 @@
         <v/>
       </c>
       <c r="E9" s="68">
-        <f>IF(OR($A9="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F9" s="68">
-        <f>IF(OR($A9="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G9" s="68">
-        <f>IF(OR($A9="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H9" s="68">
-        <f>IF(OR($A9="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I9" s="68">
-        <f>IF(OR($A9="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J9" s="68">
-        <f>IF(OR($A9="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K9" s="68">
-        <f>IF(OR($A9="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L9" s="68">
-        <f>IF(OR($A9="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M9" s="68">
-        <f>IF(OR($A9="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N9" s="68">
-        <f>IF(OR($A9="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -21704,43 +16245,35 @@
         <v/>
       </c>
       <c r="E10" s="68">
-        <f>IF(OR($A10="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F10" s="68">
-        <f>IF(OR($A10="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G10" s="68">
-        <f>IF(OR($A10="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
-        <f>IF(OR($A10="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I10" s="68">
-        <f>IF(OR($A10="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J10" s="68">
-        <f>IF(OR($A10="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K10" s="68">
-        <f>IF(OR($A10="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L10" s="68">
-        <f>IF(OR($A10="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M10" s="68">
-        <f>IF(OR($A10="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N10" s="68">
-        <f>IF(OR($A10="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -21762,43 +16295,35 @@
         <v/>
       </c>
       <c r="E11" s="68">
-        <f>IF(OR($A11="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F11" s="68">
-        <f>IF(OR($A11="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G11" s="68">
-        <f>IF(OR($A11="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
-        <f>IF(OR($A11="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I11" s="68">
-        <f>IF(OR($A11="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J11" s="68">
-        <f>IF(OR($A11="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K11" s="68">
-        <f>IF(OR($A11="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L11" s="68">
-        <f>IF(OR($A11="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M11" s="68">
-        <f>IF(OR($A11="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N11" s="68">
-        <f>IF(OR($A11="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -21820,43 +16345,35 @@
         <v/>
       </c>
       <c r="E12" s="68">
-        <f>IF(OR($A12="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F12" s="68">
-        <f>IF(OR($A12="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G12" s="68">
-        <f>IF(OR($A12="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
-        <f>IF(OR($A12="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I12" s="68">
-        <f>IF(OR($A12="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J12" s="68">
-        <f>IF(OR($A12="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K12" s="68">
-        <f>IF(OR($A12="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L12" s="68">
-        <f>IF(OR($A12="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M12" s="68">
-        <f>IF(OR($A12="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N12" s="68">
-        <f>IF(OR($A12="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -21878,43 +16395,35 @@
         <v/>
       </c>
       <c r="E13" s="68">
-        <f>IF(OR($A13="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F13" s="68">
-        <f>IF(OR($A13="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G13" s="68">
-        <f>IF(OR($A13="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
-        <f>IF(OR($A13="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I13" s="68">
-        <f>IF(OR($A13="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J13" s="68">
-        <f>IF(OR($A13="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K13" s="68">
-        <f>IF(OR($A13="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L13" s="68">
-        <f>IF(OR($A13="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M13" s="68">
-        <f>IF(OR($A13="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N13" s="68">
-        <f>IF(OR($A13="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -21936,43 +16445,35 @@
         <v/>
       </c>
       <c r="E14" s="68">
-        <f>IF(OR($A14="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F14" s="68">
-        <f>IF(OR($A14="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G14" s="68">
-        <f>IF(OR($A14="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
-        <f>IF(OR($A14="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I14" s="68">
-        <f>IF(OR($A14="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J14" s="68">
-        <f>IF(OR($A14="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K14" s="68">
-        <f>IF(OR($A14="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L14" s="68">
-        <f>IF(OR($A14="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M14" s="68">
-        <f>IF(OR($A14="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N14" s="68">
-        <f>IF(OR($A14="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -21994,43 +16495,35 @@
         <v/>
       </c>
       <c r="E15" s="68">
-        <f>IF(OR($A15="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F15" s="68">
-        <f>IF(OR($A15="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G15" s="68">
-        <f>IF(OR($A15="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
-        <f>IF(OR($A15="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I15" s="68">
-        <f>IF(OR($A15="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J15" s="68">
-        <f>IF(OR($A15="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K15" s="68">
-        <f>IF(OR($A15="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L15" s="68">
-        <f>IF(OR($A15="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M15" s="68">
-        <f>IF(OR($A15="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N15" s="68">
-        <f>IF(OR($A15="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22052,43 +16545,35 @@
         <v/>
       </c>
       <c r="E16" s="68">
-        <f>IF(OR($A16="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F16" s="68">
-        <f>IF(OR($A16="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G16" s="68">
-        <f>IF(OR($A16="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
-        <f>IF(OR($A16="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I16" s="68">
-        <f>IF(OR($A16="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J16" s="68">
-        <f>IF(OR($A16="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K16" s="68">
-        <f>IF(OR($A16="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L16" s="68">
-        <f>IF(OR($A16="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M16" s="68">
-        <f>IF(OR($A16="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N16" s="68">
-        <f>IF(OR($A16="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22110,43 +16595,35 @@
         <v/>
       </c>
       <c r="E17" s="68">
-        <f>IF(OR($A17="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F17" s="68">
-        <f>IF(OR($A17="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G17" s="68">
-        <f>IF(OR($A17="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
-        <f>IF(OR($A17="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I17" s="68">
-        <f>IF(OR($A17="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J17" s="68">
-        <f>IF(OR($A17="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K17" s="68">
-        <f>IF(OR($A17="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L17" s="68">
-        <f>IF(OR($A17="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M17" s="68">
-        <f>IF(OR($A17="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N17" s="68">
-        <f>IF(OR($A17="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22168,43 +16645,35 @@
         <v/>
       </c>
       <c r="E18" s="68">
-        <f>IF(OR($A18="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F18" s="68">
-        <f>IF(OR($A18="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G18" s="68">
-        <f>IF(OR($A18="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
-        <f>IF(OR($A18="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I18" s="68">
-        <f>IF(OR($A18="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J18" s="68">
-        <f>IF(OR($A18="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K18" s="68">
-        <f>IF(OR($A18="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L18" s="68">
-        <f>IF(OR($A18="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M18" s="68">
-        <f>IF(OR($A18="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N18" s="68">
-        <f>IF(OR($A18="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22226,43 +16695,35 @@
         <v/>
       </c>
       <c r="E19" s="68">
-        <f>IF(OR($A19="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F19" s="68">
-        <f>IF(OR($A19="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G19" s="68">
-        <f>IF(OR($A19="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
-        <f>IF(OR($A19="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I19" s="68">
-        <f>IF(OR($A19="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J19" s="68">
-        <f>IF(OR($A19="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K19" s="68">
-        <f>IF(OR($A19="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L19" s="68">
-        <f>IF(OR($A19="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M19" s="68">
-        <f>IF(OR($A19="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N19" s="68">
-        <f>IF(OR($A19="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22284,43 +16745,35 @@
         <v/>
       </c>
       <c r="E20" s="68">
-        <f>IF(OR($A20="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F20" s="68">
-        <f>IF(OR($A20="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G20" s="68">
-        <f>IF(OR($A20="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H20" s="68">
-        <f>IF(OR($A20="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I20" s="68">
-        <f>IF(OR($A20="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J20" s="68">
-        <f>IF(OR($A20="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K20" s="68">
-        <f>IF(OR($A20="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L20" s="68">
-        <f>IF(OR($A20="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M20" s="68">
-        <f>IF(OR($A20="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N20" s="68">
-        <f>IF(OR($A20="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22342,43 +16795,35 @@
         <v/>
       </c>
       <c r="E21" s="68">
-        <f>IF(OR($A21="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F21" s="68">
-        <f>IF(OR($A21="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G21" s="68">
-        <f>IF(OR($A21="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H21" s="68">
-        <f>IF(OR($A21="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I21" s="68">
-        <f>IF(OR($A21="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J21" s="68">
-        <f>IF(OR($A21="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K21" s="68">
-        <f>IF(OR($A21="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L21" s="68">
-        <f>IF(OR($A21="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M21" s="68">
-        <f>IF(OR($A21="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N21" s="68">
-        <f>IF(OR($A21="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22400,43 +16845,35 @@
         <v/>
       </c>
       <c r="E22" s="68">
-        <f>IF(OR($A22="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F22" s="68">
-        <f>IF(OR($A22="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G22" s="68">
-        <f>IF(OR($A22="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H22" s="68">
-        <f>IF(OR($A22="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I22" s="68">
-        <f>IF(OR($A22="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J22" s="68">
-        <f>IF(OR($A22="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K22" s="68">
-        <f>IF(OR($A22="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L22" s="68">
-        <f>IF(OR($A22="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M22" s="68">
-        <f>IF(OR($A22="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N22" s="68">
-        <f>IF(OR($A22="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22458,43 +16895,35 @@
         <v/>
       </c>
       <c r="E23" s="68">
-        <f>IF(OR($A23="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F23" s="68">
-        <f>IF(OR($A23="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G23" s="68">
-        <f>IF(OR($A23="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H23" s="68">
-        <f>IF(OR($A23="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I23" s="68">
-        <f>IF(OR($A23="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J23" s="68">
-        <f>IF(OR($A23="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K23" s="68">
-        <f>IF(OR($A23="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L23" s="68">
-        <f>IF(OR($A23="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M23" s="68">
-        <f>IF(OR($A23="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N23" s="68">
-        <f>IF(OR($A23="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22516,43 +16945,35 @@
         <v/>
       </c>
       <c r="E24" s="68">
-        <f>IF(OR($A24="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F24" s="68">
-        <f>IF(OR($A24="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G24" s="68">
-        <f>IF(OR($A24="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H24" s="68">
-        <f>IF(OR($A24="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I24" s="68">
-        <f>IF(OR($A24="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J24" s="68">
-        <f>IF(OR($A24="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K24" s="68">
-        <f>IF(OR($A24="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L24" s="68">
-        <f>IF(OR($A24="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M24" s="68">
-        <f>IF(OR($A24="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N24" s="68">
-        <f>IF(OR($A24="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22574,43 +16995,35 @@
         <v/>
       </c>
       <c r="E25" s="68">
-        <f>IF(OR($A25="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F25" s="68">
-        <f>IF(OR($A25="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G25" s="68">
-        <f>IF(OR($A25="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H25" s="68">
-        <f>IF(OR($A25="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I25" s="68">
-        <f>IF(OR($A25="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J25" s="68">
-        <f>IF(OR($A25="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K25" s="68">
-        <f>IF(OR($A25="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L25" s="68">
-        <f>IF(OR($A25="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M25" s="68">
-        <f>IF(OR($A25="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N25" s="68">
-        <f>IF(OR($A25="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22632,43 +17045,35 @@
         <v/>
       </c>
       <c r="E26" s="68">
-        <f>IF(OR($A26="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F26" s="68">
-        <f>IF(OR($A26="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G26" s="68">
-        <f>IF(OR($A26="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H26" s="68">
-        <f>IF(OR($A26="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I26" s="68">
-        <f>IF(OR($A26="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J26" s="68">
-        <f>IF(OR($A26="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K26" s="68">
-        <f>IF(OR($A26="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L26" s="68">
-        <f>IF(OR($A26="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M26" s="68">
-        <f>IF(OR($A26="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N26" s="68">
-        <f>IF(OR($A26="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22690,43 +17095,35 @@
         <v/>
       </c>
       <c r="E27" s="68">
-        <f>IF(OR($A27="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F27" s="68">
-        <f>IF(OR($A27="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G27" s="68">
-        <f>IF(OR($A27="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H27" s="68">
-        <f>IF(OR($A27="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I27" s="68">
-        <f>IF(OR($A27="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J27" s="68">
-        <f>IF(OR($A27="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K27" s="68">
-        <f>IF(OR($A27="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L27" s="68">
-        <f>IF(OR($A27="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M27" s="68">
-        <f>IF(OR($A27="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N27" s="68">
-        <f>IF(OR($A27="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22748,43 +17145,35 @@
         <v/>
       </c>
       <c r="E28" s="68">
-        <f>IF(OR($A28="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F28" s="68">
-        <f>IF(OR($A28="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G28" s="68">
-        <f>IF(OR($A28="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H28" s="68">
-        <f>IF(OR($A28="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I28" s="68">
-        <f>IF(OR($A28="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J28" s="68">
-        <f>IF(OR($A28="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K28" s="68">
-        <f>IF(OR($A28="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L28" s="68">
-        <f>IF(OR($A28="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M28" s="68">
-        <f>IF(OR($A28="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N28" s="68">
-        <f>IF(OR($A28="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22806,43 +17195,35 @@
         <v/>
       </c>
       <c r="E29" s="68">
-        <f>IF(OR($A29="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F29" s="68">
-        <f>IF(OR($A29="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G29" s="68">
-        <f>IF(OR($A29="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H29" s="68">
-        <f>IF(OR($A29="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I29" s="68">
-        <f>IF(OR($A29="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J29" s="68">
-        <f>IF(OR($A29="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K29" s="68">
-        <f>IF(OR($A29="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L29" s="68">
-        <f>IF(OR($A29="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M29" s="68">
-        <f>IF(OR($A29="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N29" s="68">
-        <f>IF(OR($A29="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22864,43 +17245,35 @@
         <v/>
       </c>
       <c r="E30" s="68">
-        <f>IF(OR($A30="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F30" s="68">
-        <f>IF(OR($A30="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G30" s="68">
-        <f>IF(OR($A30="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H30" s="68">
-        <f>IF(OR($A30="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I30" s="68">
-        <f>IF(OR($A30="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J30" s="68">
-        <f>IF(OR($A30="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K30" s="68">
-        <f>IF(OR($A30="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L30" s="68">
-        <f>IF(OR($A30="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M30" s="68">
-        <f>IF(OR($A30="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N30" s="68">
-        <f>IF(OR($A30="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22922,43 +17295,35 @@
         <v/>
       </c>
       <c r="E31" s="68">
-        <f>IF(OR($A31="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F31" s="68">
-        <f>IF(OR($A31="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G31" s="68">
-        <f>IF(OR($A31="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H31" s="68">
-        <f>IF(OR($A31="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I31" s="68">
-        <f>IF(OR($A31="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J31" s="68">
-        <f>IF(OR($A31="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K31" s="68">
-        <f>IF(OR($A31="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L31" s="68">
-        <f>IF(OR($A31="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M31" s="68">
-        <f>IF(OR($A31="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N31" s="68">
-        <f>IF(OR($A31="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -22980,43 +17345,35 @@
         <v/>
       </c>
       <c r="E32" s="68">
-        <f>IF(OR($A32="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F32" s="68">
-        <f>IF(OR($A32="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G32" s="68">
-        <f>IF(OR($A32="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H32" s="68">
-        <f>IF(OR($A32="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I32" s="68">
-        <f>IF(OR($A32="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J32" s="68">
-        <f>IF(OR($A32="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K32" s="68">
-        <f>IF(OR($A32="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L32" s="68">
-        <f>IF(OR($A32="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M32" s="68">
-        <f>IF(OR($A32="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N32" s="68">
-        <f>IF(OR($A32="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -23038,43 +17395,35 @@
         <v/>
       </c>
       <c r="E33" s="68">
-        <f>IF(OR($A33="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F33" s="68">
-        <f>IF(OR($A33="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G33" s="68">
-        <f>IF(OR($A33="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H33" s="68">
-        <f>IF(OR($A33="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I33" s="68">
-        <f>IF(OR($A33="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J33" s="68">
-        <f>IF(OR($A33="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K33" s="68">
-        <f>IF(OR($A33="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L33" s="68">
-        <f>IF(OR($A33="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M33" s="68">
-        <f>IF(OR($A33="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N33" s="68">
-        <f>IF(OR($A33="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -23096,43 +17445,35 @@
         <v/>
       </c>
       <c r="E34" s="68">
-        <f>IF(OR($A34="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F34" s="68">
-        <f>IF(OR($A34="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G34" s="68">
-        <f>IF(OR($A34="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H34" s="68">
-        <f>IF(OR($A34="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I34" s="68">
-        <f>IF(OR($A34="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J34" s="68">
-        <f>IF(OR($A34="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K34" s="68">
-        <f>IF(OR($A34="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L34" s="68">
-        <f>IF(OR($A34="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M34" s="68">
-        <f>IF(OR($A34="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N34" s="68">
-        <f>IF(OR($A34="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -23154,43 +17495,35 @@
         <v/>
       </c>
       <c r="E35" s="68">
-        <f>IF(OR($A35="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F35" s="68">
-        <f>IF(OR($A35="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G35" s="68">
-        <f>IF(OR($A35="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H35" s="68">
-        <f>IF(OR($A35="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I35" s="68">
-        <f>IF(OR($A35="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J35" s="68">
-        <f>IF(OR($A35="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K35" s="68">
-        <f>IF(OR($A35="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L35" s="68">
-        <f>IF(OR($A35="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M35" s="68">
-        <f>IF(OR($A35="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N35" s="68">
-        <f>IF(OR($A35="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -23212,43 +17545,35 @@
         <v/>
       </c>
       <c r="E36" s="68">
-        <f>IF(OR($A36="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F36" s="68">
-        <f>IF(OR($A36="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G36" s="68">
-        <f>IF(OR($A36="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H36" s="68">
-        <f>IF(OR($A36="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I36" s="68">
-        <f>IF(OR($A36="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J36" s="68">
-        <f>IF(OR($A36="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K36" s="68">
-        <f>IF(OR($A36="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L36" s="68">
-        <f>IF(OR($A36="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="M36" s="68">
-        <f>IF(OR($A36="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
-        <v/>
-      </c>
-      <c r="N36" s="68">
-        <f>IF(OR($A36="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -23265,8 +17590,6 @@
       <c r="J37" s="36" t="n"/>
       <c r="K37" s="36" t="n"/>
       <c r="L37" s="36" t="n"/>
-      <c r="M37" s="36" t="n"/>
-      <c r="N37" s="36" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="34">
       <c r="A38" s="36" t="n"/>
@@ -23309,14 +17632,6 @@
         <f>IF(L$4="","",COUNTIF(L7:L36,"RED"))</f>
         <v/>
       </c>
-      <c r="M38" s="68">
-        <f>IF(M$4="","",COUNTIF(M7:M36,"RED"))</f>
-        <v/>
-      </c>
-      <c r="N38" s="68">
-        <f>IF(N$4="","",COUNTIF(N7:N36,"RED"))</f>
-        <v/>
-      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="34">
       <c r="A39" s="36" t="n"/>
@@ -23359,14 +17674,6 @@
         <f>IF(L$4="","",COUNTIF(L7:L36,"YELLOW"))</f>
         <v/>
       </c>
-      <c r="M39" s="68">
-        <f>IF(M$4="","",COUNTIF(M7:M36,"YELLOW"))</f>
-        <v/>
-      </c>
-      <c r="N39" s="68">
-        <f>IF(N$4="","",COUNTIF(N7:N36,"YELLOW"))</f>
-        <v/>
-      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="34">
       <c r="A40" s="36" t="n"/>
@@ -23409,14 +17716,6 @@
         <f>IF(L$4="","",COUNTIF(L7:L36,"CLEARED"))</f>
         <v/>
       </c>
-      <c r="M40" s="68">
-        <f>IF(M$4="","",COUNTIF(M7:M36,"CLEARED"))</f>
-        <v/>
-      </c>
-      <c r="N40" s="68">
-        <f>IF(N$4="","",COUNTIF(N7:N36,"CLEARED"))</f>
-        <v/>
-      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="34">
       <c r="A41" s="36" t="n"/>
@@ -23459,14 +17758,6 @@
         <f>IF(L$4="","",IF(COUNTIF(L7:L36,"NO DATA")&gt;0,"INCOMPLETE",IF(L38&gt;0,"RED",IF(L39&gt;0,"YELLOW","GREEN"))))</f>
         <v/>
       </c>
-      <c r="M41" s="68">
-        <f>IF(M$4="","",IF(COUNTIF(M7:M36,"NO DATA")&gt;0,"INCOMPLETE",IF(M38&gt;0,"RED",IF(M39&gt;0,"YELLOW","GREEN"))))</f>
-        <v/>
-      </c>
-      <c r="N41" s="68">
-        <f>IF(N$4="","",IF(COUNTIF(N7:N36,"NO DATA")&gt;0,"INCOMPLETE",IF(N38&gt;0,"RED",IF(N39&gt;0,"YELLOW","GREEN"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="34">
       <c r="A42" s="36" t="n"/>
@@ -23509,17 +17800,9 @@
         <f>IF(L$4="","",IF(L41="GREEN","YES","NO"))</f>
         <v/>
       </c>
-      <c r="M42" s="68">
-        <f>IF(M$4="","",IF(M41="GREEN","YES","NO"))</f>
-        <v/>
-      </c>
-      <c r="N42" s="68">
-        <f>IF(N$4="","",IF(N41="GREEN","YES","NO"))</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E7:N36">
+  <conditionalFormatting sqref="E7:L36">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
       <formula>"RED"</formula>
     </cfRule>
@@ -23545,7 +17828,7 @@
       <formula>"NO DATA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E41:N42">
+  <conditionalFormatting sqref="E41:L42">
     <cfRule type="cellIs" rank="0" priority="10" equalAverage="0" operator="equal" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
       <formula>"RED"</formula>
     </cfRule>
@@ -23583,7 +17866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="33" min="1" max="1"/>
@@ -23815,7 +18098,7 @@
         <v/>
       </c>
       <c r="I9" s="68">
-        <f>IF(ISNUMBER(H9),COUNTIF($H$9:$H$18,"&lt;"&amp;H9)+1,"")</f>
+        <f>IF(ISNUMBER(H9),COUNTIF($H$9:$H$16,"&lt;"&amp;H9)+1,"")</f>
         <v/>
       </c>
       <c r="J9" s="73">
@@ -23823,7 +18106,7 @@
         <v/>
       </c>
       <c r="K9" s="68">
-        <f>IF(ISNUMBER(J9),COUNTIF($J$9:$J$18,"&lt;"&amp;J9)+1,"")</f>
+        <f>IF(ISNUMBER(J9),COUNTIF($J$9:$J$16,"&lt;"&amp;J9)+1,"")</f>
         <v/>
       </c>
       <c r="L9" s="43" t="n"/>
@@ -23850,7 +18133,7 @@
         <v/>
       </c>
       <c r="I10" s="68">
-        <f>IF(ISNUMBER(H10),COUNTIF($H$9:$H$18,"&lt;"&amp;H10)+1,"")</f>
+        <f>IF(ISNUMBER(H10),COUNTIF($H$9:$H$16,"&lt;"&amp;H10)+1,"")</f>
         <v/>
       </c>
       <c r="J10" s="73">
@@ -23858,7 +18141,7 @@
         <v/>
       </c>
       <c r="K10" s="68">
-        <f>IF(ISNUMBER(J10),COUNTIF($J$9:$J$18,"&lt;"&amp;J10)+1,"")</f>
+        <f>IF(ISNUMBER(J10),COUNTIF($J$9:$J$16,"&lt;"&amp;J10)+1,"")</f>
         <v/>
       </c>
       <c r="L10" s="43" t="n"/>
@@ -23885,7 +18168,7 @@
         <v/>
       </c>
       <c r="I11" s="68">
-        <f>IF(ISNUMBER(H11),COUNTIF($H$9:$H$18,"&lt;"&amp;H11)+1,"")</f>
+        <f>IF(ISNUMBER(H11),COUNTIF($H$9:$H$16,"&lt;"&amp;H11)+1,"")</f>
         <v/>
       </c>
       <c r="J11" s="73">
@@ -23893,7 +18176,7 @@
         <v/>
       </c>
       <c r="K11" s="68">
-        <f>IF(ISNUMBER(J11),COUNTIF($J$9:$J$18,"&lt;"&amp;J11)+1,"")</f>
+        <f>IF(ISNUMBER(J11),COUNTIF($J$9:$J$16,"&lt;"&amp;J11)+1,"")</f>
         <v/>
       </c>
       <c r="L11" s="43" t="n"/>
@@ -23920,7 +18203,7 @@
         <v/>
       </c>
       <c r="I12" s="68">
-        <f>IF(ISNUMBER(H12),COUNTIF($H$9:$H$18,"&lt;"&amp;H12)+1,"")</f>
+        <f>IF(ISNUMBER(H12),COUNTIF($H$9:$H$16,"&lt;"&amp;H12)+1,"")</f>
         <v/>
       </c>
       <c r="J12" s="73">
@@ -23928,7 +18211,7 @@
         <v/>
       </c>
       <c r="K12" s="68">
-        <f>IF(ISNUMBER(J12),COUNTIF($J$9:$J$18,"&lt;"&amp;J12)+1,"")</f>
+        <f>IF(ISNUMBER(J12),COUNTIF($J$9:$J$16,"&lt;"&amp;J12)+1,"")</f>
         <v/>
       </c>
       <c r="L12" s="43" t="n"/>
@@ -23955,7 +18238,7 @@
         <v/>
       </c>
       <c r="I13" s="68">
-        <f>IF(ISNUMBER(H13),COUNTIF($H$9:$H$18,"&lt;"&amp;H13)+1,"")</f>
+        <f>IF(ISNUMBER(H13),COUNTIF($H$9:$H$16,"&lt;"&amp;H13)+1,"")</f>
         <v/>
       </c>
       <c r="J13" s="73">
@@ -23963,7 +18246,7 @@
         <v/>
       </c>
       <c r="K13" s="68">
-        <f>IF(ISNUMBER(J13),COUNTIF($J$9:$J$18,"&lt;"&amp;J13)+1,"")</f>
+        <f>IF(ISNUMBER(J13),COUNTIF($J$9:$J$16,"&lt;"&amp;J13)+1,"")</f>
         <v/>
       </c>
       <c r="L13" s="43" t="n"/>
@@ -23990,7 +18273,7 @@
         <v/>
       </c>
       <c r="I14" s="68">
-        <f>IF(ISNUMBER(H14),COUNTIF($H$9:$H$18,"&lt;"&amp;H14)+1,"")</f>
+        <f>IF(ISNUMBER(H14),COUNTIF($H$9:$H$16,"&lt;"&amp;H14)+1,"")</f>
         <v/>
       </c>
       <c r="J14" s="73">
@@ -23998,7 +18281,7 @@
         <v/>
       </c>
       <c r="K14" s="68">
-        <f>IF(ISNUMBER(J14),COUNTIF($J$9:$J$18,"&lt;"&amp;J14)+1,"")</f>
+        <f>IF(ISNUMBER(J14),COUNTIF($J$9:$J$16,"&lt;"&amp;J14)+1,"")</f>
         <v/>
       </c>
       <c r="L14" s="43" t="n"/>
@@ -24025,7 +18308,7 @@
         <v/>
       </c>
       <c r="I15" s="68">
-        <f>IF(ISNUMBER(H15),COUNTIF($H$9:$H$18,"&lt;"&amp;H15)+1,"")</f>
+        <f>IF(ISNUMBER(H15),COUNTIF($H$9:$H$16,"&lt;"&amp;H15)+1,"")</f>
         <v/>
       </c>
       <c r="J15" s="73">
@@ -24033,7 +18316,7 @@
         <v/>
       </c>
       <c r="K15" s="68">
-        <f>IF(ISNUMBER(J15),COUNTIF($J$9:$J$18,"&lt;"&amp;J15)+1,"")</f>
+        <f>IF(ISNUMBER(J15),COUNTIF($J$9:$J$16,"&lt;"&amp;J15)+1,"")</f>
         <v/>
       </c>
       <c r="L15" s="43" t="n"/>
@@ -24060,7 +18343,7 @@
         <v/>
       </c>
       <c r="I16" s="68">
-        <f>IF(ISNUMBER(H16),COUNTIF($H$9:$H$18,"&lt;"&amp;H16)+1,"")</f>
+        <f>IF(ISNUMBER(H16),COUNTIF($H$9:$H$16,"&lt;"&amp;H16)+1,"")</f>
         <v/>
       </c>
       <c r="J16" s="73">
@@ -24068,91 +18351,45 @@
         <v/>
       </c>
       <c r="K16" s="68">
-        <f>IF(ISNUMBER(J16),COUNTIF($J$9:$J$18,"&lt;"&amp;J16)+1,"")</f>
+        <f>IF(ISNUMBER(J16),COUNTIF($J$9:$J$16,"&lt;"&amp;J16)+1,"")</f>
         <v/>
       </c>
       <c r="L16" s="43" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="34">
-      <c r="A17" s="66">
-        <f>IF('Compliance Matrix'!M4="","",'Compliance Matrix'!M4)</f>
-        <v/>
-      </c>
-      <c r="B17" s="68">
-        <f>IF(A17="","",'Compliance Matrix'!M42)</f>
-        <v/>
-      </c>
-      <c r="C17" s="72" t="n"/>
-      <c r="D17" s="72" t="n"/>
-      <c r="E17" s="72" t="n"/>
-      <c r="F17" s="73">
-        <f>IF(A17="","",IF(COUNT(C17:E17)&lt;3,"Incomplete",C17*$B$4+D17*$B$5+E17*$B$6))</f>
-        <v/>
-      </c>
-      <c r="G17" s="72" t="n"/>
-      <c r="H17" s="73">
-        <f>IF(A17="","",IF(B17&lt;&gt;"YES","Not eligible",IF(ISNUMBER(F17),F17+N(G17),"Incomplete")))</f>
-        <v/>
-      </c>
-      <c r="I17" s="68">
-        <f>IF(ISNUMBER(H17),COUNTIF($H$9:$H$18,"&lt;"&amp;H17)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="73">
-        <f>IF(A17="","",IF(ISNUMBER(F17),F17+N(G17),"Incomplete"))</f>
-        <v/>
-      </c>
-      <c r="K17" s="68">
-        <f>IF(ISNUMBER(J17),COUNTIF($J$9:$J$18,"&lt;"&amp;J17)+1,"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="43" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="36" t="n"/>
+      <c r="L17" s="36" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="34">
-      <c r="A18" s="66">
-        <f>IF('Compliance Matrix'!N4="","",'Compliance Matrix'!N4)</f>
-        <v/>
-      </c>
-      <c r="B18" s="68">
-        <f>IF(A18="","",'Compliance Matrix'!N42)</f>
-        <v/>
-      </c>
-      <c r="C18" s="72" t="n"/>
-      <c r="D18" s="72" t="n"/>
-      <c r="E18" s="72" t="n"/>
-      <c r="F18" s="73">
-        <f>IF(A18="","",IF(COUNT(C18:E18)&lt;3,"Incomplete",C18*$B$4+D18*$B$5+E18*$B$6))</f>
-        <v/>
-      </c>
-      <c r="G18" s="72" t="n"/>
-      <c r="H18" s="73">
-        <f>IF(A18="","",IF(B18&lt;&gt;"YES","Not eligible",IF(ISNUMBER(F18),F18+N(G18),"Incomplete")))</f>
-        <v/>
-      </c>
-      <c r="I18" s="68">
-        <f>IF(ISNUMBER(H18),COUNTIF($H$9:$H$18,"&lt;"&amp;H18)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="73">
-        <f>IF(A18="","",IF(ISNUMBER(F18),F18+N(G18),"Incomplete"))</f>
-        <v/>
-      </c>
-      <c r="K18" s="68">
-        <f>IF(ISNUMBER(J18),COUNTIF($J$9:$J$18,"&lt;"&amp;J18)+1,"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="43" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>Rates are SAR per m2, ex-VAT, as quoted. Adjustments: positive = added cost (e.g. priced exclusions). Quoted prices are never overwritten.</t>
         </is>
       </c>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="36" t="n"/>
+      <c r="L18" s="36" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B9:B18">
+  <conditionalFormatting sqref="B9:B16">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
       <formula>"RED"</formula>
     </cfRule>
@@ -24238,7 +18475,7 @@
         </is>
       </c>
       <c r="B4" s="39">
-        <f>IFERROR(INDEX(Evaluation!$A$9:$A$18,MATCH(1,Evaluation!$I$9:$I$18,0)),"None eligible")</f>
+        <f>IFERROR(INDEX(Evaluation!$A$9:$A$16,MATCH(1,Evaluation!$I$9:$I$16,0)),"None eligible")</f>
         <v/>
       </c>
       <c r="C4" s="36" t="n"/>
@@ -24252,7 +18489,7 @@
         </is>
       </c>
       <c r="B5" s="74">
-        <f>IFERROR(INDEX(Evaluation!$H$9:$H$18,MATCH(1,Evaluation!$I$9:$I$18,0)),"")</f>
+        <f>IFERROR(INDEX(Evaluation!$H$9:$H$16,MATCH(1,Evaluation!$I$9:$I$16,0)),"")</f>
         <v/>
       </c>
       <c r="C5" s="36" t="n"/>

--- a/P01113_template.xlsx
+++ b/P01113_template.xlsx
@@ -2372,7 +2372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S204"/>
+  <dimension ref="A1:S304"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="33" min="1" max="1"/>
@@ -13356,8 +13356,5408 @@
       <c r="R204" s="59" t="n"/>
       <c r="S204" s="60" t="n"/>
     </row>
+    <row r="205" ht="15" customHeight="1" s="34">
+      <c r="A205" s="54" t="n"/>
+      <c r="B205" s="54" t="n"/>
+      <c r="C205" s="54" t="n"/>
+      <c r="D205" s="55">
+        <f>IF($A205="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C205,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E205" s="55">
+        <f>IF($A205="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C205,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F205" s="56">
+        <f>IF($A205="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C205,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G205" s="57" t="n"/>
+      <c r="H205" s="54" t="n"/>
+      <c r="I205" s="54" t="n"/>
+      <c r="J205" s="39">
+        <f>IF($A205="","",IF($E205="Informational","GREEN",IF($G205="",IF($E205="Mandatory","RED","YELLOW"),IF($N205="Exact",IF(UPPER(TRIM($G205&amp;""))=UPPER(TRIM($F205&amp;"")),"GREEN",$P205),IF(NOT(ISNUMBER($G205)),$P205,IF($N205="Min",IF($G205&gt;=$F205,"GREEN",IF($G205&gt;=$F205-$O205,"YELLOW",$P205)),IF($N205="Max",IF($G205&lt;=$F205,"GREEN",IF($G205&lt;=$F205+$O205,"YELLOW",$P205)),IF($N205="Range",IF(ABS($G205-$F205)&lt;=$O205,"GREEN",$P205),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K205" s="39">
+        <f>IF($A205="","",IF($H205="Non-Compliant","RED",IF(AND(OR($H205="Alternative Offer",$H205="Partially Compliant"),$J205="GREEN"),"YELLOW",IF(AND($J205="GREEN",ISNUMBER($R205),$R205&lt;Baseline!$B$9),"YELLOW",$J205))))</f>
+        <v/>
+      </c>
+      <c r="L205" s="39">
+        <f>IF($A205="","",IF($K205="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A205,Exceptions!$C$5:$C$104,$B205,Exceptions!$D$5:$D$104,$C205,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K205)))</f>
+        <v/>
+      </c>
+      <c r="M205" s="39">
+        <f>IF($A205="","",IF($H205="","Declaration missing",IF($H205="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R205),$R205&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H205="Fully Compliant",$J205&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N205" s="58">
+        <f>IF($A205="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C205,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O205" s="58">
+        <f>IF($A205="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C205,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P205" s="58">
+        <f>IF($A205="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C205,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q205" s="58">
+        <f>IF($A205="","",$A205&amp;"|"&amp;$B205&amp;"|"&amp;$C205)</f>
+        <v/>
+      </c>
+      <c r="R205" s="59" t="n"/>
+      <c r="S205" s="60" t="n"/>
+    </row>
+    <row r="206" ht="15" customHeight="1" s="34">
+      <c r="A206" s="54" t="n"/>
+      <c r="B206" s="54" t="n"/>
+      <c r="C206" s="54" t="n"/>
+      <c r="D206" s="55">
+        <f>IF($A206="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C206,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E206" s="55">
+        <f>IF($A206="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C206,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F206" s="56">
+        <f>IF($A206="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C206,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G206" s="57" t="n"/>
+      <c r="H206" s="54" t="n"/>
+      <c r="I206" s="54" t="n"/>
+      <c r="J206" s="39">
+        <f>IF($A206="","",IF($E206="Informational","GREEN",IF($G206="",IF($E206="Mandatory","RED","YELLOW"),IF($N206="Exact",IF(UPPER(TRIM($G206&amp;""))=UPPER(TRIM($F206&amp;"")),"GREEN",$P206),IF(NOT(ISNUMBER($G206)),$P206,IF($N206="Min",IF($G206&gt;=$F206,"GREEN",IF($G206&gt;=$F206-$O206,"YELLOW",$P206)),IF($N206="Max",IF($G206&lt;=$F206,"GREEN",IF($G206&lt;=$F206+$O206,"YELLOW",$P206)),IF($N206="Range",IF(ABS($G206-$F206)&lt;=$O206,"GREEN",$P206),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K206" s="39">
+        <f>IF($A206="","",IF($H206="Non-Compliant","RED",IF(AND(OR($H206="Alternative Offer",$H206="Partially Compliant"),$J206="GREEN"),"YELLOW",IF(AND($J206="GREEN",ISNUMBER($R206),$R206&lt;Baseline!$B$9),"YELLOW",$J206))))</f>
+        <v/>
+      </c>
+      <c r="L206" s="39">
+        <f>IF($A206="","",IF($K206="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A206,Exceptions!$C$5:$C$104,$B206,Exceptions!$D$5:$D$104,$C206,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K206)))</f>
+        <v/>
+      </c>
+      <c r="M206" s="39">
+        <f>IF($A206="","",IF($H206="","Declaration missing",IF($H206="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R206),$R206&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H206="Fully Compliant",$J206&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N206" s="58">
+        <f>IF($A206="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C206,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O206" s="58">
+        <f>IF($A206="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C206,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P206" s="58">
+        <f>IF($A206="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C206,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q206" s="58">
+        <f>IF($A206="","",$A206&amp;"|"&amp;$B206&amp;"|"&amp;$C206)</f>
+        <v/>
+      </c>
+      <c r="R206" s="59" t="n"/>
+      <c r="S206" s="60" t="n"/>
+    </row>
+    <row r="207" ht="15" customHeight="1" s="34">
+      <c r="A207" s="54" t="n"/>
+      <c r="B207" s="54" t="n"/>
+      <c r="C207" s="54" t="n"/>
+      <c r="D207" s="55">
+        <f>IF($A207="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C207,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E207" s="55">
+        <f>IF($A207="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C207,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F207" s="56">
+        <f>IF($A207="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C207,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G207" s="57" t="n"/>
+      <c r="H207" s="54" t="n"/>
+      <c r="I207" s="54" t="n"/>
+      <c r="J207" s="39">
+        <f>IF($A207="","",IF($E207="Informational","GREEN",IF($G207="",IF($E207="Mandatory","RED","YELLOW"),IF($N207="Exact",IF(UPPER(TRIM($G207&amp;""))=UPPER(TRIM($F207&amp;"")),"GREEN",$P207),IF(NOT(ISNUMBER($G207)),$P207,IF($N207="Min",IF($G207&gt;=$F207,"GREEN",IF($G207&gt;=$F207-$O207,"YELLOW",$P207)),IF($N207="Max",IF($G207&lt;=$F207,"GREEN",IF($G207&lt;=$F207+$O207,"YELLOW",$P207)),IF($N207="Range",IF(ABS($G207-$F207)&lt;=$O207,"GREEN",$P207),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K207" s="39">
+        <f>IF($A207="","",IF($H207="Non-Compliant","RED",IF(AND(OR($H207="Alternative Offer",$H207="Partially Compliant"),$J207="GREEN"),"YELLOW",IF(AND($J207="GREEN",ISNUMBER($R207),$R207&lt;Baseline!$B$9),"YELLOW",$J207))))</f>
+        <v/>
+      </c>
+      <c r="L207" s="39">
+        <f>IF($A207="","",IF($K207="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A207,Exceptions!$C$5:$C$104,$B207,Exceptions!$D$5:$D$104,$C207,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K207)))</f>
+        <v/>
+      </c>
+      <c r="M207" s="39">
+        <f>IF($A207="","",IF($H207="","Declaration missing",IF($H207="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R207),$R207&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H207="Fully Compliant",$J207&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N207" s="58">
+        <f>IF($A207="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C207,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O207" s="58">
+        <f>IF($A207="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C207,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P207" s="58">
+        <f>IF($A207="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C207,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q207" s="58">
+        <f>IF($A207="","",$A207&amp;"|"&amp;$B207&amp;"|"&amp;$C207)</f>
+        <v/>
+      </c>
+      <c r="R207" s="59" t="n"/>
+      <c r="S207" s="60" t="n"/>
+    </row>
+    <row r="208" ht="15" customHeight="1" s="34">
+      <c r="A208" s="54" t="n"/>
+      <c r="B208" s="54" t="n"/>
+      <c r="C208" s="54" t="n"/>
+      <c r="D208" s="55">
+        <f>IF($A208="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C208,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E208" s="55">
+        <f>IF($A208="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C208,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F208" s="56">
+        <f>IF($A208="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C208,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G208" s="57" t="n"/>
+      <c r="H208" s="54" t="n"/>
+      <c r="I208" s="54" t="n"/>
+      <c r="J208" s="39">
+        <f>IF($A208="","",IF($E208="Informational","GREEN",IF($G208="",IF($E208="Mandatory","RED","YELLOW"),IF($N208="Exact",IF(UPPER(TRIM($G208&amp;""))=UPPER(TRIM($F208&amp;"")),"GREEN",$P208),IF(NOT(ISNUMBER($G208)),$P208,IF($N208="Min",IF($G208&gt;=$F208,"GREEN",IF($G208&gt;=$F208-$O208,"YELLOW",$P208)),IF($N208="Max",IF($G208&lt;=$F208,"GREEN",IF($G208&lt;=$F208+$O208,"YELLOW",$P208)),IF($N208="Range",IF(ABS($G208-$F208)&lt;=$O208,"GREEN",$P208),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K208" s="39">
+        <f>IF($A208="","",IF($H208="Non-Compliant","RED",IF(AND(OR($H208="Alternative Offer",$H208="Partially Compliant"),$J208="GREEN"),"YELLOW",IF(AND($J208="GREEN",ISNUMBER($R208),$R208&lt;Baseline!$B$9),"YELLOW",$J208))))</f>
+        <v/>
+      </c>
+      <c r="L208" s="39">
+        <f>IF($A208="","",IF($K208="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A208,Exceptions!$C$5:$C$104,$B208,Exceptions!$D$5:$D$104,$C208,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K208)))</f>
+        <v/>
+      </c>
+      <c r="M208" s="39">
+        <f>IF($A208="","",IF($H208="","Declaration missing",IF($H208="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R208),$R208&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H208="Fully Compliant",$J208&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N208" s="58">
+        <f>IF($A208="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C208,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O208" s="58">
+        <f>IF($A208="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C208,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P208" s="58">
+        <f>IF($A208="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C208,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q208" s="58">
+        <f>IF($A208="","",$A208&amp;"|"&amp;$B208&amp;"|"&amp;$C208)</f>
+        <v/>
+      </c>
+      <c r="R208" s="59" t="n"/>
+      <c r="S208" s="60" t="n"/>
+    </row>
+    <row r="209" ht="15" customHeight="1" s="34">
+      <c r="A209" s="54" t="n"/>
+      <c r="B209" s="54" t="n"/>
+      <c r="C209" s="54" t="n"/>
+      <c r="D209" s="55">
+        <f>IF($A209="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C209,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E209" s="55">
+        <f>IF($A209="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C209,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F209" s="56">
+        <f>IF($A209="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C209,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G209" s="57" t="n"/>
+      <c r="H209" s="54" t="n"/>
+      <c r="I209" s="54" t="n"/>
+      <c r="J209" s="39">
+        <f>IF($A209="","",IF($E209="Informational","GREEN",IF($G209="",IF($E209="Mandatory","RED","YELLOW"),IF($N209="Exact",IF(UPPER(TRIM($G209&amp;""))=UPPER(TRIM($F209&amp;"")),"GREEN",$P209),IF(NOT(ISNUMBER($G209)),$P209,IF($N209="Min",IF($G209&gt;=$F209,"GREEN",IF($G209&gt;=$F209-$O209,"YELLOW",$P209)),IF($N209="Max",IF($G209&lt;=$F209,"GREEN",IF($G209&lt;=$F209+$O209,"YELLOW",$P209)),IF($N209="Range",IF(ABS($G209-$F209)&lt;=$O209,"GREEN",$P209),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K209" s="39">
+        <f>IF($A209="","",IF($H209="Non-Compliant","RED",IF(AND(OR($H209="Alternative Offer",$H209="Partially Compliant"),$J209="GREEN"),"YELLOW",IF(AND($J209="GREEN",ISNUMBER($R209),$R209&lt;Baseline!$B$9),"YELLOW",$J209))))</f>
+        <v/>
+      </c>
+      <c r="L209" s="39">
+        <f>IF($A209="","",IF($K209="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A209,Exceptions!$C$5:$C$104,$B209,Exceptions!$D$5:$D$104,$C209,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K209)))</f>
+        <v/>
+      </c>
+      <c r="M209" s="39">
+        <f>IF($A209="","",IF($H209="","Declaration missing",IF($H209="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R209),$R209&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H209="Fully Compliant",$J209&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N209" s="58">
+        <f>IF($A209="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C209,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O209" s="58">
+        <f>IF($A209="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C209,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P209" s="58">
+        <f>IF($A209="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C209,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q209" s="58">
+        <f>IF($A209="","",$A209&amp;"|"&amp;$B209&amp;"|"&amp;$C209)</f>
+        <v/>
+      </c>
+      <c r="R209" s="59" t="n"/>
+      <c r="S209" s="60" t="n"/>
+    </row>
+    <row r="210" ht="15" customHeight="1" s="34">
+      <c r="A210" s="54" t="n"/>
+      <c r="B210" s="54" t="n"/>
+      <c r="C210" s="54" t="n"/>
+      <c r="D210" s="55">
+        <f>IF($A210="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C210,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E210" s="55">
+        <f>IF($A210="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C210,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F210" s="56">
+        <f>IF($A210="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C210,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G210" s="57" t="n"/>
+      <c r="H210" s="54" t="n"/>
+      <c r="I210" s="54" t="n"/>
+      <c r="J210" s="39">
+        <f>IF($A210="","",IF($E210="Informational","GREEN",IF($G210="",IF($E210="Mandatory","RED","YELLOW"),IF($N210="Exact",IF(UPPER(TRIM($G210&amp;""))=UPPER(TRIM($F210&amp;"")),"GREEN",$P210),IF(NOT(ISNUMBER($G210)),$P210,IF($N210="Min",IF($G210&gt;=$F210,"GREEN",IF($G210&gt;=$F210-$O210,"YELLOW",$P210)),IF($N210="Max",IF($G210&lt;=$F210,"GREEN",IF($G210&lt;=$F210+$O210,"YELLOW",$P210)),IF($N210="Range",IF(ABS($G210-$F210)&lt;=$O210,"GREEN",$P210),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K210" s="39">
+        <f>IF($A210="","",IF($H210="Non-Compliant","RED",IF(AND(OR($H210="Alternative Offer",$H210="Partially Compliant"),$J210="GREEN"),"YELLOW",IF(AND($J210="GREEN",ISNUMBER($R210),$R210&lt;Baseline!$B$9),"YELLOW",$J210))))</f>
+        <v/>
+      </c>
+      <c r="L210" s="39">
+        <f>IF($A210="","",IF($K210="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A210,Exceptions!$C$5:$C$104,$B210,Exceptions!$D$5:$D$104,$C210,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K210)))</f>
+        <v/>
+      </c>
+      <c r="M210" s="39">
+        <f>IF($A210="","",IF($H210="","Declaration missing",IF($H210="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R210),$R210&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H210="Fully Compliant",$J210&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N210" s="58">
+        <f>IF($A210="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C210,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O210" s="58">
+        <f>IF($A210="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C210,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P210" s="58">
+        <f>IF($A210="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C210,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q210" s="58">
+        <f>IF($A210="","",$A210&amp;"|"&amp;$B210&amp;"|"&amp;$C210)</f>
+        <v/>
+      </c>
+      <c r="R210" s="59" t="n"/>
+      <c r="S210" s="60" t="n"/>
+    </row>
+    <row r="211" ht="15" customHeight="1" s="34">
+      <c r="A211" s="54" t="n"/>
+      <c r="B211" s="54" t="n"/>
+      <c r="C211" s="54" t="n"/>
+      <c r="D211" s="55">
+        <f>IF($A211="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C211,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E211" s="55">
+        <f>IF($A211="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C211,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F211" s="56">
+        <f>IF($A211="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C211,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G211" s="57" t="n"/>
+      <c r="H211" s="54" t="n"/>
+      <c r="I211" s="54" t="n"/>
+      <c r="J211" s="39">
+        <f>IF($A211="","",IF($E211="Informational","GREEN",IF($G211="",IF($E211="Mandatory","RED","YELLOW"),IF($N211="Exact",IF(UPPER(TRIM($G211&amp;""))=UPPER(TRIM($F211&amp;"")),"GREEN",$P211),IF(NOT(ISNUMBER($G211)),$P211,IF($N211="Min",IF($G211&gt;=$F211,"GREEN",IF($G211&gt;=$F211-$O211,"YELLOW",$P211)),IF($N211="Max",IF($G211&lt;=$F211,"GREEN",IF($G211&lt;=$F211+$O211,"YELLOW",$P211)),IF($N211="Range",IF(ABS($G211-$F211)&lt;=$O211,"GREEN",$P211),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K211" s="39">
+        <f>IF($A211="","",IF($H211="Non-Compliant","RED",IF(AND(OR($H211="Alternative Offer",$H211="Partially Compliant"),$J211="GREEN"),"YELLOW",IF(AND($J211="GREEN",ISNUMBER($R211),$R211&lt;Baseline!$B$9),"YELLOW",$J211))))</f>
+        <v/>
+      </c>
+      <c r="L211" s="39">
+        <f>IF($A211="","",IF($K211="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A211,Exceptions!$C$5:$C$104,$B211,Exceptions!$D$5:$D$104,$C211,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K211)))</f>
+        <v/>
+      </c>
+      <c r="M211" s="39">
+        <f>IF($A211="","",IF($H211="","Declaration missing",IF($H211="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R211),$R211&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H211="Fully Compliant",$J211&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N211" s="58">
+        <f>IF($A211="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C211,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O211" s="58">
+        <f>IF($A211="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C211,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P211" s="58">
+        <f>IF($A211="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C211,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q211" s="58">
+        <f>IF($A211="","",$A211&amp;"|"&amp;$B211&amp;"|"&amp;$C211)</f>
+        <v/>
+      </c>
+      <c r="R211" s="59" t="n"/>
+      <c r="S211" s="60" t="n"/>
+    </row>
+    <row r="212" ht="15" customHeight="1" s="34">
+      <c r="A212" s="54" t="n"/>
+      <c r="B212" s="54" t="n"/>
+      <c r="C212" s="54" t="n"/>
+      <c r="D212" s="55">
+        <f>IF($A212="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C212,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E212" s="55">
+        <f>IF($A212="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C212,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F212" s="56">
+        <f>IF($A212="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C212,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G212" s="57" t="n"/>
+      <c r="H212" s="54" t="n"/>
+      <c r="I212" s="54" t="n"/>
+      <c r="J212" s="39">
+        <f>IF($A212="","",IF($E212="Informational","GREEN",IF($G212="",IF($E212="Mandatory","RED","YELLOW"),IF($N212="Exact",IF(UPPER(TRIM($G212&amp;""))=UPPER(TRIM($F212&amp;"")),"GREEN",$P212),IF(NOT(ISNUMBER($G212)),$P212,IF($N212="Min",IF($G212&gt;=$F212,"GREEN",IF($G212&gt;=$F212-$O212,"YELLOW",$P212)),IF($N212="Max",IF($G212&lt;=$F212,"GREEN",IF($G212&lt;=$F212+$O212,"YELLOW",$P212)),IF($N212="Range",IF(ABS($G212-$F212)&lt;=$O212,"GREEN",$P212),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K212" s="39">
+        <f>IF($A212="","",IF($H212="Non-Compliant","RED",IF(AND(OR($H212="Alternative Offer",$H212="Partially Compliant"),$J212="GREEN"),"YELLOW",IF(AND($J212="GREEN",ISNUMBER($R212),$R212&lt;Baseline!$B$9),"YELLOW",$J212))))</f>
+        <v/>
+      </c>
+      <c r="L212" s="39">
+        <f>IF($A212="","",IF($K212="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A212,Exceptions!$C$5:$C$104,$B212,Exceptions!$D$5:$D$104,$C212,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K212)))</f>
+        <v/>
+      </c>
+      <c r="M212" s="39">
+        <f>IF($A212="","",IF($H212="","Declaration missing",IF($H212="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R212),$R212&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H212="Fully Compliant",$J212&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N212" s="58">
+        <f>IF($A212="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C212,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O212" s="58">
+        <f>IF($A212="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C212,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P212" s="58">
+        <f>IF($A212="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C212,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q212" s="58">
+        <f>IF($A212="","",$A212&amp;"|"&amp;$B212&amp;"|"&amp;$C212)</f>
+        <v/>
+      </c>
+      <c r="R212" s="59" t="n"/>
+      <c r="S212" s="60" t="n"/>
+    </row>
+    <row r="213" ht="15" customHeight="1" s="34">
+      <c r="A213" s="54" t="n"/>
+      <c r="B213" s="54" t="n"/>
+      <c r="C213" s="54" t="n"/>
+      <c r="D213" s="55">
+        <f>IF($A213="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C213,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E213" s="55">
+        <f>IF($A213="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C213,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F213" s="56">
+        <f>IF($A213="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C213,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G213" s="57" t="n"/>
+      <c r="H213" s="54" t="n"/>
+      <c r="I213" s="54" t="n"/>
+      <c r="J213" s="39">
+        <f>IF($A213="","",IF($E213="Informational","GREEN",IF($G213="",IF($E213="Mandatory","RED","YELLOW"),IF($N213="Exact",IF(UPPER(TRIM($G213&amp;""))=UPPER(TRIM($F213&amp;"")),"GREEN",$P213),IF(NOT(ISNUMBER($G213)),$P213,IF($N213="Min",IF($G213&gt;=$F213,"GREEN",IF($G213&gt;=$F213-$O213,"YELLOW",$P213)),IF($N213="Max",IF($G213&lt;=$F213,"GREEN",IF($G213&lt;=$F213+$O213,"YELLOW",$P213)),IF($N213="Range",IF(ABS($G213-$F213)&lt;=$O213,"GREEN",$P213),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K213" s="39">
+        <f>IF($A213="","",IF($H213="Non-Compliant","RED",IF(AND(OR($H213="Alternative Offer",$H213="Partially Compliant"),$J213="GREEN"),"YELLOW",IF(AND($J213="GREEN",ISNUMBER($R213),$R213&lt;Baseline!$B$9),"YELLOW",$J213))))</f>
+        <v/>
+      </c>
+      <c r="L213" s="39">
+        <f>IF($A213="","",IF($K213="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A213,Exceptions!$C$5:$C$104,$B213,Exceptions!$D$5:$D$104,$C213,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K213)))</f>
+        <v/>
+      </c>
+      <c r="M213" s="39">
+        <f>IF($A213="","",IF($H213="","Declaration missing",IF($H213="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R213),$R213&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H213="Fully Compliant",$J213&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N213" s="58">
+        <f>IF($A213="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C213,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O213" s="58">
+        <f>IF($A213="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C213,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P213" s="58">
+        <f>IF($A213="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C213,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q213" s="58">
+        <f>IF($A213="","",$A213&amp;"|"&amp;$B213&amp;"|"&amp;$C213)</f>
+        <v/>
+      </c>
+      <c r="R213" s="59" t="n"/>
+      <c r="S213" s="60" t="n"/>
+    </row>
+    <row r="214" ht="15" customHeight="1" s="34">
+      <c r="A214" s="54" t="n"/>
+      <c r="B214" s="54" t="n"/>
+      <c r="C214" s="54" t="n"/>
+      <c r="D214" s="55">
+        <f>IF($A214="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C214,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E214" s="55">
+        <f>IF($A214="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C214,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F214" s="56">
+        <f>IF($A214="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C214,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G214" s="57" t="n"/>
+      <c r="H214" s="54" t="n"/>
+      <c r="I214" s="54" t="n"/>
+      <c r="J214" s="39">
+        <f>IF($A214="","",IF($E214="Informational","GREEN",IF($G214="",IF($E214="Mandatory","RED","YELLOW"),IF($N214="Exact",IF(UPPER(TRIM($G214&amp;""))=UPPER(TRIM($F214&amp;"")),"GREEN",$P214),IF(NOT(ISNUMBER($G214)),$P214,IF($N214="Min",IF($G214&gt;=$F214,"GREEN",IF($G214&gt;=$F214-$O214,"YELLOW",$P214)),IF($N214="Max",IF($G214&lt;=$F214,"GREEN",IF($G214&lt;=$F214+$O214,"YELLOW",$P214)),IF($N214="Range",IF(ABS($G214-$F214)&lt;=$O214,"GREEN",$P214),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K214" s="39">
+        <f>IF($A214="","",IF($H214="Non-Compliant","RED",IF(AND(OR($H214="Alternative Offer",$H214="Partially Compliant"),$J214="GREEN"),"YELLOW",IF(AND($J214="GREEN",ISNUMBER($R214),$R214&lt;Baseline!$B$9),"YELLOW",$J214))))</f>
+        <v/>
+      </c>
+      <c r="L214" s="39">
+        <f>IF($A214="","",IF($K214="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A214,Exceptions!$C$5:$C$104,$B214,Exceptions!$D$5:$D$104,$C214,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K214)))</f>
+        <v/>
+      </c>
+      <c r="M214" s="39">
+        <f>IF($A214="","",IF($H214="","Declaration missing",IF($H214="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R214),$R214&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H214="Fully Compliant",$J214&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N214" s="58">
+        <f>IF($A214="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C214,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O214" s="58">
+        <f>IF($A214="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C214,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P214" s="58">
+        <f>IF($A214="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C214,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q214" s="58">
+        <f>IF($A214="","",$A214&amp;"|"&amp;$B214&amp;"|"&amp;$C214)</f>
+        <v/>
+      </c>
+      <c r="R214" s="59" t="n"/>
+      <c r="S214" s="60" t="n"/>
+    </row>
+    <row r="215" ht="15" customHeight="1" s="34">
+      <c r="A215" s="54" t="n"/>
+      <c r="B215" s="54" t="n"/>
+      <c r="C215" s="54" t="n"/>
+      <c r="D215" s="55">
+        <f>IF($A215="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C215,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E215" s="55">
+        <f>IF($A215="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C215,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F215" s="56">
+        <f>IF($A215="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C215,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G215" s="57" t="n"/>
+      <c r="H215" s="54" t="n"/>
+      <c r="I215" s="54" t="n"/>
+      <c r="J215" s="39">
+        <f>IF($A215="","",IF($E215="Informational","GREEN",IF($G215="",IF($E215="Mandatory","RED","YELLOW"),IF($N215="Exact",IF(UPPER(TRIM($G215&amp;""))=UPPER(TRIM($F215&amp;"")),"GREEN",$P215),IF(NOT(ISNUMBER($G215)),$P215,IF($N215="Min",IF($G215&gt;=$F215,"GREEN",IF($G215&gt;=$F215-$O215,"YELLOW",$P215)),IF($N215="Max",IF($G215&lt;=$F215,"GREEN",IF($G215&lt;=$F215+$O215,"YELLOW",$P215)),IF($N215="Range",IF(ABS($G215-$F215)&lt;=$O215,"GREEN",$P215),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K215" s="39">
+        <f>IF($A215="","",IF($H215="Non-Compliant","RED",IF(AND(OR($H215="Alternative Offer",$H215="Partially Compliant"),$J215="GREEN"),"YELLOW",IF(AND($J215="GREEN",ISNUMBER($R215),$R215&lt;Baseline!$B$9),"YELLOW",$J215))))</f>
+        <v/>
+      </c>
+      <c r="L215" s="39">
+        <f>IF($A215="","",IF($K215="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A215,Exceptions!$C$5:$C$104,$B215,Exceptions!$D$5:$D$104,$C215,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K215)))</f>
+        <v/>
+      </c>
+      <c r="M215" s="39">
+        <f>IF($A215="","",IF($H215="","Declaration missing",IF($H215="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R215),$R215&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H215="Fully Compliant",$J215&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N215" s="58">
+        <f>IF($A215="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C215,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O215" s="58">
+        <f>IF($A215="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C215,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P215" s="58">
+        <f>IF($A215="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C215,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q215" s="58">
+        <f>IF($A215="","",$A215&amp;"|"&amp;$B215&amp;"|"&amp;$C215)</f>
+        <v/>
+      </c>
+      <c r="R215" s="59" t="n"/>
+      <c r="S215" s="60" t="n"/>
+    </row>
+    <row r="216" ht="15" customHeight="1" s="34">
+      <c r="A216" s="54" t="n"/>
+      <c r="B216" s="54" t="n"/>
+      <c r="C216" s="54" t="n"/>
+      <c r="D216" s="55">
+        <f>IF($A216="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C216,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E216" s="55">
+        <f>IF($A216="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C216,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F216" s="56">
+        <f>IF($A216="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C216,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G216" s="57" t="n"/>
+      <c r="H216" s="54" t="n"/>
+      <c r="I216" s="54" t="n"/>
+      <c r="J216" s="39">
+        <f>IF($A216="","",IF($E216="Informational","GREEN",IF($G216="",IF($E216="Mandatory","RED","YELLOW"),IF($N216="Exact",IF(UPPER(TRIM($G216&amp;""))=UPPER(TRIM($F216&amp;"")),"GREEN",$P216),IF(NOT(ISNUMBER($G216)),$P216,IF($N216="Min",IF($G216&gt;=$F216,"GREEN",IF($G216&gt;=$F216-$O216,"YELLOW",$P216)),IF($N216="Max",IF($G216&lt;=$F216,"GREEN",IF($G216&lt;=$F216+$O216,"YELLOW",$P216)),IF($N216="Range",IF(ABS($G216-$F216)&lt;=$O216,"GREEN",$P216),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K216" s="39">
+        <f>IF($A216="","",IF($H216="Non-Compliant","RED",IF(AND(OR($H216="Alternative Offer",$H216="Partially Compliant"),$J216="GREEN"),"YELLOW",IF(AND($J216="GREEN",ISNUMBER($R216),$R216&lt;Baseline!$B$9),"YELLOW",$J216))))</f>
+        <v/>
+      </c>
+      <c r="L216" s="39">
+        <f>IF($A216="","",IF($K216="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A216,Exceptions!$C$5:$C$104,$B216,Exceptions!$D$5:$D$104,$C216,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K216)))</f>
+        <v/>
+      </c>
+      <c r="M216" s="39">
+        <f>IF($A216="","",IF($H216="","Declaration missing",IF($H216="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R216),$R216&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H216="Fully Compliant",$J216&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N216" s="58">
+        <f>IF($A216="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C216,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O216" s="58">
+        <f>IF($A216="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C216,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P216" s="58">
+        <f>IF($A216="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C216,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q216" s="58">
+        <f>IF($A216="","",$A216&amp;"|"&amp;$B216&amp;"|"&amp;$C216)</f>
+        <v/>
+      </c>
+      <c r="R216" s="59" t="n"/>
+      <c r="S216" s="60" t="n"/>
+    </row>
+    <row r="217" ht="15" customHeight="1" s="34">
+      <c r="A217" s="54" t="n"/>
+      <c r="B217" s="54" t="n"/>
+      <c r="C217" s="54" t="n"/>
+      <c r="D217" s="55">
+        <f>IF($A217="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C217,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E217" s="55">
+        <f>IF($A217="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C217,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F217" s="56">
+        <f>IF($A217="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C217,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G217" s="57" t="n"/>
+      <c r="H217" s="54" t="n"/>
+      <c r="I217" s="54" t="n"/>
+      <c r="J217" s="39">
+        <f>IF($A217="","",IF($E217="Informational","GREEN",IF($G217="",IF($E217="Mandatory","RED","YELLOW"),IF($N217="Exact",IF(UPPER(TRIM($G217&amp;""))=UPPER(TRIM($F217&amp;"")),"GREEN",$P217),IF(NOT(ISNUMBER($G217)),$P217,IF($N217="Min",IF($G217&gt;=$F217,"GREEN",IF($G217&gt;=$F217-$O217,"YELLOW",$P217)),IF($N217="Max",IF($G217&lt;=$F217,"GREEN",IF($G217&lt;=$F217+$O217,"YELLOW",$P217)),IF($N217="Range",IF(ABS($G217-$F217)&lt;=$O217,"GREEN",$P217),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K217" s="39">
+        <f>IF($A217="","",IF($H217="Non-Compliant","RED",IF(AND(OR($H217="Alternative Offer",$H217="Partially Compliant"),$J217="GREEN"),"YELLOW",IF(AND($J217="GREEN",ISNUMBER($R217),$R217&lt;Baseline!$B$9),"YELLOW",$J217))))</f>
+        <v/>
+      </c>
+      <c r="L217" s="39">
+        <f>IF($A217="","",IF($K217="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A217,Exceptions!$C$5:$C$104,$B217,Exceptions!$D$5:$D$104,$C217,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K217)))</f>
+        <v/>
+      </c>
+      <c r="M217" s="39">
+        <f>IF($A217="","",IF($H217="","Declaration missing",IF($H217="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R217),$R217&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H217="Fully Compliant",$J217&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N217" s="58">
+        <f>IF($A217="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C217,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O217" s="58">
+        <f>IF($A217="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C217,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P217" s="58">
+        <f>IF($A217="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C217,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q217" s="58">
+        <f>IF($A217="","",$A217&amp;"|"&amp;$B217&amp;"|"&amp;$C217)</f>
+        <v/>
+      </c>
+      <c r="R217" s="59" t="n"/>
+      <c r="S217" s="60" t="n"/>
+    </row>
+    <row r="218" ht="15" customHeight="1" s="34">
+      <c r="A218" s="54" t="n"/>
+      <c r="B218" s="54" t="n"/>
+      <c r="C218" s="54" t="n"/>
+      <c r="D218" s="55">
+        <f>IF($A218="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C218,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E218" s="55">
+        <f>IF($A218="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C218,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F218" s="56">
+        <f>IF($A218="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C218,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G218" s="57" t="n"/>
+      <c r="H218" s="54" t="n"/>
+      <c r="I218" s="54" t="n"/>
+      <c r="J218" s="39">
+        <f>IF($A218="","",IF($E218="Informational","GREEN",IF($G218="",IF($E218="Mandatory","RED","YELLOW"),IF($N218="Exact",IF(UPPER(TRIM($G218&amp;""))=UPPER(TRIM($F218&amp;"")),"GREEN",$P218),IF(NOT(ISNUMBER($G218)),$P218,IF($N218="Min",IF($G218&gt;=$F218,"GREEN",IF($G218&gt;=$F218-$O218,"YELLOW",$P218)),IF($N218="Max",IF($G218&lt;=$F218,"GREEN",IF($G218&lt;=$F218+$O218,"YELLOW",$P218)),IF($N218="Range",IF(ABS($G218-$F218)&lt;=$O218,"GREEN",$P218),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K218" s="39">
+        <f>IF($A218="","",IF($H218="Non-Compliant","RED",IF(AND(OR($H218="Alternative Offer",$H218="Partially Compliant"),$J218="GREEN"),"YELLOW",IF(AND($J218="GREEN",ISNUMBER($R218),$R218&lt;Baseline!$B$9),"YELLOW",$J218))))</f>
+        <v/>
+      </c>
+      <c r="L218" s="39">
+        <f>IF($A218="","",IF($K218="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A218,Exceptions!$C$5:$C$104,$B218,Exceptions!$D$5:$D$104,$C218,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K218)))</f>
+        <v/>
+      </c>
+      <c r="M218" s="39">
+        <f>IF($A218="","",IF($H218="","Declaration missing",IF($H218="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R218),$R218&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H218="Fully Compliant",$J218&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N218" s="58">
+        <f>IF($A218="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C218,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O218" s="58">
+        <f>IF($A218="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C218,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P218" s="58">
+        <f>IF($A218="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C218,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q218" s="58">
+        <f>IF($A218="","",$A218&amp;"|"&amp;$B218&amp;"|"&amp;$C218)</f>
+        <v/>
+      </c>
+      <c r="R218" s="59" t="n"/>
+      <c r="S218" s="60" t="n"/>
+    </row>
+    <row r="219" ht="15" customHeight="1" s="34">
+      <c r="A219" s="54" t="n"/>
+      <c r="B219" s="54" t="n"/>
+      <c r="C219" s="54" t="n"/>
+      <c r="D219" s="55">
+        <f>IF($A219="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C219,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E219" s="55">
+        <f>IF($A219="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C219,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F219" s="56">
+        <f>IF($A219="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C219,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G219" s="57" t="n"/>
+      <c r="H219" s="54" t="n"/>
+      <c r="I219" s="54" t="n"/>
+      <c r="J219" s="39">
+        <f>IF($A219="","",IF($E219="Informational","GREEN",IF($G219="",IF($E219="Mandatory","RED","YELLOW"),IF($N219="Exact",IF(UPPER(TRIM($G219&amp;""))=UPPER(TRIM($F219&amp;"")),"GREEN",$P219),IF(NOT(ISNUMBER($G219)),$P219,IF($N219="Min",IF($G219&gt;=$F219,"GREEN",IF($G219&gt;=$F219-$O219,"YELLOW",$P219)),IF($N219="Max",IF($G219&lt;=$F219,"GREEN",IF($G219&lt;=$F219+$O219,"YELLOW",$P219)),IF($N219="Range",IF(ABS($G219-$F219)&lt;=$O219,"GREEN",$P219),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K219" s="39">
+        <f>IF($A219="","",IF($H219="Non-Compliant","RED",IF(AND(OR($H219="Alternative Offer",$H219="Partially Compliant"),$J219="GREEN"),"YELLOW",IF(AND($J219="GREEN",ISNUMBER($R219),$R219&lt;Baseline!$B$9),"YELLOW",$J219))))</f>
+        <v/>
+      </c>
+      <c r="L219" s="39">
+        <f>IF($A219="","",IF($K219="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A219,Exceptions!$C$5:$C$104,$B219,Exceptions!$D$5:$D$104,$C219,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K219)))</f>
+        <v/>
+      </c>
+      <c r="M219" s="39">
+        <f>IF($A219="","",IF($H219="","Declaration missing",IF($H219="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R219),$R219&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H219="Fully Compliant",$J219&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N219" s="58">
+        <f>IF($A219="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C219,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O219" s="58">
+        <f>IF($A219="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C219,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P219" s="58">
+        <f>IF($A219="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C219,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q219" s="58">
+        <f>IF($A219="","",$A219&amp;"|"&amp;$B219&amp;"|"&amp;$C219)</f>
+        <v/>
+      </c>
+      <c r="R219" s="59" t="n"/>
+      <c r="S219" s="60" t="n"/>
+    </row>
+    <row r="220" ht="15" customHeight="1" s="34">
+      <c r="A220" s="54" t="n"/>
+      <c r="B220" s="54" t="n"/>
+      <c r="C220" s="54" t="n"/>
+      <c r="D220" s="55">
+        <f>IF($A220="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C220,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E220" s="55">
+        <f>IF($A220="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C220,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F220" s="56">
+        <f>IF($A220="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C220,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G220" s="57" t="n"/>
+      <c r="H220" s="54" t="n"/>
+      <c r="I220" s="54" t="n"/>
+      <c r="J220" s="39">
+        <f>IF($A220="","",IF($E220="Informational","GREEN",IF($G220="",IF($E220="Mandatory","RED","YELLOW"),IF($N220="Exact",IF(UPPER(TRIM($G220&amp;""))=UPPER(TRIM($F220&amp;"")),"GREEN",$P220),IF(NOT(ISNUMBER($G220)),$P220,IF($N220="Min",IF($G220&gt;=$F220,"GREEN",IF($G220&gt;=$F220-$O220,"YELLOW",$P220)),IF($N220="Max",IF($G220&lt;=$F220,"GREEN",IF($G220&lt;=$F220+$O220,"YELLOW",$P220)),IF($N220="Range",IF(ABS($G220-$F220)&lt;=$O220,"GREEN",$P220),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K220" s="39">
+        <f>IF($A220="","",IF($H220="Non-Compliant","RED",IF(AND(OR($H220="Alternative Offer",$H220="Partially Compliant"),$J220="GREEN"),"YELLOW",IF(AND($J220="GREEN",ISNUMBER($R220),$R220&lt;Baseline!$B$9),"YELLOW",$J220))))</f>
+        <v/>
+      </c>
+      <c r="L220" s="39">
+        <f>IF($A220="","",IF($K220="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A220,Exceptions!$C$5:$C$104,$B220,Exceptions!$D$5:$D$104,$C220,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K220)))</f>
+        <v/>
+      </c>
+      <c r="M220" s="39">
+        <f>IF($A220="","",IF($H220="","Declaration missing",IF($H220="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R220),$R220&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H220="Fully Compliant",$J220&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N220" s="58">
+        <f>IF($A220="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C220,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O220" s="58">
+        <f>IF($A220="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C220,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P220" s="58">
+        <f>IF($A220="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C220,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q220" s="58">
+        <f>IF($A220="","",$A220&amp;"|"&amp;$B220&amp;"|"&amp;$C220)</f>
+        <v/>
+      </c>
+      <c r="R220" s="59" t="n"/>
+      <c r="S220" s="60" t="n"/>
+    </row>
+    <row r="221" ht="15" customHeight="1" s="34">
+      <c r="A221" s="54" t="n"/>
+      <c r="B221" s="54" t="n"/>
+      <c r="C221" s="54" t="n"/>
+      <c r="D221" s="55">
+        <f>IF($A221="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C221,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E221" s="55">
+        <f>IF($A221="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C221,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F221" s="56">
+        <f>IF($A221="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C221,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G221" s="57" t="n"/>
+      <c r="H221" s="54" t="n"/>
+      <c r="I221" s="54" t="n"/>
+      <c r="J221" s="39">
+        <f>IF($A221="","",IF($E221="Informational","GREEN",IF($G221="",IF($E221="Mandatory","RED","YELLOW"),IF($N221="Exact",IF(UPPER(TRIM($G221&amp;""))=UPPER(TRIM($F221&amp;"")),"GREEN",$P221),IF(NOT(ISNUMBER($G221)),$P221,IF($N221="Min",IF($G221&gt;=$F221,"GREEN",IF($G221&gt;=$F221-$O221,"YELLOW",$P221)),IF($N221="Max",IF($G221&lt;=$F221,"GREEN",IF($G221&lt;=$F221+$O221,"YELLOW",$P221)),IF($N221="Range",IF(ABS($G221-$F221)&lt;=$O221,"GREEN",$P221),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K221" s="39">
+        <f>IF($A221="","",IF($H221="Non-Compliant","RED",IF(AND(OR($H221="Alternative Offer",$H221="Partially Compliant"),$J221="GREEN"),"YELLOW",IF(AND($J221="GREEN",ISNUMBER($R221),$R221&lt;Baseline!$B$9),"YELLOW",$J221))))</f>
+        <v/>
+      </c>
+      <c r="L221" s="39">
+        <f>IF($A221="","",IF($K221="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A221,Exceptions!$C$5:$C$104,$B221,Exceptions!$D$5:$D$104,$C221,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K221)))</f>
+        <v/>
+      </c>
+      <c r="M221" s="39">
+        <f>IF($A221="","",IF($H221="","Declaration missing",IF($H221="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R221),$R221&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H221="Fully Compliant",$J221&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N221" s="58">
+        <f>IF($A221="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C221,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O221" s="58">
+        <f>IF($A221="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C221,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P221" s="58">
+        <f>IF($A221="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C221,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q221" s="58">
+        <f>IF($A221="","",$A221&amp;"|"&amp;$B221&amp;"|"&amp;$C221)</f>
+        <v/>
+      </c>
+      <c r="R221" s="59" t="n"/>
+      <c r="S221" s="60" t="n"/>
+    </row>
+    <row r="222" ht="15" customHeight="1" s="34">
+      <c r="A222" s="54" t="n"/>
+      <c r="B222" s="54" t="n"/>
+      <c r="C222" s="54" t="n"/>
+      <c r="D222" s="55">
+        <f>IF($A222="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C222,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E222" s="55">
+        <f>IF($A222="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C222,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F222" s="56">
+        <f>IF($A222="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C222,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G222" s="57" t="n"/>
+      <c r="H222" s="54" t="n"/>
+      <c r="I222" s="54" t="n"/>
+      <c r="J222" s="39">
+        <f>IF($A222="","",IF($E222="Informational","GREEN",IF($G222="",IF($E222="Mandatory","RED","YELLOW"),IF($N222="Exact",IF(UPPER(TRIM($G222&amp;""))=UPPER(TRIM($F222&amp;"")),"GREEN",$P222),IF(NOT(ISNUMBER($G222)),$P222,IF($N222="Min",IF($G222&gt;=$F222,"GREEN",IF($G222&gt;=$F222-$O222,"YELLOW",$P222)),IF($N222="Max",IF($G222&lt;=$F222,"GREEN",IF($G222&lt;=$F222+$O222,"YELLOW",$P222)),IF($N222="Range",IF(ABS($G222-$F222)&lt;=$O222,"GREEN",$P222),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K222" s="39">
+        <f>IF($A222="","",IF($H222="Non-Compliant","RED",IF(AND(OR($H222="Alternative Offer",$H222="Partially Compliant"),$J222="GREEN"),"YELLOW",IF(AND($J222="GREEN",ISNUMBER($R222),$R222&lt;Baseline!$B$9),"YELLOW",$J222))))</f>
+        <v/>
+      </c>
+      <c r="L222" s="39">
+        <f>IF($A222="","",IF($K222="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A222,Exceptions!$C$5:$C$104,$B222,Exceptions!$D$5:$D$104,$C222,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K222)))</f>
+        <v/>
+      </c>
+      <c r="M222" s="39">
+        <f>IF($A222="","",IF($H222="","Declaration missing",IF($H222="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R222),$R222&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H222="Fully Compliant",$J222&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N222" s="58">
+        <f>IF($A222="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C222,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O222" s="58">
+        <f>IF($A222="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C222,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P222" s="58">
+        <f>IF($A222="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C222,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q222" s="58">
+        <f>IF($A222="","",$A222&amp;"|"&amp;$B222&amp;"|"&amp;$C222)</f>
+        <v/>
+      </c>
+      <c r="R222" s="59" t="n"/>
+      <c r="S222" s="60" t="n"/>
+    </row>
+    <row r="223" ht="15" customHeight="1" s="34">
+      <c r="A223" s="54" t="n"/>
+      <c r="B223" s="54" t="n"/>
+      <c r="C223" s="54" t="n"/>
+      <c r="D223" s="55">
+        <f>IF($A223="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C223,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E223" s="55">
+        <f>IF($A223="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C223,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F223" s="56">
+        <f>IF($A223="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C223,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G223" s="57" t="n"/>
+      <c r="H223" s="54" t="n"/>
+      <c r="I223" s="54" t="n"/>
+      <c r="J223" s="39">
+        <f>IF($A223="","",IF($E223="Informational","GREEN",IF($G223="",IF($E223="Mandatory","RED","YELLOW"),IF($N223="Exact",IF(UPPER(TRIM($G223&amp;""))=UPPER(TRIM($F223&amp;"")),"GREEN",$P223),IF(NOT(ISNUMBER($G223)),$P223,IF($N223="Min",IF($G223&gt;=$F223,"GREEN",IF($G223&gt;=$F223-$O223,"YELLOW",$P223)),IF($N223="Max",IF($G223&lt;=$F223,"GREEN",IF($G223&lt;=$F223+$O223,"YELLOW",$P223)),IF($N223="Range",IF(ABS($G223-$F223)&lt;=$O223,"GREEN",$P223),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K223" s="39">
+        <f>IF($A223="","",IF($H223="Non-Compliant","RED",IF(AND(OR($H223="Alternative Offer",$H223="Partially Compliant"),$J223="GREEN"),"YELLOW",IF(AND($J223="GREEN",ISNUMBER($R223),$R223&lt;Baseline!$B$9),"YELLOW",$J223))))</f>
+        <v/>
+      </c>
+      <c r="L223" s="39">
+        <f>IF($A223="","",IF($K223="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A223,Exceptions!$C$5:$C$104,$B223,Exceptions!$D$5:$D$104,$C223,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K223)))</f>
+        <v/>
+      </c>
+      <c r="M223" s="39">
+        <f>IF($A223="","",IF($H223="","Declaration missing",IF($H223="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R223),$R223&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H223="Fully Compliant",$J223&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N223" s="58">
+        <f>IF($A223="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C223,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O223" s="58">
+        <f>IF($A223="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C223,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P223" s="58">
+        <f>IF($A223="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C223,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q223" s="58">
+        <f>IF($A223="","",$A223&amp;"|"&amp;$B223&amp;"|"&amp;$C223)</f>
+        <v/>
+      </c>
+      <c r="R223" s="59" t="n"/>
+      <c r="S223" s="60" t="n"/>
+    </row>
+    <row r="224" ht="15" customHeight="1" s="34">
+      <c r="A224" s="54" t="n"/>
+      <c r="B224" s="54" t="n"/>
+      <c r="C224" s="54" t="n"/>
+      <c r="D224" s="55">
+        <f>IF($A224="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C224,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E224" s="55">
+        <f>IF($A224="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C224,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F224" s="56">
+        <f>IF($A224="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C224,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G224" s="57" t="n"/>
+      <c r="H224" s="54" t="n"/>
+      <c r="I224" s="54" t="n"/>
+      <c r="J224" s="39">
+        <f>IF($A224="","",IF($E224="Informational","GREEN",IF($G224="",IF($E224="Mandatory","RED","YELLOW"),IF($N224="Exact",IF(UPPER(TRIM($G224&amp;""))=UPPER(TRIM($F224&amp;"")),"GREEN",$P224),IF(NOT(ISNUMBER($G224)),$P224,IF($N224="Min",IF($G224&gt;=$F224,"GREEN",IF($G224&gt;=$F224-$O224,"YELLOW",$P224)),IF($N224="Max",IF($G224&lt;=$F224,"GREEN",IF($G224&lt;=$F224+$O224,"YELLOW",$P224)),IF($N224="Range",IF(ABS($G224-$F224)&lt;=$O224,"GREEN",$P224),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K224" s="39">
+        <f>IF($A224="","",IF($H224="Non-Compliant","RED",IF(AND(OR($H224="Alternative Offer",$H224="Partially Compliant"),$J224="GREEN"),"YELLOW",IF(AND($J224="GREEN",ISNUMBER($R224),$R224&lt;Baseline!$B$9),"YELLOW",$J224))))</f>
+        <v/>
+      </c>
+      <c r="L224" s="39">
+        <f>IF($A224="","",IF($K224="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A224,Exceptions!$C$5:$C$104,$B224,Exceptions!$D$5:$D$104,$C224,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K224)))</f>
+        <v/>
+      </c>
+      <c r="M224" s="39">
+        <f>IF($A224="","",IF($H224="","Declaration missing",IF($H224="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R224),$R224&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H224="Fully Compliant",$J224&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N224" s="58">
+        <f>IF($A224="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C224,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O224" s="58">
+        <f>IF($A224="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C224,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P224" s="58">
+        <f>IF($A224="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C224,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q224" s="58">
+        <f>IF($A224="","",$A224&amp;"|"&amp;$B224&amp;"|"&amp;$C224)</f>
+        <v/>
+      </c>
+      <c r="R224" s="59" t="n"/>
+      <c r="S224" s="60" t="n"/>
+    </row>
+    <row r="225" ht="15" customHeight="1" s="34">
+      <c r="A225" s="54" t="n"/>
+      <c r="B225" s="54" t="n"/>
+      <c r="C225" s="54" t="n"/>
+      <c r="D225" s="55">
+        <f>IF($A225="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C225,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E225" s="55">
+        <f>IF($A225="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C225,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F225" s="56">
+        <f>IF($A225="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C225,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G225" s="57" t="n"/>
+      <c r="H225" s="54" t="n"/>
+      <c r="I225" s="54" t="n"/>
+      <c r="J225" s="39">
+        <f>IF($A225="","",IF($E225="Informational","GREEN",IF($G225="",IF($E225="Mandatory","RED","YELLOW"),IF($N225="Exact",IF(UPPER(TRIM($G225&amp;""))=UPPER(TRIM($F225&amp;"")),"GREEN",$P225),IF(NOT(ISNUMBER($G225)),$P225,IF($N225="Min",IF($G225&gt;=$F225,"GREEN",IF($G225&gt;=$F225-$O225,"YELLOW",$P225)),IF($N225="Max",IF($G225&lt;=$F225,"GREEN",IF($G225&lt;=$F225+$O225,"YELLOW",$P225)),IF($N225="Range",IF(ABS($G225-$F225)&lt;=$O225,"GREEN",$P225),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K225" s="39">
+        <f>IF($A225="","",IF($H225="Non-Compliant","RED",IF(AND(OR($H225="Alternative Offer",$H225="Partially Compliant"),$J225="GREEN"),"YELLOW",IF(AND($J225="GREEN",ISNUMBER($R225),$R225&lt;Baseline!$B$9),"YELLOW",$J225))))</f>
+        <v/>
+      </c>
+      <c r="L225" s="39">
+        <f>IF($A225="","",IF($K225="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A225,Exceptions!$C$5:$C$104,$B225,Exceptions!$D$5:$D$104,$C225,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K225)))</f>
+        <v/>
+      </c>
+      <c r="M225" s="39">
+        <f>IF($A225="","",IF($H225="","Declaration missing",IF($H225="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R225),$R225&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H225="Fully Compliant",$J225&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N225" s="58">
+        <f>IF($A225="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C225,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O225" s="58">
+        <f>IF($A225="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C225,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P225" s="58">
+        <f>IF($A225="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C225,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q225" s="58">
+        <f>IF($A225="","",$A225&amp;"|"&amp;$B225&amp;"|"&amp;$C225)</f>
+        <v/>
+      </c>
+      <c r="R225" s="59" t="n"/>
+      <c r="S225" s="60" t="n"/>
+    </row>
+    <row r="226" ht="15" customHeight="1" s="34">
+      <c r="A226" s="54" t="n"/>
+      <c r="B226" s="54" t="n"/>
+      <c r="C226" s="54" t="n"/>
+      <c r="D226" s="55">
+        <f>IF($A226="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C226,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E226" s="55">
+        <f>IF($A226="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C226,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F226" s="56">
+        <f>IF($A226="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C226,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G226" s="57" t="n"/>
+      <c r="H226" s="54" t="n"/>
+      <c r="I226" s="54" t="n"/>
+      <c r="J226" s="39">
+        <f>IF($A226="","",IF($E226="Informational","GREEN",IF($G226="",IF($E226="Mandatory","RED","YELLOW"),IF($N226="Exact",IF(UPPER(TRIM($G226&amp;""))=UPPER(TRIM($F226&amp;"")),"GREEN",$P226),IF(NOT(ISNUMBER($G226)),$P226,IF($N226="Min",IF($G226&gt;=$F226,"GREEN",IF($G226&gt;=$F226-$O226,"YELLOW",$P226)),IF($N226="Max",IF($G226&lt;=$F226,"GREEN",IF($G226&lt;=$F226+$O226,"YELLOW",$P226)),IF($N226="Range",IF(ABS($G226-$F226)&lt;=$O226,"GREEN",$P226),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K226" s="39">
+        <f>IF($A226="","",IF($H226="Non-Compliant","RED",IF(AND(OR($H226="Alternative Offer",$H226="Partially Compliant"),$J226="GREEN"),"YELLOW",IF(AND($J226="GREEN",ISNUMBER($R226),$R226&lt;Baseline!$B$9),"YELLOW",$J226))))</f>
+        <v/>
+      </c>
+      <c r="L226" s="39">
+        <f>IF($A226="","",IF($K226="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A226,Exceptions!$C$5:$C$104,$B226,Exceptions!$D$5:$D$104,$C226,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K226)))</f>
+        <v/>
+      </c>
+      <c r="M226" s="39">
+        <f>IF($A226="","",IF($H226="","Declaration missing",IF($H226="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R226),$R226&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H226="Fully Compliant",$J226&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N226" s="58">
+        <f>IF($A226="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C226,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O226" s="58">
+        <f>IF($A226="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C226,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P226" s="58">
+        <f>IF($A226="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C226,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q226" s="58">
+        <f>IF($A226="","",$A226&amp;"|"&amp;$B226&amp;"|"&amp;$C226)</f>
+        <v/>
+      </c>
+      <c r="R226" s="59" t="n"/>
+      <c r="S226" s="60" t="n"/>
+    </row>
+    <row r="227" ht="15" customHeight="1" s="34">
+      <c r="A227" s="54" t="n"/>
+      <c r="B227" s="54" t="n"/>
+      <c r="C227" s="54" t="n"/>
+      <c r="D227" s="55">
+        <f>IF($A227="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C227,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E227" s="55">
+        <f>IF($A227="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C227,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F227" s="56">
+        <f>IF($A227="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C227,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G227" s="57" t="n"/>
+      <c r="H227" s="54" t="n"/>
+      <c r="I227" s="54" t="n"/>
+      <c r="J227" s="39">
+        <f>IF($A227="","",IF($E227="Informational","GREEN",IF($G227="",IF($E227="Mandatory","RED","YELLOW"),IF($N227="Exact",IF(UPPER(TRIM($G227&amp;""))=UPPER(TRIM($F227&amp;"")),"GREEN",$P227),IF(NOT(ISNUMBER($G227)),$P227,IF($N227="Min",IF($G227&gt;=$F227,"GREEN",IF($G227&gt;=$F227-$O227,"YELLOW",$P227)),IF($N227="Max",IF($G227&lt;=$F227,"GREEN",IF($G227&lt;=$F227+$O227,"YELLOW",$P227)),IF($N227="Range",IF(ABS($G227-$F227)&lt;=$O227,"GREEN",$P227),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K227" s="39">
+        <f>IF($A227="","",IF($H227="Non-Compliant","RED",IF(AND(OR($H227="Alternative Offer",$H227="Partially Compliant"),$J227="GREEN"),"YELLOW",IF(AND($J227="GREEN",ISNUMBER($R227),$R227&lt;Baseline!$B$9),"YELLOW",$J227))))</f>
+        <v/>
+      </c>
+      <c r="L227" s="39">
+        <f>IF($A227="","",IF($K227="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A227,Exceptions!$C$5:$C$104,$B227,Exceptions!$D$5:$D$104,$C227,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K227)))</f>
+        <v/>
+      </c>
+      <c r="M227" s="39">
+        <f>IF($A227="","",IF($H227="","Declaration missing",IF($H227="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R227),$R227&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H227="Fully Compliant",$J227&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N227" s="58">
+        <f>IF($A227="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C227,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O227" s="58">
+        <f>IF($A227="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C227,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P227" s="58">
+        <f>IF($A227="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C227,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q227" s="58">
+        <f>IF($A227="","",$A227&amp;"|"&amp;$B227&amp;"|"&amp;$C227)</f>
+        <v/>
+      </c>
+      <c r="R227" s="59" t="n"/>
+      <c r="S227" s="60" t="n"/>
+    </row>
+    <row r="228" ht="15" customHeight="1" s="34">
+      <c r="A228" s="54" t="n"/>
+      <c r="B228" s="54" t="n"/>
+      <c r="C228" s="54" t="n"/>
+      <c r="D228" s="55">
+        <f>IF($A228="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C228,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E228" s="55">
+        <f>IF($A228="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C228,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F228" s="56">
+        <f>IF($A228="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C228,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G228" s="57" t="n"/>
+      <c r="H228" s="54" t="n"/>
+      <c r="I228" s="54" t="n"/>
+      <c r="J228" s="39">
+        <f>IF($A228="","",IF($E228="Informational","GREEN",IF($G228="",IF($E228="Mandatory","RED","YELLOW"),IF($N228="Exact",IF(UPPER(TRIM($G228&amp;""))=UPPER(TRIM($F228&amp;"")),"GREEN",$P228),IF(NOT(ISNUMBER($G228)),$P228,IF($N228="Min",IF($G228&gt;=$F228,"GREEN",IF($G228&gt;=$F228-$O228,"YELLOW",$P228)),IF($N228="Max",IF($G228&lt;=$F228,"GREEN",IF($G228&lt;=$F228+$O228,"YELLOW",$P228)),IF($N228="Range",IF(ABS($G228-$F228)&lt;=$O228,"GREEN",$P228),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K228" s="39">
+        <f>IF($A228="","",IF($H228="Non-Compliant","RED",IF(AND(OR($H228="Alternative Offer",$H228="Partially Compliant"),$J228="GREEN"),"YELLOW",IF(AND($J228="GREEN",ISNUMBER($R228),$R228&lt;Baseline!$B$9),"YELLOW",$J228))))</f>
+        <v/>
+      </c>
+      <c r="L228" s="39">
+        <f>IF($A228="","",IF($K228="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A228,Exceptions!$C$5:$C$104,$B228,Exceptions!$D$5:$D$104,$C228,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K228)))</f>
+        <v/>
+      </c>
+      <c r="M228" s="39">
+        <f>IF($A228="","",IF($H228="","Declaration missing",IF($H228="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R228),$R228&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H228="Fully Compliant",$J228&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N228" s="58">
+        <f>IF($A228="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C228,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O228" s="58">
+        <f>IF($A228="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C228,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P228" s="58">
+        <f>IF($A228="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C228,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q228" s="58">
+        <f>IF($A228="","",$A228&amp;"|"&amp;$B228&amp;"|"&amp;$C228)</f>
+        <v/>
+      </c>
+      <c r="R228" s="59" t="n"/>
+      <c r="S228" s="60" t="n"/>
+    </row>
+    <row r="229" ht="15" customHeight="1" s="34">
+      <c r="A229" s="54" t="n"/>
+      <c r="B229" s="54" t="n"/>
+      <c r="C229" s="54" t="n"/>
+      <c r="D229" s="55">
+        <f>IF($A229="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C229,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E229" s="55">
+        <f>IF($A229="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C229,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F229" s="56">
+        <f>IF($A229="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C229,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G229" s="57" t="n"/>
+      <c r="H229" s="54" t="n"/>
+      <c r="I229" s="54" t="n"/>
+      <c r="J229" s="39">
+        <f>IF($A229="","",IF($E229="Informational","GREEN",IF($G229="",IF($E229="Mandatory","RED","YELLOW"),IF($N229="Exact",IF(UPPER(TRIM($G229&amp;""))=UPPER(TRIM($F229&amp;"")),"GREEN",$P229),IF(NOT(ISNUMBER($G229)),$P229,IF($N229="Min",IF($G229&gt;=$F229,"GREEN",IF($G229&gt;=$F229-$O229,"YELLOW",$P229)),IF($N229="Max",IF($G229&lt;=$F229,"GREEN",IF($G229&lt;=$F229+$O229,"YELLOW",$P229)),IF($N229="Range",IF(ABS($G229-$F229)&lt;=$O229,"GREEN",$P229),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K229" s="39">
+        <f>IF($A229="","",IF($H229="Non-Compliant","RED",IF(AND(OR($H229="Alternative Offer",$H229="Partially Compliant"),$J229="GREEN"),"YELLOW",IF(AND($J229="GREEN",ISNUMBER($R229),$R229&lt;Baseline!$B$9),"YELLOW",$J229))))</f>
+        <v/>
+      </c>
+      <c r="L229" s="39">
+        <f>IF($A229="","",IF($K229="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A229,Exceptions!$C$5:$C$104,$B229,Exceptions!$D$5:$D$104,$C229,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K229)))</f>
+        <v/>
+      </c>
+      <c r="M229" s="39">
+        <f>IF($A229="","",IF($H229="","Declaration missing",IF($H229="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R229),$R229&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H229="Fully Compliant",$J229&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N229" s="58">
+        <f>IF($A229="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C229,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O229" s="58">
+        <f>IF($A229="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C229,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P229" s="58">
+        <f>IF($A229="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C229,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q229" s="58">
+        <f>IF($A229="","",$A229&amp;"|"&amp;$B229&amp;"|"&amp;$C229)</f>
+        <v/>
+      </c>
+      <c r="R229" s="59" t="n"/>
+      <c r="S229" s="60" t="n"/>
+    </row>
+    <row r="230" ht="15" customHeight="1" s="34">
+      <c r="A230" s="54" t="n"/>
+      <c r="B230" s="54" t="n"/>
+      <c r="C230" s="54" t="n"/>
+      <c r="D230" s="55">
+        <f>IF($A230="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C230,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E230" s="55">
+        <f>IF($A230="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C230,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F230" s="56">
+        <f>IF($A230="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C230,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G230" s="57" t="n"/>
+      <c r="H230" s="54" t="n"/>
+      <c r="I230" s="54" t="n"/>
+      <c r="J230" s="39">
+        <f>IF($A230="","",IF($E230="Informational","GREEN",IF($G230="",IF($E230="Mandatory","RED","YELLOW"),IF($N230="Exact",IF(UPPER(TRIM($G230&amp;""))=UPPER(TRIM($F230&amp;"")),"GREEN",$P230),IF(NOT(ISNUMBER($G230)),$P230,IF($N230="Min",IF($G230&gt;=$F230,"GREEN",IF($G230&gt;=$F230-$O230,"YELLOW",$P230)),IF($N230="Max",IF($G230&lt;=$F230,"GREEN",IF($G230&lt;=$F230+$O230,"YELLOW",$P230)),IF($N230="Range",IF(ABS($G230-$F230)&lt;=$O230,"GREEN",$P230),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K230" s="39">
+        <f>IF($A230="","",IF($H230="Non-Compliant","RED",IF(AND(OR($H230="Alternative Offer",$H230="Partially Compliant"),$J230="GREEN"),"YELLOW",IF(AND($J230="GREEN",ISNUMBER($R230),$R230&lt;Baseline!$B$9),"YELLOW",$J230))))</f>
+        <v/>
+      </c>
+      <c r="L230" s="39">
+        <f>IF($A230="","",IF($K230="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A230,Exceptions!$C$5:$C$104,$B230,Exceptions!$D$5:$D$104,$C230,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K230)))</f>
+        <v/>
+      </c>
+      <c r="M230" s="39">
+        <f>IF($A230="","",IF($H230="","Declaration missing",IF($H230="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R230),$R230&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H230="Fully Compliant",$J230&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N230" s="58">
+        <f>IF($A230="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C230,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O230" s="58">
+        <f>IF($A230="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C230,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P230" s="58">
+        <f>IF($A230="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C230,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q230" s="58">
+        <f>IF($A230="","",$A230&amp;"|"&amp;$B230&amp;"|"&amp;$C230)</f>
+        <v/>
+      </c>
+      <c r="R230" s="59" t="n"/>
+      <c r="S230" s="60" t="n"/>
+    </row>
+    <row r="231" ht="15" customHeight="1" s="34">
+      <c r="A231" s="54" t="n"/>
+      <c r="B231" s="54" t="n"/>
+      <c r="C231" s="54" t="n"/>
+      <c r="D231" s="55">
+        <f>IF($A231="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C231,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E231" s="55">
+        <f>IF($A231="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C231,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F231" s="56">
+        <f>IF($A231="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C231,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G231" s="57" t="n"/>
+      <c r="H231" s="54" t="n"/>
+      <c r="I231" s="54" t="n"/>
+      <c r="J231" s="39">
+        <f>IF($A231="","",IF($E231="Informational","GREEN",IF($G231="",IF($E231="Mandatory","RED","YELLOW"),IF($N231="Exact",IF(UPPER(TRIM($G231&amp;""))=UPPER(TRIM($F231&amp;"")),"GREEN",$P231),IF(NOT(ISNUMBER($G231)),$P231,IF($N231="Min",IF($G231&gt;=$F231,"GREEN",IF($G231&gt;=$F231-$O231,"YELLOW",$P231)),IF($N231="Max",IF($G231&lt;=$F231,"GREEN",IF($G231&lt;=$F231+$O231,"YELLOW",$P231)),IF($N231="Range",IF(ABS($G231-$F231)&lt;=$O231,"GREEN",$P231),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K231" s="39">
+        <f>IF($A231="","",IF($H231="Non-Compliant","RED",IF(AND(OR($H231="Alternative Offer",$H231="Partially Compliant"),$J231="GREEN"),"YELLOW",IF(AND($J231="GREEN",ISNUMBER($R231),$R231&lt;Baseline!$B$9),"YELLOW",$J231))))</f>
+        <v/>
+      </c>
+      <c r="L231" s="39">
+        <f>IF($A231="","",IF($K231="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A231,Exceptions!$C$5:$C$104,$B231,Exceptions!$D$5:$D$104,$C231,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K231)))</f>
+        <v/>
+      </c>
+      <c r="M231" s="39">
+        <f>IF($A231="","",IF($H231="","Declaration missing",IF($H231="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R231),$R231&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H231="Fully Compliant",$J231&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N231" s="58">
+        <f>IF($A231="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C231,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O231" s="58">
+        <f>IF($A231="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C231,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P231" s="58">
+        <f>IF($A231="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C231,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q231" s="58">
+        <f>IF($A231="","",$A231&amp;"|"&amp;$B231&amp;"|"&amp;$C231)</f>
+        <v/>
+      </c>
+      <c r="R231" s="59" t="n"/>
+      <c r="S231" s="60" t="n"/>
+    </row>
+    <row r="232" ht="15" customHeight="1" s="34">
+      <c r="A232" s="54" t="n"/>
+      <c r="B232" s="54" t="n"/>
+      <c r="C232" s="54" t="n"/>
+      <c r="D232" s="55">
+        <f>IF($A232="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C232,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E232" s="55">
+        <f>IF($A232="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C232,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F232" s="56">
+        <f>IF($A232="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C232,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G232" s="57" t="n"/>
+      <c r="H232" s="54" t="n"/>
+      <c r="I232" s="54" t="n"/>
+      <c r="J232" s="39">
+        <f>IF($A232="","",IF($E232="Informational","GREEN",IF($G232="",IF($E232="Mandatory","RED","YELLOW"),IF($N232="Exact",IF(UPPER(TRIM($G232&amp;""))=UPPER(TRIM($F232&amp;"")),"GREEN",$P232),IF(NOT(ISNUMBER($G232)),$P232,IF($N232="Min",IF($G232&gt;=$F232,"GREEN",IF($G232&gt;=$F232-$O232,"YELLOW",$P232)),IF($N232="Max",IF($G232&lt;=$F232,"GREEN",IF($G232&lt;=$F232+$O232,"YELLOW",$P232)),IF($N232="Range",IF(ABS($G232-$F232)&lt;=$O232,"GREEN",$P232),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K232" s="39">
+        <f>IF($A232="","",IF($H232="Non-Compliant","RED",IF(AND(OR($H232="Alternative Offer",$H232="Partially Compliant"),$J232="GREEN"),"YELLOW",IF(AND($J232="GREEN",ISNUMBER($R232),$R232&lt;Baseline!$B$9),"YELLOW",$J232))))</f>
+        <v/>
+      </c>
+      <c r="L232" s="39">
+        <f>IF($A232="","",IF($K232="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A232,Exceptions!$C$5:$C$104,$B232,Exceptions!$D$5:$D$104,$C232,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K232)))</f>
+        <v/>
+      </c>
+      <c r="M232" s="39">
+        <f>IF($A232="","",IF($H232="","Declaration missing",IF($H232="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R232),$R232&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H232="Fully Compliant",$J232&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N232" s="58">
+        <f>IF($A232="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C232,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O232" s="58">
+        <f>IF($A232="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C232,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P232" s="58">
+        <f>IF($A232="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C232,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q232" s="58">
+        <f>IF($A232="","",$A232&amp;"|"&amp;$B232&amp;"|"&amp;$C232)</f>
+        <v/>
+      </c>
+      <c r="R232" s="59" t="n"/>
+      <c r="S232" s="60" t="n"/>
+    </row>
+    <row r="233" ht="15" customHeight="1" s="34">
+      <c r="A233" s="54" t="n"/>
+      <c r="B233" s="54" t="n"/>
+      <c r="C233" s="54" t="n"/>
+      <c r="D233" s="55">
+        <f>IF($A233="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C233,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E233" s="55">
+        <f>IF($A233="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C233,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F233" s="56">
+        <f>IF($A233="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C233,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G233" s="57" t="n"/>
+      <c r="H233" s="54" t="n"/>
+      <c r="I233" s="54" t="n"/>
+      <c r="J233" s="39">
+        <f>IF($A233="","",IF($E233="Informational","GREEN",IF($G233="",IF($E233="Mandatory","RED","YELLOW"),IF($N233="Exact",IF(UPPER(TRIM($G233&amp;""))=UPPER(TRIM($F233&amp;"")),"GREEN",$P233),IF(NOT(ISNUMBER($G233)),$P233,IF($N233="Min",IF($G233&gt;=$F233,"GREEN",IF($G233&gt;=$F233-$O233,"YELLOW",$P233)),IF($N233="Max",IF($G233&lt;=$F233,"GREEN",IF($G233&lt;=$F233+$O233,"YELLOW",$P233)),IF($N233="Range",IF(ABS($G233-$F233)&lt;=$O233,"GREEN",$P233),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K233" s="39">
+        <f>IF($A233="","",IF($H233="Non-Compliant","RED",IF(AND(OR($H233="Alternative Offer",$H233="Partially Compliant"),$J233="GREEN"),"YELLOW",IF(AND($J233="GREEN",ISNUMBER($R233),$R233&lt;Baseline!$B$9),"YELLOW",$J233))))</f>
+        <v/>
+      </c>
+      <c r="L233" s="39">
+        <f>IF($A233="","",IF($K233="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A233,Exceptions!$C$5:$C$104,$B233,Exceptions!$D$5:$D$104,$C233,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K233)))</f>
+        <v/>
+      </c>
+      <c r="M233" s="39">
+        <f>IF($A233="","",IF($H233="","Declaration missing",IF($H233="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R233),$R233&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H233="Fully Compliant",$J233&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N233" s="58">
+        <f>IF($A233="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C233,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O233" s="58">
+        <f>IF($A233="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C233,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P233" s="58">
+        <f>IF($A233="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C233,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q233" s="58">
+        <f>IF($A233="","",$A233&amp;"|"&amp;$B233&amp;"|"&amp;$C233)</f>
+        <v/>
+      </c>
+      <c r="R233" s="59" t="n"/>
+      <c r="S233" s="60" t="n"/>
+    </row>
+    <row r="234" ht="15" customHeight="1" s="34">
+      <c r="A234" s="54" t="n"/>
+      <c r="B234" s="54" t="n"/>
+      <c r="C234" s="54" t="n"/>
+      <c r="D234" s="55">
+        <f>IF($A234="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C234,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E234" s="55">
+        <f>IF($A234="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C234,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F234" s="56">
+        <f>IF($A234="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C234,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G234" s="57" t="n"/>
+      <c r="H234" s="54" t="n"/>
+      <c r="I234" s="54" t="n"/>
+      <c r="J234" s="39">
+        <f>IF($A234="","",IF($E234="Informational","GREEN",IF($G234="",IF($E234="Mandatory","RED","YELLOW"),IF($N234="Exact",IF(UPPER(TRIM($G234&amp;""))=UPPER(TRIM($F234&amp;"")),"GREEN",$P234),IF(NOT(ISNUMBER($G234)),$P234,IF($N234="Min",IF($G234&gt;=$F234,"GREEN",IF($G234&gt;=$F234-$O234,"YELLOW",$P234)),IF($N234="Max",IF($G234&lt;=$F234,"GREEN",IF($G234&lt;=$F234+$O234,"YELLOW",$P234)),IF($N234="Range",IF(ABS($G234-$F234)&lt;=$O234,"GREEN",$P234),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K234" s="39">
+        <f>IF($A234="","",IF($H234="Non-Compliant","RED",IF(AND(OR($H234="Alternative Offer",$H234="Partially Compliant"),$J234="GREEN"),"YELLOW",IF(AND($J234="GREEN",ISNUMBER($R234),$R234&lt;Baseline!$B$9),"YELLOW",$J234))))</f>
+        <v/>
+      </c>
+      <c r="L234" s="39">
+        <f>IF($A234="","",IF($K234="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A234,Exceptions!$C$5:$C$104,$B234,Exceptions!$D$5:$D$104,$C234,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K234)))</f>
+        <v/>
+      </c>
+      <c r="M234" s="39">
+        <f>IF($A234="","",IF($H234="","Declaration missing",IF($H234="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R234),$R234&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H234="Fully Compliant",$J234&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N234" s="58">
+        <f>IF($A234="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C234,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O234" s="58">
+        <f>IF($A234="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C234,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P234" s="58">
+        <f>IF($A234="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C234,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q234" s="58">
+        <f>IF($A234="","",$A234&amp;"|"&amp;$B234&amp;"|"&amp;$C234)</f>
+        <v/>
+      </c>
+      <c r="R234" s="59" t="n"/>
+      <c r="S234" s="60" t="n"/>
+    </row>
+    <row r="235" ht="15" customHeight="1" s="34">
+      <c r="A235" s="54" t="n"/>
+      <c r="B235" s="54" t="n"/>
+      <c r="C235" s="54" t="n"/>
+      <c r="D235" s="55">
+        <f>IF($A235="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C235,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E235" s="55">
+        <f>IF($A235="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C235,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F235" s="56">
+        <f>IF($A235="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C235,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G235" s="57" t="n"/>
+      <c r="H235" s="54" t="n"/>
+      <c r="I235" s="54" t="n"/>
+      <c r="J235" s="39">
+        <f>IF($A235="","",IF($E235="Informational","GREEN",IF($G235="",IF($E235="Mandatory","RED","YELLOW"),IF($N235="Exact",IF(UPPER(TRIM($G235&amp;""))=UPPER(TRIM($F235&amp;"")),"GREEN",$P235),IF(NOT(ISNUMBER($G235)),$P235,IF($N235="Min",IF($G235&gt;=$F235,"GREEN",IF($G235&gt;=$F235-$O235,"YELLOW",$P235)),IF($N235="Max",IF($G235&lt;=$F235,"GREEN",IF($G235&lt;=$F235+$O235,"YELLOW",$P235)),IF($N235="Range",IF(ABS($G235-$F235)&lt;=$O235,"GREEN",$P235),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K235" s="39">
+        <f>IF($A235="","",IF($H235="Non-Compliant","RED",IF(AND(OR($H235="Alternative Offer",$H235="Partially Compliant"),$J235="GREEN"),"YELLOW",IF(AND($J235="GREEN",ISNUMBER($R235),$R235&lt;Baseline!$B$9),"YELLOW",$J235))))</f>
+        <v/>
+      </c>
+      <c r="L235" s="39">
+        <f>IF($A235="","",IF($K235="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A235,Exceptions!$C$5:$C$104,$B235,Exceptions!$D$5:$D$104,$C235,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K235)))</f>
+        <v/>
+      </c>
+      <c r="M235" s="39">
+        <f>IF($A235="","",IF($H235="","Declaration missing",IF($H235="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R235),$R235&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H235="Fully Compliant",$J235&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N235" s="58">
+        <f>IF($A235="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C235,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O235" s="58">
+        <f>IF($A235="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C235,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P235" s="58">
+        <f>IF($A235="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C235,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q235" s="58">
+        <f>IF($A235="","",$A235&amp;"|"&amp;$B235&amp;"|"&amp;$C235)</f>
+        <v/>
+      </c>
+      <c r="R235" s="59" t="n"/>
+      <c r="S235" s="60" t="n"/>
+    </row>
+    <row r="236" ht="15" customHeight="1" s="34">
+      <c r="A236" s="54" t="n"/>
+      <c r="B236" s="54" t="n"/>
+      <c r="C236" s="54" t="n"/>
+      <c r="D236" s="55">
+        <f>IF($A236="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C236,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E236" s="55">
+        <f>IF($A236="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C236,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F236" s="56">
+        <f>IF($A236="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C236,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G236" s="57" t="n"/>
+      <c r="H236" s="54" t="n"/>
+      <c r="I236" s="54" t="n"/>
+      <c r="J236" s="39">
+        <f>IF($A236="","",IF($E236="Informational","GREEN",IF($G236="",IF($E236="Mandatory","RED","YELLOW"),IF($N236="Exact",IF(UPPER(TRIM($G236&amp;""))=UPPER(TRIM($F236&amp;"")),"GREEN",$P236),IF(NOT(ISNUMBER($G236)),$P236,IF($N236="Min",IF($G236&gt;=$F236,"GREEN",IF($G236&gt;=$F236-$O236,"YELLOW",$P236)),IF($N236="Max",IF($G236&lt;=$F236,"GREEN",IF($G236&lt;=$F236+$O236,"YELLOW",$P236)),IF($N236="Range",IF(ABS($G236-$F236)&lt;=$O236,"GREEN",$P236),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K236" s="39">
+        <f>IF($A236="","",IF($H236="Non-Compliant","RED",IF(AND(OR($H236="Alternative Offer",$H236="Partially Compliant"),$J236="GREEN"),"YELLOW",IF(AND($J236="GREEN",ISNUMBER($R236),$R236&lt;Baseline!$B$9),"YELLOW",$J236))))</f>
+        <v/>
+      </c>
+      <c r="L236" s="39">
+        <f>IF($A236="","",IF($K236="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A236,Exceptions!$C$5:$C$104,$B236,Exceptions!$D$5:$D$104,$C236,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K236)))</f>
+        <v/>
+      </c>
+      <c r="M236" s="39">
+        <f>IF($A236="","",IF($H236="","Declaration missing",IF($H236="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R236),$R236&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H236="Fully Compliant",$J236&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N236" s="58">
+        <f>IF($A236="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C236,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O236" s="58">
+        <f>IF($A236="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C236,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P236" s="58">
+        <f>IF($A236="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C236,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q236" s="58">
+        <f>IF($A236="","",$A236&amp;"|"&amp;$B236&amp;"|"&amp;$C236)</f>
+        <v/>
+      </c>
+      <c r="R236" s="59" t="n"/>
+      <c r="S236" s="60" t="n"/>
+    </row>
+    <row r="237" ht="15" customHeight="1" s="34">
+      <c r="A237" s="54" t="n"/>
+      <c r="B237" s="54" t="n"/>
+      <c r="C237" s="54" t="n"/>
+      <c r="D237" s="55">
+        <f>IF($A237="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C237,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E237" s="55">
+        <f>IF($A237="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C237,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F237" s="56">
+        <f>IF($A237="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C237,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G237" s="57" t="n"/>
+      <c r="H237" s="54" t="n"/>
+      <c r="I237" s="54" t="n"/>
+      <c r="J237" s="39">
+        <f>IF($A237="","",IF($E237="Informational","GREEN",IF($G237="",IF($E237="Mandatory","RED","YELLOW"),IF($N237="Exact",IF(UPPER(TRIM($G237&amp;""))=UPPER(TRIM($F237&amp;"")),"GREEN",$P237),IF(NOT(ISNUMBER($G237)),$P237,IF($N237="Min",IF($G237&gt;=$F237,"GREEN",IF($G237&gt;=$F237-$O237,"YELLOW",$P237)),IF($N237="Max",IF($G237&lt;=$F237,"GREEN",IF($G237&lt;=$F237+$O237,"YELLOW",$P237)),IF($N237="Range",IF(ABS($G237-$F237)&lt;=$O237,"GREEN",$P237),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K237" s="39">
+        <f>IF($A237="","",IF($H237="Non-Compliant","RED",IF(AND(OR($H237="Alternative Offer",$H237="Partially Compliant"),$J237="GREEN"),"YELLOW",IF(AND($J237="GREEN",ISNUMBER($R237),$R237&lt;Baseline!$B$9),"YELLOW",$J237))))</f>
+        <v/>
+      </c>
+      <c r="L237" s="39">
+        <f>IF($A237="","",IF($K237="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A237,Exceptions!$C$5:$C$104,$B237,Exceptions!$D$5:$D$104,$C237,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K237)))</f>
+        <v/>
+      </c>
+      <c r="M237" s="39">
+        <f>IF($A237="","",IF($H237="","Declaration missing",IF($H237="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R237),$R237&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H237="Fully Compliant",$J237&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N237" s="58">
+        <f>IF($A237="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C237,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O237" s="58">
+        <f>IF($A237="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C237,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P237" s="58">
+        <f>IF($A237="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C237,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q237" s="58">
+        <f>IF($A237="","",$A237&amp;"|"&amp;$B237&amp;"|"&amp;$C237)</f>
+        <v/>
+      </c>
+      <c r="R237" s="59" t="n"/>
+      <c r="S237" s="60" t="n"/>
+    </row>
+    <row r="238" ht="15" customHeight="1" s="34">
+      <c r="A238" s="54" t="n"/>
+      <c r="B238" s="54" t="n"/>
+      <c r="C238" s="54" t="n"/>
+      <c r="D238" s="55">
+        <f>IF($A238="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C238,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E238" s="55">
+        <f>IF($A238="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C238,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F238" s="56">
+        <f>IF($A238="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C238,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G238" s="57" t="n"/>
+      <c r="H238" s="54" t="n"/>
+      <c r="I238" s="54" t="n"/>
+      <c r="J238" s="39">
+        <f>IF($A238="","",IF($E238="Informational","GREEN",IF($G238="",IF($E238="Mandatory","RED","YELLOW"),IF($N238="Exact",IF(UPPER(TRIM($G238&amp;""))=UPPER(TRIM($F238&amp;"")),"GREEN",$P238),IF(NOT(ISNUMBER($G238)),$P238,IF($N238="Min",IF($G238&gt;=$F238,"GREEN",IF($G238&gt;=$F238-$O238,"YELLOW",$P238)),IF($N238="Max",IF($G238&lt;=$F238,"GREEN",IF($G238&lt;=$F238+$O238,"YELLOW",$P238)),IF($N238="Range",IF(ABS($G238-$F238)&lt;=$O238,"GREEN",$P238),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K238" s="39">
+        <f>IF($A238="","",IF($H238="Non-Compliant","RED",IF(AND(OR($H238="Alternative Offer",$H238="Partially Compliant"),$J238="GREEN"),"YELLOW",IF(AND($J238="GREEN",ISNUMBER($R238),$R238&lt;Baseline!$B$9),"YELLOW",$J238))))</f>
+        <v/>
+      </c>
+      <c r="L238" s="39">
+        <f>IF($A238="","",IF($K238="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A238,Exceptions!$C$5:$C$104,$B238,Exceptions!$D$5:$D$104,$C238,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K238)))</f>
+        <v/>
+      </c>
+      <c r="M238" s="39">
+        <f>IF($A238="","",IF($H238="","Declaration missing",IF($H238="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R238),$R238&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H238="Fully Compliant",$J238&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N238" s="58">
+        <f>IF($A238="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C238,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O238" s="58">
+        <f>IF($A238="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C238,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P238" s="58">
+        <f>IF($A238="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C238,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q238" s="58">
+        <f>IF($A238="","",$A238&amp;"|"&amp;$B238&amp;"|"&amp;$C238)</f>
+        <v/>
+      </c>
+      <c r="R238" s="59" t="n"/>
+      <c r="S238" s="60" t="n"/>
+    </row>
+    <row r="239" ht="15" customHeight="1" s="34">
+      <c r="A239" s="54" t="n"/>
+      <c r="B239" s="54" t="n"/>
+      <c r="C239" s="54" t="n"/>
+      <c r="D239" s="55">
+        <f>IF($A239="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C239,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E239" s="55">
+        <f>IF($A239="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C239,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F239" s="56">
+        <f>IF($A239="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C239,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G239" s="57" t="n"/>
+      <c r="H239" s="54" t="n"/>
+      <c r="I239" s="54" t="n"/>
+      <c r="J239" s="39">
+        <f>IF($A239="","",IF($E239="Informational","GREEN",IF($G239="",IF($E239="Mandatory","RED","YELLOW"),IF($N239="Exact",IF(UPPER(TRIM($G239&amp;""))=UPPER(TRIM($F239&amp;"")),"GREEN",$P239),IF(NOT(ISNUMBER($G239)),$P239,IF($N239="Min",IF($G239&gt;=$F239,"GREEN",IF($G239&gt;=$F239-$O239,"YELLOW",$P239)),IF($N239="Max",IF($G239&lt;=$F239,"GREEN",IF($G239&lt;=$F239+$O239,"YELLOW",$P239)),IF($N239="Range",IF(ABS($G239-$F239)&lt;=$O239,"GREEN",$P239),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K239" s="39">
+        <f>IF($A239="","",IF($H239="Non-Compliant","RED",IF(AND(OR($H239="Alternative Offer",$H239="Partially Compliant"),$J239="GREEN"),"YELLOW",IF(AND($J239="GREEN",ISNUMBER($R239),$R239&lt;Baseline!$B$9),"YELLOW",$J239))))</f>
+        <v/>
+      </c>
+      <c r="L239" s="39">
+        <f>IF($A239="","",IF($K239="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A239,Exceptions!$C$5:$C$104,$B239,Exceptions!$D$5:$D$104,$C239,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K239)))</f>
+        <v/>
+      </c>
+      <c r="M239" s="39">
+        <f>IF($A239="","",IF($H239="","Declaration missing",IF($H239="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R239),$R239&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H239="Fully Compliant",$J239&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N239" s="58">
+        <f>IF($A239="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C239,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O239" s="58">
+        <f>IF($A239="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C239,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P239" s="58">
+        <f>IF($A239="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C239,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q239" s="58">
+        <f>IF($A239="","",$A239&amp;"|"&amp;$B239&amp;"|"&amp;$C239)</f>
+        <v/>
+      </c>
+      <c r="R239" s="59" t="n"/>
+      <c r="S239" s="60" t="n"/>
+    </row>
+    <row r="240" ht="15" customHeight="1" s="34">
+      <c r="A240" s="54" t="n"/>
+      <c r="B240" s="54" t="n"/>
+      <c r="C240" s="54" t="n"/>
+      <c r="D240" s="55">
+        <f>IF($A240="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C240,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E240" s="55">
+        <f>IF($A240="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C240,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F240" s="56">
+        <f>IF($A240="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C240,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G240" s="57" t="n"/>
+      <c r="H240" s="54" t="n"/>
+      <c r="I240" s="54" t="n"/>
+      <c r="J240" s="39">
+        <f>IF($A240="","",IF($E240="Informational","GREEN",IF($G240="",IF($E240="Mandatory","RED","YELLOW"),IF($N240="Exact",IF(UPPER(TRIM($G240&amp;""))=UPPER(TRIM($F240&amp;"")),"GREEN",$P240),IF(NOT(ISNUMBER($G240)),$P240,IF($N240="Min",IF($G240&gt;=$F240,"GREEN",IF($G240&gt;=$F240-$O240,"YELLOW",$P240)),IF($N240="Max",IF($G240&lt;=$F240,"GREEN",IF($G240&lt;=$F240+$O240,"YELLOW",$P240)),IF($N240="Range",IF(ABS($G240-$F240)&lt;=$O240,"GREEN",$P240),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K240" s="39">
+        <f>IF($A240="","",IF($H240="Non-Compliant","RED",IF(AND(OR($H240="Alternative Offer",$H240="Partially Compliant"),$J240="GREEN"),"YELLOW",IF(AND($J240="GREEN",ISNUMBER($R240),$R240&lt;Baseline!$B$9),"YELLOW",$J240))))</f>
+        <v/>
+      </c>
+      <c r="L240" s="39">
+        <f>IF($A240="","",IF($K240="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A240,Exceptions!$C$5:$C$104,$B240,Exceptions!$D$5:$D$104,$C240,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K240)))</f>
+        <v/>
+      </c>
+      <c r="M240" s="39">
+        <f>IF($A240="","",IF($H240="","Declaration missing",IF($H240="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R240),$R240&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H240="Fully Compliant",$J240&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N240" s="58">
+        <f>IF($A240="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C240,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O240" s="58">
+        <f>IF($A240="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C240,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P240" s="58">
+        <f>IF($A240="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C240,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q240" s="58">
+        <f>IF($A240="","",$A240&amp;"|"&amp;$B240&amp;"|"&amp;$C240)</f>
+        <v/>
+      </c>
+      <c r="R240" s="59" t="n"/>
+      <c r="S240" s="60" t="n"/>
+    </row>
+    <row r="241" ht="15" customHeight="1" s="34">
+      <c r="A241" s="54" t="n"/>
+      <c r="B241" s="54" t="n"/>
+      <c r="C241" s="54" t="n"/>
+      <c r="D241" s="55">
+        <f>IF($A241="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C241,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E241" s="55">
+        <f>IF($A241="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C241,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F241" s="56">
+        <f>IF($A241="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C241,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G241" s="57" t="n"/>
+      <c r="H241" s="54" t="n"/>
+      <c r="I241" s="54" t="n"/>
+      <c r="J241" s="39">
+        <f>IF($A241="","",IF($E241="Informational","GREEN",IF($G241="",IF($E241="Mandatory","RED","YELLOW"),IF($N241="Exact",IF(UPPER(TRIM($G241&amp;""))=UPPER(TRIM($F241&amp;"")),"GREEN",$P241),IF(NOT(ISNUMBER($G241)),$P241,IF($N241="Min",IF($G241&gt;=$F241,"GREEN",IF($G241&gt;=$F241-$O241,"YELLOW",$P241)),IF($N241="Max",IF($G241&lt;=$F241,"GREEN",IF($G241&lt;=$F241+$O241,"YELLOW",$P241)),IF($N241="Range",IF(ABS($G241-$F241)&lt;=$O241,"GREEN",$P241),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K241" s="39">
+        <f>IF($A241="","",IF($H241="Non-Compliant","RED",IF(AND(OR($H241="Alternative Offer",$H241="Partially Compliant"),$J241="GREEN"),"YELLOW",IF(AND($J241="GREEN",ISNUMBER($R241),$R241&lt;Baseline!$B$9),"YELLOW",$J241))))</f>
+        <v/>
+      </c>
+      <c r="L241" s="39">
+        <f>IF($A241="","",IF($K241="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A241,Exceptions!$C$5:$C$104,$B241,Exceptions!$D$5:$D$104,$C241,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K241)))</f>
+        <v/>
+      </c>
+      <c r="M241" s="39">
+        <f>IF($A241="","",IF($H241="","Declaration missing",IF($H241="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R241),$R241&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H241="Fully Compliant",$J241&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N241" s="58">
+        <f>IF($A241="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C241,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O241" s="58">
+        <f>IF($A241="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C241,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P241" s="58">
+        <f>IF($A241="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C241,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q241" s="58">
+        <f>IF($A241="","",$A241&amp;"|"&amp;$B241&amp;"|"&amp;$C241)</f>
+        <v/>
+      </c>
+      <c r="R241" s="59" t="n"/>
+      <c r="S241" s="60" t="n"/>
+    </row>
+    <row r="242" ht="15" customHeight="1" s="34">
+      <c r="A242" s="54" t="n"/>
+      <c r="B242" s="54" t="n"/>
+      <c r="C242" s="54" t="n"/>
+      <c r="D242" s="55">
+        <f>IF($A242="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C242,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E242" s="55">
+        <f>IF($A242="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C242,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F242" s="56">
+        <f>IF($A242="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C242,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G242" s="57" t="n"/>
+      <c r="H242" s="54" t="n"/>
+      <c r="I242" s="54" t="n"/>
+      <c r="J242" s="39">
+        <f>IF($A242="","",IF($E242="Informational","GREEN",IF($G242="",IF($E242="Mandatory","RED","YELLOW"),IF($N242="Exact",IF(UPPER(TRIM($G242&amp;""))=UPPER(TRIM($F242&amp;"")),"GREEN",$P242),IF(NOT(ISNUMBER($G242)),$P242,IF($N242="Min",IF($G242&gt;=$F242,"GREEN",IF($G242&gt;=$F242-$O242,"YELLOW",$P242)),IF($N242="Max",IF($G242&lt;=$F242,"GREEN",IF($G242&lt;=$F242+$O242,"YELLOW",$P242)),IF($N242="Range",IF(ABS($G242-$F242)&lt;=$O242,"GREEN",$P242),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K242" s="39">
+        <f>IF($A242="","",IF($H242="Non-Compliant","RED",IF(AND(OR($H242="Alternative Offer",$H242="Partially Compliant"),$J242="GREEN"),"YELLOW",IF(AND($J242="GREEN",ISNUMBER($R242),$R242&lt;Baseline!$B$9),"YELLOW",$J242))))</f>
+        <v/>
+      </c>
+      <c r="L242" s="39">
+        <f>IF($A242="","",IF($K242="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A242,Exceptions!$C$5:$C$104,$B242,Exceptions!$D$5:$D$104,$C242,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K242)))</f>
+        <v/>
+      </c>
+      <c r="M242" s="39">
+        <f>IF($A242="","",IF($H242="","Declaration missing",IF($H242="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R242),$R242&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H242="Fully Compliant",$J242&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N242" s="58">
+        <f>IF($A242="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C242,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O242" s="58">
+        <f>IF($A242="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C242,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P242" s="58">
+        <f>IF($A242="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C242,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q242" s="58">
+        <f>IF($A242="","",$A242&amp;"|"&amp;$B242&amp;"|"&amp;$C242)</f>
+        <v/>
+      </c>
+      <c r="R242" s="59" t="n"/>
+      <c r="S242" s="60" t="n"/>
+    </row>
+    <row r="243" ht="15" customHeight="1" s="34">
+      <c r="A243" s="54" t="n"/>
+      <c r="B243" s="54" t="n"/>
+      <c r="C243" s="54" t="n"/>
+      <c r="D243" s="55">
+        <f>IF($A243="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C243,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E243" s="55">
+        <f>IF($A243="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C243,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F243" s="56">
+        <f>IF($A243="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C243,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G243" s="57" t="n"/>
+      <c r="H243" s="54" t="n"/>
+      <c r="I243" s="54" t="n"/>
+      <c r="J243" s="39">
+        <f>IF($A243="","",IF($E243="Informational","GREEN",IF($G243="",IF($E243="Mandatory","RED","YELLOW"),IF($N243="Exact",IF(UPPER(TRIM($G243&amp;""))=UPPER(TRIM($F243&amp;"")),"GREEN",$P243),IF(NOT(ISNUMBER($G243)),$P243,IF($N243="Min",IF($G243&gt;=$F243,"GREEN",IF($G243&gt;=$F243-$O243,"YELLOW",$P243)),IF($N243="Max",IF($G243&lt;=$F243,"GREEN",IF($G243&lt;=$F243+$O243,"YELLOW",$P243)),IF($N243="Range",IF(ABS($G243-$F243)&lt;=$O243,"GREEN",$P243),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K243" s="39">
+        <f>IF($A243="","",IF($H243="Non-Compliant","RED",IF(AND(OR($H243="Alternative Offer",$H243="Partially Compliant"),$J243="GREEN"),"YELLOW",IF(AND($J243="GREEN",ISNUMBER($R243),$R243&lt;Baseline!$B$9),"YELLOW",$J243))))</f>
+        <v/>
+      </c>
+      <c r="L243" s="39">
+        <f>IF($A243="","",IF($K243="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A243,Exceptions!$C$5:$C$104,$B243,Exceptions!$D$5:$D$104,$C243,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K243)))</f>
+        <v/>
+      </c>
+      <c r="M243" s="39">
+        <f>IF($A243="","",IF($H243="","Declaration missing",IF($H243="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R243),$R243&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H243="Fully Compliant",$J243&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N243" s="58">
+        <f>IF($A243="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C243,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O243" s="58">
+        <f>IF($A243="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C243,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P243" s="58">
+        <f>IF($A243="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C243,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q243" s="58">
+        <f>IF($A243="","",$A243&amp;"|"&amp;$B243&amp;"|"&amp;$C243)</f>
+        <v/>
+      </c>
+      <c r="R243" s="59" t="n"/>
+      <c r="S243" s="60" t="n"/>
+    </row>
+    <row r="244" ht="15" customHeight="1" s="34">
+      <c r="A244" s="54" t="n"/>
+      <c r="B244" s="54" t="n"/>
+      <c r="C244" s="54" t="n"/>
+      <c r="D244" s="55">
+        <f>IF($A244="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C244,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E244" s="55">
+        <f>IF($A244="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C244,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F244" s="56">
+        <f>IF($A244="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C244,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G244" s="57" t="n"/>
+      <c r="H244" s="54" t="n"/>
+      <c r="I244" s="54" t="n"/>
+      <c r="J244" s="39">
+        <f>IF($A244="","",IF($E244="Informational","GREEN",IF($G244="",IF($E244="Mandatory","RED","YELLOW"),IF($N244="Exact",IF(UPPER(TRIM($G244&amp;""))=UPPER(TRIM($F244&amp;"")),"GREEN",$P244),IF(NOT(ISNUMBER($G244)),$P244,IF($N244="Min",IF($G244&gt;=$F244,"GREEN",IF($G244&gt;=$F244-$O244,"YELLOW",$P244)),IF($N244="Max",IF($G244&lt;=$F244,"GREEN",IF($G244&lt;=$F244+$O244,"YELLOW",$P244)),IF($N244="Range",IF(ABS($G244-$F244)&lt;=$O244,"GREEN",$P244),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K244" s="39">
+        <f>IF($A244="","",IF($H244="Non-Compliant","RED",IF(AND(OR($H244="Alternative Offer",$H244="Partially Compliant"),$J244="GREEN"),"YELLOW",IF(AND($J244="GREEN",ISNUMBER($R244),$R244&lt;Baseline!$B$9),"YELLOW",$J244))))</f>
+        <v/>
+      </c>
+      <c r="L244" s="39">
+        <f>IF($A244="","",IF($K244="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A244,Exceptions!$C$5:$C$104,$B244,Exceptions!$D$5:$D$104,$C244,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K244)))</f>
+        <v/>
+      </c>
+      <c r="M244" s="39">
+        <f>IF($A244="","",IF($H244="","Declaration missing",IF($H244="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R244),$R244&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H244="Fully Compliant",$J244&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N244" s="58">
+        <f>IF($A244="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C244,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O244" s="58">
+        <f>IF($A244="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C244,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P244" s="58">
+        <f>IF($A244="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C244,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q244" s="58">
+        <f>IF($A244="","",$A244&amp;"|"&amp;$B244&amp;"|"&amp;$C244)</f>
+        <v/>
+      </c>
+      <c r="R244" s="59" t="n"/>
+      <c r="S244" s="60" t="n"/>
+    </row>
+    <row r="245" ht="15" customHeight="1" s="34">
+      <c r="A245" s="54" t="n"/>
+      <c r="B245" s="54" t="n"/>
+      <c r="C245" s="54" t="n"/>
+      <c r="D245" s="55">
+        <f>IF($A245="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C245,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E245" s="55">
+        <f>IF($A245="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C245,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F245" s="56">
+        <f>IF($A245="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C245,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G245" s="57" t="n"/>
+      <c r="H245" s="54" t="n"/>
+      <c r="I245" s="54" t="n"/>
+      <c r="J245" s="39">
+        <f>IF($A245="","",IF($E245="Informational","GREEN",IF($G245="",IF($E245="Mandatory","RED","YELLOW"),IF($N245="Exact",IF(UPPER(TRIM($G245&amp;""))=UPPER(TRIM($F245&amp;"")),"GREEN",$P245),IF(NOT(ISNUMBER($G245)),$P245,IF($N245="Min",IF($G245&gt;=$F245,"GREEN",IF($G245&gt;=$F245-$O245,"YELLOW",$P245)),IF($N245="Max",IF($G245&lt;=$F245,"GREEN",IF($G245&lt;=$F245+$O245,"YELLOW",$P245)),IF($N245="Range",IF(ABS($G245-$F245)&lt;=$O245,"GREEN",$P245),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K245" s="39">
+        <f>IF($A245="","",IF($H245="Non-Compliant","RED",IF(AND(OR($H245="Alternative Offer",$H245="Partially Compliant"),$J245="GREEN"),"YELLOW",IF(AND($J245="GREEN",ISNUMBER($R245),$R245&lt;Baseline!$B$9),"YELLOW",$J245))))</f>
+        <v/>
+      </c>
+      <c r="L245" s="39">
+        <f>IF($A245="","",IF($K245="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A245,Exceptions!$C$5:$C$104,$B245,Exceptions!$D$5:$D$104,$C245,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K245)))</f>
+        <v/>
+      </c>
+      <c r="M245" s="39">
+        <f>IF($A245="","",IF($H245="","Declaration missing",IF($H245="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R245),$R245&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H245="Fully Compliant",$J245&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N245" s="58">
+        <f>IF($A245="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C245,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O245" s="58">
+        <f>IF($A245="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C245,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P245" s="58">
+        <f>IF($A245="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C245,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q245" s="58">
+        <f>IF($A245="","",$A245&amp;"|"&amp;$B245&amp;"|"&amp;$C245)</f>
+        <v/>
+      </c>
+      <c r="R245" s="59" t="n"/>
+      <c r="S245" s="60" t="n"/>
+    </row>
+    <row r="246" ht="15" customHeight="1" s="34">
+      <c r="A246" s="54" t="n"/>
+      <c r="B246" s="54" t="n"/>
+      <c r="C246" s="54" t="n"/>
+      <c r="D246" s="55">
+        <f>IF($A246="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C246,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E246" s="55">
+        <f>IF($A246="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C246,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F246" s="56">
+        <f>IF($A246="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C246,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G246" s="57" t="n"/>
+      <c r="H246" s="54" t="n"/>
+      <c r="I246" s="54" t="n"/>
+      <c r="J246" s="39">
+        <f>IF($A246="","",IF($E246="Informational","GREEN",IF($G246="",IF($E246="Mandatory","RED","YELLOW"),IF($N246="Exact",IF(UPPER(TRIM($G246&amp;""))=UPPER(TRIM($F246&amp;"")),"GREEN",$P246),IF(NOT(ISNUMBER($G246)),$P246,IF($N246="Min",IF($G246&gt;=$F246,"GREEN",IF($G246&gt;=$F246-$O246,"YELLOW",$P246)),IF($N246="Max",IF($G246&lt;=$F246,"GREEN",IF($G246&lt;=$F246+$O246,"YELLOW",$P246)),IF($N246="Range",IF(ABS($G246-$F246)&lt;=$O246,"GREEN",$P246),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K246" s="39">
+        <f>IF($A246="","",IF($H246="Non-Compliant","RED",IF(AND(OR($H246="Alternative Offer",$H246="Partially Compliant"),$J246="GREEN"),"YELLOW",IF(AND($J246="GREEN",ISNUMBER($R246),$R246&lt;Baseline!$B$9),"YELLOW",$J246))))</f>
+        <v/>
+      </c>
+      <c r="L246" s="39">
+        <f>IF($A246="","",IF($K246="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A246,Exceptions!$C$5:$C$104,$B246,Exceptions!$D$5:$D$104,$C246,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K246)))</f>
+        <v/>
+      </c>
+      <c r="M246" s="39">
+        <f>IF($A246="","",IF($H246="","Declaration missing",IF($H246="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R246),$R246&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H246="Fully Compliant",$J246&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N246" s="58">
+        <f>IF($A246="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C246,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O246" s="58">
+        <f>IF($A246="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C246,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P246" s="58">
+        <f>IF($A246="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C246,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q246" s="58">
+        <f>IF($A246="","",$A246&amp;"|"&amp;$B246&amp;"|"&amp;$C246)</f>
+        <v/>
+      </c>
+      <c r="R246" s="59" t="n"/>
+      <c r="S246" s="60" t="n"/>
+    </row>
+    <row r="247" ht="15" customHeight="1" s="34">
+      <c r="A247" s="54" t="n"/>
+      <c r="B247" s="54" t="n"/>
+      <c r="C247" s="54" t="n"/>
+      <c r="D247" s="55">
+        <f>IF($A247="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C247,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E247" s="55">
+        <f>IF($A247="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C247,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F247" s="56">
+        <f>IF($A247="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C247,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G247" s="57" t="n"/>
+      <c r="H247" s="54" t="n"/>
+      <c r="I247" s="54" t="n"/>
+      <c r="J247" s="39">
+        <f>IF($A247="","",IF($E247="Informational","GREEN",IF($G247="",IF($E247="Mandatory","RED","YELLOW"),IF($N247="Exact",IF(UPPER(TRIM($G247&amp;""))=UPPER(TRIM($F247&amp;"")),"GREEN",$P247),IF(NOT(ISNUMBER($G247)),$P247,IF($N247="Min",IF($G247&gt;=$F247,"GREEN",IF($G247&gt;=$F247-$O247,"YELLOW",$P247)),IF($N247="Max",IF($G247&lt;=$F247,"GREEN",IF($G247&lt;=$F247+$O247,"YELLOW",$P247)),IF($N247="Range",IF(ABS($G247-$F247)&lt;=$O247,"GREEN",$P247),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K247" s="39">
+        <f>IF($A247="","",IF($H247="Non-Compliant","RED",IF(AND(OR($H247="Alternative Offer",$H247="Partially Compliant"),$J247="GREEN"),"YELLOW",IF(AND($J247="GREEN",ISNUMBER($R247),$R247&lt;Baseline!$B$9),"YELLOW",$J247))))</f>
+        <v/>
+      </c>
+      <c r="L247" s="39">
+        <f>IF($A247="","",IF($K247="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A247,Exceptions!$C$5:$C$104,$B247,Exceptions!$D$5:$D$104,$C247,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K247)))</f>
+        <v/>
+      </c>
+      <c r="M247" s="39">
+        <f>IF($A247="","",IF($H247="","Declaration missing",IF($H247="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R247),$R247&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H247="Fully Compliant",$J247&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N247" s="58">
+        <f>IF($A247="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C247,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O247" s="58">
+        <f>IF($A247="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C247,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P247" s="58">
+        <f>IF($A247="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C247,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q247" s="58">
+        <f>IF($A247="","",$A247&amp;"|"&amp;$B247&amp;"|"&amp;$C247)</f>
+        <v/>
+      </c>
+      <c r="R247" s="59" t="n"/>
+      <c r="S247" s="60" t="n"/>
+    </row>
+    <row r="248" ht="15" customHeight="1" s="34">
+      <c r="A248" s="54" t="n"/>
+      <c r="B248" s="54" t="n"/>
+      <c r="C248" s="54" t="n"/>
+      <c r="D248" s="55">
+        <f>IF($A248="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C248,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E248" s="55">
+        <f>IF($A248="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C248,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F248" s="56">
+        <f>IF($A248="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C248,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G248" s="57" t="n"/>
+      <c r="H248" s="54" t="n"/>
+      <c r="I248" s="54" t="n"/>
+      <c r="J248" s="39">
+        <f>IF($A248="","",IF($E248="Informational","GREEN",IF($G248="",IF($E248="Mandatory","RED","YELLOW"),IF($N248="Exact",IF(UPPER(TRIM($G248&amp;""))=UPPER(TRIM($F248&amp;"")),"GREEN",$P248),IF(NOT(ISNUMBER($G248)),$P248,IF($N248="Min",IF($G248&gt;=$F248,"GREEN",IF($G248&gt;=$F248-$O248,"YELLOW",$P248)),IF($N248="Max",IF($G248&lt;=$F248,"GREEN",IF($G248&lt;=$F248+$O248,"YELLOW",$P248)),IF($N248="Range",IF(ABS($G248-$F248)&lt;=$O248,"GREEN",$P248),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K248" s="39">
+        <f>IF($A248="","",IF($H248="Non-Compliant","RED",IF(AND(OR($H248="Alternative Offer",$H248="Partially Compliant"),$J248="GREEN"),"YELLOW",IF(AND($J248="GREEN",ISNUMBER($R248),$R248&lt;Baseline!$B$9),"YELLOW",$J248))))</f>
+        <v/>
+      </c>
+      <c r="L248" s="39">
+        <f>IF($A248="","",IF($K248="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A248,Exceptions!$C$5:$C$104,$B248,Exceptions!$D$5:$D$104,$C248,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K248)))</f>
+        <v/>
+      </c>
+      <c r="M248" s="39">
+        <f>IF($A248="","",IF($H248="","Declaration missing",IF($H248="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R248),$R248&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H248="Fully Compliant",$J248&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N248" s="58">
+        <f>IF($A248="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C248,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O248" s="58">
+        <f>IF($A248="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C248,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P248" s="58">
+        <f>IF($A248="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C248,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q248" s="58">
+        <f>IF($A248="","",$A248&amp;"|"&amp;$B248&amp;"|"&amp;$C248)</f>
+        <v/>
+      </c>
+      <c r="R248" s="59" t="n"/>
+      <c r="S248" s="60" t="n"/>
+    </row>
+    <row r="249" ht="15" customHeight="1" s="34">
+      <c r="A249" s="54" t="n"/>
+      <c r="B249" s="54" t="n"/>
+      <c r="C249" s="54" t="n"/>
+      <c r="D249" s="55">
+        <f>IF($A249="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C249,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E249" s="55">
+        <f>IF($A249="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C249,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F249" s="56">
+        <f>IF($A249="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C249,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G249" s="57" t="n"/>
+      <c r="H249" s="54" t="n"/>
+      <c r="I249" s="54" t="n"/>
+      <c r="J249" s="39">
+        <f>IF($A249="","",IF($E249="Informational","GREEN",IF($G249="",IF($E249="Mandatory","RED","YELLOW"),IF($N249="Exact",IF(UPPER(TRIM($G249&amp;""))=UPPER(TRIM($F249&amp;"")),"GREEN",$P249),IF(NOT(ISNUMBER($G249)),$P249,IF($N249="Min",IF($G249&gt;=$F249,"GREEN",IF($G249&gt;=$F249-$O249,"YELLOW",$P249)),IF($N249="Max",IF($G249&lt;=$F249,"GREEN",IF($G249&lt;=$F249+$O249,"YELLOW",$P249)),IF($N249="Range",IF(ABS($G249-$F249)&lt;=$O249,"GREEN",$P249),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K249" s="39">
+        <f>IF($A249="","",IF($H249="Non-Compliant","RED",IF(AND(OR($H249="Alternative Offer",$H249="Partially Compliant"),$J249="GREEN"),"YELLOW",IF(AND($J249="GREEN",ISNUMBER($R249),$R249&lt;Baseline!$B$9),"YELLOW",$J249))))</f>
+        <v/>
+      </c>
+      <c r="L249" s="39">
+        <f>IF($A249="","",IF($K249="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A249,Exceptions!$C$5:$C$104,$B249,Exceptions!$D$5:$D$104,$C249,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K249)))</f>
+        <v/>
+      </c>
+      <c r="M249" s="39">
+        <f>IF($A249="","",IF($H249="","Declaration missing",IF($H249="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R249),$R249&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H249="Fully Compliant",$J249&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N249" s="58">
+        <f>IF($A249="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C249,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O249" s="58">
+        <f>IF($A249="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C249,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P249" s="58">
+        <f>IF($A249="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C249,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q249" s="58">
+        <f>IF($A249="","",$A249&amp;"|"&amp;$B249&amp;"|"&amp;$C249)</f>
+        <v/>
+      </c>
+      <c r="R249" s="59" t="n"/>
+      <c r="S249" s="60" t="n"/>
+    </row>
+    <row r="250" ht="15" customHeight="1" s="34">
+      <c r="A250" s="54" t="n"/>
+      <c r="B250" s="54" t="n"/>
+      <c r="C250" s="54" t="n"/>
+      <c r="D250" s="55">
+        <f>IF($A250="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C250,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E250" s="55">
+        <f>IF($A250="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C250,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F250" s="56">
+        <f>IF($A250="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C250,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G250" s="57" t="n"/>
+      <c r="H250" s="54" t="n"/>
+      <c r="I250" s="54" t="n"/>
+      <c r="J250" s="39">
+        <f>IF($A250="","",IF($E250="Informational","GREEN",IF($G250="",IF($E250="Mandatory","RED","YELLOW"),IF($N250="Exact",IF(UPPER(TRIM($G250&amp;""))=UPPER(TRIM($F250&amp;"")),"GREEN",$P250),IF(NOT(ISNUMBER($G250)),$P250,IF($N250="Min",IF($G250&gt;=$F250,"GREEN",IF($G250&gt;=$F250-$O250,"YELLOW",$P250)),IF($N250="Max",IF($G250&lt;=$F250,"GREEN",IF($G250&lt;=$F250+$O250,"YELLOW",$P250)),IF($N250="Range",IF(ABS($G250-$F250)&lt;=$O250,"GREEN",$P250),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K250" s="39">
+        <f>IF($A250="","",IF($H250="Non-Compliant","RED",IF(AND(OR($H250="Alternative Offer",$H250="Partially Compliant"),$J250="GREEN"),"YELLOW",IF(AND($J250="GREEN",ISNUMBER($R250),$R250&lt;Baseline!$B$9),"YELLOW",$J250))))</f>
+        <v/>
+      </c>
+      <c r="L250" s="39">
+        <f>IF($A250="","",IF($K250="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A250,Exceptions!$C$5:$C$104,$B250,Exceptions!$D$5:$D$104,$C250,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K250)))</f>
+        <v/>
+      </c>
+      <c r="M250" s="39">
+        <f>IF($A250="","",IF($H250="","Declaration missing",IF($H250="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R250),$R250&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H250="Fully Compliant",$J250&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N250" s="58">
+        <f>IF($A250="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C250,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O250" s="58">
+        <f>IF($A250="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C250,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P250" s="58">
+        <f>IF($A250="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C250,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q250" s="58">
+        <f>IF($A250="","",$A250&amp;"|"&amp;$B250&amp;"|"&amp;$C250)</f>
+        <v/>
+      </c>
+      <c r="R250" s="59" t="n"/>
+      <c r="S250" s="60" t="n"/>
+    </row>
+    <row r="251" ht="15" customHeight="1" s="34">
+      <c r="A251" s="54" t="n"/>
+      <c r="B251" s="54" t="n"/>
+      <c r="C251" s="54" t="n"/>
+      <c r="D251" s="55">
+        <f>IF($A251="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C251,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E251" s="55">
+        <f>IF($A251="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C251,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F251" s="56">
+        <f>IF($A251="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C251,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G251" s="57" t="n"/>
+      <c r="H251" s="54" t="n"/>
+      <c r="I251" s="54" t="n"/>
+      <c r="J251" s="39">
+        <f>IF($A251="","",IF($E251="Informational","GREEN",IF($G251="",IF($E251="Mandatory","RED","YELLOW"),IF($N251="Exact",IF(UPPER(TRIM($G251&amp;""))=UPPER(TRIM($F251&amp;"")),"GREEN",$P251),IF(NOT(ISNUMBER($G251)),$P251,IF($N251="Min",IF($G251&gt;=$F251,"GREEN",IF($G251&gt;=$F251-$O251,"YELLOW",$P251)),IF($N251="Max",IF($G251&lt;=$F251,"GREEN",IF($G251&lt;=$F251+$O251,"YELLOW",$P251)),IF($N251="Range",IF(ABS($G251-$F251)&lt;=$O251,"GREEN",$P251),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K251" s="39">
+        <f>IF($A251="","",IF($H251="Non-Compliant","RED",IF(AND(OR($H251="Alternative Offer",$H251="Partially Compliant"),$J251="GREEN"),"YELLOW",IF(AND($J251="GREEN",ISNUMBER($R251),$R251&lt;Baseline!$B$9),"YELLOW",$J251))))</f>
+        <v/>
+      </c>
+      <c r="L251" s="39">
+        <f>IF($A251="","",IF($K251="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A251,Exceptions!$C$5:$C$104,$B251,Exceptions!$D$5:$D$104,$C251,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K251)))</f>
+        <v/>
+      </c>
+      <c r="M251" s="39">
+        <f>IF($A251="","",IF($H251="","Declaration missing",IF($H251="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R251),$R251&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H251="Fully Compliant",$J251&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N251" s="58">
+        <f>IF($A251="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C251,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O251" s="58">
+        <f>IF($A251="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C251,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P251" s="58">
+        <f>IF($A251="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C251,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q251" s="58">
+        <f>IF($A251="","",$A251&amp;"|"&amp;$B251&amp;"|"&amp;$C251)</f>
+        <v/>
+      </c>
+      <c r="R251" s="59" t="n"/>
+      <c r="S251" s="60" t="n"/>
+    </row>
+    <row r="252" ht="15" customHeight="1" s="34">
+      <c r="A252" s="54" t="n"/>
+      <c r="B252" s="54" t="n"/>
+      <c r="C252" s="54" t="n"/>
+      <c r="D252" s="55">
+        <f>IF($A252="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C252,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E252" s="55">
+        <f>IF($A252="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C252,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F252" s="56">
+        <f>IF($A252="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C252,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G252" s="57" t="n"/>
+      <c r="H252" s="54" t="n"/>
+      <c r="I252" s="54" t="n"/>
+      <c r="J252" s="39">
+        <f>IF($A252="","",IF($E252="Informational","GREEN",IF($G252="",IF($E252="Mandatory","RED","YELLOW"),IF($N252="Exact",IF(UPPER(TRIM($G252&amp;""))=UPPER(TRIM($F252&amp;"")),"GREEN",$P252),IF(NOT(ISNUMBER($G252)),$P252,IF($N252="Min",IF($G252&gt;=$F252,"GREEN",IF($G252&gt;=$F252-$O252,"YELLOW",$P252)),IF($N252="Max",IF($G252&lt;=$F252,"GREEN",IF($G252&lt;=$F252+$O252,"YELLOW",$P252)),IF($N252="Range",IF(ABS($G252-$F252)&lt;=$O252,"GREEN",$P252),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K252" s="39">
+        <f>IF($A252="","",IF($H252="Non-Compliant","RED",IF(AND(OR($H252="Alternative Offer",$H252="Partially Compliant"),$J252="GREEN"),"YELLOW",IF(AND($J252="GREEN",ISNUMBER($R252),$R252&lt;Baseline!$B$9),"YELLOW",$J252))))</f>
+        <v/>
+      </c>
+      <c r="L252" s="39">
+        <f>IF($A252="","",IF($K252="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A252,Exceptions!$C$5:$C$104,$B252,Exceptions!$D$5:$D$104,$C252,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K252)))</f>
+        <v/>
+      </c>
+      <c r="M252" s="39">
+        <f>IF($A252="","",IF($H252="","Declaration missing",IF($H252="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R252),$R252&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H252="Fully Compliant",$J252&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N252" s="58">
+        <f>IF($A252="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C252,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O252" s="58">
+        <f>IF($A252="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C252,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P252" s="58">
+        <f>IF($A252="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C252,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q252" s="58">
+        <f>IF($A252="","",$A252&amp;"|"&amp;$B252&amp;"|"&amp;$C252)</f>
+        <v/>
+      </c>
+      <c r="R252" s="59" t="n"/>
+      <c r="S252" s="60" t="n"/>
+    </row>
+    <row r="253" ht="15" customHeight="1" s="34">
+      <c r="A253" s="54" t="n"/>
+      <c r="B253" s="54" t="n"/>
+      <c r="C253" s="54" t="n"/>
+      <c r="D253" s="55">
+        <f>IF($A253="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C253,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E253" s="55">
+        <f>IF($A253="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C253,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F253" s="56">
+        <f>IF($A253="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C253,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G253" s="57" t="n"/>
+      <c r="H253" s="54" t="n"/>
+      <c r="I253" s="54" t="n"/>
+      <c r="J253" s="39">
+        <f>IF($A253="","",IF($E253="Informational","GREEN",IF($G253="",IF($E253="Mandatory","RED","YELLOW"),IF($N253="Exact",IF(UPPER(TRIM($G253&amp;""))=UPPER(TRIM($F253&amp;"")),"GREEN",$P253),IF(NOT(ISNUMBER($G253)),$P253,IF($N253="Min",IF($G253&gt;=$F253,"GREEN",IF($G253&gt;=$F253-$O253,"YELLOW",$P253)),IF($N253="Max",IF($G253&lt;=$F253,"GREEN",IF($G253&lt;=$F253+$O253,"YELLOW",$P253)),IF($N253="Range",IF(ABS($G253-$F253)&lt;=$O253,"GREEN",$P253),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K253" s="39">
+        <f>IF($A253="","",IF($H253="Non-Compliant","RED",IF(AND(OR($H253="Alternative Offer",$H253="Partially Compliant"),$J253="GREEN"),"YELLOW",IF(AND($J253="GREEN",ISNUMBER($R253),$R253&lt;Baseline!$B$9),"YELLOW",$J253))))</f>
+        <v/>
+      </c>
+      <c r="L253" s="39">
+        <f>IF($A253="","",IF($K253="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A253,Exceptions!$C$5:$C$104,$B253,Exceptions!$D$5:$D$104,$C253,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K253)))</f>
+        <v/>
+      </c>
+      <c r="M253" s="39">
+        <f>IF($A253="","",IF($H253="","Declaration missing",IF($H253="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R253),$R253&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H253="Fully Compliant",$J253&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N253" s="58">
+        <f>IF($A253="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C253,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O253" s="58">
+        <f>IF($A253="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C253,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P253" s="58">
+        <f>IF($A253="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C253,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q253" s="58">
+        <f>IF($A253="","",$A253&amp;"|"&amp;$B253&amp;"|"&amp;$C253)</f>
+        <v/>
+      </c>
+      <c r="R253" s="59" t="n"/>
+      <c r="S253" s="60" t="n"/>
+    </row>
+    <row r="254" ht="15" customHeight="1" s="34">
+      <c r="A254" s="54" t="n"/>
+      <c r="B254" s="54" t="n"/>
+      <c r="C254" s="54" t="n"/>
+      <c r="D254" s="55">
+        <f>IF($A254="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C254,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E254" s="55">
+        <f>IF($A254="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C254,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F254" s="56">
+        <f>IF($A254="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C254,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G254" s="57" t="n"/>
+      <c r="H254" s="54" t="n"/>
+      <c r="I254" s="54" t="n"/>
+      <c r="J254" s="39">
+        <f>IF($A254="","",IF($E254="Informational","GREEN",IF($G254="",IF($E254="Mandatory","RED","YELLOW"),IF($N254="Exact",IF(UPPER(TRIM($G254&amp;""))=UPPER(TRIM($F254&amp;"")),"GREEN",$P254),IF(NOT(ISNUMBER($G254)),$P254,IF($N254="Min",IF($G254&gt;=$F254,"GREEN",IF($G254&gt;=$F254-$O254,"YELLOW",$P254)),IF($N254="Max",IF($G254&lt;=$F254,"GREEN",IF($G254&lt;=$F254+$O254,"YELLOW",$P254)),IF($N254="Range",IF(ABS($G254-$F254)&lt;=$O254,"GREEN",$P254),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K254" s="39">
+        <f>IF($A254="","",IF($H254="Non-Compliant","RED",IF(AND(OR($H254="Alternative Offer",$H254="Partially Compliant"),$J254="GREEN"),"YELLOW",IF(AND($J254="GREEN",ISNUMBER($R254),$R254&lt;Baseline!$B$9),"YELLOW",$J254))))</f>
+        <v/>
+      </c>
+      <c r="L254" s="39">
+        <f>IF($A254="","",IF($K254="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A254,Exceptions!$C$5:$C$104,$B254,Exceptions!$D$5:$D$104,$C254,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K254)))</f>
+        <v/>
+      </c>
+      <c r="M254" s="39">
+        <f>IF($A254="","",IF($H254="","Declaration missing",IF($H254="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R254),$R254&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H254="Fully Compliant",$J254&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N254" s="58">
+        <f>IF($A254="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C254,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O254" s="58">
+        <f>IF($A254="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C254,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P254" s="58">
+        <f>IF($A254="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C254,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q254" s="58">
+        <f>IF($A254="","",$A254&amp;"|"&amp;$B254&amp;"|"&amp;$C254)</f>
+        <v/>
+      </c>
+      <c r="R254" s="59" t="n"/>
+      <c r="S254" s="60" t="n"/>
+    </row>
+    <row r="255" ht="15" customHeight="1" s="34">
+      <c r="A255" s="54" t="n"/>
+      <c r="B255" s="54" t="n"/>
+      <c r="C255" s="54" t="n"/>
+      <c r="D255" s="55">
+        <f>IF($A255="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C255,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E255" s="55">
+        <f>IF($A255="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C255,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F255" s="56">
+        <f>IF($A255="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C255,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G255" s="57" t="n"/>
+      <c r="H255" s="54" t="n"/>
+      <c r="I255" s="54" t="n"/>
+      <c r="J255" s="39">
+        <f>IF($A255="","",IF($E255="Informational","GREEN",IF($G255="",IF($E255="Mandatory","RED","YELLOW"),IF($N255="Exact",IF(UPPER(TRIM($G255&amp;""))=UPPER(TRIM($F255&amp;"")),"GREEN",$P255),IF(NOT(ISNUMBER($G255)),$P255,IF($N255="Min",IF($G255&gt;=$F255,"GREEN",IF($G255&gt;=$F255-$O255,"YELLOW",$P255)),IF($N255="Max",IF($G255&lt;=$F255,"GREEN",IF($G255&lt;=$F255+$O255,"YELLOW",$P255)),IF($N255="Range",IF(ABS($G255-$F255)&lt;=$O255,"GREEN",$P255),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K255" s="39">
+        <f>IF($A255="","",IF($H255="Non-Compliant","RED",IF(AND(OR($H255="Alternative Offer",$H255="Partially Compliant"),$J255="GREEN"),"YELLOW",IF(AND($J255="GREEN",ISNUMBER($R255),$R255&lt;Baseline!$B$9),"YELLOW",$J255))))</f>
+        <v/>
+      </c>
+      <c r="L255" s="39">
+        <f>IF($A255="","",IF($K255="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A255,Exceptions!$C$5:$C$104,$B255,Exceptions!$D$5:$D$104,$C255,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K255)))</f>
+        <v/>
+      </c>
+      <c r="M255" s="39">
+        <f>IF($A255="","",IF($H255="","Declaration missing",IF($H255="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R255),$R255&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H255="Fully Compliant",$J255&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N255" s="58">
+        <f>IF($A255="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C255,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O255" s="58">
+        <f>IF($A255="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C255,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P255" s="58">
+        <f>IF($A255="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C255,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q255" s="58">
+        <f>IF($A255="","",$A255&amp;"|"&amp;$B255&amp;"|"&amp;$C255)</f>
+        <v/>
+      </c>
+      <c r="R255" s="59" t="n"/>
+      <c r="S255" s="60" t="n"/>
+    </row>
+    <row r="256" ht="15" customHeight="1" s="34">
+      <c r="A256" s="54" t="n"/>
+      <c r="B256" s="54" t="n"/>
+      <c r="C256" s="54" t="n"/>
+      <c r="D256" s="55">
+        <f>IF($A256="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C256,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E256" s="55">
+        <f>IF($A256="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C256,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F256" s="56">
+        <f>IF($A256="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C256,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G256" s="57" t="n"/>
+      <c r="H256" s="54" t="n"/>
+      <c r="I256" s="54" t="n"/>
+      <c r="J256" s="39">
+        <f>IF($A256="","",IF($E256="Informational","GREEN",IF($G256="",IF($E256="Mandatory","RED","YELLOW"),IF($N256="Exact",IF(UPPER(TRIM($G256&amp;""))=UPPER(TRIM($F256&amp;"")),"GREEN",$P256),IF(NOT(ISNUMBER($G256)),$P256,IF($N256="Min",IF($G256&gt;=$F256,"GREEN",IF($G256&gt;=$F256-$O256,"YELLOW",$P256)),IF($N256="Max",IF($G256&lt;=$F256,"GREEN",IF($G256&lt;=$F256+$O256,"YELLOW",$P256)),IF($N256="Range",IF(ABS($G256-$F256)&lt;=$O256,"GREEN",$P256),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K256" s="39">
+        <f>IF($A256="","",IF($H256="Non-Compliant","RED",IF(AND(OR($H256="Alternative Offer",$H256="Partially Compliant"),$J256="GREEN"),"YELLOW",IF(AND($J256="GREEN",ISNUMBER($R256),$R256&lt;Baseline!$B$9),"YELLOW",$J256))))</f>
+        <v/>
+      </c>
+      <c r="L256" s="39">
+        <f>IF($A256="","",IF($K256="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A256,Exceptions!$C$5:$C$104,$B256,Exceptions!$D$5:$D$104,$C256,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K256)))</f>
+        <v/>
+      </c>
+      <c r="M256" s="39">
+        <f>IF($A256="","",IF($H256="","Declaration missing",IF($H256="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R256),$R256&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H256="Fully Compliant",$J256&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N256" s="58">
+        <f>IF($A256="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C256,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O256" s="58">
+        <f>IF($A256="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C256,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P256" s="58">
+        <f>IF($A256="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C256,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q256" s="58">
+        <f>IF($A256="","",$A256&amp;"|"&amp;$B256&amp;"|"&amp;$C256)</f>
+        <v/>
+      </c>
+      <c r="R256" s="59" t="n"/>
+      <c r="S256" s="60" t="n"/>
+    </row>
+    <row r="257" ht="15" customHeight="1" s="34">
+      <c r="A257" s="54" t="n"/>
+      <c r="B257" s="54" t="n"/>
+      <c r="C257" s="54" t="n"/>
+      <c r="D257" s="55">
+        <f>IF($A257="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C257,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E257" s="55">
+        <f>IF($A257="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C257,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F257" s="56">
+        <f>IF($A257="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C257,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G257" s="57" t="n"/>
+      <c r="H257" s="54" t="n"/>
+      <c r="I257" s="54" t="n"/>
+      <c r="J257" s="39">
+        <f>IF($A257="","",IF($E257="Informational","GREEN",IF($G257="",IF($E257="Mandatory","RED","YELLOW"),IF($N257="Exact",IF(UPPER(TRIM($G257&amp;""))=UPPER(TRIM($F257&amp;"")),"GREEN",$P257),IF(NOT(ISNUMBER($G257)),$P257,IF($N257="Min",IF($G257&gt;=$F257,"GREEN",IF($G257&gt;=$F257-$O257,"YELLOW",$P257)),IF($N257="Max",IF($G257&lt;=$F257,"GREEN",IF($G257&lt;=$F257+$O257,"YELLOW",$P257)),IF($N257="Range",IF(ABS($G257-$F257)&lt;=$O257,"GREEN",$P257),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K257" s="39">
+        <f>IF($A257="","",IF($H257="Non-Compliant","RED",IF(AND(OR($H257="Alternative Offer",$H257="Partially Compliant"),$J257="GREEN"),"YELLOW",IF(AND($J257="GREEN",ISNUMBER($R257),$R257&lt;Baseline!$B$9),"YELLOW",$J257))))</f>
+        <v/>
+      </c>
+      <c r="L257" s="39">
+        <f>IF($A257="","",IF($K257="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A257,Exceptions!$C$5:$C$104,$B257,Exceptions!$D$5:$D$104,$C257,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K257)))</f>
+        <v/>
+      </c>
+      <c r="M257" s="39">
+        <f>IF($A257="","",IF($H257="","Declaration missing",IF($H257="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R257),$R257&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H257="Fully Compliant",$J257&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N257" s="58">
+        <f>IF($A257="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C257,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O257" s="58">
+        <f>IF($A257="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C257,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P257" s="58">
+        <f>IF($A257="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C257,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q257" s="58">
+        <f>IF($A257="","",$A257&amp;"|"&amp;$B257&amp;"|"&amp;$C257)</f>
+        <v/>
+      </c>
+      <c r="R257" s="59" t="n"/>
+      <c r="S257" s="60" t="n"/>
+    </row>
+    <row r="258" ht="15" customHeight="1" s="34">
+      <c r="A258" s="54" t="n"/>
+      <c r="B258" s="54" t="n"/>
+      <c r="C258" s="54" t="n"/>
+      <c r="D258" s="55">
+        <f>IF($A258="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C258,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E258" s="55">
+        <f>IF($A258="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C258,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F258" s="56">
+        <f>IF($A258="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C258,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G258" s="57" t="n"/>
+      <c r="H258" s="54" t="n"/>
+      <c r="I258" s="54" t="n"/>
+      <c r="J258" s="39">
+        <f>IF($A258="","",IF($E258="Informational","GREEN",IF($G258="",IF($E258="Mandatory","RED","YELLOW"),IF($N258="Exact",IF(UPPER(TRIM($G258&amp;""))=UPPER(TRIM($F258&amp;"")),"GREEN",$P258),IF(NOT(ISNUMBER($G258)),$P258,IF($N258="Min",IF($G258&gt;=$F258,"GREEN",IF($G258&gt;=$F258-$O258,"YELLOW",$P258)),IF($N258="Max",IF($G258&lt;=$F258,"GREEN",IF($G258&lt;=$F258+$O258,"YELLOW",$P258)),IF($N258="Range",IF(ABS($G258-$F258)&lt;=$O258,"GREEN",$P258),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K258" s="39">
+        <f>IF($A258="","",IF($H258="Non-Compliant","RED",IF(AND(OR($H258="Alternative Offer",$H258="Partially Compliant"),$J258="GREEN"),"YELLOW",IF(AND($J258="GREEN",ISNUMBER($R258),$R258&lt;Baseline!$B$9),"YELLOW",$J258))))</f>
+        <v/>
+      </c>
+      <c r="L258" s="39">
+        <f>IF($A258="","",IF($K258="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A258,Exceptions!$C$5:$C$104,$B258,Exceptions!$D$5:$D$104,$C258,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K258)))</f>
+        <v/>
+      </c>
+      <c r="M258" s="39">
+        <f>IF($A258="","",IF($H258="","Declaration missing",IF($H258="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R258),$R258&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H258="Fully Compliant",$J258&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N258" s="58">
+        <f>IF($A258="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C258,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O258" s="58">
+        <f>IF($A258="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C258,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P258" s="58">
+        <f>IF($A258="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C258,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q258" s="58">
+        <f>IF($A258="","",$A258&amp;"|"&amp;$B258&amp;"|"&amp;$C258)</f>
+        <v/>
+      </c>
+      <c r="R258" s="59" t="n"/>
+      <c r="S258" s="60" t="n"/>
+    </row>
+    <row r="259" ht="15" customHeight="1" s="34">
+      <c r="A259" s="54" t="n"/>
+      <c r="B259" s="54" t="n"/>
+      <c r="C259" s="54" t="n"/>
+      <c r="D259" s="55">
+        <f>IF($A259="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C259,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E259" s="55">
+        <f>IF($A259="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C259,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F259" s="56">
+        <f>IF($A259="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C259,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G259" s="57" t="n"/>
+      <c r="H259" s="54" t="n"/>
+      <c r="I259" s="54" t="n"/>
+      <c r="J259" s="39">
+        <f>IF($A259="","",IF($E259="Informational","GREEN",IF($G259="",IF($E259="Mandatory","RED","YELLOW"),IF($N259="Exact",IF(UPPER(TRIM($G259&amp;""))=UPPER(TRIM($F259&amp;"")),"GREEN",$P259),IF(NOT(ISNUMBER($G259)),$P259,IF($N259="Min",IF($G259&gt;=$F259,"GREEN",IF($G259&gt;=$F259-$O259,"YELLOW",$P259)),IF($N259="Max",IF($G259&lt;=$F259,"GREEN",IF($G259&lt;=$F259+$O259,"YELLOW",$P259)),IF($N259="Range",IF(ABS($G259-$F259)&lt;=$O259,"GREEN",$P259),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K259" s="39">
+        <f>IF($A259="","",IF($H259="Non-Compliant","RED",IF(AND(OR($H259="Alternative Offer",$H259="Partially Compliant"),$J259="GREEN"),"YELLOW",IF(AND($J259="GREEN",ISNUMBER($R259),$R259&lt;Baseline!$B$9),"YELLOW",$J259))))</f>
+        <v/>
+      </c>
+      <c r="L259" s="39">
+        <f>IF($A259="","",IF($K259="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A259,Exceptions!$C$5:$C$104,$B259,Exceptions!$D$5:$D$104,$C259,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K259)))</f>
+        <v/>
+      </c>
+      <c r="M259" s="39">
+        <f>IF($A259="","",IF($H259="","Declaration missing",IF($H259="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R259),$R259&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H259="Fully Compliant",$J259&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N259" s="58">
+        <f>IF($A259="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C259,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O259" s="58">
+        <f>IF($A259="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C259,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P259" s="58">
+        <f>IF($A259="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C259,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q259" s="58">
+        <f>IF($A259="","",$A259&amp;"|"&amp;$B259&amp;"|"&amp;$C259)</f>
+        <v/>
+      </c>
+      <c r="R259" s="59" t="n"/>
+      <c r="S259" s="60" t="n"/>
+    </row>
+    <row r="260" ht="15" customHeight="1" s="34">
+      <c r="A260" s="54" t="n"/>
+      <c r="B260" s="54" t="n"/>
+      <c r="C260" s="54" t="n"/>
+      <c r="D260" s="55">
+        <f>IF($A260="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C260,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E260" s="55">
+        <f>IF($A260="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C260,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F260" s="56">
+        <f>IF($A260="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C260,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G260" s="57" t="n"/>
+      <c r="H260" s="54" t="n"/>
+      <c r="I260" s="54" t="n"/>
+      <c r="J260" s="39">
+        <f>IF($A260="","",IF($E260="Informational","GREEN",IF($G260="",IF($E260="Mandatory","RED","YELLOW"),IF($N260="Exact",IF(UPPER(TRIM($G260&amp;""))=UPPER(TRIM($F260&amp;"")),"GREEN",$P260),IF(NOT(ISNUMBER($G260)),$P260,IF($N260="Min",IF($G260&gt;=$F260,"GREEN",IF($G260&gt;=$F260-$O260,"YELLOW",$P260)),IF($N260="Max",IF($G260&lt;=$F260,"GREEN",IF($G260&lt;=$F260+$O260,"YELLOW",$P260)),IF($N260="Range",IF(ABS($G260-$F260)&lt;=$O260,"GREEN",$P260),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K260" s="39">
+        <f>IF($A260="","",IF($H260="Non-Compliant","RED",IF(AND(OR($H260="Alternative Offer",$H260="Partially Compliant"),$J260="GREEN"),"YELLOW",IF(AND($J260="GREEN",ISNUMBER($R260),$R260&lt;Baseline!$B$9),"YELLOW",$J260))))</f>
+        <v/>
+      </c>
+      <c r="L260" s="39">
+        <f>IF($A260="","",IF($K260="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A260,Exceptions!$C$5:$C$104,$B260,Exceptions!$D$5:$D$104,$C260,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K260)))</f>
+        <v/>
+      </c>
+      <c r="M260" s="39">
+        <f>IF($A260="","",IF($H260="","Declaration missing",IF($H260="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R260),$R260&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H260="Fully Compliant",$J260&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N260" s="58">
+        <f>IF($A260="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C260,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O260" s="58">
+        <f>IF($A260="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C260,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P260" s="58">
+        <f>IF($A260="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C260,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q260" s="58">
+        <f>IF($A260="","",$A260&amp;"|"&amp;$B260&amp;"|"&amp;$C260)</f>
+        <v/>
+      </c>
+      <c r="R260" s="59" t="n"/>
+      <c r="S260" s="60" t="n"/>
+    </row>
+    <row r="261" ht="15" customHeight="1" s="34">
+      <c r="A261" s="54" t="n"/>
+      <c r="B261" s="54" t="n"/>
+      <c r="C261" s="54" t="n"/>
+      <c r="D261" s="55">
+        <f>IF($A261="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C261,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E261" s="55">
+        <f>IF($A261="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C261,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F261" s="56">
+        <f>IF($A261="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C261,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G261" s="57" t="n"/>
+      <c r="H261" s="54" t="n"/>
+      <c r="I261" s="54" t="n"/>
+      <c r="J261" s="39">
+        <f>IF($A261="","",IF($E261="Informational","GREEN",IF($G261="",IF($E261="Mandatory","RED","YELLOW"),IF($N261="Exact",IF(UPPER(TRIM($G261&amp;""))=UPPER(TRIM($F261&amp;"")),"GREEN",$P261),IF(NOT(ISNUMBER($G261)),$P261,IF($N261="Min",IF($G261&gt;=$F261,"GREEN",IF($G261&gt;=$F261-$O261,"YELLOW",$P261)),IF($N261="Max",IF($G261&lt;=$F261,"GREEN",IF($G261&lt;=$F261+$O261,"YELLOW",$P261)),IF($N261="Range",IF(ABS($G261-$F261)&lt;=$O261,"GREEN",$P261),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K261" s="39">
+        <f>IF($A261="","",IF($H261="Non-Compliant","RED",IF(AND(OR($H261="Alternative Offer",$H261="Partially Compliant"),$J261="GREEN"),"YELLOW",IF(AND($J261="GREEN",ISNUMBER($R261),$R261&lt;Baseline!$B$9),"YELLOW",$J261))))</f>
+        <v/>
+      </c>
+      <c r="L261" s="39">
+        <f>IF($A261="","",IF($K261="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A261,Exceptions!$C$5:$C$104,$B261,Exceptions!$D$5:$D$104,$C261,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K261)))</f>
+        <v/>
+      </c>
+      <c r="M261" s="39">
+        <f>IF($A261="","",IF($H261="","Declaration missing",IF($H261="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R261),$R261&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H261="Fully Compliant",$J261&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N261" s="58">
+        <f>IF($A261="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C261,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O261" s="58">
+        <f>IF($A261="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C261,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P261" s="58">
+        <f>IF($A261="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C261,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q261" s="58">
+        <f>IF($A261="","",$A261&amp;"|"&amp;$B261&amp;"|"&amp;$C261)</f>
+        <v/>
+      </c>
+      <c r="R261" s="59" t="n"/>
+      <c r="S261" s="60" t="n"/>
+    </row>
+    <row r="262" ht="15" customHeight="1" s="34">
+      <c r="A262" s="54" t="n"/>
+      <c r="B262" s="54" t="n"/>
+      <c r="C262" s="54" t="n"/>
+      <c r="D262" s="55">
+        <f>IF($A262="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C262,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E262" s="55">
+        <f>IF($A262="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C262,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F262" s="56">
+        <f>IF($A262="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C262,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G262" s="57" t="n"/>
+      <c r="H262" s="54" t="n"/>
+      <c r="I262" s="54" t="n"/>
+      <c r="J262" s="39">
+        <f>IF($A262="","",IF($E262="Informational","GREEN",IF($G262="",IF($E262="Mandatory","RED","YELLOW"),IF($N262="Exact",IF(UPPER(TRIM($G262&amp;""))=UPPER(TRIM($F262&amp;"")),"GREEN",$P262),IF(NOT(ISNUMBER($G262)),$P262,IF($N262="Min",IF($G262&gt;=$F262,"GREEN",IF($G262&gt;=$F262-$O262,"YELLOW",$P262)),IF($N262="Max",IF($G262&lt;=$F262,"GREEN",IF($G262&lt;=$F262+$O262,"YELLOW",$P262)),IF($N262="Range",IF(ABS($G262-$F262)&lt;=$O262,"GREEN",$P262),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K262" s="39">
+        <f>IF($A262="","",IF($H262="Non-Compliant","RED",IF(AND(OR($H262="Alternative Offer",$H262="Partially Compliant"),$J262="GREEN"),"YELLOW",IF(AND($J262="GREEN",ISNUMBER($R262),$R262&lt;Baseline!$B$9),"YELLOW",$J262))))</f>
+        <v/>
+      </c>
+      <c r="L262" s="39">
+        <f>IF($A262="","",IF($K262="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A262,Exceptions!$C$5:$C$104,$B262,Exceptions!$D$5:$D$104,$C262,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K262)))</f>
+        <v/>
+      </c>
+      <c r="M262" s="39">
+        <f>IF($A262="","",IF($H262="","Declaration missing",IF($H262="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R262),$R262&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H262="Fully Compliant",$J262&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N262" s="58">
+        <f>IF($A262="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C262,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O262" s="58">
+        <f>IF($A262="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C262,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P262" s="58">
+        <f>IF($A262="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C262,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q262" s="58">
+        <f>IF($A262="","",$A262&amp;"|"&amp;$B262&amp;"|"&amp;$C262)</f>
+        <v/>
+      </c>
+      <c r="R262" s="59" t="n"/>
+      <c r="S262" s="60" t="n"/>
+    </row>
+    <row r="263" ht="15" customHeight="1" s="34">
+      <c r="A263" s="54" t="n"/>
+      <c r="B263" s="54" t="n"/>
+      <c r="C263" s="54" t="n"/>
+      <c r="D263" s="55">
+        <f>IF($A263="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C263,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E263" s="55">
+        <f>IF($A263="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C263,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F263" s="56">
+        <f>IF($A263="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C263,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G263" s="57" t="n"/>
+      <c r="H263" s="54" t="n"/>
+      <c r="I263" s="54" t="n"/>
+      <c r="J263" s="39">
+        <f>IF($A263="","",IF($E263="Informational","GREEN",IF($G263="",IF($E263="Mandatory","RED","YELLOW"),IF($N263="Exact",IF(UPPER(TRIM($G263&amp;""))=UPPER(TRIM($F263&amp;"")),"GREEN",$P263),IF(NOT(ISNUMBER($G263)),$P263,IF($N263="Min",IF($G263&gt;=$F263,"GREEN",IF($G263&gt;=$F263-$O263,"YELLOW",$P263)),IF($N263="Max",IF($G263&lt;=$F263,"GREEN",IF($G263&lt;=$F263+$O263,"YELLOW",$P263)),IF($N263="Range",IF(ABS($G263-$F263)&lt;=$O263,"GREEN",$P263),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K263" s="39">
+        <f>IF($A263="","",IF($H263="Non-Compliant","RED",IF(AND(OR($H263="Alternative Offer",$H263="Partially Compliant"),$J263="GREEN"),"YELLOW",IF(AND($J263="GREEN",ISNUMBER($R263),$R263&lt;Baseline!$B$9),"YELLOW",$J263))))</f>
+        <v/>
+      </c>
+      <c r="L263" s="39">
+        <f>IF($A263="","",IF($K263="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A263,Exceptions!$C$5:$C$104,$B263,Exceptions!$D$5:$D$104,$C263,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K263)))</f>
+        <v/>
+      </c>
+      <c r="M263" s="39">
+        <f>IF($A263="","",IF($H263="","Declaration missing",IF($H263="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R263),$R263&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H263="Fully Compliant",$J263&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N263" s="58">
+        <f>IF($A263="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C263,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O263" s="58">
+        <f>IF($A263="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C263,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P263" s="58">
+        <f>IF($A263="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C263,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q263" s="58">
+        <f>IF($A263="","",$A263&amp;"|"&amp;$B263&amp;"|"&amp;$C263)</f>
+        <v/>
+      </c>
+      <c r="R263" s="59" t="n"/>
+      <c r="S263" s="60" t="n"/>
+    </row>
+    <row r="264" ht="15" customHeight="1" s="34">
+      <c r="A264" s="54" t="n"/>
+      <c r="B264" s="54" t="n"/>
+      <c r="C264" s="54" t="n"/>
+      <c r="D264" s="55">
+        <f>IF($A264="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C264,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E264" s="55">
+        <f>IF($A264="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C264,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F264" s="56">
+        <f>IF($A264="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C264,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G264" s="57" t="n"/>
+      <c r="H264" s="54" t="n"/>
+      <c r="I264" s="54" t="n"/>
+      <c r="J264" s="39">
+        <f>IF($A264="","",IF($E264="Informational","GREEN",IF($G264="",IF($E264="Mandatory","RED","YELLOW"),IF($N264="Exact",IF(UPPER(TRIM($G264&amp;""))=UPPER(TRIM($F264&amp;"")),"GREEN",$P264),IF(NOT(ISNUMBER($G264)),$P264,IF($N264="Min",IF($G264&gt;=$F264,"GREEN",IF($G264&gt;=$F264-$O264,"YELLOW",$P264)),IF($N264="Max",IF($G264&lt;=$F264,"GREEN",IF($G264&lt;=$F264+$O264,"YELLOW",$P264)),IF($N264="Range",IF(ABS($G264-$F264)&lt;=$O264,"GREEN",$P264),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K264" s="39">
+        <f>IF($A264="","",IF($H264="Non-Compliant","RED",IF(AND(OR($H264="Alternative Offer",$H264="Partially Compliant"),$J264="GREEN"),"YELLOW",IF(AND($J264="GREEN",ISNUMBER($R264),$R264&lt;Baseline!$B$9),"YELLOW",$J264))))</f>
+        <v/>
+      </c>
+      <c r="L264" s="39">
+        <f>IF($A264="","",IF($K264="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A264,Exceptions!$C$5:$C$104,$B264,Exceptions!$D$5:$D$104,$C264,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K264)))</f>
+        <v/>
+      </c>
+      <c r="M264" s="39">
+        <f>IF($A264="","",IF($H264="","Declaration missing",IF($H264="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R264),$R264&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H264="Fully Compliant",$J264&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N264" s="58">
+        <f>IF($A264="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C264,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O264" s="58">
+        <f>IF($A264="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C264,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P264" s="58">
+        <f>IF($A264="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C264,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q264" s="58">
+        <f>IF($A264="","",$A264&amp;"|"&amp;$B264&amp;"|"&amp;$C264)</f>
+        <v/>
+      </c>
+      <c r="R264" s="59" t="n"/>
+      <c r="S264" s="60" t="n"/>
+    </row>
+    <row r="265" ht="15" customHeight="1" s="34">
+      <c r="A265" s="54" t="n"/>
+      <c r="B265" s="54" t="n"/>
+      <c r="C265" s="54" t="n"/>
+      <c r="D265" s="55">
+        <f>IF($A265="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C265,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E265" s="55">
+        <f>IF($A265="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C265,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F265" s="56">
+        <f>IF($A265="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C265,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G265" s="57" t="n"/>
+      <c r="H265" s="54" t="n"/>
+      <c r="I265" s="54" t="n"/>
+      <c r="J265" s="39">
+        <f>IF($A265="","",IF($E265="Informational","GREEN",IF($G265="",IF($E265="Mandatory","RED","YELLOW"),IF($N265="Exact",IF(UPPER(TRIM($G265&amp;""))=UPPER(TRIM($F265&amp;"")),"GREEN",$P265),IF(NOT(ISNUMBER($G265)),$P265,IF($N265="Min",IF($G265&gt;=$F265,"GREEN",IF($G265&gt;=$F265-$O265,"YELLOW",$P265)),IF($N265="Max",IF($G265&lt;=$F265,"GREEN",IF($G265&lt;=$F265+$O265,"YELLOW",$P265)),IF($N265="Range",IF(ABS($G265-$F265)&lt;=$O265,"GREEN",$P265),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K265" s="39">
+        <f>IF($A265="","",IF($H265="Non-Compliant","RED",IF(AND(OR($H265="Alternative Offer",$H265="Partially Compliant"),$J265="GREEN"),"YELLOW",IF(AND($J265="GREEN",ISNUMBER($R265),$R265&lt;Baseline!$B$9),"YELLOW",$J265))))</f>
+        <v/>
+      </c>
+      <c r="L265" s="39">
+        <f>IF($A265="","",IF($K265="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A265,Exceptions!$C$5:$C$104,$B265,Exceptions!$D$5:$D$104,$C265,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K265)))</f>
+        <v/>
+      </c>
+      <c r="M265" s="39">
+        <f>IF($A265="","",IF($H265="","Declaration missing",IF($H265="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R265),$R265&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H265="Fully Compliant",$J265&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N265" s="58">
+        <f>IF($A265="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C265,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O265" s="58">
+        <f>IF($A265="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C265,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P265" s="58">
+        <f>IF($A265="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C265,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q265" s="58">
+        <f>IF($A265="","",$A265&amp;"|"&amp;$B265&amp;"|"&amp;$C265)</f>
+        <v/>
+      </c>
+      <c r="R265" s="59" t="n"/>
+      <c r="S265" s="60" t="n"/>
+    </row>
+    <row r="266" ht="15" customHeight="1" s="34">
+      <c r="A266" s="54" t="n"/>
+      <c r="B266" s="54" t="n"/>
+      <c r="C266" s="54" t="n"/>
+      <c r="D266" s="55">
+        <f>IF($A266="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C266,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E266" s="55">
+        <f>IF($A266="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C266,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F266" s="56">
+        <f>IF($A266="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C266,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G266" s="57" t="n"/>
+      <c r="H266" s="54" t="n"/>
+      <c r="I266" s="54" t="n"/>
+      <c r="J266" s="39">
+        <f>IF($A266="","",IF($E266="Informational","GREEN",IF($G266="",IF($E266="Mandatory","RED","YELLOW"),IF($N266="Exact",IF(UPPER(TRIM($G266&amp;""))=UPPER(TRIM($F266&amp;"")),"GREEN",$P266),IF(NOT(ISNUMBER($G266)),$P266,IF($N266="Min",IF($G266&gt;=$F266,"GREEN",IF($G266&gt;=$F266-$O266,"YELLOW",$P266)),IF($N266="Max",IF($G266&lt;=$F266,"GREEN",IF($G266&lt;=$F266+$O266,"YELLOW",$P266)),IF($N266="Range",IF(ABS($G266-$F266)&lt;=$O266,"GREEN",$P266),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K266" s="39">
+        <f>IF($A266="","",IF($H266="Non-Compliant","RED",IF(AND(OR($H266="Alternative Offer",$H266="Partially Compliant"),$J266="GREEN"),"YELLOW",IF(AND($J266="GREEN",ISNUMBER($R266),$R266&lt;Baseline!$B$9),"YELLOW",$J266))))</f>
+        <v/>
+      </c>
+      <c r="L266" s="39">
+        <f>IF($A266="","",IF($K266="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A266,Exceptions!$C$5:$C$104,$B266,Exceptions!$D$5:$D$104,$C266,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K266)))</f>
+        <v/>
+      </c>
+      <c r="M266" s="39">
+        <f>IF($A266="","",IF($H266="","Declaration missing",IF($H266="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R266),$R266&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H266="Fully Compliant",$J266&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N266" s="58">
+        <f>IF($A266="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C266,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O266" s="58">
+        <f>IF($A266="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C266,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P266" s="58">
+        <f>IF($A266="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C266,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q266" s="58">
+        <f>IF($A266="","",$A266&amp;"|"&amp;$B266&amp;"|"&amp;$C266)</f>
+        <v/>
+      </c>
+      <c r="R266" s="59" t="n"/>
+      <c r="S266" s="60" t="n"/>
+    </row>
+    <row r="267" ht="15" customHeight="1" s="34">
+      <c r="A267" s="54" t="n"/>
+      <c r="B267" s="54" t="n"/>
+      <c r="C267" s="54" t="n"/>
+      <c r="D267" s="55">
+        <f>IF($A267="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C267,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E267" s="55">
+        <f>IF($A267="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C267,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F267" s="56">
+        <f>IF($A267="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C267,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G267" s="57" t="n"/>
+      <c r="H267" s="54" t="n"/>
+      <c r="I267" s="54" t="n"/>
+      <c r="J267" s="39">
+        <f>IF($A267="","",IF($E267="Informational","GREEN",IF($G267="",IF($E267="Mandatory","RED","YELLOW"),IF($N267="Exact",IF(UPPER(TRIM($G267&amp;""))=UPPER(TRIM($F267&amp;"")),"GREEN",$P267),IF(NOT(ISNUMBER($G267)),$P267,IF($N267="Min",IF($G267&gt;=$F267,"GREEN",IF($G267&gt;=$F267-$O267,"YELLOW",$P267)),IF($N267="Max",IF($G267&lt;=$F267,"GREEN",IF($G267&lt;=$F267+$O267,"YELLOW",$P267)),IF($N267="Range",IF(ABS($G267-$F267)&lt;=$O267,"GREEN",$P267),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K267" s="39">
+        <f>IF($A267="","",IF($H267="Non-Compliant","RED",IF(AND(OR($H267="Alternative Offer",$H267="Partially Compliant"),$J267="GREEN"),"YELLOW",IF(AND($J267="GREEN",ISNUMBER($R267),$R267&lt;Baseline!$B$9),"YELLOW",$J267))))</f>
+        <v/>
+      </c>
+      <c r="L267" s="39">
+        <f>IF($A267="","",IF($K267="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A267,Exceptions!$C$5:$C$104,$B267,Exceptions!$D$5:$D$104,$C267,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K267)))</f>
+        <v/>
+      </c>
+      <c r="M267" s="39">
+        <f>IF($A267="","",IF($H267="","Declaration missing",IF($H267="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R267),$R267&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H267="Fully Compliant",$J267&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N267" s="58">
+        <f>IF($A267="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C267,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O267" s="58">
+        <f>IF($A267="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C267,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P267" s="58">
+        <f>IF($A267="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C267,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q267" s="58">
+        <f>IF($A267="","",$A267&amp;"|"&amp;$B267&amp;"|"&amp;$C267)</f>
+        <v/>
+      </c>
+      <c r="R267" s="59" t="n"/>
+      <c r="S267" s="60" t="n"/>
+    </row>
+    <row r="268" ht="15" customHeight="1" s="34">
+      <c r="A268" s="54" t="n"/>
+      <c r="B268" s="54" t="n"/>
+      <c r="C268" s="54" t="n"/>
+      <c r="D268" s="55">
+        <f>IF($A268="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C268,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E268" s="55">
+        <f>IF($A268="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C268,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F268" s="56">
+        <f>IF($A268="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C268,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G268" s="57" t="n"/>
+      <c r="H268" s="54" t="n"/>
+      <c r="I268" s="54" t="n"/>
+      <c r="J268" s="39">
+        <f>IF($A268="","",IF($E268="Informational","GREEN",IF($G268="",IF($E268="Mandatory","RED","YELLOW"),IF($N268="Exact",IF(UPPER(TRIM($G268&amp;""))=UPPER(TRIM($F268&amp;"")),"GREEN",$P268),IF(NOT(ISNUMBER($G268)),$P268,IF($N268="Min",IF($G268&gt;=$F268,"GREEN",IF($G268&gt;=$F268-$O268,"YELLOW",$P268)),IF($N268="Max",IF($G268&lt;=$F268,"GREEN",IF($G268&lt;=$F268+$O268,"YELLOW",$P268)),IF($N268="Range",IF(ABS($G268-$F268)&lt;=$O268,"GREEN",$P268),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K268" s="39">
+        <f>IF($A268="","",IF($H268="Non-Compliant","RED",IF(AND(OR($H268="Alternative Offer",$H268="Partially Compliant"),$J268="GREEN"),"YELLOW",IF(AND($J268="GREEN",ISNUMBER($R268),$R268&lt;Baseline!$B$9),"YELLOW",$J268))))</f>
+        <v/>
+      </c>
+      <c r="L268" s="39">
+        <f>IF($A268="","",IF($K268="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A268,Exceptions!$C$5:$C$104,$B268,Exceptions!$D$5:$D$104,$C268,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K268)))</f>
+        <v/>
+      </c>
+      <c r="M268" s="39">
+        <f>IF($A268="","",IF($H268="","Declaration missing",IF($H268="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R268),$R268&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H268="Fully Compliant",$J268&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N268" s="58">
+        <f>IF($A268="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C268,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O268" s="58">
+        <f>IF($A268="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C268,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P268" s="58">
+        <f>IF($A268="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C268,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q268" s="58">
+        <f>IF($A268="","",$A268&amp;"|"&amp;$B268&amp;"|"&amp;$C268)</f>
+        <v/>
+      </c>
+      <c r="R268" s="59" t="n"/>
+      <c r="S268" s="60" t="n"/>
+    </row>
+    <row r="269" ht="15" customHeight="1" s="34">
+      <c r="A269" s="54" t="n"/>
+      <c r="B269" s="54" t="n"/>
+      <c r="C269" s="54" t="n"/>
+      <c r="D269" s="55">
+        <f>IF($A269="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C269,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E269" s="55">
+        <f>IF($A269="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C269,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F269" s="56">
+        <f>IF($A269="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C269,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G269" s="57" t="n"/>
+      <c r="H269" s="54" t="n"/>
+      <c r="I269" s="54" t="n"/>
+      <c r="J269" s="39">
+        <f>IF($A269="","",IF($E269="Informational","GREEN",IF($G269="",IF($E269="Mandatory","RED","YELLOW"),IF($N269="Exact",IF(UPPER(TRIM($G269&amp;""))=UPPER(TRIM($F269&amp;"")),"GREEN",$P269),IF(NOT(ISNUMBER($G269)),$P269,IF($N269="Min",IF($G269&gt;=$F269,"GREEN",IF($G269&gt;=$F269-$O269,"YELLOW",$P269)),IF($N269="Max",IF($G269&lt;=$F269,"GREEN",IF($G269&lt;=$F269+$O269,"YELLOW",$P269)),IF($N269="Range",IF(ABS($G269-$F269)&lt;=$O269,"GREEN",$P269),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K269" s="39">
+        <f>IF($A269="","",IF($H269="Non-Compliant","RED",IF(AND(OR($H269="Alternative Offer",$H269="Partially Compliant"),$J269="GREEN"),"YELLOW",IF(AND($J269="GREEN",ISNUMBER($R269),$R269&lt;Baseline!$B$9),"YELLOW",$J269))))</f>
+        <v/>
+      </c>
+      <c r="L269" s="39">
+        <f>IF($A269="","",IF($K269="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A269,Exceptions!$C$5:$C$104,$B269,Exceptions!$D$5:$D$104,$C269,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K269)))</f>
+        <v/>
+      </c>
+      <c r="M269" s="39">
+        <f>IF($A269="","",IF($H269="","Declaration missing",IF($H269="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R269),$R269&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H269="Fully Compliant",$J269&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N269" s="58">
+        <f>IF($A269="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C269,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O269" s="58">
+        <f>IF($A269="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C269,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P269" s="58">
+        <f>IF($A269="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C269,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q269" s="58">
+        <f>IF($A269="","",$A269&amp;"|"&amp;$B269&amp;"|"&amp;$C269)</f>
+        <v/>
+      </c>
+      <c r="R269" s="59" t="n"/>
+      <c r="S269" s="60" t="n"/>
+    </row>
+    <row r="270" ht="15" customHeight="1" s="34">
+      <c r="A270" s="54" t="n"/>
+      <c r="B270" s="54" t="n"/>
+      <c r="C270" s="54" t="n"/>
+      <c r="D270" s="55">
+        <f>IF($A270="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C270,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E270" s="55">
+        <f>IF($A270="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C270,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F270" s="56">
+        <f>IF($A270="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C270,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G270" s="57" t="n"/>
+      <c r="H270" s="54" t="n"/>
+      <c r="I270" s="54" t="n"/>
+      <c r="J270" s="39">
+        <f>IF($A270="","",IF($E270="Informational","GREEN",IF($G270="",IF($E270="Mandatory","RED","YELLOW"),IF($N270="Exact",IF(UPPER(TRIM($G270&amp;""))=UPPER(TRIM($F270&amp;"")),"GREEN",$P270),IF(NOT(ISNUMBER($G270)),$P270,IF($N270="Min",IF($G270&gt;=$F270,"GREEN",IF($G270&gt;=$F270-$O270,"YELLOW",$P270)),IF($N270="Max",IF($G270&lt;=$F270,"GREEN",IF($G270&lt;=$F270+$O270,"YELLOW",$P270)),IF($N270="Range",IF(ABS($G270-$F270)&lt;=$O270,"GREEN",$P270),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K270" s="39">
+        <f>IF($A270="","",IF($H270="Non-Compliant","RED",IF(AND(OR($H270="Alternative Offer",$H270="Partially Compliant"),$J270="GREEN"),"YELLOW",IF(AND($J270="GREEN",ISNUMBER($R270),$R270&lt;Baseline!$B$9),"YELLOW",$J270))))</f>
+        <v/>
+      </c>
+      <c r="L270" s="39">
+        <f>IF($A270="","",IF($K270="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A270,Exceptions!$C$5:$C$104,$B270,Exceptions!$D$5:$D$104,$C270,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K270)))</f>
+        <v/>
+      </c>
+      <c r="M270" s="39">
+        <f>IF($A270="","",IF($H270="","Declaration missing",IF($H270="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R270),$R270&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H270="Fully Compliant",$J270&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N270" s="58">
+        <f>IF($A270="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C270,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O270" s="58">
+        <f>IF($A270="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C270,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P270" s="58">
+        <f>IF($A270="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C270,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q270" s="58">
+        <f>IF($A270="","",$A270&amp;"|"&amp;$B270&amp;"|"&amp;$C270)</f>
+        <v/>
+      </c>
+      <c r="R270" s="59" t="n"/>
+      <c r="S270" s="60" t="n"/>
+    </row>
+    <row r="271" ht="15" customHeight="1" s="34">
+      <c r="A271" s="54" t="n"/>
+      <c r="B271" s="54" t="n"/>
+      <c r="C271" s="54" t="n"/>
+      <c r="D271" s="55">
+        <f>IF($A271="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C271,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E271" s="55">
+        <f>IF($A271="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C271,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F271" s="56">
+        <f>IF($A271="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C271,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G271" s="57" t="n"/>
+      <c r="H271" s="54" t="n"/>
+      <c r="I271" s="54" t="n"/>
+      <c r="J271" s="39">
+        <f>IF($A271="","",IF($E271="Informational","GREEN",IF($G271="",IF($E271="Mandatory","RED","YELLOW"),IF($N271="Exact",IF(UPPER(TRIM($G271&amp;""))=UPPER(TRIM($F271&amp;"")),"GREEN",$P271),IF(NOT(ISNUMBER($G271)),$P271,IF($N271="Min",IF($G271&gt;=$F271,"GREEN",IF($G271&gt;=$F271-$O271,"YELLOW",$P271)),IF($N271="Max",IF($G271&lt;=$F271,"GREEN",IF($G271&lt;=$F271+$O271,"YELLOW",$P271)),IF($N271="Range",IF(ABS($G271-$F271)&lt;=$O271,"GREEN",$P271),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K271" s="39">
+        <f>IF($A271="","",IF($H271="Non-Compliant","RED",IF(AND(OR($H271="Alternative Offer",$H271="Partially Compliant"),$J271="GREEN"),"YELLOW",IF(AND($J271="GREEN",ISNUMBER($R271),$R271&lt;Baseline!$B$9),"YELLOW",$J271))))</f>
+        <v/>
+      </c>
+      <c r="L271" s="39">
+        <f>IF($A271="","",IF($K271="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A271,Exceptions!$C$5:$C$104,$B271,Exceptions!$D$5:$D$104,$C271,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K271)))</f>
+        <v/>
+      </c>
+      <c r="M271" s="39">
+        <f>IF($A271="","",IF($H271="","Declaration missing",IF($H271="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R271),$R271&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H271="Fully Compliant",$J271&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N271" s="58">
+        <f>IF($A271="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C271,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O271" s="58">
+        <f>IF($A271="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C271,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P271" s="58">
+        <f>IF($A271="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C271,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q271" s="58">
+        <f>IF($A271="","",$A271&amp;"|"&amp;$B271&amp;"|"&amp;$C271)</f>
+        <v/>
+      </c>
+      <c r="R271" s="59" t="n"/>
+      <c r="S271" s="60" t="n"/>
+    </row>
+    <row r="272" ht="15" customHeight="1" s="34">
+      <c r="A272" s="54" t="n"/>
+      <c r="B272" s="54" t="n"/>
+      <c r="C272" s="54" t="n"/>
+      <c r="D272" s="55">
+        <f>IF($A272="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C272,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E272" s="55">
+        <f>IF($A272="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C272,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F272" s="56">
+        <f>IF($A272="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C272,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G272" s="57" t="n"/>
+      <c r="H272" s="54" t="n"/>
+      <c r="I272" s="54" t="n"/>
+      <c r="J272" s="39">
+        <f>IF($A272="","",IF($E272="Informational","GREEN",IF($G272="",IF($E272="Mandatory","RED","YELLOW"),IF($N272="Exact",IF(UPPER(TRIM($G272&amp;""))=UPPER(TRIM($F272&amp;"")),"GREEN",$P272),IF(NOT(ISNUMBER($G272)),$P272,IF($N272="Min",IF($G272&gt;=$F272,"GREEN",IF($G272&gt;=$F272-$O272,"YELLOW",$P272)),IF($N272="Max",IF($G272&lt;=$F272,"GREEN",IF($G272&lt;=$F272+$O272,"YELLOW",$P272)),IF($N272="Range",IF(ABS($G272-$F272)&lt;=$O272,"GREEN",$P272),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K272" s="39">
+        <f>IF($A272="","",IF($H272="Non-Compliant","RED",IF(AND(OR($H272="Alternative Offer",$H272="Partially Compliant"),$J272="GREEN"),"YELLOW",IF(AND($J272="GREEN",ISNUMBER($R272),$R272&lt;Baseline!$B$9),"YELLOW",$J272))))</f>
+        <v/>
+      </c>
+      <c r="L272" s="39">
+        <f>IF($A272="","",IF($K272="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A272,Exceptions!$C$5:$C$104,$B272,Exceptions!$D$5:$D$104,$C272,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K272)))</f>
+        <v/>
+      </c>
+      <c r="M272" s="39">
+        <f>IF($A272="","",IF($H272="","Declaration missing",IF($H272="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R272),$R272&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H272="Fully Compliant",$J272&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N272" s="58">
+        <f>IF($A272="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C272,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O272" s="58">
+        <f>IF($A272="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C272,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P272" s="58">
+        <f>IF($A272="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C272,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q272" s="58">
+        <f>IF($A272="","",$A272&amp;"|"&amp;$B272&amp;"|"&amp;$C272)</f>
+        <v/>
+      </c>
+      <c r="R272" s="59" t="n"/>
+      <c r="S272" s="60" t="n"/>
+    </row>
+    <row r="273" ht="15" customHeight="1" s="34">
+      <c r="A273" s="54" t="n"/>
+      <c r="B273" s="54" t="n"/>
+      <c r="C273" s="54" t="n"/>
+      <c r="D273" s="55">
+        <f>IF($A273="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C273,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E273" s="55">
+        <f>IF($A273="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C273,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F273" s="56">
+        <f>IF($A273="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C273,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G273" s="57" t="n"/>
+      <c r="H273" s="54" t="n"/>
+      <c r="I273" s="54" t="n"/>
+      <c r="J273" s="39">
+        <f>IF($A273="","",IF($E273="Informational","GREEN",IF($G273="",IF($E273="Mandatory","RED","YELLOW"),IF($N273="Exact",IF(UPPER(TRIM($G273&amp;""))=UPPER(TRIM($F273&amp;"")),"GREEN",$P273),IF(NOT(ISNUMBER($G273)),$P273,IF($N273="Min",IF($G273&gt;=$F273,"GREEN",IF($G273&gt;=$F273-$O273,"YELLOW",$P273)),IF($N273="Max",IF($G273&lt;=$F273,"GREEN",IF($G273&lt;=$F273+$O273,"YELLOW",$P273)),IF($N273="Range",IF(ABS($G273-$F273)&lt;=$O273,"GREEN",$P273),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K273" s="39">
+        <f>IF($A273="","",IF($H273="Non-Compliant","RED",IF(AND(OR($H273="Alternative Offer",$H273="Partially Compliant"),$J273="GREEN"),"YELLOW",IF(AND($J273="GREEN",ISNUMBER($R273),$R273&lt;Baseline!$B$9),"YELLOW",$J273))))</f>
+        <v/>
+      </c>
+      <c r="L273" s="39">
+        <f>IF($A273="","",IF($K273="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A273,Exceptions!$C$5:$C$104,$B273,Exceptions!$D$5:$D$104,$C273,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K273)))</f>
+        <v/>
+      </c>
+      <c r="M273" s="39">
+        <f>IF($A273="","",IF($H273="","Declaration missing",IF($H273="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R273),$R273&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H273="Fully Compliant",$J273&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N273" s="58">
+        <f>IF($A273="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C273,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O273" s="58">
+        <f>IF($A273="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C273,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P273" s="58">
+        <f>IF($A273="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C273,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q273" s="58">
+        <f>IF($A273="","",$A273&amp;"|"&amp;$B273&amp;"|"&amp;$C273)</f>
+        <v/>
+      </c>
+      <c r="R273" s="59" t="n"/>
+      <c r="S273" s="60" t="n"/>
+    </row>
+    <row r="274" ht="15" customHeight="1" s="34">
+      <c r="A274" s="54" t="n"/>
+      <c r="B274" s="54" t="n"/>
+      <c r="C274" s="54" t="n"/>
+      <c r="D274" s="55">
+        <f>IF($A274="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C274,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E274" s="55">
+        <f>IF($A274="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C274,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F274" s="56">
+        <f>IF($A274="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C274,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G274" s="57" t="n"/>
+      <c r="H274" s="54" t="n"/>
+      <c r="I274" s="54" t="n"/>
+      <c r="J274" s="39">
+        <f>IF($A274="","",IF($E274="Informational","GREEN",IF($G274="",IF($E274="Mandatory","RED","YELLOW"),IF($N274="Exact",IF(UPPER(TRIM($G274&amp;""))=UPPER(TRIM($F274&amp;"")),"GREEN",$P274),IF(NOT(ISNUMBER($G274)),$P274,IF($N274="Min",IF($G274&gt;=$F274,"GREEN",IF($G274&gt;=$F274-$O274,"YELLOW",$P274)),IF($N274="Max",IF($G274&lt;=$F274,"GREEN",IF($G274&lt;=$F274+$O274,"YELLOW",$P274)),IF($N274="Range",IF(ABS($G274-$F274)&lt;=$O274,"GREEN",$P274),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K274" s="39">
+        <f>IF($A274="","",IF($H274="Non-Compliant","RED",IF(AND(OR($H274="Alternative Offer",$H274="Partially Compliant"),$J274="GREEN"),"YELLOW",IF(AND($J274="GREEN",ISNUMBER($R274),$R274&lt;Baseline!$B$9),"YELLOW",$J274))))</f>
+        <v/>
+      </c>
+      <c r="L274" s="39">
+        <f>IF($A274="","",IF($K274="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A274,Exceptions!$C$5:$C$104,$B274,Exceptions!$D$5:$D$104,$C274,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K274)))</f>
+        <v/>
+      </c>
+      <c r="M274" s="39">
+        <f>IF($A274="","",IF($H274="","Declaration missing",IF($H274="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R274),$R274&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H274="Fully Compliant",$J274&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N274" s="58">
+        <f>IF($A274="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C274,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O274" s="58">
+        <f>IF($A274="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C274,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P274" s="58">
+        <f>IF($A274="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C274,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q274" s="58">
+        <f>IF($A274="","",$A274&amp;"|"&amp;$B274&amp;"|"&amp;$C274)</f>
+        <v/>
+      </c>
+      <c r="R274" s="59" t="n"/>
+      <c r="S274" s="60" t="n"/>
+    </row>
+    <row r="275" ht="15" customHeight="1" s="34">
+      <c r="A275" s="54" t="n"/>
+      <c r="B275" s="54" t="n"/>
+      <c r="C275" s="54" t="n"/>
+      <c r="D275" s="55">
+        <f>IF($A275="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C275,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E275" s="55">
+        <f>IF($A275="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C275,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F275" s="56">
+        <f>IF($A275="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C275,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G275" s="57" t="n"/>
+      <c r="H275" s="54" t="n"/>
+      <c r="I275" s="54" t="n"/>
+      <c r="J275" s="39">
+        <f>IF($A275="","",IF($E275="Informational","GREEN",IF($G275="",IF($E275="Mandatory","RED","YELLOW"),IF($N275="Exact",IF(UPPER(TRIM($G275&amp;""))=UPPER(TRIM($F275&amp;"")),"GREEN",$P275),IF(NOT(ISNUMBER($G275)),$P275,IF($N275="Min",IF($G275&gt;=$F275,"GREEN",IF($G275&gt;=$F275-$O275,"YELLOW",$P275)),IF($N275="Max",IF($G275&lt;=$F275,"GREEN",IF($G275&lt;=$F275+$O275,"YELLOW",$P275)),IF($N275="Range",IF(ABS($G275-$F275)&lt;=$O275,"GREEN",$P275),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K275" s="39">
+        <f>IF($A275="","",IF($H275="Non-Compliant","RED",IF(AND(OR($H275="Alternative Offer",$H275="Partially Compliant"),$J275="GREEN"),"YELLOW",IF(AND($J275="GREEN",ISNUMBER($R275),$R275&lt;Baseline!$B$9),"YELLOW",$J275))))</f>
+        <v/>
+      </c>
+      <c r="L275" s="39">
+        <f>IF($A275="","",IF($K275="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A275,Exceptions!$C$5:$C$104,$B275,Exceptions!$D$5:$D$104,$C275,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K275)))</f>
+        <v/>
+      </c>
+      <c r="M275" s="39">
+        <f>IF($A275="","",IF($H275="","Declaration missing",IF($H275="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R275),$R275&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H275="Fully Compliant",$J275&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N275" s="58">
+        <f>IF($A275="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C275,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O275" s="58">
+        <f>IF($A275="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C275,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P275" s="58">
+        <f>IF($A275="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C275,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q275" s="58">
+        <f>IF($A275="","",$A275&amp;"|"&amp;$B275&amp;"|"&amp;$C275)</f>
+        <v/>
+      </c>
+      <c r="R275" s="59" t="n"/>
+      <c r="S275" s="60" t="n"/>
+    </row>
+    <row r="276" ht="15" customHeight="1" s="34">
+      <c r="A276" s="54" t="n"/>
+      <c r="B276" s="54" t="n"/>
+      <c r="C276" s="54" t="n"/>
+      <c r="D276" s="55">
+        <f>IF($A276="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C276,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E276" s="55">
+        <f>IF($A276="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C276,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F276" s="56">
+        <f>IF($A276="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C276,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G276" s="57" t="n"/>
+      <c r="H276" s="54" t="n"/>
+      <c r="I276" s="54" t="n"/>
+      <c r="J276" s="39">
+        <f>IF($A276="","",IF($E276="Informational","GREEN",IF($G276="",IF($E276="Mandatory","RED","YELLOW"),IF($N276="Exact",IF(UPPER(TRIM($G276&amp;""))=UPPER(TRIM($F276&amp;"")),"GREEN",$P276),IF(NOT(ISNUMBER($G276)),$P276,IF($N276="Min",IF($G276&gt;=$F276,"GREEN",IF($G276&gt;=$F276-$O276,"YELLOW",$P276)),IF($N276="Max",IF($G276&lt;=$F276,"GREEN",IF($G276&lt;=$F276+$O276,"YELLOW",$P276)),IF($N276="Range",IF(ABS($G276-$F276)&lt;=$O276,"GREEN",$P276),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K276" s="39">
+        <f>IF($A276="","",IF($H276="Non-Compliant","RED",IF(AND(OR($H276="Alternative Offer",$H276="Partially Compliant"),$J276="GREEN"),"YELLOW",IF(AND($J276="GREEN",ISNUMBER($R276),$R276&lt;Baseline!$B$9),"YELLOW",$J276))))</f>
+        <v/>
+      </c>
+      <c r="L276" s="39">
+        <f>IF($A276="","",IF($K276="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A276,Exceptions!$C$5:$C$104,$B276,Exceptions!$D$5:$D$104,$C276,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K276)))</f>
+        <v/>
+      </c>
+      <c r="M276" s="39">
+        <f>IF($A276="","",IF($H276="","Declaration missing",IF($H276="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R276),$R276&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H276="Fully Compliant",$J276&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N276" s="58">
+        <f>IF($A276="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C276,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O276" s="58">
+        <f>IF($A276="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C276,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P276" s="58">
+        <f>IF($A276="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C276,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q276" s="58">
+        <f>IF($A276="","",$A276&amp;"|"&amp;$B276&amp;"|"&amp;$C276)</f>
+        <v/>
+      </c>
+      <c r="R276" s="59" t="n"/>
+      <c r="S276" s="60" t="n"/>
+    </row>
+    <row r="277" ht="15" customHeight="1" s="34">
+      <c r="A277" s="54" t="n"/>
+      <c r="B277" s="54" t="n"/>
+      <c r="C277" s="54" t="n"/>
+      <c r="D277" s="55">
+        <f>IF($A277="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C277,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E277" s="55">
+        <f>IF($A277="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C277,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F277" s="56">
+        <f>IF($A277="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C277,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G277" s="57" t="n"/>
+      <c r="H277" s="54" t="n"/>
+      <c r="I277" s="54" t="n"/>
+      <c r="J277" s="39">
+        <f>IF($A277="","",IF($E277="Informational","GREEN",IF($G277="",IF($E277="Mandatory","RED","YELLOW"),IF($N277="Exact",IF(UPPER(TRIM($G277&amp;""))=UPPER(TRIM($F277&amp;"")),"GREEN",$P277),IF(NOT(ISNUMBER($G277)),$P277,IF($N277="Min",IF($G277&gt;=$F277,"GREEN",IF($G277&gt;=$F277-$O277,"YELLOW",$P277)),IF($N277="Max",IF($G277&lt;=$F277,"GREEN",IF($G277&lt;=$F277+$O277,"YELLOW",$P277)),IF($N277="Range",IF(ABS($G277-$F277)&lt;=$O277,"GREEN",$P277),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K277" s="39">
+        <f>IF($A277="","",IF($H277="Non-Compliant","RED",IF(AND(OR($H277="Alternative Offer",$H277="Partially Compliant"),$J277="GREEN"),"YELLOW",IF(AND($J277="GREEN",ISNUMBER($R277),$R277&lt;Baseline!$B$9),"YELLOW",$J277))))</f>
+        <v/>
+      </c>
+      <c r="L277" s="39">
+        <f>IF($A277="","",IF($K277="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A277,Exceptions!$C$5:$C$104,$B277,Exceptions!$D$5:$D$104,$C277,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K277)))</f>
+        <v/>
+      </c>
+      <c r="M277" s="39">
+        <f>IF($A277="","",IF($H277="","Declaration missing",IF($H277="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R277),$R277&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H277="Fully Compliant",$J277&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N277" s="58">
+        <f>IF($A277="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C277,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O277" s="58">
+        <f>IF($A277="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C277,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P277" s="58">
+        <f>IF($A277="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C277,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q277" s="58">
+        <f>IF($A277="","",$A277&amp;"|"&amp;$B277&amp;"|"&amp;$C277)</f>
+        <v/>
+      </c>
+      <c r="R277" s="59" t="n"/>
+      <c r="S277" s="60" t="n"/>
+    </row>
+    <row r="278" ht="15" customHeight="1" s="34">
+      <c r="A278" s="54" t="n"/>
+      <c r="B278" s="54" t="n"/>
+      <c r="C278" s="54" t="n"/>
+      <c r="D278" s="55">
+        <f>IF($A278="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C278,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E278" s="55">
+        <f>IF($A278="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C278,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F278" s="56">
+        <f>IF($A278="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C278,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G278" s="57" t="n"/>
+      <c r="H278" s="54" t="n"/>
+      <c r="I278" s="54" t="n"/>
+      <c r="J278" s="39">
+        <f>IF($A278="","",IF($E278="Informational","GREEN",IF($G278="",IF($E278="Mandatory","RED","YELLOW"),IF($N278="Exact",IF(UPPER(TRIM($G278&amp;""))=UPPER(TRIM($F278&amp;"")),"GREEN",$P278),IF(NOT(ISNUMBER($G278)),$P278,IF($N278="Min",IF($G278&gt;=$F278,"GREEN",IF($G278&gt;=$F278-$O278,"YELLOW",$P278)),IF($N278="Max",IF($G278&lt;=$F278,"GREEN",IF($G278&lt;=$F278+$O278,"YELLOW",$P278)),IF($N278="Range",IF(ABS($G278-$F278)&lt;=$O278,"GREEN",$P278),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K278" s="39">
+        <f>IF($A278="","",IF($H278="Non-Compliant","RED",IF(AND(OR($H278="Alternative Offer",$H278="Partially Compliant"),$J278="GREEN"),"YELLOW",IF(AND($J278="GREEN",ISNUMBER($R278),$R278&lt;Baseline!$B$9),"YELLOW",$J278))))</f>
+        <v/>
+      </c>
+      <c r="L278" s="39">
+        <f>IF($A278="","",IF($K278="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A278,Exceptions!$C$5:$C$104,$B278,Exceptions!$D$5:$D$104,$C278,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K278)))</f>
+        <v/>
+      </c>
+      <c r="M278" s="39">
+        <f>IF($A278="","",IF($H278="","Declaration missing",IF($H278="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R278),$R278&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H278="Fully Compliant",$J278&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N278" s="58">
+        <f>IF($A278="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C278,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O278" s="58">
+        <f>IF($A278="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C278,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P278" s="58">
+        <f>IF($A278="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C278,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q278" s="58">
+        <f>IF($A278="","",$A278&amp;"|"&amp;$B278&amp;"|"&amp;$C278)</f>
+        <v/>
+      </c>
+      <c r="R278" s="59" t="n"/>
+      <c r="S278" s="60" t="n"/>
+    </row>
+    <row r="279" ht="15" customHeight="1" s="34">
+      <c r="A279" s="54" t="n"/>
+      <c r="B279" s="54" t="n"/>
+      <c r="C279" s="54" t="n"/>
+      <c r="D279" s="55">
+        <f>IF($A279="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C279,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E279" s="55">
+        <f>IF($A279="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C279,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F279" s="56">
+        <f>IF($A279="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C279,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G279" s="57" t="n"/>
+      <c r="H279" s="54" t="n"/>
+      <c r="I279" s="54" t="n"/>
+      <c r="J279" s="39">
+        <f>IF($A279="","",IF($E279="Informational","GREEN",IF($G279="",IF($E279="Mandatory","RED","YELLOW"),IF($N279="Exact",IF(UPPER(TRIM($G279&amp;""))=UPPER(TRIM($F279&amp;"")),"GREEN",$P279),IF(NOT(ISNUMBER($G279)),$P279,IF($N279="Min",IF($G279&gt;=$F279,"GREEN",IF($G279&gt;=$F279-$O279,"YELLOW",$P279)),IF($N279="Max",IF($G279&lt;=$F279,"GREEN",IF($G279&lt;=$F279+$O279,"YELLOW",$P279)),IF($N279="Range",IF(ABS($G279-$F279)&lt;=$O279,"GREEN",$P279),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K279" s="39">
+        <f>IF($A279="","",IF($H279="Non-Compliant","RED",IF(AND(OR($H279="Alternative Offer",$H279="Partially Compliant"),$J279="GREEN"),"YELLOW",IF(AND($J279="GREEN",ISNUMBER($R279),$R279&lt;Baseline!$B$9),"YELLOW",$J279))))</f>
+        <v/>
+      </c>
+      <c r="L279" s="39">
+        <f>IF($A279="","",IF($K279="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A279,Exceptions!$C$5:$C$104,$B279,Exceptions!$D$5:$D$104,$C279,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K279)))</f>
+        <v/>
+      </c>
+      <c r="M279" s="39">
+        <f>IF($A279="","",IF($H279="","Declaration missing",IF($H279="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R279),$R279&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H279="Fully Compliant",$J279&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N279" s="58">
+        <f>IF($A279="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C279,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O279" s="58">
+        <f>IF($A279="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C279,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P279" s="58">
+        <f>IF($A279="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C279,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q279" s="58">
+        <f>IF($A279="","",$A279&amp;"|"&amp;$B279&amp;"|"&amp;$C279)</f>
+        <v/>
+      </c>
+      <c r="R279" s="59" t="n"/>
+      <c r="S279" s="60" t="n"/>
+    </row>
+    <row r="280" ht="15" customHeight="1" s="34">
+      <c r="A280" s="54" t="n"/>
+      <c r="B280" s="54" t="n"/>
+      <c r="C280" s="54" t="n"/>
+      <c r="D280" s="55">
+        <f>IF($A280="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C280,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E280" s="55">
+        <f>IF($A280="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C280,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F280" s="56">
+        <f>IF($A280="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C280,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G280" s="57" t="n"/>
+      <c r="H280" s="54" t="n"/>
+      <c r="I280" s="54" t="n"/>
+      <c r="J280" s="39">
+        <f>IF($A280="","",IF($E280="Informational","GREEN",IF($G280="",IF($E280="Mandatory","RED","YELLOW"),IF($N280="Exact",IF(UPPER(TRIM($G280&amp;""))=UPPER(TRIM($F280&amp;"")),"GREEN",$P280),IF(NOT(ISNUMBER($G280)),$P280,IF($N280="Min",IF($G280&gt;=$F280,"GREEN",IF($G280&gt;=$F280-$O280,"YELLOW",$P280)),IF($N280="Max",IF($G280&lt;=$F280,"GREEN",IF($G280&lt;=$F280+$O280,"YELLOW",$P280)),IF($N280="Range",IF(ABS($G280-$F280)&lt;=$O280,"GREEN",$P280),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K280" s="39">
+        <f>IF($A280="","",IF($H280="Non-Compliant","RED",IF(AND(OR($H280="Alternative Offer",$H280="Partially Compliant"),$J280="GREEN"),"YELLOW",IF(AND($J280="GREEN",ISNUMBER($R280),$R280&lt;Baseline!$B$9),"YELLOW",$J280))))</f>
+        <v/>
+      </c>
+      <c r="L280" s="39">
+        <f>IF($A280="","",IF($K280="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A280,Exceptions!$C$5:$C$104,$B280,Exceptions!$D$5:$D$104,$C280,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K280)))</f>
+        <v/>
+      </c>
+      <c r="M280" s="39">
+        <f>IF($A280="","",IF($H280="","Declaration missing",IF($H280="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R280),$R280&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H280="Fully Compliant",$J280&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N280" s="58">
+        <f>IF($A280="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C280,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O280" s="58">
+        <f>IF($A280="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C280,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P280" s="58">
+        <f>IF($A280="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C280,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q280" s="58">
+        <f>IF($A280="","",$A280&amp;"|"&amp;$B280&amp;"|"&amp;$C280)</f>
+        <v/>
+      </c>
+      <c r="R280" s="59" t="n"/>
+      <c r="S280" s="60" t="n"/>
+    </row>
+    <row r="281" ht="15" customHeight="1" s="34">
+      <c r="A281" s="54" t="n"/>
+      <c r="B281" s="54" t="n"/>
+      <c r="C281" s="54" t="n"/>
+      <c r="D281" s="55">
+        <f>IF($A281="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C281,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E281" s="55">
+        <f>IF($A281="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C281,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F281" s="56">
+        <f>IF($A281="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C281,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G281" s="57" t="n"/>
+      <c r="H281" s="54" t="n"/>
+      <c r="I281" s="54" t="n"/>
+      <c r="J281" s="39">
+        <f>IF($A281="","",IF($E281="Informational","GREEN",IF($G281="",IF($E281="Mandatory","RED","YELLOW"),IF($N281="Exact",IF(UPPER(TRIM($G281&amp;""))=UPPER(TRIM($F281&amp;"")),"GREEN",$P281),IF(NOT(ISNUMBER($G281)),$P281,IF($N281="Min",IF($G281&gt;=$F281,"GREEN",IF($G281&gt;=$F281-$O281,"YELLOW",$P281)),IF($N281="Max",IF($G281&lt;=$F281,"GREEN",IF($G281&lt;=$F281+$O281,"YELLOW",$P281)),IF($N281="Range",IF(ABS($G281-$F281)&lt;=$O281,"GREEN",$P281),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K281" s="39">
+        <f>IF($A281="","",IF($H281="Non-Compliant","RED",IF(AND(OR($H281="Alternative Offer",$H281="Partially Compliant"),$J281="GREEN"),"YELLOW",IF(AND($J281="GREEN",ISNUMBER($R281),$R281&lt;Baseline!$B$9),"YELLOW",$J281))))</f>
+        <v/>
+      </c>
+      <c r="L281" s="39">
+        <f>IF($A281="","",IF($K281="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A281,Exceptions!$C$5:$C$104,$B281,Exceptions!$D$5:$D$104,$C281,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K281)))</f>
+        <v/>
+      </c>
+      <c r="M281" s="39">
+        <f>IF($A281="","",IF($H281="","Declaration missing",IF($H281="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R281),$R281&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H281="Fully Compliant",$J281&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N281" s="58">
+        <f>IF($A281="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C281,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O281" s="58">
+        <f>IF($A281="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C281,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P281" s="58">
+        <f>IF($A281="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C281,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q281" s="58">
+        <f>IF($A281="","",$A281&amp;"|"&amp;$B281&amp;"|"&amp;$C281)</f>
+        <v/>
+      </c>
+      <c r="R281" s="59" t="n"/>
+      <c r="S281" s="60" t="n"/>
+    </row>
+    <row r="282" ht="15" customHeight="1" s="34">
+      <c r="A282" s="54" t="n"/>
+      <c r="B282" s="54" t="n"/>
+      <c r="C282" s="54" t="n"/>
+      <c r="D282" s="55">
+        <f>IF($A282="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C282,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E282" s="55">
+        <f>IF($A282="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C282,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F282" s="56">
+        <f>IF($A282="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C282,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G282" s="57" t="n"/>
+      <c r="H282" s="54" t="n"/>
+      <c r="I282" s="54" t="n"/>
+      <c r="J282" s="39">
+        <f>IF($A282="","",IF($E282="Informational","GREEN",IF($G282="",IF($E282="Mandatory","RED","YELLOW"),IF($N282="Exact",IF(UPPER(TRIM($G282&amp;""))=UPPER(TRIM($F282&amp;"")),"GREEN",$P282),IF(NOT(ISNUMBER($G282)),$P282,IF($N282="Min",IF($G282&gt;=$F282,"GREEN",IF($G282&gt;=$F282-$O282,"YELLOW",$P282)),IF($N282="Max",IF($G282&lt;=$F282,"GREEN",IF($G282&lt;=$F282+$O282,"YELLOW",$P282)),IF($N282="Range",IF(ABS($G282-$F282)&lt;=$O282,"GREEN",$P282),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K282" s="39">
+        <f>IF($A282="","",IF($H282="Non-Compliant","RED",IF(AND(OR($H282="Alternative Offer",$H282="Partially Compliant"),$J282="GREEN"),"YELLOW",IF(AND($J282="GREEN",ISNUMBER($R282),$R282&lt;Baseline!$B$9),"YELLOW",$J282))))</f>
+        <v/>
+      </c>
+      <c r="L282" s="39">
+        <f>IF($A282="","",IF($K282="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A282,Exceptions!$C$5:$C$104,$B282,Exceptions!$D$5:$D$104,$C282,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K282)))</f>
+        <v/>
+      </c>
+      <c r="M282" s="39">
+        <f>IF($A282="","",IF($H282="","Declaration missing",IF($H282="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R282),$R282&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H282="Fully Compliant",$J282&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N282" s="58">
+        <f>IF($A282="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C282,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O282" s="58">
+        <f>IF($A282="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C282,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P282" s="58">
+        <f>IF($A282="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C282,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q282" s="58">
+        <f>IF($A282="","",$A282&amp;"|"&amp;$B282&amp;"|"&amp;$C282)</f>
+        <v/>
+      </c>
+      <c r="R282" s="59" t="n"/>
+      <c r="S282" s="60" t="n"/>
+    </row>
+    <row r="283" ht="15" customHeight="1" s="34">
+      <c r="A283" s="54" t="n"/>
+      <c r="B283" s="54" t="n"/>
+      <c r="C283" s="54" t="n"/>
+      <c r="D283" s="55">
+        <f>IF($A283="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C283,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E283" s="55">
+        <f>IF($A283="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C283,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F283" s="56">
+        <f>IF($A283="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C283,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G283" s="57" t="n"/>
+      <c r="H283" s="54" t="n"/>
+      <c r="I283" s="54" t="n"/>
+      <c r="J283" s="39">
+        <f>IF($A283="","",IF($E283="Informational","GREEN",IF($G283="",IF($E283="Mandatory","RED","YELLOW"),IF($N283="Exact",IF(UPPER(TRIM($G283&amp;""))=UPPER(TRIM($F283&amp;"")),"GREEN",$P283),IF(NOT(ISNUMBER($G283)),$P283,IF($N283="Min",IF($G283&gt;=$F283,"GREEN",IF($G283&gt;=$F283-$O283,"YELLOW",$P283)),IF($N283="Max",IF($G283&lt;=$F283,"GREEN",IF($G283&lt;=$F283+$O283,"YELLOW",$P283)),IF($N283="Range",IF(ABS($G283-$F283)&lt;=$O283,"GREEN",$P283),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K283" s="39">
+        <f>IF($A283="","",IF($H283="Non-Compliant","RED",IF(AND(OR($H283="Alternative Offer",$H283="Partially Compliant"),$J283="GREEN"),"YELLOW",IF(AND($J283="GREEN",ISNUMBER($R283),$R283&lt;Baseline!$B$9),"YELLOW",$J283))))</f>
+        <v/>
+      </c>
+      <c r="L283" s="39">
+        <f>IF($A283="","",IF($K283="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A283,Exceptions!$C$5:$C$104,$B283,Exceptions!$D$5:$D$104,$C283,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K283)))</f>
+        <v/>
+      </c>
+      <c r="M283" s="39">
+        <f>IF($A283="","",IF($H283="","Declaration missing",IF($H283="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R283),$R283&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H283="Fully Compliant",$J283&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N283" s="58">
+        <f>IF($A283="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C283,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O283" s="58">
+        <f>IF($A283="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C283,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P283" s="58">
+        <f>IF($A283="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C283,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q283" s="58">
+        <f>IF($A283="","",$A283&amp;"|"&amp;$B283&amp;"|"&amp;$C283)</f>
+        <v/>
+      </c>
+      <c r="R283" s="59" t="n"/>
+      <c r="S283" s="60" t="n"/>
+    </row>
+    <row r="284" ht="15" customHeight="1" s="34">
+      <c r="A284" s="54" t="n"/>
+      <c r="B284" s="54" t="n"/>
+      <c r="C284" s="54" t="n"/>
+      <c r="D284" s="55">
+        <f>IF($A284="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C284,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E284" s="55">
+        <f>IF($A284="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C284,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F284" s="56">
+        <f>IF($A284="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C284,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G284" s="57" t="n"/>
+      <c r="H284" s="54" t="n"/>
+      <c r="I284" s="54" t="n"/>
+      <c r="J284" s="39">
+        <f>IF($A284="","",IF($E284="Informational","GREEN",IF($G284="",IF($E284="Mandatory","RED","YELLOW"),IF($N284="Exact",IF(UPPER(TRIM($G284&amp;""))=UPPER(TRIM($F284&amp;"")),"GREEN",$P284),IF(NOT(ISNUMBER($G284)),$P284,IF($N284="Min",IF($G284&gt;=$F284,"GREEN",IF($G284&gt;=$F284-$O284,"YELLOW",$P284)),IF($N284="Max",IF($G284&lt;=$F284,"GREEN",IF($G284&lt;=$F284+$O284,"YELLOW",$P284)),IF($N284="Range",IF(ABS($G284-$F284)&lt;=$O284,"GREEN",$P284),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K284" s="39">
+        <f>IF($A284="","",IF($H284="Non-Compliant","RED",IF(AND(OR($H284="Alternative Offer",$H284="Partially Compliant"),$J284="GREEN"),"YELLOW",IF(AND($J284="GREEN",ISNUMBER($R284),$R284&lt;Baseline!$B$9),"YELLOW",$J284))))</f>
+        <v/>
+      </c>
+      <c r="L284" s="39">
+        <f>IF($A284="","",IF($K284="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A284,Exceptions!$C$5:$C$104,$B284,Exceptions!$D$5:$D$104,$C284,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K284)))</f>
+        <v/>
+      </c>
+      <c r="M284" s="39">
+        <f>IF($A284="","",IF($H284="","Declaration missing",IF($H284="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R284),$R284&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H284="Fully Compliant",$J284&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N284" s="58">
+        <f>IF($A284="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C284,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O284" s="58">
+        <f>IF($A284="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C284,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P284" s="58">
+        <f>IF($A284="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C284,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q284" s="58">
+        <f>IF($A284="","",$A284&amp;"|"&amp;$B284&amp;"|"&amp;$C284)</f>
+        <v/>
+      </c>
+      <c r="R284" s="59" t="n"/>
+      <c r="S284" s="60" t="n"/>
+    </row>
+    <row r="285" ht="15" customHeight="1" s="34">
+      <c r="A285" s="54" t="n"/>
+      <c r="B285" s="54" t="n"/>
+      <c r="C285" s="54" t="n"/>
+      <c r="D285" s="55">
+        <f>IF($A285="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C285,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E285" s="55">
+        <f>IF($A285="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C285,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F285" s="56">
+        <f>IF($A285="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C285,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G285" s="57" t="n"/>
+      <c r="H285" s="54" t="n"/>
+      <c r="I285" s="54" t="n"/>
+      <c r="J285" s="39">
+        <f>IF($A285="","",IF($E285="Informational","GREEN",IF($G285="",IF($E285="Mandatory","RED","YELLOW"),IF($N285="Exact",IF(UPPER(TRIM($G285&amp;""))=UPPER(TRIM($F285&amp;"")),"GREEN",$P285),IF(NOT(ISNUMBER($G285)),$P285,IF($N285="Min",IF($G285&gt;=$F285,"GREEN",IF($G285&gt;=$F285-$O285,"YELLOW",$P285)),IF($N285="Max",IF($G285&lt;=$F285,"GREEN",IF($G285&lt;=$F285+$O285,"YELLOW",$P285)),IF($N285="Range",IF(ABS($G285-$F285)&lt;=$O285,"GREEN",$P285),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K285" s="39">
+        <f>IF($A285="","",IF($H285="Non-Compliant","RED",IF(AND(OR($H285="Alternative Offer",$H285="Partially Compliant"),$J285="GREEN"),"YELLOW",IF(AND($J285="GREEN",ISNUMBER($R285),$R285&lt;Baseline!$B$9),"YELLOW",$J285))))</f>
+        <v/>
+      </c>
+      <c r="L285" s="39">
+        <f>IF($A285="","",IF($K285="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A285,Exceptions!$C$5:$C$104,$B285,Exceptions!$D$5:$D$104,$C285,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K285)))</f>
+        <v/>
+      </c>
+      <c r="M285" s="39">
+        <f>IF($A285="","",IF($H285="","Declaration missing",IF($H285="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R285),$R285&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H285="Fully Compliant",$J285&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N285" s="58">
+        <f>IF($A285="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C285,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O285" s="58">
+        <f>IF($A285="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C285,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P285" s="58">
+        <f>IF($A285="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C285,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q285" s="58">
+        <f>IF($A285="","",$A285&amp;"|"&amp;$B285&amp;"|"&amp;$C285)</f>
+        <v/>
+      </c>
+      <c r="R285" s="59" t="n"/>
+      <c r="S285" s="60" t="n"/>
+    </row>
+    <row r="286" ht="15" customHeight="1" s="34">
+      <c r="A286" s="54" t="n"/>
+      <c r="B286" s="54" t="n"/>
+      <c r="C286" s="54" t="n"/>
+      <c r="D286" s="55">
+        <f>IF($A286="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C286,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E286" s="55">
+        <f>IF($A286="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C286,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F286" s="56">
+        <f>IF($A286="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C286,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G286" s="57" t="n"/>
+      <c r="H286" s="54" t="n"/>
+      <c r="I286" s="54" t="n"/>
+      <c r="J286" s="39">
+        <f>IF($A286="","",IF($E286="Informational","GREEN",IF($G286="",IF($E286="Mandatory","RED","YELLOW"),IF($N286="Exact",IF(UPPER(TRIM($G286&amp;""))=UPPER(TRIM($F286&amp;"")),"GREEN",$P286),IF(NOT(ISNUMBER($G286)),$P286,IF($N286="Min",IF($G286&gt;=$F286,"GREEN",IF($G286&gt;=$F286-$O286,"YELLOW",$P286)),IF($N286="Max",IF($G286&lt;=$F286,"GREEN",IF($G286&lt;=$F286+$O286,"YELLOW",$P286)),IF($N286="Range",IF(ABS($G286-$F286)&lt;=$O286,"GREEN",$P286),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K286" s="39">
+        <f>IF($A286="","",IF($H286="Non-Compliant","RED",IF(AND(OR($H286="Alternative Offer",$H286="Partially Compliant"),$J286="GREEN"),"YELLOW",IF(AND($J286="GREEN",ISNUMBER($R286),$R286&lt;Baseline!$B$9),"YELLOW",$J286))))</f>
+        <v/>
+      </c>
+      <c r="L286" s="39">
+        <f>IF($A286="","",IF($K286="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A286,Exceptions!$C$5:$C$104,$B286,Exceptions!$D$5:$D$104,$C286,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K286)))</f>
+        <v/>
+      </c>
+      <c r="M286" s="39">
+        <f>IF($A286="","",IF($H286="","Declaration missing",IF($H286="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R286),$R286&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H286="Fully Compliant",$J286&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N286" s="58">
+        <f>IF($A286="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C286,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O286" s="58">
+        <f>IF($A286="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C286,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P286" s="58">
+        <f>IF($A286="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C286,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q286" s="58">
+        <f>IF($A286="","",$A286&amp;"|"&amp;$B286&amp;"|"&amp;$C286)</f>
+        <v/>
+      </c>
+      <c r="R286" s="59" t="n"/>
+      <c r="S286" s="60" t="n"/>
+    </row>
+    <row r="287" ht="15" customHeight="1" s="34">
+      <c r="A287" s="54" t="n"/>
+      <c r="B287" s="54" t="n"/>
+      <c r="C287" s="54" t="n"/>
+      <c r="D287" s="55">
+        <f>IF($A287="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C287,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E287" s="55">
+        <f>IF($A287="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C287,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F287" s="56">
+        <f>IF($A287="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C287,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G287" s="57" t="n"/>
+      <c r="H287" s="54" t="n"/>
+      <c r="I287" s="54" t="n"/>
+      <c r="J287" s="39">
+        <f>IF($A287="","",IF($E287="Informational","GREEN",IF($G287="",IF($E287="Mandatory","RED","YELLOW"),IF($N287="Exact",IF(UPPER(TRIM($G287&amp;""))=UPPER(TRIM($F287&amp;"")),"GREEN",$P287),IF(NOT(ISNUMBER($G287)),$P287,IF($N287="Min",IF($G287&gt;=$F287,"GREEN",IF($G287&gt;=$F287-$O287,"YELLOW",$P287)),IF($N287="Max",IF($G287&lt;=$F287,"GREEN",IF($G287&lt;=$F287+$O287,"YELLOW",$P287)),IF($N287="Range",IF(ABS($G287-$F287)&lt;=$O287,"GREEN",$P287),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K287" s="39">
+        <f>IF($A287="","",IF($H287="Non-Compliant","RED",IF(AND(OR($H287="Alternative Offer",$H287="Partially Compliant"),$J287="GREEN"),"YELLOW",IF(AND($J287="GREEN",ISNUMBER($R287),$R287&lt;Baseline!$B$9),"YELLOW",$J287))))</f>
+        <v/>
+      </c>
+      <c r="L287" s="39">
+        <f>IF($A287="","",IF($K287="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A287,Exceptions!$C$5:$C$104,$B287,Exceptions!$D$5:$D$104,$C287,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K287)))</f>
+        <v/>
+      </c>
+      <c r="M287" s="39">
+        <f>IF($A287="","",IF($H287="","Declaration missing",IF($H287="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R287),$R287&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H287="Fully Compliant",$J287&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N287" s="58">
+        <f>IF($A287="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C287,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O287" s="58">
+        <f>IF($A287="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C287,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P287" s="58">
+        <f>IF($A287="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C287,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q287" s="58">
+        <f>IF($A287="","",$A287&amp;"|"&amp;$B287&amp;"|"&amp;$C287)</f>
+        <v/>
+      </c>
+      <c r="R287" s="59" t="n"/>
+      <c r="S287" s="60" t="n"/>
+    </row>
+    <row r="288" ht="15" customHeight="1" s="34">
+      <c r="A288" s="54" t="n"/>
+      <c r="B288" s="54" t="n"/>
+      <c r="C288" s="54" t="n"/>
+      <c r="D288" s="55">
+        <f>IF($A288="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C288,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E288" s="55">
+        <f>IF($A288="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C288,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F288" s="56">
+        <f>IF($A288="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C288,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G288" s="57" t="n"/>
+      <c r="H288" s="54" t="n"/>
+      <c r="I288" s="54" t="n"/>
+      <c r="J288" s="39">
+        <f>IF($A288="","",IF($E288="Informational","GREEN",IF($G288="",IF($E288="Mandatory","RED","YELLOW"),IF($N288="Exact",IF(UPPER(TRIM($G288&amp;""))=UPPER(TRIM($F288&amp;"")),"GREEN",$P288),IF(NOT(ISNUMBER($G288)),$P288,IF($N288="Min",IF($G288&gt;=$F288,"GREEN",IF($G288&gt;=$F288-$O288,"YELLOW",$P288)),IF($N288="Max",IF($G288&lt;=$F288,"GREEN",IF($G288&lt;=$F288+$O288,"YELLOW",$P288)),IF($N288="Range",IF(ABS($G288-$F288)&lt;=$O288,"GREEN",$P288),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K288" s="39">
+        <f>IF($A288="","",IF($H288="Non-Compliant","RED",IF(AND(OR($H288="Alternative Offer",$H288="Partially Compliant"),$J288="GREEN"),"YELLOW",IF(AND($J288="GREEN",ISNUMBER($R288),$R288&lt;Baseline!$B$9),"YELLOW",$J288))))</f>
+        <v/>
+      </c>
+      <c r="L288" s="39">
+        <f>IF($A288="","",IF($K288="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A288,Exceptions!$C$5:$C$104,$B288,Exceptions!$D$5:$D$104,$C288,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K288)))</f>
+        <v/>
+      </c>
+      <c r="M288" s="39">
+        <f>IF($A288="","",IF($H288="","Declaration missing",IF($H288="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R288),$R288&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H288="Fully Compliant",$J288&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N288" s="58">
+        <f>IF($A288="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C288,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O288" s="58">
+        <f>IF($A288="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C288,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P288" s="58">
+        <f>IF($A288="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C288,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q288" s="58">
+        <f>IF($A288="","",$A288&amp;"|"&amp;$B288&amp;"|"&amp;$C288)</f>
+        <v/>
+      </c>
+      <c r="R288" s="59" t="n"/>
+      <c r="S288" s="60" t="n"/>
+    </row>
+    <row r="289" ht="15" customHeight="1" s="34">
+      <c r="A289" s="54" t="n"/>
+      <c r="B289" s="54" t="n"/>
+      <c r="C289" s="54" t="n"/>
+      <c r="D289" s="55">
+        <f>IF($A289="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C289,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E289" s="55">
+        <f>IF($A289="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C289,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F289" s="56">
+        <f>IF($A289="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C289,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G289" s="57" t="n"/>
+      <c r="H289" s="54" t="n"/>
+      <c r="I289" s="54" t="n"/>
+      <c r="J289" s="39">
+        <f>IF($A289="","",IF($E289="Informational","GREEN",IF($G289="",IF($E289="Mandatory","RED","YELLOW"),IF($N289="Exact",IF(UPPER(TRIM($G289&amp;""))=UPPER(TRIM($F289&amp;"")),"GREEN",$P289),IF(NOT(ISNUMBER($G289)),$P289,IF($N289="Min",IF($G289&gt;=$F289,"GREEN",IF($G289&gt;=$F289-$O289,"YELLOW",$P289)),IF($N289="Max",IF($G289&lt;=$F289,"GREEN",IF($G289&lt;=$F289+$O289,"YELLOW",$P289)),IF($N289="Range",IF(ABS($G289-$F289)&lt;=$O289,"GREEN",$P289),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K289" s="39">
+        <f>IF($A289="","",IF($H289="Non-Compliant","RED",IF(AND(OR($H289="Alternative Offer",$H289="Partially Compliant"),$J289="GREEN"),"YELLOW",IF(AND($J289="GREEN",ISNUMBER($R289),$R289&lt;Baseline!$B$9),"YELLOW",$J289))))</f>
+        <v/>
+      </c>
+      <c r="L289" s="39">
+        <f>IF($A289="","",IF($K289="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A289,Exceptions!$C$5:$C$104,$B289,Exceptions!$D$5:$D$104,$C289,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K289)))</f>
+        <v/>
+      </c>
+      <c r="M289" s="39">
+        <f>IF($A289="","",IF($H289="","Declaration missing",IF($H289="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R289),$R289&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H289="Fully Compliant",$J289&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N289" s="58">
+        <f>IF($A289="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C289,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O289" s="58">
+        <f>IF($A289="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C289,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P289" s="58">
+        <f>IF($A289="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C289,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q289" s="58">
+        <f>IF($A289="","",$A289&amp;"|"&amp;$B289&amp;"|"&amp;$C289)</f>
+        <v/>
+      </c>
+      <c r="R289" s="59" t="n"/>
+      <c r="S289" s="60" t="n"/>
+    </row>
+    <row r="290" ht="15" customHeight="1" s="34">
+      <c r="A290" s="54" t="n"/>
+      <c r="B290" s="54" t="n"/>
+      <c r="C290" s="54" t="n"/>
+      <c r="D290" s="55">
+        <f>IF($A290="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C290,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E290" s="55">
+        <f>IF($A290="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C290,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F290" s="56">
+        <f>IF($A290="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C290,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G290" s="57" t="n"/>
+      <c r="H290" s="54" t="n"/>
+      <c r="I290" s="54" t="n"/>
+      <c r="J290" s="39">
+        <f>IF($A290="","",IF($E290="Informational","GREEN",IF($G290="",IF($E290="Mandatory","RED","YELLOW"),IF($N290="Exact",IF(UPPER(TRIM($G290&amp;""))=UPPER(TRIM($F290&amp;"")),"GREEN",$P290),IF(NOT(ISNUMBER($G290)),$P290,IF($N290="Min",IF($G290&gt;=$F290,"GREEN",IF($G290&gt;=$F290-$O290,"YELLOW",$P290)),IF($N290="Max",IF($G290&lt;=$F290,"GREEN",IF($G290&lt;=$F290+$O290,"YELLOW",$P290)),IF($N290="Range",IF(ABS($G290-$F290)&lt;=$O290,"GREEN",$P290),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K290" s="39">
+        <f>IF($A290="","",IF($H290="Non-Compliant","RED",IF(AND(OR($H290="Alternative Offer",$H290="Partially Compliant"),$J290="GREEN"),"YELLOW",IF(AND($J290="GREEN",ISNUMBER($R290),$R290&lt;Baseline!$B$9),"YELLOW",$J290))))</f>
+        <v/>
+      </c>
+      <c r="L290" s="39">
+        <f>IF($A290="","",IF($K290="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A290,Exceptions!$C$5:$C$104,$B290,Exceptions!$D$5:$D$104,$C290,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K290)))</f>
+        <v/>
+      </c>
+      <c r="M290" s="39">
+        <f>IF($A290="","",IF($H290="","Declaration missing",IF($H290="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R290),$R290&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H290="Fully Compliant",$J290&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N290" s="58">
+        <f>IF($A290="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C290,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O290" s="58">
+        <f>IF($A290="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C290,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P290" s="58">
+        <f>IF($A290="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C290,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q290" s="58">
+        <f>IF($A290="","",$A290&amp;"|"&amp;$B290&amp;"|"&amp;$C290)</f>
+        <v/>
+      </c>
+      <c r="R290" s="59" t="n"/>
+      <c r="S290" s="60" t="n"/>
+    </row>
+    <row r="291" ht="15" customHeight="1" s="34">
+      <c r="A291" s="54" t="n"/>
+      <c r="B291" s="54" t="n"/>
+      <c r="C291" s="54" t="n"/>
+      <c r="D291" s="55">
+        <f>IF($A291="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C291,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E291" s="55">
+        <f>IF($A291="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C291,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F291" s="56">
+        <f>IF($A291="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C291,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G291" s="57" t="n"/>
+      <c r="H291" s="54" t="n"/>
+      <c r="I291" s="54" t="n"/>
+      <c r="J291" s="39">
+        <f>IF($A291="","",IF($E291="Informational","GREEN",IF($G291="",IF($E291="Mandatory","RED","YELLOW"),IF($N291="Exact",IF(UPPER(TRIM($G291&amp;""))=UPPER(TRIM($F291&amp;"")),"GREEN",$P291),IF(NOT(ISNUMBER($G291)),$P291,IF($N291="Min",IF($G291&gt;=$F291,"GREEN",IF($G291&gt;=$F291-$O291,"YELLOW",$P291)),IF($N291="Max",IF($G291&lt;=$F291,"GREEN",IF($G291&lt;=$F291+$O291,"YELLOW",$P291)),IF($N291="Range",IF(ABS($G291-$F291)&lt;=$O291,"GREEN",$P291),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K291" s="39">
+        <f>IF($A291="","",IF($H291="Non-Compliant","RED",IF(AND(OR($H291="Alternative Offer",$H291="Partially Compliant"),$J291="GREEN"),"YELLOW",IF(AND($J291="GREEN",ISNUMBER($R291),$R291&lt;Baseline!$B$9),"YELLOW",$J291))))</f>
+        <v/>
+      </c>
+      <c r="L291" s="39">
+        <f>IF($A291="","",IF($K291="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A291,Exceptions!$C$5:$C$104,$B291,Exceptions!$D$5:$D$104,$C291,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K291)))</f>
+        <v/>
+      </c>
+      <c r="M291" s="39">
+        <f>IF($A291="","",IF($H291="","Declaration missing",IF($H291="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R291),$R291&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H291="Fully Compliant",$J291&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N291" s="58">
+        <f>IF($A291="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C291,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O291" s="58">
+        <f>IF($A291="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C291,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P291" s="58">
+        <f>IF($A291="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C291,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q291" s="58">
+        <f>IF($A291="","",$A291&amp;"|"&amp;$B291&amp;"|"&amp;$C291)</f>
+        <v/>
+      </c>
+      <c r="R291" s="59" t="n"/>
+      <c r="S291" s="60" t="n"/>
+    </row>
+    <row r="292" ht="15" customHeight="1" s="34">
+      <c r="A292" s="54" t="n"/>
+      <c r="B292" s="54" t="n"/>
+      <c r="C292" s="54" t="n"/>
+      <c r="D292" s="55">
+        <f>IF($A292="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C292,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E292" s="55">
+        <f>IF($A292="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C292,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F292" s="56">
+        <f>IF($A292="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C292,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G292" s="57" t="n"/>
+      <c r="H292" s="54" t="n"/>
+      <c r="I292" s="54" t="n"/>
+      <c r="J292" s="39">
+        <f>IF($A292="","",IF($E292="Informational","GREEN",IF($G292="",IF($E292="Mandatory","RED","YELLOW"),IF($N292="Exact",IF(UPPER(TRIM($G292&amp;""))=UPPER(TRIM($F292&amp;"")),"GREEN",$P292),IF(NOT(ISNUMBER($G292)),$P292,IF($N292="Min",IF($G292&gt;=$F292,"GREEN",IF($G292&gt;=$F292-$O292,"YELLOW",$P292)),IF($N292="Max",IF($G292&lt;=$F292,"GREEN",IF($G292&lt;=$F292+$O292,"YELLOW",$P292)),IF($N292="Range",IF(ABS($G292-$F292)&lt;=$O292,"GREEN",$P292),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K292" s="39">
+        <f>IF($A292="","",IF($H292="Non-Compliant","RED",IF(AND(OR($H292="Alternative Offer",$H292="Partially Compliant"),$J292="GREEN"),"YELLOW",IF(AND($J292="GREEN",ISNUMBER($R292),$R292&lt;Baseline!$B$9),"YELLOW",$J292))))</f>
+        <v/>
+      </c>
+      <c r="L292" s="39">
+        <f>IF($A292="","",IF($K292="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A292,Exceptions!$C$5:$C$104,$B292,Exceptions!$D$5:$D$104,$C292,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K292)))</f>
+        <v/>
+      </c>
+      <c r="M292" s="39">
+        <f>IF($A292="","",IF($H292="","Declaration missing",IF($H292="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R292),$R292&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H292="Fully Compliant",$J292&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N292" s="58">
+        <f>IF($A292="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C292,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O292" s="58">
+        <f>IF($A292="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C292,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P292" s="58">
+        <f>IF($A292="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C292,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q292" s="58">
+        <f>IF($A292="","",$A292&amp;"|"&amp;$B292&amp;"|"&amp;$C292)</f>
+        <v/>
+      </c>
+      <c r="R292" s="59" t="n"/>
+      <c r="S292" s="60" t="n"/>
+    </row>
+    <row r="293" ht="15" customHeight="1" s="34">
+      <c r="A293" s="54" t="n"/>
+      <c r="B293" s="54" t="n"/>
+      <c r="C293" s="54" t="n"/>
+      <c r="D293" s="55">
+        <f>IF($A293="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C293,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E293" s="55">
+        <f>IF($A293="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C293,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F293" s="56">
+        <f>IF($A293="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C293,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G293" s="57" t="n"/>
+      <c r="H293" s="54" t="n"/>
+      <c r="I293" s="54" t="n"/>
+      <c r="J293" s="39">
+        <f>IF($A293="","",IF($E293="Informational","GREEN",IF($G293="",IF($E293="Mandatory","RED","YELLOW"),IF($N293="Exact",IF(UPPER(TRIM($G293&amp;""))=UPPER(TRIM($F293&amp;"")),"GREEN",$P293),IF(NOT(ISNUMBER($G293)),$P293,IF($N293="Min",IF($G293&gt;=$F293,"GREEN",IF($G293&gt;=$F293-$O293,"YELLOW",$P293)),IF($N293="Max",IF($G293&lt;=$F293,"GREEN",IF($G293&lt;=$F293+$O293,"YELLOW",$P293)),IF($N293="Range",IF(ABS($G293-$F293)&lt;=$O293,"GREEN",$P293),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K293" s="39">
+        <f>IF($A293="","",IF($H293="Non-Compliant","RED",IF(AND(OR($H293="Alternative Offer",$H293="Partially Compliant"),$J293="GREEN"),"YELLOW",IF(AND($J293="GREEN",ISNUMBER($R293),$R293&lt;Baseline!$B$9),"YELLOW",$J293))))</f>
+        <v/>
+      </c>
+      <c r="L293" s="39">
+        <f>IF($A293="","",IF($K293="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A293,Exceptions!$C$5:$C$104,$B293,Exceptions!$D$5:$D$104,$C293,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K293)))</f>
+        <v/>
+      </c>
+      <c r="M293" s="39">
+        <f>IF($A293="","",IF($H293="","Declaration missing",IF($H293="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R293),$R293&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H293="Fully Compliant",$J293&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N293" s="58">
+        <f>IF($A293="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C293,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O293" s="58">
+        <f>IF($A293="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C293,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P293" s="58">
+        <f>IF($A293="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C293,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q293" s="58">
+        <f>IF($A293="","",$A293&amp;"|"&amp;$B293&amp;"|"&amp;$C293)</f>
+        <v/>
+      </c>
+      <c r="R293" s="59" t="n"/>
+      <c r="S293" s="60" t="n"/>
+    </row>
+    <row r="294" ht="15" customHeight="1" s="34">
+      <c r="A294" s="54" t="n"/>
+      <c r="B294" s="54" t="n"/>
+      <c r="C294" s="54" t="n"/>
+      <c r="D294" s="55">
+        <f>IF($A294="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C294,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E294" s="55">
+        <f>IF($A294="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C294,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F294" s="56">
+        <f>IF($A294="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C294,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G294" s="57" t="n"/>
+      <c r="H294" s="54" t="n"/>
+      <c r="I294" s="54" t="n"/>
+      <c r="J294" s="39">
+        <f>IF($A294="","",IF($E294="Informational","GREEN",IF($G294="",IF($E294="Mandatory","RED","YELLOW"),IF($N294="Exact",IF(UPPER(TRIM($G294&amp;""))=UPPER(TRIM($F294&amp;"")),"GREEN",$P294),IF(NOT(ISNUMBER($G294)),$P294,IF($N294="Min",IF($G294&gt;=$F294,"GREEN",IF($G294&gt;=$F294-$O294,"YELLOW",$P294)),IF($N294="Max",IF($G294&lt;=$F294,"GREEN",IF($G294&lt;=$F294+$O294,"YELLOW",$P294)),IF($N294="Range",IF(ABS($G294-$F294)&lt;=$O294,"GREEN",$P294),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K294" s="39">
+        <f>IF($A294="","",IF($H294="Non-Compliant","RED",IF(AND(OR($H294="Alternative Offer",$H294="Partially Compliant"),$J294="GREEN"),"YELLOW",IF(AND($J294="GREEN",ISNUMBER($R294),$R294&lt;Baseline!$B$9),"YELLOW",$J294))))</f>
+        <v/>
+      </c>
+      <c r="L294" s="39">
+        <f>IF($A294="","",IF($K294="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A294,Exceptions!$C$5:$C$104,$B294,Exceptions!$D$5:$D$104,$C294,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K294)))</f>
+        <v/>
+      </c>
+      <c r="M294" s="39">
+        <f>IF($A294="","",IF($H294="","Declaration missing",IF($H294="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R294),$R294&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H294="Fully Compliant",$J294&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N294" s="58">
+        <f>IF($A294="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C294,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O294" s="58">
+        <f>IF($A294="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C294,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P294" s="58">
+        <f>IF($A294="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C294,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q294" s="58">
+        <f>IF($A294="","",$A294&amp;"|"&amp;$B294&amp;"|"&amp;$C294)</f>
+        <v/>
+      </c>
+      <c r="R294" s="59" t="n"/>
+      <c r="S294" s="60" t="n"/>
+    </row>
+    <row r="295" ht="15" customHeight="1" s="34">
+      <c r="A295" s="54" t="n"/>
+      <c r="B295" s="54" t="n"/>
+      <c r="C295" s="54" t="n"/>
+      <c r="D295" s="55">
+        <f>IF($A295="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C295,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E295" s="55">
+        <f>IF($A295="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C295,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F295" s="56">
+        <f>IF($A295="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C295,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G295" s="57" t="n"/>
+      <c r="H295" s="54" t="n"/>
+      <c r="I295" s="54" t="n"/>
+      <c r="J295" s="39">
+        <f>IF($A295="","",IF($E295="Informational","GREEN",IF($G295="",IF($E295="Mandatory","RED","YELLOW"),IF($N295="Exact",IF(UPPER(TRIM($G295&amp;""))=UPPER(TRIM($F295&amp;"")),"GREEN",$P295),IF(NOT(ISNUMBER($G295)),$P295,IF($N295="Min",IF($G295&gt;=$F295,"GREEN",IF($G295&gt;=$F295-$O295,"YELLOW",$P295)),IF($N295="Max",IF($G295&lt;=$F295,"GREEN",IF($G295&lt;=$F295+$O295,"YELLOW",$P295)),IF($N295="Range",IF(ABS($G295-$F295)&lt;=$O295,"GREEN",$P295),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K295" s="39">
+        <f>IF($A295="","",IF($H295="Non-Compliant","RED",IF(AND(OR($H295="Alternative Offer",$H295="Partially Compliant"),$J295="GREEN"),"YELLOW",IF(AND($J295="GREEN",ISNUMBER($R295),$R295&lt;Baseline!$B$9),"YELLOW",$J295))))</f>
+        <v/>
+      </c>
+      <c r="L295" s="39">
+        <f>IF($A295="","",IF($K295="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A295,Exceptions!$C$5:$C$104,$B295,Exceptions!$D$5:$D$104,$C295,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K295)))</f>
+        <v/>
+      </c>
+      <c r="M295" s="39">
+        <f>IF($A295="","",IF($H295="","Declaration missing",IF($H295="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R295),$R295&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H295="Fully Compliant",$J295&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N295" s="58">
+        <f>IF($A295="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C295,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O295" s="58">
+        <f>IF($A295="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C295,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P295" s="58">
+        <f>IF($A295="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C295,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q295" s="58">
+        <f>IF($A295="","",$A295&amp;"|"&amp;$B295&amp;"|"&amp;$C295)</f>
+        <v/>
+      </c>
+      <c r="R295" s="59" t="n"/>
+      <c r="S295" s="60" t="n"/>
+    </row>
+    <row r="296" ht="15" customHeight="1" s="34">
+      <c r="A296" s="54" t="n"/>
+      <c r="B296" s="54" t="n"/>
+      <c r="C296" s="54" t="n"/>
+      <c r="D296" s="55">
+        <f>IF($A296="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C296,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E296" s="55">
+        <f>IF($A296="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C296,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F296" s="56">
+        <f>IF($A296="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C296,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G296" s="57" t="n"/>
+      <c r="H296" s="54" t="n"/>
+      <c r="I296" s="54" t="n"/>
+      <c r="J296" s="39">
+        <f>IF($A296="","",IF($E296="Informational","GREEN",IF($G296="",IF($E296="Mandatory","RED","YELLOW"),IF($N296="Exact",IF(UPPER(TRIM($G296&amp;""))=UPPER(TRIM($F296&amp;"")),"GREEN",$P296),IF(NOT(ISNUMBER($G296)),$P296,IF($N296="Min",IF($G296&gt;=$F296,"GREEN",IF($G296&gt;=$F296-$O296,"YELLOW",$P296)),IF($N296="Max",IF($G296&lt;=$F296,"GREEN",IF($G296&lt;=$F296+$O296,"YELLOW",$P296)),IF($N296="Range",IF(ABS($G296-$F296)&lt;=$O296,"GREEN",$P296),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K296" s="39">
+        <f>IF($A296="","",IF($H296="Non-Compliant","RED",IF(AND(OR($H296="Alternative Offer",$H296="Partially Compliant"),$J296="GREEN"),"YELLOW",IF(AND($J296="GREEN",ISNUMBER($R296),$R296&lt;Baseline!$B$9),"YELLOW",$J296))))</f>
+        <v/>
+      </c>
+      <c r="L296" s="39">
+        <f>IF($A296="","",IF($K296="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A296,Exceptions!$C$5:$C$104,$B296,Exceptions!$D$5:$D$104,$C296,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K296)))</f>
+        <v/>
+      </c>
+      <c r="M296" s="39">
+        <f>IF($A296="","",IF($H296="","Declaration missing",IF($H296="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R296),$R296&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H296="Fully Compliant",$J296&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N296" s="58">
+        <f>IF($A296="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C296,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O296" s="58">
+        <f>IF($A296="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C296,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P296" s="58">
+        <f>IF($A296="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C296,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q296" s="58">
+        <f>IF($A296="","",$A296&amp;"|"&amp;$B296&amp;"|"&amp;$C296)</f>
+        <v/>
+      </c>
+      <c r="R296" s="59" t="n"/>
+      <c r="S296" s="60" t="n"/>
+    </row>
+    <row r="297" ht="15" customHeight="1" s="34">
+      <c r="A297" s="54" t="n"/>
+      <c r="B297" s="54" t="n"/>
+      <c r="C297" s="54" t="n"/>
+      <c r="D297" s="55">
+        <f>IF($A297="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C297,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E297" s="55">
+        <f>IF($A297="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C297,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F297" s="56">
+        <f>IF($A297="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C297,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G297" s="57" t="n"/>
+      <c r="H297" s="54" t="n"/>
+      <c r="I297" s="54" t="n"/>
+      <c r="J297" s="39">
+        <f>IF($A297="","",IF($E297="Informational","GREEN",IF($G297="",IF($E297="Mandatory","RED","YELLOW"),IF($N297="Exact",IF(UPPER(TRIM($G297&amp;""))=UPPER(TRIM($F297&amp;"")),"GREEN",$P297),IF(NOT(ISNUMBER($G297)),$P297,IF($N297="Min",IF($G297&gt;=$F297,"GREEN",IF($G297&gt;=$F297-$O297,"YELLOW",$P297)),IF($N297="Max",IF($G297&lt;=$F297,"GREEN",IF($G297&lt;=$F297+$O297,"YELLOW",$P297)),IF($N297="Range",IF(ABS($G297-$F297)&lt;=$O297,"GREEN",$P297),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K297" s="39">
+        <f>IF($A297="","",IF($H297="Non-Compliant","RED",IF(AND(OR($H297="Alternative Offer",$H297="Partially Compliant"),$J297="GREEN"),"YELLOW",IF(AND($J297="GREEN",ISNUMBER($R297),$R297&lt;Baseline!$B$9),"YELLOW",$J297))))</f>
+        <v/>
+      </c>
+      <c r="L297" s="39">
+        <f>IF($A297="","",IF($K297="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A297,Exceptions!$C$5:$C$104,$B297,Exceptions!$D$5:$D$104,$C297,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K297)))</f>
+        <v/>
+      </c>
+      <c r="M297" s="39">
+        <f>IF($A297="","",IF($H297="","Declaration missing",IF($H297="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R297),$R297&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H297="Fully Compliant",$J297&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N297" s="58">
+        <f>IF($A297="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C297,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O297" s="58">
+        <f>IF($A297="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C297,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P297" s="58">
+        <f>IF($A297="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C297,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q297" s="58">
+        <f>IF($A297="","",$A297&amp;"|"&amp;$B297&amp;"|"&amp;$C297)</f>
+        <v/>
+      </c>
+      <c r="R297" s="59" t="n"/>
+      <c r="S297" s="60" t="n"/>
+    </row>
+    <row r="298" ht="15" customHeight="1" s="34">
+      <c r="A298" s="54" t="n"/>
+      <c r="B298" s="54" t="n"/>
+      <c r="C298" s="54" t="n"/>
+      <c r="D298" s="55">
+        <f>IF($A298="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C298,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E298" s="55">
+        <f>IF($A298="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C298,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F298" s="56">
+        <f>IF($A298="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C298,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G298" s="57" t="n"/>
+      <c r="H298" s="54" t="n"/>
+      <c r="I298" s="54" t="n"/>
+      <c r="J298" s="39">
+        <f>IF($A298="","",IF($E298="Informational","GREEN",IF($G298="",IF($E298="Mandatory","RED","YELLOW"),IF($N298="Exact",IF(UPPER(TRIM($G298&amp;""))=UPPER(TRIM($F298&amp;"")),"GREEN",$P298),IF(NOT(ISNUMBER($G298)),$P298,IF($N298="Min",IF($G298&gt;=$F298,"GREEN",IF($G298&gt;=$F298-$O298,"YELLOW",$P298)),IF($N298="Max",IF($G298&lt;=$F298,"GREEN",IF($G298&lt;=$F298+$O298,"YELLOW",$P298)),IF($N298="Range",IF(ABS($G298-$F298)&lt;=$O298,"GREEN",$P298),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K298" s="39">
+        <f>IF($A298="","",IF($H298="Non-Compliant","RED",IF(AND(OR($H298="Alternative Offer",$H298="Partially Compliant"),$J298="GREEN"),"YELLOW",IF(AND($J298="GREEN",ISNUMBER($R298),$R298&lt;Baseline!$B$9),"YELLOW",$J298))))</f>
+        <v/>
+      </c>
+      <c r="L298" s="39">
+        <f>IF($A298="","",IF($K298="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A298,Exceptions!$C$5:$C$104,$B298,Exceptions!$D$5:$D$104,$C298,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K298)))</f>
+        <v/>
+      </c>
+      <c r="M298" s="39">
+        <f>IF($A298="","",IF($H298="","Declaration missing",IF($H298="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R298),$R298&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H298="Fully Compliant",$J298&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N298" s="58">
+        <f>IF($A298="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C298,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O298" s="58">
+        <f>IF($A298="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C298,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P298" s="58">
+        <f>IF($A298="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C298,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q298" s="58">
+        <f>IF($A298="","",$A298&amp;"|"&amp;$B298&amp;"|"&amp;$C298)</f>
+        <v/>
+      </c>
+      <c r="R298" s="59" t="n"/>
+      <c r="S298" s="60" t="n"/>
+    </row>
+    <row r="299" ht="15" customHeight="1" s="34">
+      <c r="A299" s="54" t="n"/>
+      <c r="B299" s="54" t="n"/>
+      <c r="C299" s="54" t="n"/>
+      <c r="D299" s="55">
+        <f>IF($A299="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C299,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E299" s="55">
+        <f>IF($A299="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C299,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F299" s="56">
+        <f>IF($A299="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C299,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G299" s="57" t="n"/>
+      <c r="H299" s="54" t="n"/>
+      <c r="I299" s="54" t="n"/>
+      <c r="J299" s="39">
+        <f>IF($A299="","",IF($E299="Informational","GREEN",IF($G299="",IF($E299="Mandatory","RED","YELLOW"),IF($N299="Exact",IF(UPPER(TRIM($G299&amp;""))=UPPER(TRIM($F299&amp;"")),"GREEN",$P299),IF(NOT(ISNUMBER($G299)),$P299,IF($N299="Min",IF($G299&gt;=$F299,"GREEN",IF($G299&gt;=$F299-$O299,"YELLOW",$P299)),IF($N299="Max",IF($G299&lt;=$F299,"GREEN",IF($G299&lt;=$F299+$O299,"YELLOW",$P299)),IF($N299="Range",IF(ABS($G299-$F299)&lt;=$O299,"GREEN",$P299),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K299" s="39">
+        <f>IF($A299="","",IF($H299="Non-Compliant","RED",IF(AND(OR($H299="Alternative Offer",$H299="Partially Compliant"),$J299="GREEN"),"YELLOW",IF(AND($J299="GREEN",ISNUMBER($R299),$R299&lt;Baseline!$B$9),"YELLOW",$J299))))</f>
+        <v/>
+      </c>
+      <c r="L299" s="39">
+        <f>IF($A299="","",IF($K299="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A299,Exceptions!$C$5:$C$104,$B299,Exceptions!$D$5:$D$104,$C299,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K299)))</f>
+        <v/>
+      </c>
+      <c r="M299" s="39">
+        <f>IF($A299="","",IF($H299="","Declaration missing",IF($H299="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R299),$R299&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H299="Fully Compliant",$J299&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N299" s="58">
+        <f>IF($A299="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C299,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O299" s="58">
+        <f>IF($A299="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C299,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P299" s="58">
+        <f>IF($A299="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C299,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q299" s="58">
+        <f>IF($A299="","",$A299&amp;"|"&amp;$B299&amp;"|"&amp;$C299)</f>
+        <v/>
+      </c>
+      <c r="R299" s="59" t="n"/>
+      <c r="S299" s="60" t="n"/>
+    </row>
+    <row r="300" ht="15" customHeight="1" s="34">
+      <c r="A300" s="54" t="n"/>
+      <c r="B300" s="54" t="n"/>
+      <c r="C300" s="54" t="n"/>
+      <c r="D300" s="55">
+        <f>IF($A300="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C300,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E300" s="55">
+        <f>IF($A300="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C300,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F300" s="56">
+        <f>IF($A300="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C300,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G300" s="57" t="n"/>
+      <c r="H300" s="54" t="n"/>
+      <c r="I300" s="54" t="n"/>
+      <c r="J300" s="39">
+        <f>IF($A300="","",IF($E300="Informational","GREEN",IF($G300="",IF($E300="Mandatory","RED","YELLOW"),IF($N300="Exact",IF(UPPER(TRIM($G300&amp;""))=UPPER(TRIM($F300&amp;"")),"GREEN",$P300),IF(NOT(ISNUMBER($G300)),$P300,IF($N300="Min",IF($G300&gt;=$F300,"GREEN",IF($G300&gt;=$F300-$O300,"YELLOW",$P300)),IF($N300="Max",IF($G300&lt;=$F300,"GREEN",IF($G300&lt;=$F300+$O300,"YELLOW",$P300)),IF($N300="Range",IF(ABS($G300-$F300)&lt;=$O300,"GREEN",$P300),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K300" s="39">
+        <f>IF($A300="","",IF($H300="Non-Compliant","RED",IF(AND(OR($H300="Alternative Offer",$H300="Partially Compliant"),$J300="GREEN"),"YELLOW",IF(AND($J300="GREEN",ISNUMBER($R300),$R300&lt;Baseline!$B$9),"YELLOW",$J300))))</f>
+        <v/>
+      </c>
+      <c r="L300" s="39">
+        <f>IF($A300="","",IF($K300="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A300,Exceptions!$C$5:$C$104,$B300,Exceptions!$D$5:$D$104,$C300,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K300)))</f>
+        <v/>
+      </c>
+      <c r="M300" s="39">
+        <f>IF($A300="","",IF($H300="","Declaration missing",IF($H300="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R300),$R300&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H300="Fully Compliant",$J300&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N300" s="58">
+        <f>IF($A300="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C300,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O300" s="58">
+        <f>IF($A300="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C300,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P300" s="58">
+        <f>IF($A300="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C300,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q300" s="58">
+        <f>IF($A300="","",$A300&amp;"|"&amp;$B300&amp;"|"&amp;$C300)</f>
+        <v/>
+      </c>
+      <c r="R300" s="59" t="n"/>
+      <c r="S300" s="60" t="n"/>
+    </row>
+    <row r="301" ht="15" customHeight="1" s="34">
+      <c r="A301" s="54" t="n"/>
+      <c r="B301" s="54" t="n"/>
+      <c r="C301" s="54" t="n"/>
+      <c r="D301" s="55">
+        <f>IF($A301="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C301,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E301" s="55">
+        <f>IF($A301="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C301,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F301" s="56">
+        <f>IF($A301="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C301,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G301" s="57" t="n"/>
+      <c r="H301" s="54" t="n"/>
+      <c r="I301" s="54" t="n"/>
+      <c r="J301" s="39">
+        <f>IF($A301="","",IF($E301="Informational","GREEN",IF($G301="",IF($E301="Mandatory","RED","YELLOW"),IF($N301="Exact",IF(UPPER(TRIM($G301&amp;""))=UPPER(TRIM($F301&amp;"")),"GREEN",$P301),IF(NOT(ISNUMBER($G301)),$P301,IF($N301="Min",IF($G301&gt;=$F301,"GREEN",IF($G301&gt;=$F301-$O301,"YELLOW",$P301)),IF($N301="Max",IF($G301&lt;=$F301,"GREEN",IF($G301&lt;=$F301+$O301,"YELLOW",$P301)),IF($N301="Range",IF(ABS($G301-$F301)&lt;=$O301,"GREEN",$P301),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K301" s="39">
+        <f>IF($A301="","",IF($H301="Non-Compliant","RED",IF(AND(OR($H301="Alternative Offer",$H301="Partially Compliant"),$J301="GREEN"),"YELLOW",IF(AND($J301="GREEN",ISNUMBER($R301),$R301&lt;Baseline!$B$9),"YELLOW",$J301))))</f>
+        <v/>
+      </c>
+      <c r="L301" s="39">
+        <f>IF($A301="","",IF($K301="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A301,Exceptions!$C$5:$C$104,$B301,Exceptions!$D$5:$D$104,$C301,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K301)))</f>
+        <v/>
+      </c>
+      <c r="M301" s="39">
+        <f>IF($A301="","",IF($H301="","Declaration missing",IF($H301="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R301),$R301&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H301="Fully Compliant",$J301&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N301" s="58">
+        <f>IF($A301="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C301,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O301" s="58">
+        <f>IF($A301="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C301,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P301" s="58">
+        <f>IF($A301="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C301,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q301" s="58">
+        <f>IF($A301="","",$A301&amp;"|"&amp;$B301&amp;"|"&amp;$C301)</f>
+        <v/>
+      </c>
+      <c r="R301" s="59" t="n"/>
+      <c r="S301" s="60" t="n"/>
+    </row>
+    <row r="302" ht="15" customHeight="1" s="34">
+      <c r="A302" s="54" t="n"/>
+      <c r="B302" s="54" t="n"/>
+      <c r="C302" s="54" t="n"/>
+      <c r="D302" s="55">
+        <f>IF($A302="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C302,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E302" s="55">
+        <f>IF($A302="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C302,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F302" s="56">
+        <f>IF($A302="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C302,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G302" s="57" t="n"/>
+      <c r="H302" s="54" t="n"/>
+      <c r="I302" s="54" t="n"/>
+      <c r="J302" s="39">
+        <f>IF($A302="","",IF($E302="Informational","GREEN",IF($G302="",IF($E302="Mandatory","RED","YELLOW"),IF($N302="Exact",IF(UPPER(TRIM($G302&amp;""))=UPPER(TRIM($F302&amp;"")),"GREEN",$P302),IF(NOT(ISNUMBER($G302)),$P302,IF($N302="Min",IF($G302&gt;=$F302,"GREEN",IF($G302&gt;=$F302-$O302,"YELLOW",$P302)),IF($N302="Max",IF($G302&lt;=$F302,"GREEN",IF($G302&lt;=$F302+$O302,"YELLOW",$P302)),IF($N302="Range",IF(ABS($G302-$F302)&lt;=$O302,"GREEN",$P302),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K302" s="39">
+        <f>IF($A302="","",IF($H302="Non-Compliant","RED",IF(AND(OR($H302="Alternative Offer",$H302="Partially Compliant"),$J302="GREEN"),"YELLOW",IF(AND($J302="GREEN",ISNUMBER($R302),$R302&lt;Baseline!$B$9),"YELLOW",$J302))))</f>
+        <v/>
+      </c>
+      <c r="L302" s="39">
+        <f>IF($A302="","",IF($K302="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A302,Exceptions!$C$5:$C$104,$B302,Exceptions!$D$5:$D$104,$C302,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K302)))</f>
+        <v/>
+      </c>
+      <c r="M302" s="39">
+        <f>IF($A302="","",IF($H302="","Declaration missing",IF($H302="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R302),$R302&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H302="Fully Compliant",$J302&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N302" s="58">
+        <f>IF($A302="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C302,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O302" s="58">
+        <f>IF($A302="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C302,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P302" s="58">
+        <f>IF($A302="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C302,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q302" s="58">
+        <f>IF($A302="","",$A302&amp;"|"&amp;$B302&amp;"|"&amp;$C302)</f>
+        <v/>
+      </c>
+      <c r="R302" s="59" t="n"/>
+      <c r="S302" s="60" t="n"/>
+    </row>
+    <row r="303" ht="15" customHeight="1" s="34">
+      <c r="A303" s="54" t="n"/>
+      <c r="B303" s="54" t="n"/>
+      <c r="C303" s="54" t="n"/>
+      <c r="D303" s="55">
+        <f>IF($A303="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C303,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E303" s="55">
+        <f>IF($A303="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C303,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F303" s="56">
+        <f>IF($A303="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C303,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G303" s="57" t="n"/>
+      <c r="H303" s="54" t="n"/>
+      <c r="I303" s="54" t="n"/>
+      <c r="J303" s="39">
+        <f>IF($A303="","",IF($E303="Informational","GREEN",IF($G303="",IF($E303="Mandatory","RED","YELLOW"),IF($N303="Exact",IF(UPPER(TRIM($G303&amp;""))=UPPER(TRIM($F303&amp;"")),"GREEN",$P303),IF(NOT(ISNUMBER($G303)),$P303,IF($N303="Min",IF($G303&gt;=$F303,"GREEN",IF($G303&gt;=$F303-$O303,"YELLOW",$P303)),IF($N303="Max",IF($G303&lt;=$F303,"GREEN",IF($G303&lt;=$F303+$O303,"YELLOW",$P303)),IF($N303="Range",IF(ABS($G303-$F303)&lt;=$O303,"GREEN",$P303),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K303" s="39">
+        <f>IF($A303="","",IF($H303="Non-Compliant","RED",IF(AND(OR($H303="Alternative Offer",$H303="Partially Compliant"),$J303="GREEN"),"YELLOW",IF(AND($J303="GREEN",ISNUMBER($R303),$R303&lt;Baseline!$B$9),"YELLOW",$J303))))</f>
+        <v/>
+      </c>
+      <c r="L303" s="39">
+        <f>IF($A303="","",IF($K303="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A303,Exceptions!$C$5:$C$104,$B303,Exceptions!$D$5:$D$104,$C303,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K303)))</f>
+        <v/>
+      </c>
+      <c r="M303" s="39">
+        <f>IF($A303="","",IF($H303="","Declaration missing",IF($H303="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R303),$R303&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H303="Fully Compliant",$J303&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N303" s="58">
+        <f>IF($A303="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C303,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O303" s="58">
+        <f>IF($A303="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C303,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P303" s="58">
+        <f>IF($A303="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C303,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q303" s="58">
+        <f>IF($A303="","",$A303&amp;"|"&amp;$B303&amp;"|"&amp;$C303)</f>
+        <v/>
+      </c>
+      <c r="R303" s="59" t="n"/>
+      <c r="S303" s="60" t="n"/>
+    </row>
+    <row r="304" ht="15" customHeight="1" s="34">
+      <c r="A304" s="54" t="n"/>
+      <c r="B304" s="54" t="n"/>
+      <c r="C304" s="54" t="n"/>
+      <c r="D304" s="55">
+        <f>IF($A304="","",IFERROR(INDEX(Baseline!$B$20:$B$49,MATCH($C304,Baseline!$A$20:$A$49,0)),"Line not in baseline"))</f>
+        <v/>
+      </c>
+      <c r="E304" s="55">
+        <f>IF($A304="","",IFERROR(INDEX(Baseline!$C$20:$C$49,MATCH($C304,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F304" s="56">
+        <f>IF($A304="","",IFERROR(INDEX(Baseline!$E$20:$E$49,MATCH($C304,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G304" s="57" t="n"/>
+      <c r="H304" s="54" t="n"/>
+      <c r="I304" s="54" t="n"/>
+      <c r="J304" s="39">
+        <f>IF($A304="","",IF($E304="Informational","GREEN",IF($G304="",IF($E304="Mandatory","RED","YELLOW"),IF($N304="Exact",IF(UPPER(TRIM($G304&amp;""))=UPPER(TRIM($F304&amp;"")),"GREEN",$P304),IF(NOT(ISNUMBER($G304)),$P304,IF($N304="Min",IF($G304&gt;=$F304,"GREEN",IF($G304&gt;=$F304-$O304,"YELLOW",$P304)),IF($N304="Max",IF($G304&lt;=$F304,"GREEN",IF($G304&lt;=$F304+$O304,"YELLOW",$P304)),IF($N304="Range",IF(ABS($G304-$F304)&lt;=$O304,"GREEN",$P304),"CHECK RULE"))))))))</f>
+        <v/>
+      </c>
+      <c r="K304" s="39">
+        <f>IF($A304="","",IF($H304="Non-Compliant","RED",IF(AND(OR($H304="Alternative Offer",$H304="Partially Compliant"),$J304="GREEN"),"YELLOW",IF(AND($J304="GREEN",ISNUMBER($R304),$R304&lt;Baseline!$B$9),"YELLOW",$J304))))</f>
+        <v/>
+      </c>
+      <c r="L304" s="39">
+        <f>IF($A304="","",IF($K304="GREEN","GREEN",IF(COUNTIFS(Exceptions!$B$5:$B$104,$A304,Exceptions!$C$5:$C$104,$B304,Exceptions!$D$5:$D$104,$C304,Exceptions!$G$5:$G$104,"Accepted",Exceptions!$H$5:$H$104,"&lt;&gt;")&gt;0,"CLEARED",$K304)))</f>
+        <v/>
+      </c>
+      <c r="M304" s="39">
+        <f>IF($A304="","",IF($H304="","Declaration missing",IF($H304="Not Stated","Not stated in quotation",IF(AND(ISNUMBER($R304),$R304&lt;Baseline!$B$9),"Low AI confidence - verify",IF(AND($H304="Fully Compliant",$J304&lt;&gt;"GREEN"),"Declared Fully - evidence differs","")))))</f>
+        <v/>
+      </c>
+      <c r="N304" s="58">
+        <f>IF($A304="","",IFERROR(INDEX(Baseline!$D$20:$D$49,MATCH($C304,Baseline!$A$20:$A$49,0)),""))</f>
+        <v/>
+      </c>
+      <c r="O304" s="58">
+        <f>IF($A304="","",IFERROR(INDEX(Baseline!$F$20:$F$49,MATCH($C304,Baseline!$A$20:$A$49,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P304" s="58">
+        <f>IF($A304="","",IFERROR(INDEX(Baseline!$G$20:$G$49,MATCH($C304,Baseline!$A$20:$A$49,0)),"RED"))</f>
+        <v/>
+      </c>
+      <c r="Q304" s="58">
+        <f>IF($A304="","",$A304&amp;"|"&amp;$B304&amp;"|"&amp;$C304)</f>
+        <v/>
+      </c>
+      <c r="R304" s="59" t="n"/>
+      <c r="S304" s="60" t="n"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J5:L204">
+  <conditionalFormatting sqref="J5:L304">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
       <formula>"RED"</formula>
     </cfRule>
@@ -13384,7 +18784,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H5:H304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Fully Compliant,Partially Compliant,Non-Compliant,Alternative Offer,Not Stated"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -15899,7 +21299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="33" min="1" max="1"/>
@@ -15907,6 +21307,15 @@
     <col width="13" customWidth="1" style="33" min="3" max="3"/>
     <col width="22" customWidth="1" style="33" min="4" max="4"/>
     <col width="13" customWidth="1" style="33" min="5" max="12"/>
+    <col width="13" customWidth="1" style="34" min="6" max="6"/>
+    <col width="13" customWidth="1" style="34" min="7" max="7"/>
+    <col width="13" customWidth="1" style="34" min="8" max="8"/>
+    <col width="13" customWidth="1" style="34" min="9" max="9"/>
+    <col width="13" customWidth="1" style="34" min="10" max="10"/>
+    <col width="13" customWidth="1" style="34" min="11" max="11"/>
+    <col width="13" customWidth="1" style="34" min="12" max="12"/>
+    <col width="13" customWidth="1" style="34" min="13" max="13"/>
+    <col width="13" customWidth="1" style="34" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" s="34">
@@ -15926,6 +21335,8 @@
       <c r="J1" s="36" t="n"/>
       <c r="K1" s="36" t="n"/>
       <c r="L1" s="36" t="n"/>
+      <c r="M1" s="36" t="n"/>
+      <c r="N1" s="36" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="34">
       <c r="A2" s="36" t="n"/>
@@ -15940,6 +21351,8 @@
       <c r="J2" s="36" t="n"/>
       <c r="K2" s="36" t="n"/>
       <c r="L2" s="36" t="n"/>
+      <c r="M2" s="36" t="n"/>
+      <c r="N2" s="36" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="34">
       <c r="A3" s="36" t="n"/>
@@ -15954,6 +21367,8 @@
       <c r="J3" s="36" t="n"/>
       <c r="K3" s="36" t="n"/>
       <c r="L3" s="36" t="n"/>
+      <c r="M3" s="36" t="n"/>
+      <c r="N3" s="36" t="n"/>
     </row>
     <row r="4" ht="27.75" customHeight="1" s="34">
       <c r="A4" s="36" t="n"/>
@@ -15972,6 +21387,8 @@
       <c r="J4" s="64" t="n"/>
       <c r="K4" s="64" t="n"/>
       <c r="L4" s="64" t="n"/>
+      <c r="M4" s="64" t="n"/>
+      <c r="N4" s="64" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="34">
       <c r="A5" s="36" t="n"/>
@@ -15983,35 +21400,43 @@
         </is>
       </c>
       <c r="E5" s="65">
-        <f>IF(E4="","",IF(COUNTIF(Submissions!$A$5:$A$204,E4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=E4)*Submissions!$B$5:$B$204))))</f>
+        <f>IF(E4="","",IF(COUNTIF(Submissions!$A$5:$A$304,E4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=E4)*Submissions!$B$5:$B$304))))</f>
         <v/>
       </c>
       <c r="F5" s="65">
-        <f>IF(F4="","",IF(COUNTIF(Submissions!$A$5:$A$204,F4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=F4)*Submissions!$B$5:$B$204))))</f>
+        <f>IF(F4="","",IF(COUNTIF(Submissions!$A$5:$A$304,F4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=F4)*Submissions!$B$5:$B$304))))</f>
         <v/>
       </c>
       <c r="G5" s="65">
-        <f>IF(G4="","",IF(COUNTIF(Submissions!$A$5:$A$204,G4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=G4)*Submissions!$B$5:$B$204))))</f>
+        <f>IF(G4="","",IF(COUNTIF(Submissions!$A$5:$A$304,G4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=G4)*Submissions!$B$5:$B$304))))</f>
         <v/>
       </c>
       <c r="H5" s="65">
-        <f>IF(H4="","",IF(COUNTIF(Submissions!$A$5:$A$204,H4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=H4)*Submissions!$B$5:$B$204))))</f>
+        <f>IF(H4="","",IF(COUNTIF(Submissions!$A$5:$A$304,H4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=H4)*Submissions!$B$5:$B$304))))</f>
         <v/>
       </c>
       <c r="I5" s="65">
-        <f>IF(I4="","",IF(COUNTIF(Submissions!$A$5:$A$204,I4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=I4)*Submissions!$B$5:$B$204))))</f>
+        <f>IF(I4="","",IF(COUNTIF(Submissions!$A$5:$A$304,I4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=I4)*Submissions!$B$5:$B$304))))</f>
         <v/>
       </c>
       <c r="J5" s="65">
-        <f>IF(J4="","",IF(COUNTIF(Submissions!$A$5:$A$204,J4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=J4)*Submissions!$B$5:$B$204))))</f>
+        <f>IF(J4="","",IF(COUNTIF(Submissions!$A$5:$A$304,J4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=J4)*Submissions!$B$5:$B$304))))</f>
         <v/>
       </c>
       <c r="K5" s="65">
-        <f>IF(K4="","",IF(COUNTIF(Submissions!$A$5:$A$204,K4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=K4)*Submissions!$B$5:$B$204))))</f>
+        <f>IF(K4="","",IF(COUNTIF(Submissions!$A$5:$A$304,K4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=K4)*Submissions!$B$5:$B$304))))</f>
         <v/>
       </c>
       <c r="L5" s="65">
-        <f>IF(L4="","",IF(COUNTIF(Submissions!$A$5:$A$204,L4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$204=L4)*Submissions!$B$5:$B$204))))</f>
+        <f>IF(L4="","",IF(COUNTIF(Submissions!$A$5:$A$304,L4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=L4)*Submissions!$B$5:$B$304))))</f>
+        <v/>
+      </c>
+      <c r="M5" s="65">
+        <f>IF(M4="","",IF(COUNTIF(Submissions!$A$5:$A$304,M4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=M4)*Submissions!$B$5:$B$304))))</f>
+        <v/>
+      </c>
+      <c r="N5" s="65">
+        <f>IF(N4="","",IF(COUNTIF(Submissions!$A$5:$A$304,N4)=0,"",SUMPRODUCT(MAX((Submissions!$A$5:$A$304=N4)*Submissions!$B$5:$B$304))))</f>
         <v/>
       </c>
     </row>
@@ -16072,6 +21497,16 @@
         </is>
       </c>
       <c r="L6" s="48" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="M6" s="48" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="N6" s="48" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -16095,35 +21530,43 @@
         <v/>
       </c>
       <c r="E7" s="68">
-        <f>IF(OR($A7="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F7" s="68">
-        <f>IF(OR($A7="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G7" s="68">
-        <f>IF(OR($A7="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H7" s="68">
-        <f>IF(OR($A7="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I7" s="68">
-        <f>IF(OR($A7="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J7" s="68">
-        <f>IF(OR($A7="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K7" s="68">
-        <f>IF(OR($A7="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L7" s="68">
-        <f>IF(OR($A7="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A7="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M7" s="68">
+        <f>IF(OR($A7="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N7" s="68">
+        <f>IF(OR($A7="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A7,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16145,35 +21588,43 @@
         <v/>
       </c>
       <c r="E8" s="68">
-        <f>IF(OR($A8="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F8" s="68">
-        <f>IF(OR($A8="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G8" s="68">
-        <f>IF(OR($A8="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H8" s="68">
-        <f>IF(OR($A8="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I8" s="68">
-        <f>IF(OR($A8="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J8" s="68">
-        <f>IF(OR($A8="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K8" s="68">
-        <f>IF(OR($A8="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L8" s="68">
-        <f>IF(OR($A8="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A8="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M8" s="68">
+        <f>IF(OR($A8="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N8" s="68">
+        <f>IF(OR($A8="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A8,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16195,35 +21646,43 @@
         <v/>
       </c>
       <c r="E9" s="68">
-        <f>IF(OR($A9="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F9" s="68">
-        <f>IF(OR($A9="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G9" s="68">
-        <f>IF(OR($A9="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H9" s="68">
-        <f>IF(OR($A9="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I9" s="68">
-        <f>IF(OR($A9="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J9" s="68">
-        <f>IF(OR($A9="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K9" s="68">
-        <f>IF(OR($A9="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L9" s="68">
-        <f>IF(OR($A9="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A9="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M9" s="68">
+        <f>IF(OR($A9="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N9" s="68">
+        <f>IF(OR($A9="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A9,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16245,35 +21704,43 @@
         <v/>
       </c>
       <c r="E10" s="68">
-        <f>IF(OR($A10="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F10" s="68">
-        <f>IF(OR($A10="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G10" s="68">
-        <f>IF(OR($A10="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
-        <f>IF(OR($A10="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I10" s="68">
-        <f>IF(OR($A10="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J10" s="68">
-        <f>IF(OR($A10="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K10" s="68">
-        <f>IF(OR($A10="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L10" s="68">
-        <f>IF(OR($A10="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A10="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M10" s="68">
+        <f>IF(OR($A10="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N10" s="68">
+        <f>IF(OR($A10="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A10,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16295,35 +21762,43 @@
         <v/>
       </c>
       <c r="E11" s="68">
-        <f>IF(OR($A11="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F11" s="68">
-        <f>IF(OR($A11="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G11" s="68">
-        <f>IF(OR($A11="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
-        <f>IF(OR($A11="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I11" s="68">
-        <f>IF(OR($A11="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J11" s="68">
-        <f>IF(OR($A11="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K11" s="68">
-        <f>IF(OR($A11="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L11" s="68">
-        <f>IF(OR($A11="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A11="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M11" s="68">
+        <f>IF(OR($A11="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N11" s="68">
+        <f>IF(OR($A11="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A11,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16345,35 +21820,43 @@
         <v/>
       </c>
       <c r="E12" s="68">
-        <f>IF(OR($A12="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F12" s="68">
-        <f>IF(OR($A12="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G12" s="68">
-        <f>IF(OR($A12="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
-        <f>IF(OR($A12="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I12" s="68">
-        <f>IF(OR($A12="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J12" s="68">
-        <f>IF(OR($A12="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K12" s="68">
-        <f>IF(OR($A12="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L12" s="68">
-        <f>IF(OR($A12="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A12="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M12" s="68">
+        <f>IF(OR($A12="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N12" s="68">
+        <f>IF(OR($A12="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A12,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16395,35 +21878,43 @@
         <v/>
       </c>
       <c r="E13" s="68">
-        <f>IF(OR($A13="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F13" s="68">
-        <f>IF(OR($A13="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G13" s="68">
-        <f>IF(OR($A13="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
-        <f>IF(OR($A13="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I13" s="68">
-        <f>IF(OR($A13="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J13" s="68">
-        <f>IF(OR($A13="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K13" s="68">
-        <f>IF(OR($A13="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L13" s="68">
-        <f>IF(OR($A13="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A13="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M13" s="68">
+        <f>IF(OR($A13="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N13" s="68">
+        <f>IF(OR($A13="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A13,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16445,35 +21936,43 @@
         <v/>
       </c>
       <c r="E14" s="68">
-        <f>IF(OR($A14="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F14" s="68">
-        <f>IF(OR($A14="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G14" s="68">
-        <f>IF(OR($A14="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
-        <f>IF(OR($A14="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I14" s="68">
-        <f>IF(OR($A14="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J14" s="68">
-        <f>IF(OR($A14="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K14" s="68">
-        <f>IF(OR($A14="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L14" s="68">
-        <f>IF(OR($A14="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A14="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M14" s="68">
+        <f>IF(OR($A14="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N14" s="68">
+        <f>IF(OR($A14="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A14,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16495,35 +21994,43 @@
         <v/>
       </c>
       <c r="E15" s="68">
-        <f>IF(OR($A15="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F15" s="68">
-        <f>IF(OR($A15="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G15" s="68">
-        <f>IF(OR($A15="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
-        <f>IF(OR($A15="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I15" s="68">
-        <f>IF(OR($A15="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J15" s="68">
-        <f>IF(OR($A15="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K15" s="68">
-        <f>IF(OR($A15="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L15" s="68">
-        <f>IF(OR($A15="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A15="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M15" s="68">
+        <f>IF(OR($A15="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N15" s="68">
+        <f>IF(OR($A15="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A15,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16545,35 +22052,43 @@
         <v/>
       </c>
       <c r="E16" s="68">
-        <f>IF(OR($A16="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F16" s="68">
-        <f>IF(OR($A16="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G16" s="68">
-        <f>IF(OR($A16="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
-        <f>IF(OR($A16="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I16" s="68">
-        <f>IF(OR($A16="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J16" s="68">
-        <f>IF(OR($A16="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K16" s="68">
-        <f>IF(OR($A16="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L16" s="68">
-        <f>IF(OR($A16="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A16="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M16" s="68">
+        <f>IF(OR($A16="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N16" s="68">
+        <f>IF(OR($A16="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A16,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16595,35 +22110,43 @@
         <v/>
       </c>
       <c r="E17" s="68">
-        <f>IF(OR($A17="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F17" s="68">
-        <f>IF(OR($A17="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G17" s="68">
-        <f>IF(OR($A17="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
-        <f>IF(OR($A17="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I17" s="68">
-        <f>IF(OR($A17="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J17" s="68">
-        <f>IF(OR($A17="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K17" s="68">
-        <f>IF(OR($A17="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L17" s="68">
-        <f>IF(OR($A17="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A17="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M17" s="68">
+        <f>IF(OR($A17="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N17" s="68">
+        <f>IF(OR($A17="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A17,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16645,35 +22168,43 @@
         <v/>
       </c>
       <c r="E18" s="68">
-        <f>IF(OR($A18="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F18" s="68">
-        <f>IF(OR($A18="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G18" s="68">
-        <f>IF(OR($A18="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
-        <f>IF(OR($A18="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I18" s="68">
-        <f>IF(OR($A18="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J18" s="68">
-        <f>IF(OR($A18="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K18" s="68">
-        <f>IF(OR($A18="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L18" s="68">
-        <f>IF(OR($A18="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A18="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M18" s="68">
+        <f>IF(OR($A18="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N18" s="68">
+        <f>IF(OR($A18="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A18,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16695,35 +22226,43 @@
         <v/>
       </c>
       <c r="E19" s="68">
-        <f>IF(OR($A19="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F19" s="68">
-        <f>IF(OR($A19="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G19" s="68">
-        <f>IF(OR($A19="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
-        <f>IF(OR($A19="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I19" s="68">
-        <f>IF(OR($A19="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J19" s="68">
-        <f>IF(OR($A19="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K19" s="68">
-        <f>IF(OR($A19="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L19" s="68">
-        <f>IF(OR($A19="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A19="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M19" s="68">
+        <f>IF(OR($A19="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N19" s="68">
+        <f>IF(OR($A19="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A19,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16745,35 +22284,43 @@
         <v/>
       </c>
       <c r="E20" s="68">
-        <f>IF(OR($A20="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F20" s="68">
-        <f>IF(OR($A20="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G20" s="68">
-        <f>IF(OR($A20="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H20" s="68">
-        <f>IF(OR($A20="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I20" s="68">
-        <f>IF(OR($A20="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J20" s="68">
-        <f>IF(OR($A20="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K20" s="68">
-        <f>IF(OR($A20="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L20" s="68">
-        <f>IF(OR($A20="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A20="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M20" s="68">
+        <f>IF(OR($A20="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N20" s="68">
+        <f>IF(OR($A20="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A20,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16795,35 +22342,43 @@
         <v/>
       </c>
       <c r="E21" s="68">
-        <f>IF(OR($A21="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F21" s="68">
-        <f>IF(OR($A21="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G21" s="68">
-        <f>IF(OR($A21="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H21" s="68">
-        <f>IF(OR($A21="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I21" s="68">
-        <f>IF(OR($A21="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J21" s="68">
-        <f>IF(OR($A21="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K21" s="68">
-        <f>IF(OR($A21="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L21" s="68">
-        <f>IF(OR($A21="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A21="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M21" s="68">
+        <f>IF(OR($A21="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N21" s="68">
+        <f>IF(OR($A21="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A21,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16845,35 +22400,43 @@
         <v/>
       </c>
       <c r="E22" s="68">
-        <f>IF(OR($A22="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F22" s="68">
-        <f>IF(OR($A22="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G22" s="68">
-        <f>IF(OR($A22="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H22" s="68">
-        <f>IF(OR($A22="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I22" s="68">
-        <f>IF(OR($A22="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J22" s="68">
-        <f>IF(OR($A22="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K22" s="68">
-        <f>IF(OR($A22="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L22" s="68">
-        <f>IF(OR($A22="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A22="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M22" s="68">
+        <f>IF(OR($A22="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N22" s="68">
+        <f>IF(OR($A22="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A22,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16895,35 +22458,43 @@
         <v/>
       </c>
       <c r="E23" s="68">
-        <f>IF(OR($A23="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F23" s="68">
-        <f>IF(OR($A23="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G23" s="68">
-        <f>IF(OR($A23="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H23" s="68">
-        <f>IF(OR($A23="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I23" s="68">
-        <f>IF(OR($A23="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J23" s="68">
-        <f>IF(OR($A23="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K23" s="68">
-        <f>IF(OR($A23="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L23" s="68">
-        <f>IF(OR($A23="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A23="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M23" s="68">
+        <f>IF(OR($A23="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N23" s="68">
+        <f>IF(OR($A23="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A23,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16945,35 +22516,43 @@
         <v/>
       </c>
       <c r="E24" s="68">
-        <f>IF(OR($A24="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F24" s="68">
-        <f>IF(OR($A24="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G24" s="68">
-        <f>IF(OR($A24="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H24" s="68">
-        <f>IF(OR($A24="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I24" s="68">
-        <f>IF(OR($A24="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J24" s="68">
-        <f>IF(OR($A24="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K24" s="68">
-        <f>IF(OR($A24="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L24" s="68">
-        <f>IF(OR($A24="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A24="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M24" s="68">
+        <f>IF(OR($A24="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N24" s="68">
+        <f>IF(OR($A24="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A24,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -16995,35 +22574,43 @@
         <v/>
       </c>
       <c r="E25" s="68">
-        <f>IF(OR($A25="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F25" s="68">
-        <f>IF(OR($A25="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G25" s="68">
-        <f>IF(OR($A25="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H25" s="68">
-        <f>IF(OR($A25="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I25" s="68">
-        <f>IF(OR($A25="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J25" s="68">
-        <f>IF(OR($A25="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K25" s="68">
-        <f>IF(OR($A25="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L25" s="68">
-        <f>IF(OR($A25="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A25="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M25" s="68">
+        <f>IF(OR($A25="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N25" s="68">
+        <f>IF(OR($A25="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A25,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17045,35 +22632,43 @@
         <v/>
       </c>
       <c r="E26" s="68">
-        <f>IF(OR($A26="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F26" s="68">
-        <f>IF(OR($A26="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G26" s="68">
-        <f>IF(OR($A26="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H26" s="68">
-        <f>IF(OR($A26="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I26" s="68">
-        <f>IF(OR($A26="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J26" s="68">
-        <f>IF(OR($A26="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K26" s="68">
-        <f>IF(OR($A26="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L26" s="68">
-        <f>IF(OR($A26="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A26="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M26" s="68">
+        <f>IF(OR($A26="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N26" s="68">
+        <f>IF(OR($A26="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A26,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17095,35 +22690,43 @@
         <v/>
       </c>
       <c r="E27" s="68">
-        <f>IF(OR($A27="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F27" s="68">
-        <f>IF(OR($A27="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G27" s="68">
-        <f>IF(OR($A27="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H27" s="68">
-        <f>IF(OR($A27="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I27" s="68">
-        <f>IF(OR($A27="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J27" s="68">
-        <f>IF(OR($A27="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K27" s="68">
-        <f>IF(OR($A27="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L27" s="68">
-        <f>IF(OR($A27="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A27="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M27" s="68">
+        <f>IF(OR($A27="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N27" s="68">
+        <f>IF(OR($A27="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A27,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17145,35 +22748,43 @@
         <v/>
       </c>
       <c r="E28" s="68">
-        <f>IF(OR($A28="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F28" s="68">
-        <f>IF(OR($A28="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G28" s="68">
-        <f>IF(OR($A28="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H28" s="68">
-        <f>IF(OR($A28="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I28" s="68">
-        <f>IF(OR($A28="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J28" s="68">
-        <f>IF(OR($A28="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K28" s="68">
-        <f>IF(OR($A28="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L28" s="68">
-        <f>IF(OR($A28="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A28="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M28" s="68">
+        <f>IF(OR($A28="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N28" s="68">
+        <f>IF(OR($A28="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A28,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17195,35 +22806,43 @@
         <v/>
       </c>
       <c r="E29" s="68">
-        <f>IF(OR($A29="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F29" s="68">
-        <f>IF(OR($A29="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G29" s="68">
-        <f>IF(OR($A29="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H29" s="68">
-        <f>IF(OR($A29="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I29" s="68">
-        <f>IF(OR($A29="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J29" s="68">
-        <f>IF(OR($A29="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K29" s="68">
-        <f>IF(OR($A29="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L29" s="68">
-        <f>IF(OR($A29="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A29="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M29" s="68">
+        <f>IF(OR($A29="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N29" s="68">
+        <f>IF(OR($A29="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A29,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17245,35 +22864,43 @@
         <v/>
       </c>
       <c r="E30" s="68">
-        <f>IF(OR($A30="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F30" s="68">
-        <f>IF(OR($A30="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G30" s="68">
-        <f>IF(OR($A30="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H30" s="68">
-        <f>IF(OR($A30="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I30" s="68">
-        <f>IF(OR($A30="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J30" s="68">
-        <f>IF(OR($A30="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K30" s="68">
-        <f>IF(OR($A30="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L30" s="68">
-        <f>IF(OR($A30="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A30="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M30" s="68">
+        <f>IF(OR($A30="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N30" s="68">
+        <f>IF(OR($A30="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A30,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17295,35 +22922,43 @@
         <v/>
       </c>
       <c r="E31" s="68">
-        <f>IF(OR($A31="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F31" s="68">
-        <f>IF(OR($A31="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G31" s="68">
-        <f>IF(OR($A31="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H31" s="68">
-        <f>IF(OR($A31="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I31" s="68">
-        <f>IF(OR($A31="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J31" s="68">
-        <f>IF(OR($A31="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K31" s="68">
-        <f>IF(OR($A31="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L31" s="68">
-        <f>IF(OR($A31="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A31="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M31" s="68">
+        <f>IF(OR($A31="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N31" s="68">
+        <f>IF(OR($A31="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A31,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17345,35 +22980,43 @@
         <v/>
       </c>
       <c r="E32" s="68">
-        <f>IF(OR($A32="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F32" s="68">
-        <f>IF(OR($A32="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G32" s="68">
-        <f>IF(OR($A32="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H32" s="68">
-        <f>IF(OR($A32="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I32" s="68">
-        <f>IF(OR($A32="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J32" s="68">
-        <f>IF(OR($A32="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K32" s="68">
-        <f>IF(OR($A32="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L32" s="68">
-        <f>IF(OR($A32="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A32="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M32" s="68">
+        <f>IF(OR($A32="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N32" s="68">
+        <f>IF(OR($A32="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A32,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17395,35 +23038,43 @@
         <v/>
       </c>
       <c r="E33" s="68">
-        <f>IF(OR($A33="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F33" s="68">
-        <f>IF(OR($A33="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G33" s="68">
-        <f>IF(OR($A33="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H33" s="68">
-        <f>IF(OR($A33="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I33" s="68">
-        <f>IF(OR($A33="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J33" s="68">
-        <f>IF(OR($A33="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K33" s="68">
-        <f>IF(OR($A33="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L33" s="68">
-        <f>IF(OR($A33="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A33="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M33" s="68">
+        <f>IF(OR($A33="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N33" s="68">
+        <f>IF(OR($A33="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A33,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17445,35 +23096,43 @@
         <v/>
       </c>
       <c r="E34" s="68">
-        <f>IF(OR($A34="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F34" s="68">
-        <f>IF(OR($A34="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G34" s="68">
-        <f>IF(OR($A34="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H34" s="68">
-        <f>IF(OR($A34="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I34" s="68">
-        <f>IF(OR($A34="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J34" s="68">
-        <f>IF(OR($A34="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K34" s="68">
-        <f>IF(OR($A34="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L34" s="68">
-        <f>IF(OR($A34="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A34="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M34" s="68">
+        <f>IF(OR($A34="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N34" s="68">
+        <f>IF(OR($A34="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A34,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17495,35 +23154,43 @@
         <v/>
       </c>
       <c r="E35" s="68">
-        <f>IF(OR($A35="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F35" s="68">
-        <f>IF(OR($A35="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G35" s="68">
-        <f>IF(OR($A35="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H35" s="68">
-        <f>IF(OR($A35="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I35" s="68">
-        <f>IF(OR($A35="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J35" s="68">
-        <f>IF(OR($A35="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K35" s="68">
-        <f>IF(OR($A35="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L35" s="68">
-        <f>IF(OR($A35="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A35="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M35" s="68">
+        <f>IF(OR($A35="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N35" s="68">
+        <f>IF(OR($A35="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A35,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17545,35 +23212,43 @@
         <v/>
       </c>
       <c r="E36" s="68">
-        <f>IF(OR($A36="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",E$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(E$4&amp;"|"&amp;E$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="F36" s="68">
-        <f>IF(OR($A36="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",F$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(F$4&amp;"|"&amp;F$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="G36" s="68">
-        <f>IF(OR($A36="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",G$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(G$4&amp;"|"&amp;G$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="H36" s="68">
-        <f>IF(OR($A36="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",H$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(H$4&amp;"|"&amp;H$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="I36" s="68">
-        <f>IF(OR($A36="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",I$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(I$4&amp;"|"&amp;I$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="J36" s="68">
-        <f>IF(OR($A36="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",J$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(J$4&amp;"|"&amp;J$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="K36" s="68">
-        <f>IF(OR($A36="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",K$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(K$4&amp;"|"&amp;K$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
       <c r="L36" s="68">
-        <f>IF(OR($A36="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$204,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$204,0)),"NO DATA"))</f>
+        <f>IF(OR($A36="",L$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(L$4&amp;"|"&amp;L$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="M36" s="68">
+        <f>IF(OR($A36="",M$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(M$4&amp;"|"&amp;M$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
+        <v/>
+      </c>
+      <c r="N36" s="68">
+        <f>IF(OR($A36="",N$4=""),"",IFERROR(INDEX(Submissions!$L$5:$L$304,MATCH(N$4&amp;"|"&amp;N$5&amp;"|"&amp;$A36,Submissions!$Q$5:$Q$304,0)),"NO DATA"))</f>
         <v/>
       </c>
     </row>
@@ -17590,6 +23265,8 @@
       <c r="J37" s="36" t="n"/>
       <c r="K37" s="36" t="n"/>
       <c r="L37" s="36" t="n"/>
+      <c r="M37" s="36" t="n"/>
+      <c r="N37" s="36" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="34">
       <c r="A38" s="36" t="n"/>
@@ -17632,6 +23309,14 @@
         <f>IF(L$4="","",COUNTIF(L7:L36,"RED"))</f>
         <v/>
       </c>
+      <c r="M38" s="68">
+        <f>IF(M$4="","",COUNTIF(M7:M36,"RED"))</f>
+        <v/>
+      </c>
+      <c r="N38" s="68">
+        <f>IF(N$4="","",COUNTIF(N7:N36,"RED"))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="34">
       <c r="A39" s="36" t="n"/>
@@ -17674,6 +23359,14 @@
         <f>IF(L$4="","",COUNTIF(L7:L36,"YELLOW"))</f>
         <v/>
       </c>
+      <c r="M39" s="68">
+        <f>IF(M$4="","",COUNTIF(M7:M36,"YELLOW"))</f>
+        <v/>
+      </c>
+      <c r="N39" s="68">
+        <f>IF(N$4="","",COUNTIF(N7:N36,"YELLOW"))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="34">
       <c r="A40" s="36" t="n"/>
@@ -17716,6 +23409,14 @@
         <f>IF(L$4="","",COUNTIF(L7:L36,"CLEARED"))</f>
         <v/>
       </c>
+      <c r="M40" s="68">
+        <f>IF(M$4="","",COUNTIF(M7:M36,"CLEARED"))</f>
+        <v/>
+      </c>
+      <c r="N40" s="68">
+        <f>IF(N$4="","",COUNTIF(N7:N36,"CLEARED"))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="34">
       <c r="A41" s="36" t="n"/>
@@ -17758,6 +23459,14 @@
         <f>IF(L$4="","",IF(COUNTIF(L7:L36,"NO DATA")&gt;0,"INCOMPLETE",IF(L38&gt;0,"RED",IF(L39&gt;0,"YELLOW","GREEN"))))</f>
         <v/>
       </c>
+      <c r="M41" s="68">
+        <f>IF(M$4="","",IF(COUNTIF(M7:M36,"NO DATA")&gt;0,"INCOMPLETE",IF(M38&gt;0,"RED",IF(M39&gt;0,"YELLOW","GREEN"))))</f>
+        <v/>
+      </c>
+      <c r="N41" s="68">
+        <f>IF(N$4="","",IF(COUNTIF(N7:N36,"NO DATA")&gt;0,"INCOMPLETE",IF(N38&gt;0,"RED",IF(N39&gt;0,"YELLOW","GREEN"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="34">
       <c r="A42" s="36" t="n"/>
@@ -17800,9 +23509,17 @@
         <f>IF(L$4="","",IF(L41="GREEN","YES","NO"))</f>
         <v/>
       </c>
+      <c r="M42" s="68">
+        <f>IF(M$4="","",IF(M41="GREEN","YES","NO"))</f>
+        <v/>
+      </c>
+      <c r="N42" s="68">
+        <f>IF(N$4="","",IF(N41="GREEN","YES","NO"))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E7:L36">
+  <conditionalFormatting sqref="E7:N36">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
       <formula>"RED"</formula>
     </cfRule>
@@ -17828,7 +23545,7 @@
       <formula>"NO DATA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E41:L42">
+  <conditionalFormatting sqref="E41:N42">
     <cfRule type="cellIs" rank="0" priority="10" equalAverage="0" operator="equal" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
       <formula>"RED"</formula>
     </cfRule>
@@ -17866,7 +23583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="33" min="1" max="1"/>
@@ -18098,7 +23815,7 @@
         <v/>
       </c>
       <c r="I9" s="68">
-        <f>IF(ISNUMBER(H9),COUNTIF($H$9:$H$16,"&lt;"&amp;H9)+1,"")</f>
+        <f>IF(ISNUMBER(H9),COUNTIF($H$9:$H$18,"&lt;"&amp;H9)+1,"")</f>
         <v/>
       </c>
       <c r="J9" s="73">
@@ -18106,7 +23823,7 @@
         <v/>
       </c>
       <c r="K9" s="68">
-        <f>IF(ISNUMBER(J9),COUNTIF($J$9:$J$16,"&lt;"&amp;J9)+1,"")</f>
+        <f>IF(ISNUMBER(J9),COUNTIF($J$9:$J$18,"&lt;"&amp;J9)+1,"")</f>
         <v/>
       </c>
       <c r="L9" s="43" t="n"/>
@@ -18133,7 +23850,7 @@
         <v/>
       </c>
       <c r="I10" s="68">
-        <f>IF(ISNUMBER(H10),COUNTIF($H$9:$H$16,"&lt;"&amp;H10)+1,"")</f>
+        <f>IF(ISNUMBER(H10),COUNTIF($H$9:$H$18,"&lt;"&amp;H10)+1,"")</f>
         <v/>
       </c>
       <c r="J10" s="73">
@@ -18141,7 +23858,7 @@
         <v/>
       </c>
       <c r="K10" s="68">
-        <f>IF(ISNUMBER(J10),COUNTIF($J$9:$J$16,"&lt;"&amp;J10)+1,"")</f>
+        <f>IF(ISNUMBER(J10),COUNTIF($J$9:$J$18,"&lt;"&amp;J10)+1,"")</f>
         <v/>
       </c>
       <c r="L10" s="43" t="n"/>
@@ -18168,7 +23885,7 @@
         <v/>
       </c>
       <c r="I11" s="68">
-        <f>IF(ISNUMBER(H11),COUNTIF($H$9:$H$16,"&lt;"&amp;H11)+1,"")</f>
+        <f>IF(ISNUMBER(H11),COUNTIF($H$9:$H$18,"&lt;"&amp;H11)+1,"")</f>
         <v/>
       </c>
       <c r="J11" s="73">
@@ -18176,7 +23893,7 @@
         <v/>
       </c>
       <c r="K11" s="68">
-        <f>IF(ISNUMBER(J11),COUNTIF($J$9:$J$16,"&lt;"&amp;J11)+1,"")</f>
+        <f>IF(ISNUMBER(J11),COUNTIF($J$9:$J$18,"&lt;"&amp;J11)+1,"")</f>
         <v/>
       </c>
       <c r="L11" s="43" t="n"/>
@@ -18203,7 +23920,7 @@
         <v/>
       </c>
       <c r="I12" s="68">
-        <f>IF(ISNUMBER(H12),COUNTIF($H$9:$H$16,"&lt;"&amp;H12)+1,"")</f>
+        <f>IF(ISNUMBER(H12),COUNTIF($H$9:$H$18,"&lt;"&amp;H12)+1,"")</f>
         <v/>
       </c>
       <c r="J12" s="73">
@@ -18211,7 +23928,7 @@
         <v/>
       </c>
       <c r="K12" s="68">
-        <f>IF(ISNUMBER(J12),COUNTIF($J$9:$J$16,"&lt;"&amp;J12)+1,"")</f>
+        <f>IF(ISNUMBER(J12),COUNTIF($J$9:$J$18,"&lt;"&amp;J12)+1,"")</f>
         <v/>
       </c>
       <c r="L12" s="43" t="n"/>
@@ -18238,7 +23955,7 @@
         <v/>
       </c>
       <c r="I13" s="68">
-        <f>IF(ISNUMBER(H13),COUNTIF($H$9:$H$16,"&lt;"&amp;H13)+1,"")</f>
+        <f>IF(ISNUMBER(H13),COUNTIF($H$9:$H$18,"&lt;"&amp;H13)+1,"")</f>
         <v/>
       </c>
       <c r="J13" s="73">
@@ -18246,7 +23963,7 @@
         <v/>
       </c>
       <c r="K13" s="68">
-        <f>IF(ISNUMBER(J13),COUNTIF($J$9:$J$16,"&lt;"&amp;J13)+1,"")</f>
+        <f>IF(ISNUMBER(J13),COUNTIF($J$9:$J$18,"&lt;"&amp;J13)+1,"")</f>
         <v/>
       </c>
       <c r="L13" s="43" t="n"/>
@@ -18273,7 +23990,7 @@
         <v/>
       </c>
       <c r="I14" s="68">
-        <f>IF(ISNUMBER(H14),COUNTIF($H$9:$H$16,"&lt;"&amp;H14)+1,"")</f>
+        <f>IF(ISNUMBER(H14),COUNTIF($H$9:$H$18,"&lt;"&amp;H14)+1,"")</f>
         <v/>
       </c>
       <c r="J14" s="73">
@@ -18281,7 +23998,7 @@
         <v/>
       </c>
       <c r="K14" s="68">
-        <f>IF(ISNUMBER(J14),COUNTIF($J$9:$J$16,"&lt;"&amp;J14)+1,"")</f>
+        <f>IF(ISNUMBER(J14),COUNTIF($J$9:$J$18,"&lt;"&amp;J14)+1,"")</f>
         <v/>
       </c>
       <c r="L14" s="43" t="n"/>
@@ -18308,7 +24025,7 @@
         <v/>
       </c>
       <c r="I15" s="68">
-        <f>IF(ISNUMBER(H15),COUNTIF($H$9:$H$16,"&lt;"&amp;H15)+1,"")</f>
+        <f>IF(ISNUMBER(H15),COUNTIF($H$9:$H$18,"&lt;"&amp;H15)+1,"")</f>
         <v/>
       </c>
       <c r="J15" s="73">
@@ -18316,7 +24033,7 @@
         <v/>
       </c>
       <c r="K15" s="68">
-        <f>IF(ISNUMBER(J15),COUNTIF($J$9:$J$16,"&lt;"&amp;J15)+1,"")</f>
+        <f>IF(ISNUMBER(J15),COUNTIF($J$9:$J$18,"&lt;"&amp;J15)+1,"")</f>
         <v/>
       </c>
       <c r="L15" s="43" t="n"/>
@@ -18343,7 +24060,7 @@
         <v/>
       </c>
       <c r="I16" s="68">
-        <f>IF(ISNUMBER(H16),COUNTIF($H$9:$H$16,"&lt;"&amp;H16)+1,"")</f>
+        <f>IF(ISNUMBER(H16),COUNTIF($H$9:$H$18,"&lt;"&amp;H16)+1,"")</f>
         <v/>
       </c>
       <c r="J16" s="73">
@@ -18351,45 +24068,91 @@
         <v/>
       </c>
       <c r="K16" s="68">
-        <f>IF(ISNUMBER(J16),COUNTIF($J$9:$J$16,"&lt;"&amp;J16)+1,"")</f>
+        <f>IF(ISNUMBER(J16),COUNTIF($J$9:$J$18,"&lt;"&amp;J16)+1,"")</f>
         <v/>
       </c>
       <c r="L16" s="43" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="34">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="36" t="n"/>
-      <c r="I17" s="36" t="n"/>
-      <c r="J17" s="36" t="n"/>
-      <c r="K17" s="36" t="n"/>
-      <c r="L17" s="36" t="n"/>
+      <c r="A17" s="66">
+        <f>IF('Compliance Matrix'!M4="","",'Compliance Matrix'!M4)</f>
+        <v/>
+      </c>
+      <c r="B17" s="68">
+        <f>IF(A17="","",'Compliance Matrix'!M42)</f>
+        <v/>
+      </c>
+      <c r="C17" s="72" t="n"/>
+      <c r="D17" s="72" t="n"/>
+      <c r="E17" s="72" t="n"/>
+      <c r="F17" s="73">
+        <f>IF(A17="","",IF(COUNT(C17:E17)&lt;3,"Incomplete",C17*$B$4+D17*$B$5+E17*$B$6))</f>
+        <v/>
+      </c>
+      <c r="G17" s="72" t="n"/>
+      <c r="H17" s="73">
+        <f>IF(A17="","",IF(B17&lt;&gt;"YES","Not eligible",IF(ISNUMBER(F17),F17+N(G17),"Incomplete")))</f>
+        <v/>
+      </c>
+      <c r="I17" s="68">
+        <f>IF(ISNUMBER(H17),COUNTIF($H$9:$H$18,"&lt;"&amp;H17)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="73">
+        <f>IF(A17="","",IF(ISNUMBER(F17),F17+N(G17),"Incomplete"))</f>
+        <v/>
+      </c>
+      <c r="K17" s="68">
+        <f>IF(ISNUMBER(J17),COUNTIF($J$9:$J$18,"&lt;"&amp;J17)+1,"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="43" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="34">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="66">
+        <f>IF('Compliance Matrix'!N4="","",'Compliance Matrix'!N4)</f>
+        <v/>
+      </c>
+      <c r="B18" s="68">
+        <f>IF(A18="","",'Compliance Matrix'!N42)</f>
+        <v/>
+      </c>
+      <c r="C18" s="72" t="n"/>
+      <c r="D18" s="72" t="n"/>
+      <c r="E18" s="72" t="n"/>
+      <c r="F18" s="73">
+        <f>IF(A18="","",IF(COUNT(C18:E18)&lt;3,"Incomplete",C18*$B$4+D18*$B$5+E18*$B$6))</f>
+        <v/>
+      </c>
+      <c r="G18" s="72" t="n"/>
+      <c r="H18" s="73">
+        <f>IF(A18="","",IF(B18&lt;&gt;"YES","Not eligible",IF(ISNUMBER(F18),F18+N(G18),"Incomplete")))</f>
+        <v/>
+      </c>
+      <c r="I18" s="68">
+        <f>IF(ISNUMBER(H18),COUNTIF($H$9:$H$18,"&lt;"&amp;H18)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="73">
+        <f>IF(A18="","",IF(ISNUMBER(F18),F18+N(G18),"Incomplete"))</f>
+        <v/>
+      </c>
+      <c r="K18" s="68">
+        <f>IF(ISNUMBER(J18),COUNTIF($J$9:$J$18,"&lt;"&amp;J18)+1,"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="43" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>Rates are SAR per m2, ex-VAT, as quoted. Adjustments: positive = added cost (e.g. priced exclusions). Quoted prices are never overwritten.</t>
         </is>
       </c>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
-      <c r="I18" s="36" t="n"/>
-      <c r="J18" s="36" t="n"/>
-      <c r="K18" s="36" t="n"/>
-      <c r="L18" s="36" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B9:B16">
+  <conditionalFormatting sqref="B9:B18">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
       <formula>"RED"</formula>
     </cfRule>
@@ -18475,7 +24238,7 @@
         </is>
       </c>
       <c r="B4" s="39">
-        <f>IFERROR(INDEX(Evaluation!$A$9:$A$16,MATCH(1,Evaluation!$I$9:$I$16,0)),"None eligible")</f>
+        <f>IFERROR(INDEX(Evaluation!$A$9:$A$18,MATCH(1,Evaluation!$I$9:$I$18,0)),"None eligible")</f>
         <v/>
       </c>
       <c r="C4" s="36" t="n"/>
@@ -18489,7 +24252,7 @@
         </is>
       </c>
       <c r="B5" s="74">
-        <f>IFERROR(INDEX(Evaluation!$H$9:$H$16,MATCH(1,Evaluation!$I$9:$I$16,0)),"")</f>
+        <f>IFERROR(INDEX(Evaluation!$H$9:$H$18,MATCH(1,Evaluation!$I$9:$I$18,0)),"")</f>
         <v/>
       </c>
       <c r="C5" s="36" t="n"/>
